--- a/BuddhaVest_Progress.xlsx
+++ b/BuddhaVest_Progress.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,11 +30,6 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="16"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="00888888"/>
-      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -53,17 +48,8 @@
       <color rgb="00000000"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -87,26 +73,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C8E6C9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E3F2FD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00546E7A"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -127,26 +98,6 @@
       <bottom style="thin">
         <color rgb="00CCCCCC"/>
       </bottom>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00CCCCCC"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00CCCCCC"/>
-      </right>
-      <top style="thin">
-        <color rgb="00CCCCCC"/>
-      </top>
-      <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -176,84 +127,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -620,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -631,681 +531,787 @@
     <col width="54" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>BuddhaVest App — Development Tracker</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Last updated: 2026-07-10  |  Session 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="B1" t="inlineStr"/>
+      <c r="C1" t="inlineStr"/>
+      <c r="D1" t="inlineStr"/>
+      <c r="E1" t="inlineStr"/>
+      <c r="F1" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Last updated: 2026-07-11  |  Session 3</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Files Affected</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>✅  LIVE — Active in backend/server now</t>
         </is>
       </c>
-      <c r="B4" s="22" t="n"/>
-      <c r="C4" s="22" t="n"/>
-      <c r="D4" s="22" t="n"/>
-      <c r="E4" s="22" t="n"/>
-      <c r="F4" s="23" t="n"/>
-    </row>
-    <row r="5" ht="42" customHeight="1">
-      <c r="A5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr"/>
+      <c r="C4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>FCF fix (Free Cash Flow ≠ OCF)</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>assets/1BuddhaVest/analyzer.py</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>Try 'Free Cash Flow' row directly; fallback OCF - CapEx with 4 aliases. Deployed to Render.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="42" customHeight="1">
-      <c r="A6" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>analyzer.py</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>Fallback OCF-CapEx with 4 aliases. Deployed to Render.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Tiingo API token secured</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>Backend / Security</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>Render environment variable</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>TIINGO_TOKEN stored as env var in Render dashboard. Removed from code.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="42" customHeight="1">
-      <c r="A7" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>Render env var</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>TIINGO_TOKEN stored as env var. Removed from code.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Privacy Policy endpoint</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>assets/1BuddhaVest/main.py</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>main.py</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t>Live at https://buddhavest.onrender.com/privacy</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="42" customHeight="1">
-      <c r="A8" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>UptimeRobot keep-alive</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>Backend / DevOps</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>External — UptimeRobot</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>Pings Render every 5 min to prevent cold start on free tier.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>UptimeRobot</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>Pings Render every 5 min to prevent cold start.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>עדכון תנאי שימוש (ToS) — Section 5</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Legal / i18n</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>✅ Live (OTA)</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>constants/i18n.js</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>"Free &amp; non-commercial use" → "Service &amp; License". כל 4 שפות. מאפשר מונטיזציה.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>✅  LIVE — In installed APK (no reinstall needed)</t>
         </is>
       </c>
-      <c r="B9" s="22" t="n"/>
-      <c r="C9" s="22" t="n"/>
-      <c r="D9" s="22" t="n"/>
-      <c r="E9" s="22" t="n"/>
-      <c r="F9" s="23" t="n"/>
-    </row>
-    <row r="10" ht="42" customHeight="1">
-      <c r="A10" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr"/>
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr"/>
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>Chart number formatting (M / B / T)</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>✅ In APK</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
         <is>
           <t>components/PriceChart.js</t>
         </is>
       </c>
-      <c r="F10" s="12" t="inlineStr">
-        <is>
-          <t>fmtPrice() and Y-axis now show 8.11B instead of 8113000000.0K.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="42" customHeight="1">
-      <c r="A11" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>Y-axis + tooltip מציגים 8.11B במקום מספרים גולמיים.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>Remove $ from Dividend &amp; Buyback charts</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>✅ In APK</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>screens/MetricHistoryScreen.js</t>
         </is>
       </c>
-      <c r="F11" s="12" t="inlineStr">
-        <is>
-          <t>Added 'dividend' and 'buyback' to RATIO_METRICS set — no currency symbol in tooltip/axis.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="42" customHeight="1">
-      <c r="A12" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>RATIO_METRICS — אין סימן מטבע.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>T/B/M/K in metric current-value display</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>✅ In APK</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E13" s="9" t="inlineStr">
         <is>
           <t>screens/MetricHistoryScreen.js</t>
         </is>
       </c>
-      <c r="F12" s="12" t="inlineStr">
-        <is>
-          <t>Bottom display under chart now shows e.g. $8.11B instead of raw large number.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>תצוגה תחתית מציגה $8.11B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>⏳  IN CODE — Waiting for next APK build</t>
         </is>
       </c>
-      <c r="B13" s="22" t="n"/>
-      <c r="C13" s="22" t="n"/>
-      <c r="D13" s="22" t="n"/>
-      <c r="E13" s="22" t="n"/>
-      <c r="F13" s="23" t="n"/>
-    </row>
-    <row r="14" ht="42" customHeight="1">
-      <c r="A14" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr"/>
+      <c r="C14" s="4" t="inlineStr"/>
+      <c r="D14" s="4" t="inlineStr"/>
+      <c r="E14" s="4" t="inlineStr"/>
+      <c r="F14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>OTA (Over The Air) update config</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>Infrastructure</t>
         </is>
       </c>
-      <c r="D14" s="15" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>⏳ Next APK</t>
         </is>
       </c>
-      <c r="E14" s="16" t="inlineStr">
+      <c r="E15" s="9" t="inlineStr">
         <is>
           <t>app.json, eas.json</t>
         </is>
       </c>
-      <c r="F14" s="16" t="inlineStr">
-        <is>
-          <t>updates.url and runtimeVersion added to app.json; channel added to eas.json build profiles. Active from next build.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="42" customHeight="1">
-      <c r="A15" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="B15" s="14" t="inlineStr">
-        <is>
-          <t>VIX emoji dynamic by fear level</t>
-        </is>
-      </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>updates.url + runtimeVersion + channel בprofiles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>VIX emoji דינמי לפי רמת פחד</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="D15" s="15" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>⏳ Next APK</t>
         </is>
       </c>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>screens/HomeScreen.js, constants/i18n.js</t>
-        </is>
-      </c>
-      <c r="F15" s="16" t="inlineStr">
-        <is>
-          <t>vixIcon() and vixLabel() functions added. &lt;15=😌 15-20=😐 20-30=😟 &gt;30=😱. i18n keys added for all 4 languages.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="42" customHeight="1">
-      <c r="A16" s="9" t="n">
-        <v>11</v>
-      </c>
-      <c r="B16" s="22" t="n"/>
-      <c r="C16" s="22" t="n"/>
-      <c r="D16" s="22" t="n"/>
-      <c r="E16" s="22" t="n"/>
-      <c r="F16" s="23" t="n"/>
-    </row>
-    <row r="17" ht="42" customHeight="1">
-      <c r="A17" s="13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B17" s="14" t="inlineStr">
-        <is>
-          <t>תרגום חדשות — batch request אחד</t>
-        </is>
-      </c>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>HomeScreen.js, i18n.js</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>vixIcon(): &lt;15=😌 15-20=😐 20-30=😟 &gt;30=😱. כל 4 שפות.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>תרגום חדשות — batch request</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>Frontend / Performance</t>
         </is>
       </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>⏳ Next APK</t>
         </is>
       </c>
-      <c r="E17" s="16" t="inlineStr">
+      <c r="E17" s="9" t="inlineStr">
         <is>
           <t>utils/translate.js</t>
         </is>
       </c>
-      <c r="F17" s="16" t="inlineStr">
-        <is>
-          <t>במקום N requests (כותרת = request) — עכשיו כל הכותרות מחוברות ב-separator אחד ונשלחות ב-request יחיד. מהיר פי N.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="42" customHeight="1">
-      <c r="A18" s="13" t="n">
-        <v>13</v>
-      </c>
-      <c r="B18" s="14" t="inlineStr">
-        <is>
-          <t>תרגום חדשות במסך הבית — תיקון langReady</t>
-        </is>
-      </c>
-      <c r="C18" s="13" t="inlineStr">
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>כל כותרות ב-request אחד עם separator. מהיר פי N.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>תרגום חדשות — תיקון langReady</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>Frontend / Bug Fix</t>
         </is>
       </c>
-      <c r="D18" s="15" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>⏳ Next APK</t>
         </is>
       </c>
-      <c r="E18" s="16" t="inlineStr">
-        <is>
-          <t>constants/AppContext.js, screens/HomeScreen.js, screens/NewsScreen.js</t>
-        </is>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>lang מתחיל כ-'en' עד שAsyncStorage נטען. הוספנו langReady flag — HomeScreen ו-NewsScreen ממתינים לפני הבקשה הראשונה. מתרגם נכון מהפעם הראשונה.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="42" customHeight="1">
-      <c r="A19" s="24" t="n">
-        <v>14</v>
-      </c>
-      <c r="B19" s="22" t="n"/>
-      <c r="C19" s="22" t="n"/>
-      <c r="D19" s="22" t="n"/>
-      <c r="E19" s="22" t="n"/>
-      <c r="F19" s="23" t="n"/>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>AppContext.js, HomeScreen.js, NewsScreen.js</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>langReady flag — ממתין לAsyncStorage לפני בקשה ראשונה.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>נורמליזציית גדלי נזירים</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Frontend / Assets</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>⏳ Next APK</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>assets/monk_*.png</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>PIL: crop לbounding box + resize לגודל נזיר קנה (357×434).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>App launcher icon</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Assets</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>⏳ Next APK</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>assets/icon.png, adaptive-icon.png</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>נזיר על חץ זהב — 1024×1024, רקע לבן.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Feature graphic</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Store Assets</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>⏳ Next APK</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>assets/feature-graphic.png</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>באנר 1024×500 לGoogle Play.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Store listing texts</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Store Assets</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>✅ מוכן</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>store-listing.md</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>כותרת + תיאור קצר + מלא ב-he/en/ru/es.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Screenshot templates</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Store Assets</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>⚠️ Manual</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>assets/screenshots/</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>5 מסכים (1080×1920) — להחליף בצילומים מהמכשיר.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Production AAB build</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>⏳ לאחר בדיקה</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr"/>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>eas build --profile production → AAB חתום לPlay Store.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>🔜  NOT YET STARTED</t>
         </is>
       </c>
-      <c r="B20" s="23" t="n"/>
-      <c r="C20" s="22" t="n"/>
-      <c r="D20" s="22" t="n"/>
-      <c r="E20" s="22" t="n"/>
-      <c r="F20" s="23" t="n"/>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>Google Play submission</t>
-        </is>
-      </c>
-      <c r="C21" s="22" t="n"/>
-      <c r="D21" s="22" t="n"/>
-      <c r="E21" s="22" t="n"/>
-      <c r="F21" s="23" t="n"/>
-    </row>
-    <row r="22" ht="18" customHeight="1"/>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="21" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr"/>
+      <c r="C25" s="4" t="inlineStr"/>
+      <c r="D25" s="4" t="inlineStr"/>
+      <c r="E25" s="4" t="inlineStr"/>
+      <c r="F25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Google Play Console — הגשה לחנות</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>Distribution</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>🔜</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr"/>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>חשבון מפתח ($25) + העלאת AAB + store listing + screenshots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>Legend</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>Deployed and active on Render backend — visible to all users now</t>
-        </is>
-      </c>
-      <c r="C24" s="22" t="n"/>
-      <c r="D24" s="22" t="n"/>
-      <c r="E24" s="22" t="n"/>
-      <c r="F24" s="23" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>פרוס ופעיל ב-Render — נראה לכל המשתמשים</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr"/>
+      <c r="D28" s="8" t="inlineStr"/>
+      <c r="E28" s="9" t="inlineStr"/>
+      <c r="F28" s="9" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>✅ In APK</t>
         </is>
       </c>
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>Included in the installed APK — visible to all users now</t>
-        </is>
-      </c>
-      <c r="C25" s="22" t="n"/>
-      <c r="D25" s="22" t="n"/>
-      <c r="E25" s="22" t="n"/>
-      <c r="F25" s="23" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="15" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>כלול ב-APK המותקן — נראה לכל המשתמשים</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr"/>
+      <c r="D29" s="8" t="inlineStr"/>
+      <c r="E29" s="9" t="inlineStr"/>
+      <c r="F29" s="9" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>⏳ Next APK</t>
         </is>
       </c>
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>Code is merged but requires a new APK build + reinstall to activate</t>
-        </is>
-      </c>
-      <c r="C26" s="22" t="n"/>
-      <c r="D26" s="22" t="n"/>
-      <c r="E26" s="22" t="n"/>
-      <c r="F26" s="23" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="15" t="inlineStr">
-        <is>
-          <t>App launcher icon</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
-        <is>
-          <t>Replace black-circle icon with monk-on-golden-chart image; white background 1024×1024</t>
-        </is>
-      </c>
-      <c r="C27" s="22" t="inlineStr">
-        <is>
-          <t>Needs new APK build</t>
-        </is>
-      </c>
-      <c r="D27" s="22" t="inlineStr">
-        <is>
-          <t>icon.png + adaptive-icon.png generated from SCREEN LOGO.jfif</t>
-        </is>
-      </c>
-      <c r="E27" s="22" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="15" t="inlineStr">
-        <is>
-          <t>Feature graphic</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>1024×500 Play Store banner image</t>
-        </is>
-      </c>
-      <c r="C28" s="22" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="D28" s="22" t="inlineStr">
-        <is>
-          <t>assets/feature-graphic.png</t>
-        </is>
-      </c>
-      <c r="E28" s="22" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="15" t="inlineStr">
-        <is>
-          <t>Store listing texts</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>Title + short + full description in he/en/ru/es</t>
-        </is>
-      </c>
-      <c r="C29" s="22" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="D29" s="22" t="inlineStr">
-        <is>
-          <t>store-listing.md</t>
-        </is>
-      </c>
-      <c r="E29" s="22" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="15" t="inlineStr">
-        <is>
-          <t>Screenshot templates</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>5 placeholder screens (1080×1920) — replace with real device screenshots</t>
-        </is>
-      </c>
-      <c r="C30" s="22" t="inlineStr">
-        <is>
-          <t>⚠️ Manual</t>
-        </is>
-      </c>
-      <c r="D30" s="22" t="inlineStr">
-        <is>
-          <t>assets/screenshots/</t>
-        </is>
-      </c>
-      <c r="E30" s="22" t="inlineStr">
-        <is>
-          <t>🔲</t>
-        </is>
-      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>הקוד מוזג — דורש build ו-APK חדש</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr"/>
+      <c r="D30" s="8" t="inlineStr"/>
+      <c r="E30" s="9" t="inlineStr"/>
+      <c r="F30" s="9" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="15" t="inlineStr">
-        <is>
-          <t>Production AAB build</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="inlineStr">
-        <is>
-          <t>eas build --platform android --profile production → signed AAB for Play Store</t>
-        </is>
-      </c>
-      <c r="C31" s="22" t="inlineStr">
-        <is>
-          <t>⏳ Run after push</t>
-        </is>
-      </c>
-      <c r="D31" s="22" t="inlineStr"/>
-      <c r="E31" s="22" t="inlineStr">
-        <is>
-          <t>🔲</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="19" t="inlineStr">
-        <is>
-          <t>🔜 Pending</t>
-        </is>
-      </c>
-      <c r="B32" s="20" t="inlineStr">
-        <is>
-          <t>Not yet coded — needs implementation and then a new APK build</t>
-        </is>
-      </c>
-      <c r="C32" s="22" t="n"/>
-      <c r="D32" s="22" t="n"/>
-      <c r="E32" s="22" t="n"/>
-      <c r="F32" s="23" t="n"/>
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>✅ Live (OTA)</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>שינוי JS — מועבר אוטומטית בהפעלה הבאה</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr"/>
+      <c r="D31" s="8" t="inlineStr"/>
+      <c r="E31" s="9" t="inlineStr"/>
+      <c r="F31" s="9" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="B21:F21"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="B23:F23"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="B22:F22"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/BuddhaVest_Progress.xlsx
+++ b/BuddhaVest_Progress.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,8 +48,12 @@
       <color rgb="00000000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -74,6 +78,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00546E7A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001a7340"/>
       </patternFill>
     </fill>
   </fills>
@@ -127,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -155,6 +164,7 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -520,7 +530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -537,23 +547,13 @@
           <t>BuddhaVest App — Development Tracker</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr"/>
-      <c r="C1" t="inlineStr"/>
-      <c r="D1" t="inlineStr"/>
-      <c r="E1" t="inlineStr"/>
-      <c r="F1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Last updated: 2026-07-11  |  Session 3</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>Last updated: 2026-07-12  |  Session 5</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>✅ Live</t>
+          <t>⚠️ תוקן שוב</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>TIINGO_TOKEN stored as env var. Removed from code.</t>
+          <t>הביקורת מצאה שה-fallback עם הטוקן האמיתי נשאר בקוד (חשוף ב-GitHub). הוסר (פריט 40). מומלץ לג׳נרט טוקן חדש ב-Tiingo.</t>
         </is>
       </c>
     </row>
@@ -713,7 +713,7 @@
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>✅ Live</t>
+          <t>❌ הוחלף</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>Pings Render every 5 min to prevent cold start.</t>
+          <t>המוניטור הוחלף בחדש; הבעיה האמיתית: השרת לא ענה ל-HEAD (פריט 39). self-ping (33) שומר על השרת ער בכל מקרה.</t>
         </is>
       </c>
     </row>
@@ -897,7 +897,7 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>⏳ Next APK</t>
+          <t>✅ Live</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>updates.url + runtimeVersion + channel בprofiles.</t>
+          <t>updates.url + runtimeVersion + channel מוגדרים. EAS update פועל.</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>⏳ Next APK</t>
+          <t>✅ Live (OTA)</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>vixIcon(): &lt;15=😌 15-20=😐 20-30=😟 &gt;30=😱. כל 4 שפות.</t>
+          <t>אומת בביקורת: vixEmoji() קיים ופעיל. שינוי JS — כבר חי דרך OTA.</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>⏳ Next APK</t>
+          <t>✅ Live (OTA)</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>כל כותרות ב-request אחד עם separator. מהיר פי N.</t>
+          <t>אומת בביקורת: BATCH_SEP קיים ב-utils/translate.js. חי דרך OTA.</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>⏳ Next APK</t>
+          <t>✅ Live (OTA)</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>langReady flag — ממתין לAsyncStorage לפני בקשה ראשונה.</t>
+          <t>אומת בביקורת: קיים ב-AppContext, HomeScreen, NewsScreen. חי דרך OTA.</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>⏳ Next APK</t>
+          <t>✅ Live (OTA)</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>PIL: crop לbounding box + resize לגודל נזיר קנה (357×434).</t>
+          <t>אומת: כל הנזירים 357×434. Assets נשלחים גם ב-OTA — חי.</t>
         </is>
       </c>
     </row>
@@ -1196,122 +1196,902 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>✅  LIVE — Session 4 (2026-07-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>NYT removed from news feed</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Backend / UX</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>assets/1BuddhaVest/main.py</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>_NO_SHOW_DOMAINS + _filter_articles() — nytimes.com/nyti.ms מסוננים ב-/news ו-/news/{ticker}</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Article translation — server-side via /translate-article</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Backend + Frontend</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>main.py, screens/ArticleScreen.js, utils/linkUtils.js</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>curl_cffi chrome124 TLS impersonation → Yahoo Finance עובד. JSON-LD extraction. תרגום מלא ב-backend.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Article error fallback — HTTP 500 → WebView original URL</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Backend / Bug Fix</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>assets/1BuddhaVest/main.py</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>נדחף ופרוס. הוחלף בהמשך בארכיטקטורת Session 5 (פריט 27).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ArticleScreen rewrite — backend translation + WebView fallback</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>✅ Live (OTA)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>screens/ArticleScreen.js</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>הוחלף בארכיטקטורת Session 5: חילוץ מהדף בטלפון + /translate-batch (פריט 27).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>✅  LIVE — Session 5 (2026-07-12): תרגום כתבות, ביצועים, יציבות</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>פענוח קישורי Google News בשרת</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>main.py</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>ה-redirect של גוגל הוא JavaScript; פענוח דרך batchexecute API. /news מחזיר קישורים ישירים.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>תרגום מקבילי — פסקאות וכותרות</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Backend / Performance</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>main.py</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>10 במקביל. כתבה: 15-25 שנ׳ → ~3 שנ׳. כותרות: 10-15 שנ׳ → ~2 שנ׳.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>זיהוי דפי חסימת בוטים</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Backend / Bug Fix</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>main.py</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Reuters/WSJ מגישים captcha לשרתים — מזוהה ומוחזר 500 במקום לתרגם את דף השגיאה.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>תרגום מהדף שנטען בטלפון — DOM extraction + /translate-batch</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Backend + Frontend</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>✅ Live (OTA)</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>main.py, screens/ArticleScreen.js</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>הטלפון שולף כותרת+פסקאות מהדף שכבר נטען, השרת רק מתרגם. עובד גם באתרים שחוסמים שרתים. החליף את proxy translate.goog.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>חסימת מקורות בתשלום מהפיד</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Backend / UX</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>main.py</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>WSJ, Reuters, Bloomberg, Barron׳s, FT, IBD, Seeking Alpha, MarketWatch ועוד — נשארו רק מקורות שנקראים חופשי.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Stooq fallback לטבלת השוק והמדדים</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>main.py, stooq_fallback.py</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>כשיאהו חוסם — מחיר/שינוי/נפח מ-Stooq (כולל תיקון User-Agent). תוצאה ריקה לא נכנסת ל-cache.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>תג "מתורגם" + חיווי "מתרגם..." בשפת המשתמש</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Frontend / i18n</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>✅ Live (OTA)</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>screens/ArticleScreen.js</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>he/ru/es/en — קודם היה קבוע בעברית.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>מטבע מקומי ליד הדולר בכל השפות</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>✅ Live (OTA)</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>screens/HomeScreen.js</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>₪/₽/€ לפי שפת המשתמש ברשימת המניות — קודם רק בעברית.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>מעבר שפות מהיר — cache חדשות משותף</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Backend / Performance</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>main.py</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>איסוף+פענוח פעם אחת לכל השפות; החלפת שפה = תרגום כותרות בלבד. גם ב-/news/{ticker}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Self-ping keep-alive — סוף ל-cold start</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Backend / DevOps</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>main.py</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>השרת מעיר את עצמו כל 10 דק׳ (RENDER_EXTERNAL_URL/status). מחליף את UptimeRobot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>תרגום מקדים ברקע של כתבות מובילות</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Backend / Performance</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>main.py</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>6 הכתבות הראשונות מתורגמות ברקע לשפה שנטענה — פתיחת כתבה מיידית מה-cache.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>הגנת OTA בספלאש — לא לאתחל באמצע שימוש</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>✅ Live (OTA)</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>screens/SplashScreen.js</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>קומט ונדחף יחד עם תיקון StockScreen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>StockScreen נטען מחדש בהחלפת שפה</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Frontend / Bug Fix</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>✅ Live (OTA)</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>screens/StockScreen.js</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>תיאור חברה/מטבע משני נשארו בשפה הקודמת — useEffect היה תלוי רק ב-ticker, עכשיו גם ב-lang.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>חסימת דומיינים שלא ניתנים לתרגום</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Backend / UX</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>main.py</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>fool.com (חוסם בוטים) ו-theglobeandmail.com (paywall) הוסרו מהפיד. סינון לפי דומיין בלבד — כתבות Motley Fool דרך יאהו נשארות.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>endpoint בדיקה: GET /translate-batch</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Backend / Debug</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>main.py</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>וריאנט GET לבדיקת מנוע התרגום מדפדפן. אומת: התרגום עובד.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>תמיכה ב-HEAD על /status — תיקון המוניטור</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Backend / DevOps</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>⏳ ממתין ל-push</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>main.py</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>נמצא ה-root cause של ה-502/405: מוניטורים חינמיים בודקים עם HEAD ו-FastAPI החזיר 405 Method Not Allowed. אחרי push המוניטור יוריק.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>אבטחה: טוקן Tiingo הוסר סופית מהקוד</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>⏳ ממתין לקומיט</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>main.py</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>נמצא בביקורת: fallback חשוף ב-repo ציבורי. עכשיו env var בלבד (מוגדר ב-Render). לג׳נרט מפתח חדש ב-Tiingo כי הישן בהיסטוריית git.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>תיקון package.json — babel-preset-expo כפול</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>⏳ ממתין לקומיט</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>package.json</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>היה גם ב-dependencies (54.x) וגם ב-devDependencies (13.x) — סיכון build. הוסר הכפול.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>תוויות VIX ב-5 רמות תואמות אימוג׳י</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Frontend / i18n</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>⏳ ממתין לקומיט</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>screens/HomeScreen.js</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>vixLabel() חדש — very_calm/calm/elevated/fear/volatile, תואם את מדרגות האימוג׳י, בכל 4 השפות.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>ביקורת פרה-פרודקשן מלאה</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>✅ הושלם</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>כל הקבצים</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>קומפילציה לכל קבצי JS+Python · i18n: 229 מפתחות מלאים ב-4 שפות · 15 endpoints נבדקו חיים · אבטחה · קונפיג build · assets בגדלים נכונים.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>🔜  NOT YET STARTED</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr"/>
-      <c r="C25" s="4" t="inlineStr"/>
-      <c r="D25" s="4" t="inlineStr"/>
-      <c r="E25" s="4" t="inlineStr"/>
-      <c r="F25" s="5" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="B51" s="5" t="inlineStr"/>
+      <c r="C51" s="4" t="inlineStr"/>
+      <c r="D51" s="4" t="inlineStr"/>
+      <c r="E51" s="4" t="inlineStr"/>
+      <c r="F51" s="5" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B52" s="7" t="inlineStr">
         <is>
           <t>Google Play Console — הגשה לחנות</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C52" s="6" t="inlineStr">
         <is>
           <t>Distribution</t>
         </is>
       </c>
-      <c r="D26" s="8" t="inlineStr">
+      <c r="D52" s="8" t="inlineStr">
         <is>
           <t>🔜</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr"/>
-      <c r="F26" s="9" t="inlineStr">
+      <c r="E52" s="9" t="inlineStr"/>
+      <c r="F52" s="9" t="inlineStr">
         <is>
           <t>חשבון מפתח ($25) + העלאת AAB + store listing + screenshots.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="10" t="inlineStr">
         <is>
           <t>Legend</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B54" s="7" t="inlineStr">
         <is>
           <t>פרוס ופעיל ב-Render — נראה לכל המשתמשים</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr"/>
-      <c r="D28" s="8" t="inlineStr"/>
-      <c r="E28" s="9" t="inlineStr"/>
-      <c r="F28" s="9" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
+      <c r="C54" s="6" t="inlineStr"/>
+      <c r="D54" s="8" t="inlineStr"/>
+      <c r="E54" s="9" t="inlineStr"/>
+      <c r="F54" s="9" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>✅ In APK</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B55" s="7" t="inlineStr">
         <is>
           <t>כלול ב-APK המותקן — נראה לכל המשתמשים</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr"/>
-      <c r="D29" s="8" t="inlineStr"/>
-      <c r="E29" s="9" t="inlineStr"/>
-      <c r="F29" s="9" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="C55" s="6" t="inlineStr"/>
+      <c r="D55" s="8" t="inlineStr"/>
+      <c r="E55" s="9" t="inlineStr"/>
+      <c r="F55" s="9" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t>⏳ Next APK</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B56" s="7" t="inlineStr">
         <is>
           <t>הקוד מוזג — דורש build ו-APK חדש</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr"/>
-      <c r="D30" s="8" t="inlineStr"/>
-      <c r="E30" s="9" t="inlineStr"/>
-      <c r="F30" s="9" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
+      <c r="C56" s="6" t="inlineStr"/>
+      <c r="D56" s="8" t="inlineStr"/>
+      <c r="E56" s="9" t="inlineStr"/>
+      <c r="F56" s="9" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B57" s="7" t="inlineStr">
         <is>
           <t>שינוי JS — מועבר אוטומטית בהפעלה הבאה</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="8" t="inlineStr"/>
-      <c r="E31" s="9" t="inlineStr"/>
-      <c r="F31" s="9" t="inlineStr"/>
+      <c r="C57" s="6" t="inlineStr"/>
+      <c r="D57" s="8" t="inlineStr"/>
+      <c r="E57" s="9" t="inlineStr"/>
+      <c r="F57" s="9" t="inlineStr"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A25:F25"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/BuddhaVest_Progress.xlsx
+++ b/BuddhaVest_Progress.xlsx
@@ -530,7 +530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>⏳ ממתין ל-push</t>
+          <t>✅ Live</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>נמצא ה-root cause של ה-502/405: מוניטורים חינמיים בודקים עם HEAD ו-FastAPI החזיר 405 Method Not Allowed. אחרי push המוניטור יוריק.</t>
+          <t>נדחף ופרוס. המוניטור החדש ירוק — הסאגה נסגרה.</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>⏳ ממתין לקומיט</t>
+          <t>✅ Live</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>נמצא בביקורת: fallback חשוף ב-repo ציבורי. עכשיו env var בלבד (מוגדר ב-Render). לג׳נרט מפתח חדש ב-Tiingo כי הישן בהיסטוריית git.</t>
+          <t>נדחף. בנוסף בוצעה רוטציית מפתח ב-Tiingo והחדש הוגדר ב-Render — הישן חסר ערך. אומת: גרף היסטוריה עובד.</t>
         </is>
       </c>
     </row>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>⏳ ממתין לקומיט</t>
+          <t>✅ בקומיט</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>היה גם ב-dependencies (54.x) וגם ב-devDependencies (13.x) — סיכון build. הוסר הכפול.</t>
+          <t>נדחף. חשף צורך בסנכרון package-lock (פריט 50).</t>
         </is>
       </c>
     </row>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>⏳ ממתין לקומיט</t>
+          <t>✅ בקומיט</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>vixLabel() חדש — very_calm/calm/elevated/fear/volatile, תואם את מדרגות האימוג׳י, בכל 4 השפות.</t>
+          <t>נדחף עם קומיט הביקורת.</t>
         </is>
       </c>
     </row>
@@ -1978,115 +1978,371 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>התראות אמיתיות — תזוזות במניות המעקב</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Backend + Frontend</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>⏳ ממתין ל-push</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>main.py, BrandHeader.js, api.js, i18n.js</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>endpoint חדש /quotes; מניות מעקב שזזו ≥2% היום מופיעות בפעמון עם נקודה אדומה, ב-4 שפות. סוגר את הבטחת "כאן יופיעו עדכונים".</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>לוגו מרענן גם במסכי מעקב וחדשות</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Frontend / Bug Fix</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>⏳ ממתין ל-push</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>WatchlistScreen.js, NewsScreen.js</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>ביקורת הבטחות: הטקסט הבטיח רענון מעקב אך הלוגו לא היה מחובר שם.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>תווית גרסה v1.0.0 (היה v1.2)</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>⏳ ממתין ל-push</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>MoreScreen.js</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>יישור מול version בחנות.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>תיקוני נוסח: ToS/מי-אני + גילוי תרגום בפרטיות</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Legal / i18n</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>⏳ ממתין ל-push</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>constants/i18n.js</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>"אין לי רישיון" (היה "לא רישוי"); גילוי Google Translate בסעיף הפרטיות ב-4 שפות; אומת שהנוסחה 40/35/25 תואמת את analyzer.py.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>מעבר דיקציה מלא — 4 שפות</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>QA / i18n</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>✅ הושלם</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>constants/i18n.js</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>232 מפתחות בכל שפה, אפס זליגות/placeholders שבורים/מחרוזות לא מתורגמות. תוקן ¿? חסר בספרדית.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>רוטציית מפתח Tiingo</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>✅ הושלם</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Tiingo + Render env</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Rotate API Token בוצע; TIINGO_TOKEN עודכן ב-Render; אומת חי.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>סנכרון package-lock.json</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Build / Bug Fix</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>⏳ npm install + commit</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>package-lock.json</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>בניית preview נכשלה ב-Install dependencies בגלל lock לא מסונכרן אחרי הסרת הכפילות.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>בניית preview APK (אימות אייקון/ספלאש)</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>⏳ בתהליך</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>EAS</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>אחרי ה-push: eas build --profile preview → התקנה → בדיקת אייקון, ספלאש, התראות.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>🔜  NOT YET STARTED</t>
         </is>
       </c>
-      <c r="B51" s="5" t="inlineStr"/>
-      <c r="C51" s="4" t="inlineStr"/>
-      <c r="D51" s="4" t="inlineStr"/>
-      <c r="E51" s="4" t="inlineStr"/>
-      <c r="F51" s="5" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="6" t="inlineStr">
+      <c r="B59" s="5" t="inlineStr"/>
+      <c r="C59" s="4" t="inlineStr"/>
+      <c r="D59" s="4" t="inlineStr"/>
+      <c r="E59" s="4" t="inlineStr"/>
+      <c r="F59" s="5" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B52" s="7" t="inlineStr">
+      <c r="B60" s="7" t="inlineStr">
         <is>
           <t>Google Play Console — הגשה לחנות</t>
         </is>
       </c>
-      <c r="C52" s="6" t="inlineStr">
+      <c r="C60" s="6" t="inlineStr">
         <is>
           <t>Distribution</t>
         </is>
       </c>
-      <c r="D52" s="8" t="inlineStr">
+      <c r="D60" s="8" t="inlineStr">
         <is>
           <t>🔜</t>
         </is>
       </c>
-      <c r="E52" s="9" t="inlineStr"/>
-      <c r="F52" s="9" t="inlineStr">
+      <c r="E60" s="9" t="inlineStr"/>
+      <c r="F60" s="9" t="inlineStr">
         <is>
           <t>חשבון מפתח ($25) + העלאת AAB + store listing + screenshots.</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="10" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="10" t="inlineStr">
         <is>
           <t>Legend</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="6" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
       </c>
-      <c r="B54" s="7" t="inlineStr">
+      <c r="B62" s="7" t="inlineStr">
         <is>
           <t>פרוס ופעיל ב-Render — נראה לכל המשתמשים</t>
         </is>
       </c>
-      <c r="C54" s="6" t="inlineStr"/>
-      <c r="D54" s="8" t="inlineStr"/>
-      <c r="E54" s="9" t="inlineStr"/>
-      <c r="F54" s="9" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="6" t="inlineStr">
+      <c r="C62" s="6" t="inlineStr"/>
+      <c r="D62" s="8" t="inlineStr"/>
+      <c r="E62" s="9" t="inlineStr"/>
+      <c r="F62" s="9" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
         <is>
           <t>✅ In APK</t>
         </is>
       </c>
-      <c r="B55" s="7" t="inlineStr">
+      <c r="B63" s="7" t="inlineStr">
         <is>
           <t>כלול ב-APK המותקן — נראה לכל המשתמשים</t>
         </is>
       </c>
-      <c r="C55" s="6" t="inlineStr"/>
-      <c r="D55" s="8" t="inlineStr"/>
-      <c r="E55" s="9" t="inlineStr"/>
-      <c r="F55" s="9" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="6" t="inlineStr">
+      <c r="C63" s="6" t="inlineStr"/>
+      <c r="D63" s="8" t="inlineStr"/>
+      <c r="E63" s="9" t="inlineStr"/>
+      <c r="F63" s="9" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
         <is>
           <t>⏳ Next APK</t>
         </is>
       </c>
-      <c r="B56" s="7" t="inlineStr">
+      <c r="B64" s="7" t="inlineStr">
         <is>
           <t>הקוד מוזג — דורש build ו-APK חדש</t>
         </is>
       </c>
-      <c r="C56" s="6" t="inlineStr"/>
-      <c r="D56" s="8" t="inlineStr"/>
-      <c r="E56" s="9" t="inlineStr"/>
-      <c r="F56" s="9" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="6" t="inlineStr">
+      <c r="C64" s="6" t="inlineStr"/>
+      <c r="D64" s="8" t="inlineStr"/>
+      <c r="E64" s="9" t="inlineStr"/>
+      <c r="F64" s="9" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
       </c>
-      <c r="B57" s="7" t="inlineStr">
+      <c r="B65" s="7" t="inlineStr">
         <is>
           <t>שינוי JS — מועבר אוטומטית בהפעלה הבאה</t>
         </is>
       </c>
-      <c r="C57" s="6" t="inlineStr"/>
-      <c r="D57" s="8" t="inlineStr"/>
-      <c r="E57" s="9" t="inlineStr"/>
-      <c r="F57" s="9" t="inlineStr"/>
+      <c r="C65" s="6" t="inlineStr"/>
+      <c r="D65" s="8" t="inlineStr"/>
+      <c r="E65" s="9" t="inlineStr"/>
+      <c r="F65" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/BuddhaVest_Progress.xlsx
+++ b/BuddhaVest_Progress.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,8 +52,17 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -83,6 +92,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001a7340"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001A7340"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -136,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -165,6 +184,42 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -530,7 +585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -551,7 +606,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Last updated: 2026-07-12  |  Session 5</t>
+          <t>Last updated: 2026-07-25  |  Session 6</t>
         </is>
       </c>
     </row>
@@ -2234,118 +2289,1390 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="inlineStr">
+      <c r="A59" s="12" t="inlineStr">
+        <is>
+          <t>✅  Session 6 (2026-07-24/25): מרוצים, אבטחה, ביצועים, משפטי — ביקורת מלאה</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="13" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B60" s="14" t="inlineStr">
+        <is>
+          <t>מרוץ שפות — 5 מסכים/רכיבים</t>
+        </is>
+      </c>
+      <c r="C60" s="13" t="inlineStr">
+        <is>
+          <t>Frontend / Bug Fix</t>
+        </is>
+      </c>
+      <c r="D60" s="15" t="inlineStr">
+        <is>
+          <t>✅ Live (OTA)</t>
+        </is>
+      </c>
+      <c r="E60" s="16" t="inlineStr">
+        <is>
+          <t>NewsScreen, NewsCard, WatchlistScreen, HomeScreen, StockScreen</t>
+        </is>
+      </c>
+      <c r="F60" s="16" t="inlineStr">
+        <is>
+          <t>טוקן reqId מונוטוני בכל טעינה. תגובה איטית בשפה ישנה כבר לא דורסת את החדשה — הטקסט הפסיק לקפוץ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="13" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="B61" s="14" t="inlineStr">
+        <is>
+          <t>Volume/Avg Vol ריקים לסירוגין</t>
+        </is>
+      </c>
+      <c r="C61" s="13" t="inlineStr">
+        <is>
+          <t>Backend / Bug Fix</t>
+        </is>
+      </c>
+      <c r="D61" s="15" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="E61" s="16" t="inlineStr">
+        <is>
+          <t>main.py</t>
+        </is>
+      </c>
+      <c r="F61" s="16" t="inlineStr">
+        <is>
+          <t>Last-known-good לכל טיקר + שמירה לדיסק (/tmp) כדי לשרוד restart של Render. גם trigger ל-Stooq כשחסר נפח ולא רק מחיר.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="13" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="B62" s="14" t="inlineStr">
+        <is>
+          <t>המרת אגורות→שקל למניות ת"א</t>
+        </is>
+      </c>
+      <c r="C62" s="13" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="D62" s="15" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="E62" s="16" t="inlineStr">
+        <is>
+          <t>main.py</t>
+        </is>
+      </c>
+      <c r="F62" s="16" t="inlineStr">
+        <is>
+          <t>דלק הציגה 8173 במקום 81.73. זיהוי לפי סיומת .TA וגם שדה currency (ILA/ILS). הומר: מחיר, טווח 52 שבועות, היסטוריה, אירועי דיבידנד.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="13" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="B63" s="14" t="inlineStr">
+        <is>
+          <t>באג יחידות ב-Buyback (3500000000%)</t>
+        </is>
+      </c>
+      <c r="C63" s="13" t="inlineStr">
+        <is>
+          <t>Backend + Frontend</t>
+        </is>
+      </c>
+      <c r="D63" s="15" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="E63" s="16" t="inlineStr">
+        <is>
+          <t>analyzer.py, StockScreen.js</t>
+        </is>
+      </c>
+      <c r="F63" s="16" t="inlineStr">
+        <is>
+          <t>value_unit='percent'/'currency'. בלי שווי שוק הערך הוא סכום גולמי — הוצג עם % ויצר מספר אבסורדי.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="13" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="B64" s="14" t="inlineStr">
+        <is>
+          <t>תיקוני נכונות במנוע הציון</t>
+        </is>
+      </c>
+      <c r="C64" s="13" t="inlineStr">
+        <is>
+          <t>Backend / Scoring</t>
+        </is>
+      </c>
+      <c r="D64" s="15" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="E64" s="16" t="inlineStr">
+        <is>
+          <t>analyzer.py</t>
+        </is>
+      </c>
+      <c r="F64" s="16" t="inlineStr">
+        <is>
+          <t>FCF עמיד לסימן (ocf-abs(capex)); מיון סדרות לפני iloc[0]/iloc[1] כדי שמגמת רווח לא תתהפך; מיון דיבידנדים לפני index[-1]/tail(4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="13" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="B65" s="14" t="inlineStr">
+        <is>
+          <t>ניסוח דיבידנד כן — לא "משולם בעקביות"</t>
+        </is>
+      </c>
+      <c r="C65" s="13" t="inlineStr">
+        <is>
+          <t>Legal / Accuracy</t>
+        </is>
+      </c>
+      <c r="D65" s="15" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="E65" s="16" t="inlineStr">
+        <is>
+          <t>analyzer.py, i18n_data.py</t>
+        </is>
+      </c>
+      <c r="F65" s="16" t="inlineStr">
+        <is>
+          <t>הנתון מודד טווח היסטוריה, לא רציפות תשלומים. חברה שהפסיקה וחידשה היתה מקבלת אותו מספר.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="13" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="B66" s="14" t="inlineStr">
+        <is>
+          <t>SSRF — /translate-article</t>
+        </is>
+      </c>
+      <c r="C66" s="13" t="inlineStr">
+        <is>
+          <t>Backend / Security</t>
+        </is>
+      </c>
+      <c r="D66" s="15" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="E66" s="16" t="inlineStr">
+        <is>
+          <t>main.py</t>
+        </is>
+      </c>
+      <c r="F66" s="16" t="inlineStr">
+        <is>
+          <t>חסימת loopback/פרטי/link-local/metadata (169.254.169.254), כולל בדיקה שנייה על canonical URL שמגיע מהדף עצמו.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="13" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="B67" s="14" t="inlineStr">
+        <is>
+          <t>XSS ב-WebView של הכתבות</t>
+        </is>
+      </c>
+      <c r="C67" s="13" t="inlineStr">
+        <is>
+          <t>Frontend / Security</t>
+        </is>
+      </c>
+      <c r="D67" s="15" t="inlineStr">
+        <is>
+          <t>✅ Live (OTA)</t>
+        </is>
+      </c>
+      <c r="E67" s="16" t="inlineStr">
+        <is>
+          <t>ArticleScreen.js</t>
+        </is>
+      </c>
+      <c r="F67" s="16" t="inlineStr">
+        <is>
+          <t>שמות תגיות מהדף עברו ל-whitelist (p/h2/h3) וטקסט עובר escape — דף עוין יכול היה לשלוח tag:"script".</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="13" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B68" s="14" t="inlineStr">
+        <is>
+          <t>הסרת /debug-pe ו-/debug-rows</t>
+        </is>
+      </c>
+      <c r="C68" s="13" t="inlineStr">
+        <is>
+          <t>Backend / Security</t>
+        </is>
+      </c>
+      <c r="D68" s="15" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="E68" s="16" t="inlineStr">
+        <is>
+          <t>main.py</t>
+        </is>
+      </c>
+      <c r="F68" s="16" t="inlineStr">
+        <is>
+          <t>ראוטים ציבוריים שהחזירו traceback מלא, לא ולידציה על טיקר, ובלי מטמון — דרך לרוקן זיכרון לשרת.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="13" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="B69" s="14" t="inlineStr">
+        <is>
+          <t>5 דליפות של פרטי חריגה ללקוח</t>
+        </is>
+      </c>
+      <c r="C69" s="13" t="inlineStr">
+        <is>
+          <t>Backend / Security</t>
+        </is>
+      </c>
+      <c r="D69" s="15" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="E69" s="16" t="inlineStr">
+        <is>
+          <t>main.py</t>
+        </is>
+      </c>
+      <c r="F69" s="16" t="inlineStr">
+        <is>
+          <t>str(e) הוחלף בהודעה גנרית + לוג פנימי.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="13" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="B70" s="14" t="inlineStr">
+        <is>
+          <t>פיצוץ זיכרון בעליית השרת</t>
+        </is>
+      </c>
+      <c r="C70" s="13" t="inlineStr">
+        <is>
+          <t>Backend / Performance</t>
+        </is>
+      </c>
+      <c r="D70" s="15" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="E70" s="16" t="inlineStr">
+        <is>
+          <t>main.py</t>
+        </is>
+      </c>
+      <c r="F70" s="16" t="inlineStr">
+        <is>
+          <t>_BOOTING מדכא תרגום מקדים בזמן החימום; השפות מרווחות (15s ואז 10s). 18 הורדות כבדות בדקה הראשונה → 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="13" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="B71" s="14" t="inlineStr">
+        <is>
+          <t>תקרת מטמון + single-flight</t>
+        </is>
+      </c>
+      <c r="C71" s="13" t="inlineStr">
+        <is>
+          <t>Backend / Performance</t>
+        </is>
+      </c>
+      <c r="D71" s="15" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="E71" s="16" t="inlineStr">
+        <is>
+          <t>main.py</t>
+        </is>
+      </c>
+      <c r="F71" s="16" t="inlineStr">
+        <is>
+          <t>_CACHE_MAX=300 ונעילה לכל מפתח — N משתמשים על אותו טיקר = שליפה אחת מיאהו במקום N.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="13" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="B72" s="14" t="inlineStr">
+        <is>
+          <t>חלון היסטוריה 10y במקום max</t>
+        </is>
+      </c>
+      <c r="C72" s="13" t="inlineStr">
+        <is>
+          <t>Backend / Performance</t>
+        </is>
+      </c>
+      <c r="D72" s="15" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="E72" s="16" t="inlineStr">
+        <is>
+          <t>main.py</t>
+        </is>
+      </c>
+      <c r="F72" s="16" t="inlineStr">
+        <is>
+          <t>KO נסחרת מ-1962: 16,000 שורות יומיות לתוך pandas כדי להפיק 44 נקודות. ~84% פחות נתונים.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="13" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="B73" s="14" t="inlineStr">
+        <is>
+          <t>Debounce בחיפוש</t>
+        </is>
+      </c>
+      <c r="C73" s="13" t="inlineStr">
+        <is>
+          <t>Frontend / Performance</t>
+        </is>
+      </c>
+      <c r="D73" s="15" t="inlineStr">
+        <is>
+          <t>✅ Live (OTA)</t>
+        </is>
+      </c>
+      <c r="E73" s="16" t="inlineStr">
+        <is>
+          <t>SearchScreen.js</t>
+        </is>
+      </c>
+      <c r="F73" s="16" t="inlineStr">
+        <is>
+          <t>הקלדת AAPL שלחה 4 בקשות; עכשיו אחת אחרי 300ms שקט.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="13" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="B74" s="14" t="inlineStr">
+        <is>
+          <t>תקציב זמן ל-Stooq</t>
+        </is>
+      </c>
+      <c r="C74" s="13" t="inlineStr">
+        <is>
+          <t>Backend / Performance</t>
+        </is>
+      </c>
+      <c r="D74" s="15" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="E74" s="16" t="inlineStr">
+        <is>
+          <t>stooq_fallback.py</t>
+        </is>
+      </c>
+      <c r="F74" s="16" t="inlineStr">
+        <is>
+          <t>8 סיומות × 4s = 32s לסימול שלא קיים, הרבה אחרי שהאפליקציה ויתרה. עכשיו תקרה של 10s; סימול עם סיומת לא מנסה עוד.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="13" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="B75" s="14" t="inlineStr">
+        <is>
+          <t>אובדן נתונים ביומן המחקר</t>
+        </is>
+      </c>
+      <c r="C75" s="13" t="inlineStr">
+        <is>
+          <t>Frontend / Bug Fix</t>
+        </is>
+      </c>
+      <c r="D75" s="15" t="inlineStr">
+        <is>
+          <t>✅ Live (OTA)</t>
+        </is>
+      </c>
+      <c r="E75" s="16" t="inlineStr">
+        <is>
+          <t>MoreScreen.js</t>
+        </is>
+      </c>
+      <c r="F75" s="16" t="inlineStr">
+        <is>
+          <t>שמירה מוזגה מול הדיסק ולא מול state; מחיקה לפי זהות (תאריך+טקסט) ולא לפי אינדקס.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="17" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="B76" s="18" t="inlineStr">
+        <is>
+          <t>תמיכת טאבלט</t>
+        </is>
+      </c>
+      <c r="C76" s="17" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="D76" s="19" t="inlineStr">
+        <is>
+          <t>⏳ דורש build</t>
+        </is>
+      </c>
+      <c r="E76" s="20" t="inlineStr">
+        <is>
+          <t>App.js, app.json, PriceChart.js, FloatingThemeToggle.js</t>
+        </is>
+      </c>
+      <c r="F76" s="20" t="inlineStr">
+        <is>
+          <t>TabletFrame (רוחב ≥700 ממורכז ל-600), שחרור סיבוב לטאבלט ונעילת portrait לטלפון, כפתור צף שנצמד מחדש בסיבוב. supportsTablet=true.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="13" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="B77" s="14" t="inlineStr">
+        <is>
+          <t>מסך הסכמה בהפעלה ראשונה</t>
+        </is>
+      </c>
+      <c r="C77" s="13" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="D77" s="15" t="inlineStr">
+        <is>
+          <t>✅ Live (OTA)</t>
+        </is>
+      </c>
+      <c r="E77" s="16" t="inlineStr">
+        <is>
+          <t>App.js, i18n.js</t>
+        </is>
+      </c>
+      <c r="F77" s="16" t="inlineStr">
+        <is>
+          <t>"כלי מחקר, לא ייעוץ" — הסכמה מפורשת חזקה משתיקה. 4 שפות, מוצג פעם אחת.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="13" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="B78" s="14" t="inlineStr">
+        <is>
+          <t>שכתוב תיאור החנות — בלי הבטחות</t>
+        </is>
+      </c>
+      <c r="C78" s="13" t="inlineStr">
+        <is>
+          <t>Legal / Store</t>
+        </is>
+      </c>
+      <c r="D78" s="15" t="inlineStr">
+        <is>
+          <t>✅ מוכן</t>
+        </is>
+      </c>
+      <c r="E78" s="16" t="inlineStr">
+        <is>
+          <t>store-listing.md</t>
+        </is>
+      </c>
+      <c r="F78" s="16" t="inlineStr">
+        <is>
+          <t>הוסרו טענות "יועץ AI"; הודגש שהציון הוא חישוב מתמטי. AI לא מודגש בניסוח.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="13" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="B79" s="14" t="inlineStr">
+        <is>
+          <t>מדריך צילומי מסך לחנות</t>
+        </is>
+      </c>
+      <c r="C79" s="13" t="inlineStr">
+        <is>
+          <t>Store Assets</t>
+        </is>
+      </c>
+      <c r="D79" s="15" t="inlineStr">
+        <is>
+          <t>✅ הושלם</t>
+        </is>
+      </c>
+      <c r="E79" s="16" t="inlineStr">
+        <is>
+          <t>מדריך-צילומי-מסך-לחנות.docx</t>
+        </is>
+      </c>
+      <c r="F79" s="16" t="inlineStr">
+        <is>
+          <t>5 מסכים, מידות, והנחיות צילום.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="13" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="B80" s="14" t="inlineStr">
+        <is>
+          <t>RTL בכל המסכים</t>
+        </is>
+      </c>
+      <c r="C80" s="13" t="inlineStr">
+        <is>
+          <t>Frontend / i18n</t>
+        </is>
+      </c>
+      <c r="D80" s="15" t="inlineStr">
+        <is>
+          <t>✅ Live (OTA)</t>
+        </is>
+      </c>
+      <c r="E80" s="16" t="inlineStr">
+        <is>
+          <t>8 מסכים/רכיבים</t>
+        </is>
+      </c>
+      <c r="F80" s="16" t="inlineStr">
+        <is>
+          <t>כל משפט מתורגם ארוך קיבל textAlign+writingDirection. עברית היחידה RTL מבין ה-4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="13" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="B81" s="14" t="inlineStr">
+        <is>
+          <t>תווית גרסה מ-app.json</t>
+        </is>
+      </c>
+      <c r="C81" s="13" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="D81" s="15" t="inlineStr">
+        <is>
+          <t>✅ Live (OTA)</t>
+        </is>
+      </c>
+      <c r="E81" s="16" t="inlineStr">
+        <is>
+          <t>MoreScreen.js</t>
+        </is>
+      </c>
+      <c r="F81" s="16" t="inlineStr">
+        <is>
+          <t>היה מחרוזת קשיחה — bump גרסה היה משאיר את המסך על 1.0.0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="13" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="B82" s="14" t="inlineStr">
+        <is>
+          <t>טעינה דו-שלבית ברשימת המעקב</t>
+        </is>
+      </c>
+      <c r="C82" s="13" t="inlineStr">
+        <is>
+          <t>Frontend / Performance</t>
+        </is>
+      </c>
+      <c r="D82" s="15" t="inlineStr">
+        <is>
+          <t>✅ Live (OTA)</t>
+        </is>
+      </c>
+      <c r="E82" s="16" t="inlineStr">
+        <is>
+          <t>WatchlistScreen.js, main.py</t>
+        </is>
+      </c>
+      <c r="F82" s="16" t="inlineStr">
+        <is>
+          <t>/quotes קל לכל הרשימה תחילה, ואז /analyze בקבוצות עם ציור מצטבר. זמן עד תוכן ראשון: 4000ms → 400ms (פי 10). שער חליפין במקביל.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="13" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="B83" s="14" t="inlineStr">
+        <is>
+          <t>/quotes: אגורות, שם חברה, מטבע</t>
+        </is>
+      </c>
+      <c r="C83" s="13" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="D83" s="15" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="E83" s="16" t="inlineStr">
+        <is>
+          <t>main.py</t>
+        </is>
+      </c>
+      <c r="F83" s="16" t="inlineStr">
+        <is>
+          <t>הפאזה המהירה היתה מהבהבת 8445 לפני התיקון. longName כדי שהשם לא יתחלף שנייה אחרי.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="13" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="B84" s="14" t="inlineStr">
+        <is>
+          <t>מיזוג במקום החלפה ברשימת המעקב</t>
+        </is>
+      </c>
+      <c r="C84" s="13" t="inlineStr">
+        <is>
+          <t>Frontend / Bug Fix</t>
+        </is>
+      </c>
+      <c r="D84" s="15" t="inlineStr">
+        <is>
+          <t>✅ Live (OTA)</t>
+        </is>
+      </c>
+      <c r="E84" s="16" t="inlineStr">
+        <is>
+          <t>WatchlistScreen.js</t>
+        </is>
+      </c>
+      <c r="F84" s="16" t="inlineStr">
+        <is>
+          <t>פאזה 1 מחקה את כל הציונים בכל רענון אוטומטי (כל 90 שניות) — הבהוב בכל מחזור.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="13" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="B85" s="14" t="inlineStr">
+        <is>
+          <t>מרוץ במסך הבית — market/FX</t>
+        </is>
+      </c>
+      <c r="C85" s="13" t="inlineStr">
+        <is>
+          <t>Frontend / Bug Fix</t>
+        </is>
+      </c>
+      <c r="D85" s="15" t="inlineStr">
+        <is>
+          <t>✅ Live (OTA)</t>
+        </is>
+      </c>
+      <c r="E85" s="16" t="inlineStr">
+        <is>
+          <t>HomeScreen.js</t>
+        </is>
+      </c>
+      <c r="F85" s="16" t="inlineStr">
+        <is>
+          <t>שרת קר: קריאה שנכשלה ב-20s ומנסה שוב ב-50s חוזרת אחרונה ודורסת נתונים טריים. מונים נפרדים ל-market ול-FX.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="13" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="B86" s="14" t="inlineStr">
+        <is>
+          <t>תשובה ריקה לא מוחקת נתונים טובים</t>
+        </is>
+      </c>
+      <c r="C86" s="13" t="inlineStr">
+        <is>
+          <t>Frontend / Bug Fix</t>
+        </is>
+      </c>
+      <c r="D86" s="15" t="inlineStr">
+        <is>
+          <t>✅ Live (OTA)</t>
+        </is>
+      </c>
+      <c r="E86" s="16" t="inlineStr">
+        <is>
+          <t>HomeScreen.js</t>
+        </is>
+      </c>
+      <c r="F86" s="16" t="inlineStr">
+        <is>
+          <t>הסיבה ל"פעם יש נתונים פעם אין" בטבלת המניות.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="13" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="B87" s="14" t="inlineStr">
+        <is>
+          <t>תרגום כתבה ישנה דלף לחדשה</t>
+        </is>
+      </c>
+      <c r="C87" s="13" t="inlineStr">
+        <is>
+          <t>Frontend / Bug Fix</t>
+        </is>
+      </c>
+      <c r="D87" s="15" t="inlineStr">
+        <is>
+          <t>✅ Live (OTA)</t>
+        </is>
+      </c>
+      <c r="E87" s="16" t="inlineStr">
+        <is>
+          <t>ArticleScreen.js</t>
+        </is>
+      </c>
+      <c r="F87" s="16" t="inlineStr">
+        <is>
+          <t>נתיב ה-DOM לא בוטל אף פעם; מעבר לכתבה אחרת הציג את הטקסט הקודם. גם ספינר תקוע בתשובה קצרה.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="13" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="B88" s="14" t="inlineStr">
+        <is>
+          <t>מרוץ ב"נסה שוב" של פירוט מדד</t>
+        </is>
+      </c>
+      <c r="C88" s="13" t="inlineStr">
+        <is>
+          <t>Frontend / Bug Fix</t>
+        </is>
+      </c>
+      <c r="D88" s="15" t="inlineStr">
+        <is>
+          <t>✅ Live (OTA)</t>
+        </is>
+      </c>
+      <c r="E88" s="16" t="inlineStr">
+        <is>
+          <t>MetricHistoryScreen.js</t>
+        </is>
+      </c>
+      <c r="F88" s="16" t="inlineStr">
+        <is>
+          <t>לחיצה כפולה: הכישלון האיטי חוזר אחרי ההצלחה ומחליף גרף תקין במסך שגיאה.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="13" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="B89" s="14" t="inlineStr">
+        <is>
+          <t>סולם VIX לא מונוטוני</t>
+        </is>
+      </c>
+      <c r="C89" s="13" t="inlineStr">
+        <is>
+          <t>Frontend / i18n</t>
+        </is>
+      </c>
+      <c r="D89" s="15" t="inlineStr">
+        <is>
+          <t>✅ Live (OTA)</t>
+        </is>
+      </c>
+      <c r="E89" s="16" t="inlineStr">
+        <is>
+          <t>i18n.js</t>
+        </is>
+      </c>
+      <c r="F89" s="16" t="inlineStr">
+        <is>
+          <t>VIX 27 = "פחד קיצוני" אבל VIX 45 = "תנודתיות גבוהה" — אזהרה רכה יותר במצב חמור יותר. תוקן ב-4 שפות.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="13" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="B90" s="14" t="inlineStr">
+        <is>
+          <t>תיקוני תוכן בספרדית</t>
+        </is>
+      </c>
+      <c r="C90" s="13" t="inlineStr">
+        <is>
+          <t>i18n / Accuracy</t>
+        </is>
+      </c>
+      <c r="D90" s="15" t="inlineStr">
+        <is>
+          <t>✅ Live (OTA)</t>
+        </is>
+      </c>
+      <c r="E90" s="16" t="inlineStr">
+        <is>
+          <t>i18n.js</t>
+        </is>
+      </c>
+      <c r="F90" s="16" t="inlineStr">
+        <is>
+          <t>הסבר הדיבידנד השמיט את חצי המשפט על יציבות; טקסט הצהיר "servidor local" בעוד השרת ב-Render.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="17" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="B91" s="18" t="inlineStr">
+        <is>
+          <t>Cache-Control: no-store על כל ה-API</t>
+        </is>
+      </c>
+      <c r="C91" s="17" t="inlineStr">
+        <is>
+          <t>Backend / Bug Fix</t>
+        </is>
+      </c>
+      <c r="D91" s="19" t="inlineStr">
+        <is>
+          <t>⏳ ממתין ל-push</t>
+        </is>
+      </c>
+      <c r="E91" s="20" t="inlineStr">
+        <is>
+          <t>main.py</t>
+        </is>
+      </c>
+      <c r="F91" s="20" t="inlineStr">
+        <is>
+          <t>הסיבה האמיתית שדלק חזרה: OkHttp של אנדרואיד שמר תשובה שנוצרה בגרסת קוד ישנה. הוכח — אותה מניה ב-en החזירה 8173 וב-ru החזירה 84.45.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="17" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="B92" s="18" t="inlineStr">
+        <is>
+          <t>סדרה שנתית = סוף שנה, לא ינואר</t>
+        </is>
+      </c>
+      <c r="C92" s="17" t="inlineStr">
+        <is>
+          <t>Backend / Bug Fix</t>
+        </is>
+      </c>
+      <c r="D92" s="19" t="inlineStr">
+        <is>
+          <t>⏳ ממתין ל-push</t>
+        </is>
+      </c>
+      <c r="E92" s="20" t="inlineStr">
+        <is>
+          <t>main.py</t>
+        </is>
+      </c>
+      <c r="F92" s="20" t="inlineStr">
+        <is>
+          <t>הגרף השנתי הציג את ינואר בתווית של השנה. KO 2023: הוצג 25.25 במקום 22.19 — סטייה 12%. תוקן ב-4 מקומות.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="17" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="B93" s="18" t="inlineStr">
+        <is>
+          <t>TTM של Buyback דרש 2 רבעונים</t>
+        </is>
+      </c>
+      <c r="C93" s="17" t="inlineStr">
+        <is>
+          <t>Backend / Bug Fix</t>
+        </is>
+      </c>
+      <c r="D93" s="19" t="inlineStr">
+        <is>
+          <t>⏳ ממתין ל-push</t>
+        </is>
+      </c>
+      <c r="E93" s="20" t="inlineStr">
+        <is>
+          <t>main.py</t>
+        </is>
+      </c>
+      <c r="F93" s="20" t="inlineStr">
+        <is>
+          <t>"תשואה שנתית" יכלה להיות סכום של חצי שנה. הועלה ל-4 כמו כל שאר חישובי ה-TTM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="13" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="B94" s="14" t="inlineStr">
+        <is>
+          <t>ניקוי ריפו — cloudflared.exe 52MB</t>
+        </is>
+      </c>
+      <c r="C94" s="13" t="inlineStr">
+        <is>
+          <t>DevOps</t>
+        </is>
+      </c>
+      <c r="D94" s="15" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="E94" s="16" t="inlineStr">
+        <is>
+          <t>‎.gitignore</t>
+        </is>
+      </c>
+      <c r="F94" s="16" t="inlineStr">
+        <is>
+          <t>יצא ממעקב git, נשאר על הדיסק המקומי.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="13" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="B95" s="14" t="inlineStr">
+        <is>
+          <t>דיוק עמוד הפרטיות בנוגע ללוגים</t>
+        </is>
+      </c>
+      <c r="C95" s="13" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="D95" s="15" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="E95" s="16" t="inlineStr">
+        <is>
+          <t>main.py</t>
+        </is>
+      </c>
+      <c r="F95" s="16" t="inlineStr">
+        <is>
+          <t>ההצהרה "איננו רושמים כתובות IP" לא היתה מדויקת — uvicorn ו-Render כן שומרים לוגים טכניים. נוסח מחדש.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="13" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="B96" s="14" t="inlineStr">
+        <is>
+          <t>ביקורת קוד מלאה — 35 קבצים</t>
+        </is>
+      </c>
+      <c r="C96" s="13" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="D96" s="15" t="inlineStr">
+        <is>
+          <t>✅ הושלם</t>
+        </is>
+      </c>
+      <c r="E96" s="16" t="inlineStr">
+        <is>
+          <t>כל הקבצים</t>
+        </is>
+      </c>
+      <c r="F96" s="16" t="inlineStr">
+        <is>
+          <t>11,646 שורות נקראו במלואן. 27 חבילות בדיקה התנהגותיות. אימות חי מול ה-API בייצור (זה מה שחשף פריטים 83-85).</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
         <is>
           <t>🔜  NOT YET STARTED</t>
         </is>
       </c>
-      <c r="B59" s="5" t="inlineStr"/>
-      <c r="C59" s="4" t="inlineStr"/>
-      <c r="D59" s="4" t="inlineStr"/>
-      <c r="E59" s="4" t="inlineStr"/>
-      <c r="F59" s="5" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="6" t="inlineStr">
+      <c r="B97" s="5" t="inlineStr"/>
+      <c r="C97" s="4" t="inlineStr"/>
+      <c r="D97" s="4" t="inlineStr"/>
+      <c r="E97" s="4" t="inlineStr"/>
+      <c r="F97" s="5" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B60" s="7" t="inlineStr">
+      <c r="B98" s="7" t="inlineStr">
         <is>
           <t>Google Play Console — הגשה לחנות</t>
         </is>
       </c>
-      <c r="C60" s="6" t="inlineStr">
+      <c r="C98" s="6" t="inlineStr">
         <is>
           <t>Distribution</t>
         </is>
       </c>
-      <c r="D60" s="8" t="inlineStr">
+      <c r="D98" s="8" t="inlineStr">
         <is>
           <t>🔜</t>
         </is>
       </c>
-      <c r="E60" s="9" t="inlineStr"/>
-      <c r="F60" s="9" t="inlineStr">
+      <c r="E98" s="9" t="inlineStr"/>
+      <c r="F98" s="9" t="inlineStr">
         <is>
           <t>חשבון מפתח ($25) + העלאת AAB + store listing + screenshots.</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="10" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="10" t="inlineStr">
         <is>
           <t>Legend</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="6" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="6" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
       </c>
-      <c r="B62" s="7" t="inlineStr">
+      <c r="B100" s="7" t="inlineStr">
         <is>
           <t>פרוס ופעיל ב-Render — נראה לכל המשתמשים</t>
         </is>
       </c>
-      <c r="C62" s="6" t="inlineStr"/>
-      <c r="D62" s="8" t="inlineStr"/>
-      <c r="E62" s="9" t="inlineStr"/>
-      <c r="F62" s="9" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="6" t="inlineStr">
+      <c r="C100" s="6" t="inlineStr"/>
+      <c r="D100" s="8" t="inlineStr"/>
+      <c r="E100" s="9" t="inlineStr"/>
+      <c r="F100" s="9" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="6" t="inlineStr">
         <is>
           <t>✅ In APK</t>
         </is>
       </c>
-      <c r="B63" s="7" t="inlineStr">
+      <c r="B101" s="7" t="inlineStr">
         <is>
           <t>כלול ב-APK המותקן — נראה לכל המשתמשים</t>
         </is>
       </c>
-      <c r="C63" s="6" t="inlineStr"/>
-      <c r="D63" s="8" t="inlineStr"/>
-      <c r="E63" s="9" t="inlineStr"/>
-      <c r="F63" s="9" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="6" t="inlineStr">
+      <c r="C101" s="6" t="inlineStr"/>
+      <c r="D101" s="8" t="inlineStr"/>
+      <c r="E101" s="9" t="inlineStr"/>
+      <c r="F101" s="9" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="6" t="inlineStr">
         <is>
           <t>⏳ Next APK</t>
         </is>
       </c>
-      <c r="B64" s="7" t="inlineStr">
+      <c r="B102" s="7" t="inlineStr">
         <is>
           <t>הקוד מוזג — דורש build ו-APK חדש</t>
         </is>
       </c>
-      <c r="C64" s="6" t="inlineStr"/>
-      <c r="D64" s="8" t="inlineStr"/>
-      <c r="E64" s="9" t="inlineStr"/>
-      <c r="F64" s="9" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="6" t="inlineStr">
+      <c r="C102" s="6" t="inlineStr"/>
+      <c r="D102" s="8" t="inlineStr"/>
+      <c r="E102" s="9" t="inlineStr"/>
+      <c r="F102" s="9" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="6" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
       </c>
-      <c r="B65" s="7" t="inlineStr">
+      <c r="B103" s="7" t="inlineStr">
         <is>
           <t>שינוי JS — מועבר אוטומטית בהפעלה הבאה</t>
         </is>
       </c>
-      <c r="C65" s="6" t="inlineStr"/>
-      <c r="D65" s="8" t="inlineStr"/>
-      <c r="E65" s="9" t="inlineStr"/>
-      <c r="F65" s="9" t="inlineStr"/>
+      <c r="C103" s="6" t="inlineStr"/>
+      <c r="D103" s="8" t="inlineStr"/>
+      <c r="E103" s="9" t="inlineStr"/>
+      <c r="F103" s="9" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="21" t="inlineStr">
+        <is>
+          <t>⏳ ממתין ל-push</t>
+        </is>
+      </c>
+      <c r="B104" s="22" t="inlineStr">
+        <is>
+          <t>הקוד מוכן מקומית — טרם נדחף/נפרס</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="21" t="inlineStr">
+        <is>
+          <t>⏳ דורש build</t>
+        </is>
+      </c>
+      <c r="B105" s="22" t="inlineStr">
+        <is>
+          <t>שינוי נייטיב — OTA לא מספיק, צריך AAB/APK חדש</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="23" t="inlineStr">
+        <is>
+          <t>סיכום Session 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="24" t="n"/>
+      <c r="B108" s="25" t="inlineStr">
+        <is>
+          <t>37  —  פריטים חדשים שנוספו (52-88)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="24" t="n"/>
+      <c r="B109" s="25" t="inlineStr">
+        <is>
+          <t>32  —  כבר חיים בייצור או ב-OTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="24" t="n"/>
+      <c r="B110" s="25" t="inlineStr">
+        <is>
+          <t>3  —  ממתינים ל-push: no-store, סדרה שנתית, TTM של buyback</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="24" t="n"/>
+      <c r="B111" s="25" t="inlineStr">
+        <is>
+          <t>1  —  דורש build חדש: תמיכת טאבלט</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="24" t="n"/>
+      <c r="B112" s="25" t="inlineStr">
+        <is>
+          <t>11,646  —  שורות קוד שנקראו במלואן, 35 קבצים</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="24" t="n"/>
+      <c r="B113" s="25" t="inlineStr">
+        <is>
+          <t>27  —  חבילות בדיקה התנהגותיות עוברות</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="3">
+    <mergeCell ref="A107:F107"/>
+    <mergeCell ref="A59:F59"/>
     <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/BuddhaVest_Progress.xlsx
+++ b/BuddhaVest_Progress.xlsx
@@ -105,7 +105,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -151,11 +151,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -219,6 +239,25 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -585,7 +624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F113"/>
+  <dimension ref="A1:F123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -606,7 +645,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Last updated: 2026-07-25  |  Session 6</t>
+          <t>Last updated: 2026-07-25  |  Session 7</t>
         </is>
       </c>
     </row>
@@ -2033,130 +2072,130 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="29" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="29" t="inlineStr">
         <is>
           <t>התראות אמיתיות — תזוזות במניות המעקב</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="29" t="inlineStr">
         <is>
           <t>Backend + Frontend</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>⏳ ממתין ל-push</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
+      <c r="D51" s="29" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="E51" s="29" t="inlineStr">
         <is>
           <t>main.py, BrandHeader.js, api.js, i18n.js</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>endpoint חדש /quotes; מניות מעקב שזזו ≥2% היום מופיעות בפעמון עם נקודה אדומה, ב-4 שפות. סוגר את הבטחת "כאן יופיעו עדכונים".</t>
+      <c r="F51" s="29" t="inlineStr">
+        <is>
+          <t>endpoint חדש /quotes; מניות מעקב שזזו ≥2% היום מופיעות בפעמון עם נקודה אדומה, ב-4 שפות. סוגר את הבטחת "כאן יופיעו עדכונים". תיוג התיישן — אומת שהקוד קיים בענף המרוחק.</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="29" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="29" t="inlineStr">
         <is>
           <t>לוגו מרענן גם במסכי מעקב וחדשות</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="29" t="inlineStr">
         <is>
           <t>Frontend / Bug Fix</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>⏳ ממתין ל-push</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
+      <c r="D52" s="29" t="inlineStr">
+        <is>
+          <t>✅ Live (OTA)</t>
+        </is>
+      </c>
+      <c r="E52" s="29" t="inlineStr">
         <is>
           <t>WatchlistScreen.js, NewsScreen.js</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>ביקורת הבטחות: הטקסט הבטיח רענון מעקב אך הלוגו לא היה מחובר שם.</t>
+      <c r="F52" s="29" t="inlineStr">
+        <is>
+          <t>ביקורת הבטחות: הטקסט הבטיח רענון מעקב אך הלוגו לא היה מחובר שם. תיוג התיישן — אומת שהקוד קיים בענף המרוחק.</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="29" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="29" t="inlineStr">
         <is>
           <t>תווית גרסה v1.0.0 (היה v1.2)</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="29" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>⏳ ממתין ל-push</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
+      <c r="D53" s="29" t="inlineStr">
+        <is>
+          <t>✅ Live (OTA)</t>
+        </is>
+      </c>
+      <c r="E53" s="29" t="inlineStr">
         <is>
           <t>MoreScreen.js</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>יישור מול version בחנות.</t>
+      <c r="F53" s="29" t="inlineStr">
+        <is>
+          <t>יישור מול version בחנות. תיוג התיישן — אומת שהקוד קיים בענף המרוחק.</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="29" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="29" t="inlineStr">
         <is>
           <t>תיקוני נוסח: ToS/מי-אני + גילוי תרגום בפרטיות</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="29" t="inlineStr">
         <is>
           <t>Legal / i18n</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>⏳ ממתין ל-push</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
+      <c r="D54" s="29" t="inlineStr">
+        <is>
+          <t>✅ Live (OTA)</t>
+        </is>
+      </c>
+      <c r="E54" s="29" t="inlineStr">
         <is>
           <t>constants/i18n.js</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>"אין לי רישיון" (היה "לא רישוי"); גילוי Google Translate בסעיף הפרטיות ב-4 שפות; אומת שהנוסחה 40/35/25 תואמת את analyzer.py.</t>
+      <c r="F54" s="29" t="inlineStr">
+        <is>
+          <t>"אין לי רישיון" (היה "לא רישוי"); גילוי Google Translate בסעיף הפרטיות ב-4 שפות; אומת שהנוסחה 40/35/25 תואמת את analyzer.py. תיוג התיישן — אומת שהקוד קיים בענף המרוחק.</t>
         </is>
       </c>
     </row>
@@ -2296,22 +2335,22 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="13" t="inlineStr">
+      <c r="A60" s="26" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="B60" s="14" t="inlineStr">
+      <c r="B60" s="27" t="inlineStr">
         <is>
           <t>מרוץ שפות — 5 מסכים/רכיבים</t>
         </is>
       </c>
-      <c r="C60" s="13" t="inlineStr">
+      <c r="C60" s="26" t="inlineStr">
         <is>
           <t>Frontend / Bug Fix</t>
         </is>
       </c>
-      <c r="D60" s="15" t="inlineStr">
+      <c r="D60" s="28" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -2328,22 +2367,22 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="13" t="inlineStr">
+      <c r="A61" s="26" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="B61" s="14" t="inlineStr">
+      <c r="B61" s="27" t="inlineStr">
         <is>
           <t>Volume/Avg Vol ריקים לסירוגין</t>
         </is>
       </c>
-      <c r="C61" s="13" t="inlineStr">
+      <c r="C61" s="26" t="inlineStr">
         <is>
           <t>Backend / Bug Fix</t>
         </is>
       </c>
-      <c r="D61" s="15" t="inlineStr">
+      <c r="D61" s="28" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
@@ -2360,22 +2399,22 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="13" t="inlineStr">
+      <c r="A62" s="26" t="inlineStr">
         <is>
           <t>54</t>
         </is>
       </c>
-      <c r="B62" s="14" t="inlineStr">
+      <c r="B62" s="27" t="inlineStr">
         <is>
           <t>המרת אגורות→שקל למניות ת"א</t>
         </is>
       </c>
-      <c r="C62" s="13" t="inlineStr">
+      <c r="C62" s="26" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="D62" s="15" t="inlineStr">
+      <c r="D62" s="28" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
@@ -2392,22 +2431,22 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="13" t="inlineStr">
+      <c r="A63" s="26" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="B63" s="14" t="inlineStr">
+      <c r="B63" s="27" t="inlineStr">
         <is>
           <t>באג יחידות ב-Buyback (3500000000%)</t>
         </is>
       </c>
-      <c r="C63" s="13" t="inlineStr">
+      <c r="C63" s="26" t="inlineStr">
         <is>
           <t>Backend + Frontend</t>
         </is>
       </c>
-      <c r="D63" s="15" t="inlineStr">
+      <c r="D63" s="28" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
@@ -2424,22 +2463,22 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="13" t="inlineStr">
+      <c r="A64" s="26" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="B64" s="14" t="inlineStr">
+      <c r="B64" s="27" t="inlineStr">
         <is>
           <t>תיקוני נכונות במנוע הציון</t>
         </is>
       </c>
-      <c r="C64" s="13" t="inlineStr">
+      <c r="C64" s="26" t="inlineStr">
         <is>
           <t>Backend / Scoring</t>
         </is>
       </c>
-      <c r="D64" s="15" t="inlineStr">
+      <c r="D64" s="28" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
@@ -2456,22 +2495,22 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="13" t="inlineStr">
+      <c r="A65" s="26" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="B65" s="14" t="inlineStr">
+      <c r="B65" s="27" t="inlineStr">
         <is>
           <t>ניסוח דיבידנד כן — לא "משולם בעקביות"</t>
         </is>
       </c>
-      <c r="C65" s="13" t="inlineStr">
+      <c r="C65" s="26" t="inlineStr">
         <is>
           <t>Legal / Accuracy</t>
         </is>
       </c>
-      <c r="D65" s="15" t="inlineStr">
+      <c r="D65" s="28" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
@@ -2488,22 +2527,22 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="13" t="inlineStr">
+      <c r="A66" s="26" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="B66" s="14" t="inlineStr">
+      <c r="B66" s="27" t="inlineStr">
         <is>
           <t>SSRF — /translate-article</t>
         </is>
       </c>
-      <c r="C66" s="13" t="inlineStr">
+      <c r="C66" s="26" t="inlineStr">
         <is>
           <t>Backend / Security</t>
         </is>
       </c>
-      <c r="D66" s="15" t="inlineStr">
+      <c r="D66" s="28" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
@@ -2520,22 +2559,22 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="13" t="inlineStr">
+      <c r="A67" s="26" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="B67" s="14" t="inlineStr">
+      <c r="B67" s="27" t="inlineStr">
         <is>
           <t>XSS ב-WebView של הכתבות</t>
         </is>
       </c>
-      <c r="C67" s="13" t="inlineStr">
+      <c r="C67" s="26" t="inlineStr">
         <is>
           <t>Frontend / Security</t>
         </is>
       </c>
-      <c r="D67" s="15" t="inlineStr">
+      <c r="D67" s="28" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -2552,22 +2591,22 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="13" t="inlineStr">
+      <c r="A68" s="26" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="B68" s="14" t="inlineStr">
+      <c r="B68" s="27" t="inlineStr">
         <is>
           <t>הסרת /debug-pe ו-/debug-rows</t>
         </is>
       </c>
-      <c r="C68" s="13" t="inlineStr">
+      <c r="C68" s="26" t="inlineStr">
         <is>
           <t>Backend / Security</t>
         </is>
       </c>
-      <c r="D68" s="15" t="inlineStr">
+      <c r="D68" s="28" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
@@ -2584,22 +2623,22 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="13" t="inlineStr">
+      <c r="A69" s="26" t="inlineStr">
         <is>
           <t>61</t>
         </is>
       </c>
-      <c r="B69" s="14" t="inlineStr">
+      <c r="B69" s="27" t="inlineStr">
         <is>
           <t>5 דליפות של פרטי חריגה ללקוח</t>
         </is>
       </c>
-      <c r="C69" s="13" t="inlineStr">
+      <c r="C69" s="26" t="inlineStr">
         <is>
           <t>Backend / Security</t>
         </is>
       </c>
-      <c r="D69" s="15" t="inlineStr">
+      <c r="D69" s="28" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
@@ -2616,22 +2655,22 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="13" t="inlineStr">
+      <c r="A70" s="26" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="B70" s="14" t="inlineStr">
+      <c r="B70" s="27" t="inlineStr">
         <is>
           <t>פיצוץ זיכרון בעליית השרת</t>
         </is>
       </c>
-      <c r="C70" s="13" t="inlineStr">
+      <c r="C70" s="26" t="inlineStr">
         <is>
           <t>Backend / Performance</t>
         </is>
       </c>
-      <c r="D70" s="15" t="inlineStr">
+      <c r="D70" s="28" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
@@ -2648,22 +2687,22 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="13" t="inlineStr">
+      <c r="A71" s="26" t="inlineStr">
         <is>
           <t>63</t>
         </is>
       </c>
-      <c r="B71" s="14" t="inlineStr">
+      <c r="B71" s="27" t="inlineStr">
         <is>
           <t>תקרת מטמון + single-flight</t>
         </is>
       </c>
-      <c r="C71" s="13" t="inlineStr">
+      <c r="C71" s="26" t="inlineStr">
         <is>
           <t>Backend / Performance</t>
         </is>
       </c>
-      <c r="D71" s="15" t="inlineStr">
+      <c r="D71" s="28" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
@@ -2680,22 +2719,22 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="13" t="inlineStr">
+      <c r="A72" s="26" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="B72" s="14" t="inlineStr">
+      <c r="B72" s="27" t="inlineStr">
         <is>
           <t>חלון היסטוריה 10y במקום max</t>
         </is>
       </c>
-      <c r="C72" s="13" t="inlineStr">
+      <c r="C72" s="26" t="inlineStr">
         <is>
           <t>Backend / Performance</t>
         </is>
       </c>
-      <c r="D72" s="15" t="inlineStr">
+      <c r="D72" s="28" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
@@ -2712,22 +2751,22 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="13" t="inlineStr">
+      <c r="A73" s="26" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="B73" s="14" t="inlineStr">
+      <c r="B73" s="27" t="inlineStr">
         <is>
           <t>Debounce בחיפוש</t>
         </is>
       </c>
-      <c r="C73" s="13" t="inlineStr">
+      <c r="C73" s="26" t="inlineStr">
         <is>
           <t>Frontend / Performance</t>
         </is>
       </c>
-      <c r="D73" s="15" t="inlineStr">
+      <c r="D73" s="28" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -2744,22 +2783,22 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="13" t="inlineStr">
+      <c r="A74" s="26" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="B74" s="14" t="inlineStr">
+      <c r="B74" s="27" t="inlineStr">
         <is>
           <t>תקציב זמן ל-Stooq</t>
         </is>
       </c>
-      <c r="C74" s="13" t="inlineStr">
+      <c r="C74" s="26" t="inlineStr">
         <is>
           <t>Backend / Performance</t>
         </is>
       </c>
-      <c r="D74" s="15" t="inlineStr">
+      <c r="D74" s="28" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
@@ -2776,22 +2815,22 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="13" t="inlineStr">
+      <c r="A75" s="26" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="B75" s="14" t="inlineStr">
+      <c r="B75" s="27" t="inlineStr">
         <is>
           <t>אובדן נתונים ביומן המחקר</t>
         </is>
       </c>
-      <c r="C75" s="13" t="inlineStr">
+      <c r="C75" s="26" t="inlineStr">
         <is>
           <t>Frontend / Bug Fix</t>
         </is>
       </c>
-      <c r="D75" s="15" t="inlineStr">
+      <c r="D75" s="28" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -2840,22 +2879,22 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="13" t="inlineStr">
+      <c r="A77" s="26" t="inlineStr">
         <is>
           <t>69</t>
         </is>
       </c>
-      <c r="B77" s="14" t="inlineStr">
+      <c r="B77" s="27" t="inlineStr">
         <is>
           <t>מסך הסכמה בהפעלה ראשונה</t>
         </is>
       </c>
-      <c r="C77" s="13" t="inlineStr">
+      <c r="C77" s="26" t="inlineStr">
         <is>
           <t>Legal</t>
         </is>
       </c>
-      <c r="D77" s="15" t="inlineStr">
+      <c r="D77" s="28" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -2872,22 +2911,22 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="13" t="inlineStr">
+      <c r="A78" s="26" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="B78" s="14" t="inlineStr">
+      <c r="B78" s="27" t="inlineStr">
         <is>
           <t>שכתוב תיאור החנות — בלי הבטחות</t>
         </is>
       </c>
-      <c r="C78" s="13" t="inlineStr">
+      <c r="C78" s="26" t="inlineStr">
         <is>
           <t>Legal / Store</t>
         </is>
       </c>
-      <c r="D78" s="15" t="inlineStr">
+      <c r="D78" s="28" t="inlineStr">
         <is>
           <t>✅ מוכן</t>
         </is>
@@ -2904,22 +2943,22 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="13" t="inlineStr">
+      <c r="A79" s="26" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="B79" s="14" t="inlineStr">
+      <c r="B79" s="27" t="inlineStr">
         <is>
           <t>מדריך צילומי מסך לחנות</t>
         </is>
       </c>
-      <c r="C79" s="13" t="inlineStr">
+      <c r="C79" s="26" t="inlineStr">
         <is>
           <t>Store Assets</t>
         </is>
       </c>
-      <c r="D79" s="15" t="inlineStr">
+      <c r="D79" s="28" t="inlineStr">
         <is>
           <t>✅ הושלם</t>
         </is>
@@ -2936,22 +2975,22 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="13" t="inlineStr">
+      <c r="A80" s="26" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="B80" s="14" t="inlineStr">
+      <c r="B80" s="27" t="inlineStr">
         <is>
           <t>RTL בכל המסכים</t>
         </is>
       </c>
-      <c r="C80" s="13" t="inlineStr">
+      <c r="C80" s="26" t="inlineStr">
         <is>
           <t>Frontend / i18n</t>
         </is>
       </c>
-      <c r="D80" s="15" t="inlineStr">
+      <c r="D80" s="28" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -2968,22 +3007,22 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="13" t="inlineStr">
+      <c r="A81" s="26" t="inlineStr">
         <is>
           <t>73</t>
         </is>
       </c>
-      <c r="B81" s="14" t="inlineStr">
+      <c r="B81" s="27" t="inlineStr">
         <is>
           <t>תווית גרסה מ-app.json</t>
         </is>
       </c>
-      <c r="C81" s="13" t="inlineStr">
+      <c r="C81" s="26" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="D81" s="15" t="inlineStr">
+      <c r="D81" s="28" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -3000,22 +3039,22 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="13" t="inlineStr">
+      <c r="A82" s="26" t="inlineStr">
         <is>
           <t>74</t>
         </is>
       </c>
-      <c r="B82" s="14" t="inlineStr">
+      <c r="B82" s="27" t="inlineStr">
         <is>
           <t>טעינה דו-שלבית ברשימת המעקב</t>
         </is>
       </c>
-      <c r="C82" s="13" t="inlineStr">
+      <c r="C82" s="26" t="inlineStr">
         <is>
           <t>Frontend / Performance</t>
         </is>
       </c>
-      <c r="D82" s="15" t="inlineStr">
+      <c r="D82" s="28" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -3032,22 +3071,22 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="13" t="inlineStr">
+      <c r="A83" s="26" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="B83" s="14" t="inlineStr">
+      <c r="B83" s="27" t="inlineStr">
         <is>
           <t>/quotes: אגורות, שם חברה, מטבע</t>
         </is>
       </c>
-      <c r="C83" s="13" t="inlineStr">
+      <c r="C83" s="26" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="D83" s="15" t="inlineStr">
+      <c r="D83" s="28" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
@@ -3064,22 +3103,22 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="13" t="inlineStr">
+      <c r="A84" s="26" t="inlineStr">
         <is>
           <t>76</t>
         </is>
       </c>
-      <c r="B84" s="14" t="inlineStr">
+      <c r="B84" s="27" t="inlineStr">
         <is>
           <t>מיזוג במקום החלפה ברשימת המעקב</t>
         </is>
       </c>
-      <c r="C84" s="13" t="inlineStr">
+      <c r="C84" s="26" t="inlineStr">
         <is>
           <t>Frontend / Bug Fix</t>
         </is>
       </c>
-      <c r="D84" s="15" t="inlineStr">
+      <c r="D84" s="28" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -3096,22 +3135,22 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="13" t="inlineStr">
+      <c r="A85" s="26" t="inlineStr">
         <is>
           <t>77</t>
         </is>
       </c>
-      <c r="B85" s="14" t="inlineStr">
+      <c r="B85" s="27" t="inlineStr">
         <is>
           <t>מרוץ במסך הבית — market/FX</t>
         </is>
       </c>
-      <c r="C85" s="13" t="inlineStr">
+      <c r="C85" s="26" t="inlineStr">
         <is>
           <t>Frontend / Bug Fix</t>
         </is>
       </c>
-      <c r="D85" s="15" t="inlineStr">
+      <c r="D85" s="28" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -3128,22 +3167,22 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="13" t="inlineStr">
+      <c r="A86" s="26" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="B86" s="14" t="inlineStr">
+      <c r="B86" s="27" t="inlineStr">
         <is>
           <t>תשובה ריקה לא מוחקת נתונים טובים</t>
         </is>
       </c>
-      <c r="C86" s="13" t="inlineStr">
+      <c r="C86" s="26" t="inlineStr">
         <is>
           <t>Frontend / Bug Fix</t>
         </is>
       </c>
-      <c r="D86" s="15" t="inlineStr">
+      <c r="D86" s="28" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -3160,22 +3199,22 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="13" t="inlineStr">
+      <c r="A87" s="26" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="B87" s="14" t="inlineStr">
+      <c r="B87" s="27" t="inlineStr">
         <is>
           <t>תרגום כתבה ישנה דלף לחדשה</t>
         </is>
       </c>
-      <c r="C87" s="13" t="inlineStr">
+      <c r="C87" s="26" t="inlineStr">
         <is>
           <t>Frontend / Bug Fix</t>
         </is>
       </c>
-      <c r="D87" s="15" t="inlineStr">
+      <c r="D87" s="28" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -3192,22 +3231,22 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="13" t="inlineStr">
+      <c r="A88" s="26" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="B88" s="14" t="inlineStr">
+      <c r="B88" s="27" t="inlineStr">
         <is>
           <t>מרוץ ב"נסה שוב" של פירוט מדד</t>
         </is>
       </c>
-      <c r="C88" s="13" t="inlineStr">
+      <c r="C88" s="26" t="inlineStr">
         <is>
           <t>Frontend / Bug Fix</t>
         </is>
       </c>
-      <c r="D88" s="15" t="inlineStr">
+      <c r="D88" s="28" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -3224,22 +3263,22 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="13" t="inlineStr">
+      <c r="A89" s="26" t="inlineStr">
         <is>
           <t>81</t>
         </is>
       </c>
-      <c r="B89" s="14" t="inlineStr">
+      <c r="B89" s="27" t="inlineStr">
         <is>
           <t>סולם VIX לא מונוטוני</t>
         </is>
       </c>
-      <c r="C89" s="13" t="inlineStr">
+      <c r="C89" s="26" t="inlineStr">
         <is>
           <t>Frontend / i18n</t>
         </is>
       </c>
-      <c r="D89" s="15" t="inlineStr">
+      <c r="D89" s="28" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -3256,22 +3295,22 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="13" t="inlineStr">
+      <c r="A90" s="26" t="inlineStr">
         <is>
           <t>82</t>
         </is>
       </c>
-      <c r="B90" s="14" t="inlineStr">
+      <c r="B90" s="27" t="inlineStr">
         <is>
           <t>תיקוני תוכן בספרדית</t>
         </is>
       </c>
-      <c r="C90" s="13" t="inlineStr">
+      <c r="C90" s="26" t="inlineStr">
         <is>
           <t>i18n / Accuracy</t>
         </is>
       </c>
-      <c r="D90" s="15" t="inlineStr">
+      <c r="D90" s="28" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -3288,389 +3327,670 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="17" t="inlineStr">
+      <c r="A91" s="26" t="inlineStr">
         <is>
           <t>83</t>
         </is>
       </c>
-      <c r="B91" s="18" t="inlineStr">
+      <c r="B91" s="27" t="inlineStr">
         <is>
           <t>Cache-Control: no-store על כל ה-API</t>
         </is>
       </c>
-      <c r="C91" s="17" t="inlineStr">
+      <c r="C91" s="26" t="inlineStr">
         <is>
           <t>Backend / Bug Fix</t>
         </is>
       </c>
-      <c r="D91" s="19" t="inlineStr">
+      <c r="D91" s="28" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="E91" s="16" t="inlineStr">
+        <is>
+          <t>main.py</t>
+        </is>
+      </c>
+      <c r="F91" s="16" t="inlineStr">
+        <is>
+          <t>הסיבה האמיתית שדלק חזרה: OkHttp של אנדרואיד שמר תשובה שנוצרה בגרסת קוד ישנה. הוכח — אותה מניה ב-en החזירה 8173 וב-ru החזירה 84.45. נדחף ונפרס; אומת חי מול השרת.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="26" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="B92" s="27" t="inlineStr">
+        <is>
+          <t>סדרה שנתית = סוף שנה, לא ינואר</t>
+        </is>
+      </c>
+      <c r="C92" s="26" t="inlineStr">
+        <is>
+          <t>Backend / Bug Fix</t>
+        </is>
+      </c>
+      <c r="D92" s="28" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="E92" s="16" t="inlineStr">
+        <is>
+          <t>main.py</t>
+        </is>
+      </c>
+      <c r="F92" s="16" t="inlineStr">
+        <is>
+          <t>הגרף השנתי הציג את ינואר בתווית של השנה. KO 2023: הוצג 25.25 במקום 22.19 — סטייה 12%. תוקן ב-4 מקומות. נדחף ונפרס; אומת חי מול השרת.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="26" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="B93" s="27" t="inlineStr">
+        <is>
+          <t>TTM של Buyback דרש 2 רבעונים</t>
+        </is>
+      </c>
+      <c r="C93" s="26" t="inlineStr">
+        <is>
+          <t>Backend / Bug Fix</t>
+        </is>
+      </c>
+      <c r="D93" s="28" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="E93" s="16" t="inlineStr">
+        <is>
+          <t>main.py</t>
+        </is>
+      </c>
+      <c r="F93" s="16" t="inlineStr">
+        <is>
+          <t>"תשואה שנתית" יכלה להיות סכום של חצי שנה. הועלה ל-4 כמו כל שאר חישובי ה-TTM. נדחף ונפרס; אומת חי מול השרת.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="26" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="B94" s="27" t="inlineStr">
+        <is>
+          <t>ניקוי ריפו — cloudflared.exe 52MB</t>
+        </is>
+      </c>
+      <c r="C94" s="26" t="inlineStr">
+        <is>
+          <t>DevOps</t>
+        </is>
+      </c>
+      <c r="D94" s="28" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="E94" s="16" t="inlineStr">
+        <is>
+          <t>‎.gitignore</t>
+        </is>
+      </c>
+      <c r="F94" s="16" t="inlineStr">
+        <is>
+          <t>יצא ממעקב git, נשאר על הדיסק המקומי.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="26" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="B95" s="27" t="inlineStr">
+        <is>
+          <t>דיוק עמוד הפרטיות בנוגע ללוגים</t>
+        </is>
+      </c>
+      <c r="C95" s="26" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="D95" s="28" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="E95" s="16" t="inlineStr">
+        <is>
+          <t>main.py</t>
+        </is>
+      </c>
+      <c r="F95" s="16" t="inlineStr">
+        <is>
+          <t>ההצהרה "איננו רושמים כתובות IP" לא היתה מדויקת — uvicorn ו-Render כן שומרים לוגים טכניים. נוסח מחדש.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="26" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="B96" s="27" t="inlineStr">
+        <is>
+          <t>ביקורת קוד מלאה — 35 קבצים</t>
+        </is>
+      </c>
+      <c r="C96" s="26" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="D96" s="28" t="inlineStr">
+        <is>
+          <t>✅ הושלם</t>
+        </is>
+      </c>
+      <c r="E96" s="16" t="inlineStr">
+        <is>
+          <t>כל הקבצים</t>
+        </is>
+      </c>
+      <c r="F96" s="16" t="inlineStr">
+        <is>
+          <t>11,646 שורות נקראו במלואן. 27 חבילות בדיקה התנהגותיות. אימות חי מול ה-API בייצור (זה מה שחשף פריטים 83-85).</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="12" t="inlineStr">
+        <is>
+          <t>✅  Session 7 (2026-07-25): עקביות חזותית, הצהרת ספים, כיסוי שפות</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="26" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="B98" s="27" t="inlineStr">
+        <is>
+          <t>צבע הגרף לפי כיוון המדד</t>
+        </is>
+      </c>
+      <c r="C98" s="26" t="inlineStr">
+        <is>
+          <t>Frontend / UX</t>
+        </is>
+      </c>
+      <c r="D98" s="28" t="inlineStr">
+        <is>
+          <t>✅ Live (OTA)</t>
+        </is>
+      </c>
+      <c r="E98" s="16" t="inlineStr">
+        <is>
+          <t>PriceChart.js, MetricHistoryScreen.js</t>
+        </is>
+      </c>
+      <c r="F98" s="16" t="inlineStr">
+        <is>
+          <t>הגרף צבע לפי מגמה בלבד: P/B שעלה מ-4.3 ל-7.81 קיבל ירוק ("עולה") בעוד האריח צבע את אותו מספר אדום ("יקר"). עכשיו במכפילים שבהם נמוך=טוב ירידה היא הירוקה. גרף מחיר-תחליף נשאר בלוגיקה רגילה.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="26" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B99" s="27" t="inlineStr">
+        <is>
+          <t>הצהרת טווח מלא לכל 24 המדדים</t>
+        </is>
+      </c>
+      <c r="C99" s="26" t="inlineStr">
+        <is>
+          <t>UX / Accuracy</t>
+        </is>
+      </c>
+      <c r="D99" s="28" t="inlineStr">
+        <is>
+          <t>✅ Live (OTA)</t>
+        </is>
+      </c>
+      <c r="E99" s="16" t="inlineStr">
+        <is>
+          <t>constants/i18n.js</t>
+        </is>
+      </c>
+      <c r="F99" s="16" t="inlineStr">
+        <is>
+          <t>האפליקציה צבעה אדום לפי סף שלא סיפרה עליו ("מתחת ל-1 זול" בלבד). עכשיו כל מדד מצהיר מינימום/אמצע/מקסימום — או אומר במפורש שאין לו סף ולמה. 15 מדדים עם מספרים אומתו מול הקוד. 4 שפות.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="26" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="B100" s="27" t="inlineStr">
+        <is>
+          <t>מדד שלא היה לו הסבר בכלל</t>
+        </is>
+      </c>
+      <c r="C100" s="26" t="inlineStr">
+        <is>
+          <t>UX / Bug Fix</t>
+        </is>
+      </c>
+      <c r="D100" s="28" t="inlineStr">
+        <is>
+          <t>✅ Live (OTA)</t>
+        </is>
+      </c>
+      <c r="E100" s="16" t="inlineStr">
+        <is>
+          <t>constants/i18n.js</t>
+        </is>
+      </c>
+      <c r="F100" s="16" t="inlineStr">
+        <is>
+          <t>net_income_trend הופיע ברשימת שמות המדדים אך חסר לגמרי במילון ההסברים — לחיצה על האריח הציגה כלום. נוסף ב-4 שפות עם ארבעת המצבים מ-analyzer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="26" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="B101" s="27" t="inlineStr">
+        <is>
+          <t>מספר וכיתוב באותו צבע</t>
+        </is>
+      </c>
+      <c r="C101" s="26" t="inlineStr">
+        <is>
+          <t>Frontend / UX</t>
+        </is>
+      </c>
+      <c r="D101" s="28" t="inlineStr">
+        <is>
+          <t>✅ Live (OTA)</t>
+        </is>
+      </c>
+      <c r="E101" s="16" t="inlineStr">
+        <is>
+          <t>MetricTile.js, StockScreen.js</t>
+        </is>
+      </c>
+      <c r="F101" s="16" t="inlineStr">
+        <is>
+          <t>שני סוגי האריחים צבעו הפוך זה מזה: באריחי הציון המספר ניטרלי והכיתוב צבוע, במכפילים הנוספים להפך. עכשיו שניהם נושאים סיגנל אחד.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="26" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="B102" s="27" t="inlineStr">
+        <is>
+          <t>כתום רק כשיש אזהרה</t>
+        </is>
+      </c>
+      <c r="C102" s="26" t="inlineStr">
+        <is>
+          <t>Frontend / UX</t>
+        </is>
+      </c>
+      <c r="D102" s="28" t="inlineStr">
+        <is>
+          <t>✅ Live (OTA)</t>
+        </is>
+      </c>
+      <c r="E102" s="16" t="inlineStr">
+        <is>
+          <t>MetricHistoryScreen.js</t>
+        </is>
+      </c>
+      <c r="F102" s="16" t="inlineStr">
+        <is>
+          <t>colors.purple הוא בפועל #f59e0b (כתום), ו-tileScoreColor(null) החזיר אותו — כך שכל תיבות ההסבר במסך הפירוט נראו כאזהרה. אין ציון = אין פסק דין = ניטרלי.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="26" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="B103" s="27" t="inlineStr">
+        <is>
+          <t>הצבע שורד את המעבר בין מסכים</t>
+        </is>
+      </c>
+      <c r="C103" s="26" t="inlineStr">
+        <is>
+          <t>Frontend / Bug Fix</t>
+        </is>
+      </c>
+      <c r="D103" s="28" t="inlineStr">
+        <is>
+          <t>✅ Live (OTA)</t>
+        </is>
+      </c>
+      <c r="E103" s="16" t="inlineStr">
+        <is>
+          <t>StockScreen.js, MetricHistoryScreen.js</t>
+        </is>
+      </c>
+      <c r="F103" s="16" t="inlineStr">
+        <is>
+          <t>P/B 7.81 היה אדום באריח והופך כתום במסך הפירוט, כי המכפילים הנוספים מגיעים בלי ציון. האריח מעביר עכשיו tileSignal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="26" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="B104" s="27" t="inlineStr">
+        <is>
+          <t>חומת ההסכמה של גוגל — רוסית וספרדית</t>
+        </is>
+      </c>
+      <c r="C104" s="26" t="inlineStr">
+        <is>
+          <t>Frontend / i18n</t>
+        </is>
+      </c>
+      <c r="D104" s="28" t="inlineStr">
+        <is>
+          <t>✅ Live (OTA)</t>
+        </is>
+      </c>
+      <c r="E104" s="16" t="inlineStr">
+        <is>
+          <t>screens/ArticleScreen.js</t>
+        </is>
+      </c>
+      <c r="F104" s="16" t="inlineStr">
+        <is>
+          <t>הסקריפט מזהה את כפתור האישור לפי טקסט, וגוגל מציגה את החומה בשפת המכשיר. נתמכו רק אנגלית ועברית — מכשיר ברוסית/ספרדית נתקע על מסך ההסכמה במקום להגיע לכתבה. נוספו принять/согласен/принимаю ו-aceptar/acepto/de acuerdo, אומת על 11 וריאציות.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="26" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="B105" s="27" t="inlineStr">
+        <is>
+          <t>ביקורת כיסוי-שפות לכל השינויים</t>
+        </is>
+      </c>
+      <c r="C105" s="26" t="inlineStr">
+        <is>
+          <t>QA / i18n</t>
+        </is>
+      </c>
+      <c r="D105" s="28" t="inlineStr">
+        <is>
+          <t>✅ הושלם</t>
+        </is>
+      </c>
+      <c r="E105" s="16" t="inlineStr">
+        <is>
+          <t>כל הקבצים</t>
+        </is>
+      </c>
+      <c r="F105" s="16" t="inlineStr">
+        <is>
+          <t>כל שינוי בהפעלה סווג: תלוי-שפה נבדק ל-4, לא-תלוי אומת שהוא באמת לא תלוי. חיפוש מחרוזות חד-לשוניות חשף את פריט 95. 29 חבילות בדיקה.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="30" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="B106" s="31" t="inlineStr">
+        <is>
+          <t>מדדים דו-משמעיים — הגרף לא טוען טענה</t>
+        </is>
+      </c>
+      <c r="C106" s="30" t="inlineStr">
+        <is>
+          <t>Frontend / Accuracy</t>
+        </is>
+      </c>
+      <c r="D106" s="32" t="inlineStr">
+        <is>
+          <t>✅ Live (OTA)</t>
+        </is>
+      </c>
+      <c r="E106" s="16" t="inlineStr">
+        <is>
+          <t>PriceChart.js, MetricHistoryScreen.js</t>
+        </is>
+      </c>
+      <c r="F106" s="16" t="inlineStr">
+        <is>
+          <t>תשואת דיבידנד/רכישה חוזרת יורדת גם כשהתשלום נחתך (רע) וגם כשהמחיר עולה מהר יותר (טוב). וולמארט העלתה דיבידנד 52 שנה ברציפות והתשואה ירדה 3.2%→0.9% — הגרף צבע את זה אדום. מהתשואה לבדה אי אפשר להבחין, אז הקו כחול = מידע ולא פסק דין.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>🔜  NOT YET STARTED</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="inlineStr"/>
+      <c r="C107" s="4" t="inlineStr"/>
+      <c r="D107" s="4" t="inlineStr"/>
+      <c r="E107" s="4" t="inlineStr"/>
+      <c r="F107" s="5" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="n"/>
+      <c r="C108" s="4" t="n"/>
+      <c r="D108" s="4" t="n"/>
+      <c r="E108" s="4" t="n"/>
+      <c r="F108" s="5" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="10" t="inlineStr">
+        <is>
+          <t>Legend</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="B110" s="7" t="inlineStr">
+        <is>
+          <t>פרוס ופעיל ב-Render — נראה לכל המשתמשים</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="inlineStr"/>
+      <c r="D110" s="8" t="inlineStr"/>
+      <c r="E110" s="9" t="inlineStr"/>
+      <c r="F110" s="9" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="6" t="inlineStr">
+        <is>
+          <t>✅ In APK</t>
+        </is>
+      </c>
+      <c r="B111" s="7" t="inlineStr">
+        <is>
+          <t>כלול ב-APK המותקן — נראה לכל המשתמשים</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="inlineStr"/>
+      <c r="D111" s="8" t="inlineStr"/>
+      <c r="E111" s="9" t="inlineStr"/>
+      <c r="F111" s="9" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t>⏳ Next APK</t>
+        </is>
+      </c>
+      <c r="B112" s="7" t="inlineStr">
+        <is>
+          <t>הקוד מוזג — דורש build ו-APK חדש</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="inlineStr"/>
+      <c r="D112" s="8" t="inlineStr"/>
+      <c r="E112" s="9" t="inlineStr"/>
+      <c r="F112" s="9" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t>✅ Live (OTA)</t>
+        </is>
+      </c>
+      <c r="B113" s="7" t="inlineStr">
+        <is>
+          <t>שינוי JS — מועבר אוטומטית בהפעלה הבאה</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="inlineStr"/>
+      <c r="D113" s="8" t="inlineStr"/>
+      <c r="E113" s="9" t="inlineStr"/>
+      <c r="F113" s="9" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="21" t="inlineStr">
         <is>
           <t>⏳ ממתין ל-push</t>
         </is>
       </c>
-      <c r="E91" s="20" t="inlineStr">
-        <is>
-          <t>main.py</t>
-        </is>
-      </c>
-      <c r="F91" s="20" t="inlineStr">
-        <is>
-          <t>הסיבה האמיתית שדלק חזרה: OkHttp של אנדרואיד שמר תשובה שנוצרה בגרסת קוד ישנה. הוכח — אותה מניה ב-en החזירה 8173 וב-ru החזירה 84.45.</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="17" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="B92" s="18" t="inlineStr">
-        <is>
-          <t>סדרה שנתית = סוף שנה, לא ינואר</t>
-        </is>
-      </c>
-      <c r="C92" s="17" t="inlineStr">
-        <is>
-          <t>Backend / Bug Fix</t>
-        </is>
-      </c>
-      <c r="D92" s="19" t="inlineStr">
-        <is>
-          <t>⏳ ממתין ל-push</t>
-        </is>
-      </c>
-      <c r="E92" s="20" t="inlineStr">
-        <is>
-          <t>main.py</t>
-        </is>
-      </c>
-      <c r="F92" s="20" t="inlineStr">
-        <is>
-          <t>הגרף השנתי הציג את ינואר בתווית של השנה. KO 2023: הוצג 25.25 במקום 22.19 — סטייה 12%. תוקן ב-4 מקומות.</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="17" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="B93" s="18" t="inlineStr">
-        <is>
-          <t>TTM של Buyback דרש 2 רבעונים</t>
-        </is>
-      </c>
-      <c r="C93" s="17" t="inlineStr">
-        <is>
-          <t>Backend / Bug Fix</t>
-        </is>
-      </c>
-      <c r="D93" s="19" t="inlineStr">
-        <is>
-          <t>⏳ ממתין ל-push</t>
-        </is>
-      </c>
-      <c r="E93" s="20" t="inlineStr">
-        <is>
-          <t>main.py</t>
-        </is>
-      </c>
-      <c r="F93" s="20" t="inlineStr">
-        <is>
-          <t>"תשואה שנתית" יכלה להיות סכום של חצי שנה. הועלה ל-4 כמו כל שאר חישובי ה-TTM.</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="13" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="B94" s="14" t="inlineStr">
-        <is>
-          <t>ניקוי ריפו — cloudflared.exe 52MB</t>
-        </is>
-      </c>
-      <c r="C94" s="13" t="inlineStr">
-        <is>
-          <t>DevOps</t>
-        </is>
-      </c>
-      <c r="D94" s="15" t="inlineStr">
-        <is>
-          <t>✅ Live</t>
-        </is>
-      </c>
-      <c r="E94" s="16" t="inlineStr">
-        <is>
-          <t>‎.gitignore</t>
-        </is>
-      </c>
-      <c r="F94" s="16" t="inlineStr">
-        <is>
-          <t>יצא ממעקב git, נשאר על הדיסק המקומי.</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="13" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="B95" s="14" t="inlineStr">
-        <is>
-          <t>דיוק עמוד הפרטיות בנוגע ללוגים</t>
-        </is>
-      </c>
-      <c r="C95" s="13" t="inlineStr">
-        <is>
-          <t>Legal</t>
-        </is>
-      </c>
-      <c r="D95" s="15" t="inlineStr">
-        <is>
-          <t>✅ Live</t>
-        </is>
-      </c>
-      <c r="E95" s="16" t="inlineStr">
-        <is>
-          <t>main.py</t>
-        </is>
-      </c>
-      <c r="F95" s="16" t="inlineStr">
-        <is>
-          <t>ההצהרה "איננו רושמים כתובות IP" לא היתה מדויקת — uvicorn ו-Render כן שומרים לוגים טכניים. נוסח מחדש.</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="13" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="B96" s="14" t="inlineStr">
-        <is>
-          <t>ביקורת קוד מלאה — 35 קבצים</t>
-        </is>
-      </c>
-      <c r="C96" s="13" t="inlineStr">
-        <is>
-          <t>QA</t>
-        </is>
-      </c>
-      <c r="D96" s="15" t="inlineStr">
-        <is>
-          <t>✅ הושלם</t>
-        </is>
-      </c>
-      <c r="E96" s="16" t="inlineStr">
-        <is>
-          <t>כל הקבצים</t>
-        </is>
-      </c>
-      <c r="F96" s="16" t="inlineStr">
-        <is>
-          <t>11,646 שורות נקראו במלואן. 27 חבילות בדיקה התנהגותיות. אימות חי מול ה-API בייצור (זה מה שחשף פריטים 83-85).</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="3" t="inlineStr">
-        <is>
-          <t>🔜  NOT YET STARTED</t>
-        </is>
-      </c>
-      <c r="B97" s="5" t="inlineStr"/>
-      <c r="C97" s="4" t="inlineStr"/>
-      <c r="D97" s="4" t="inlineStr"/>
-      <c r="E97" s="4" t="inlineStr"/>
-      <c r="F97" s="5" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="6" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B98" s="7" t="inlineStr">
-        <is>
-          <t>Google Play Console — הגשה לחנות</t>
-        </is>
-      </c>
-      <c r="C98" s="6" t="inlineStr">
-        <is>
-          <t>Distribution</t>
-        </is>
-      </c>
-      <c r="D98" s="8" t="inlineStr">
-        <is>
-          <t>🔜</t>
-        </is>
-      </c>
-      <c r="E98" s="9" t="inlineStr"/>
-      <c r="F98" s="9" t="inlineStr">
-        <is>
-          <t>חשבון מפתח ($25) + העלאת AAB + store listing + screenshots.</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="10" t="inlineStr">
-        <is>
-          <t>Legend</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="6" t="inlineStr">
-        <is>
-          <t>✅ Live</t>
-        </is>
-      </c>
-      <c r="B100" s="7" t="inlineStr">
-        <is>
-          <t>פרוס ופעיל ב-Render — נראה לכל המשתמשים</t>
-        </is>
-      </c>
-      <c r="C100" s="6" t="inlineStr"/>
-      <c r="D100" s="8" t="inlineStr"/>
-      <c r="E100" s="9" t="inlineStr"/>
-      <c r="F100" s="9" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="6" t="inlineStr">
-        <is>
-          <t>✅ In APK</t>
-        </is>
-      </c>
-      <c r="B101" s="7" t="inlineStr">
-        <is>
-          <t>כלול ב-APK המותקן — נראה לכל המשתמשים</t>
-        </is>
-      </c>
-      <c r="C101" s="6" t="inlineStr"/>
-      <c r="D101" s="8" t="inlineStr"/>
-      <c r="E101" s="9" t="inlineStr"/>
-      <c r="F101" s="9" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="6" t="inlineStr">
-        <is>
-          <t>⏳ Next APK</t>
-        </is>
-      </c>
-      <c r="B102" s="7" t="inlineStr">
-        <is>
-          <t>הקוד מוזג — דורש build ו-APK חדש</t>
-        </is>
-      </c>
-      <c r="C102" s="6" t="inlineStr"/>
-      <c r="D102" s="8" t="inlineStr"/>
-      <c r="E102" s="9" t="inlineStr"/>
-      <c r="F102" s="9" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="6" t="inlineStr">
-        <is>
-          <t>✅ Live (OTA)</t>
-        </is>
-      </c>
-      <c r="B103" s="7" t="inlineStr">
-        <is>
-          <t>שינוי JS — מועבר אוטומטית בהפעלה הבאה</t>
-        </is>
-      </c>
-      <c r="C103" s="6" t="inlineStr"/>
-      <c r="D103" s="8" t="inlineStr"/>
-      <c r="E103" s="9" t="inlineStr"/>
-      <c r="F103" s="9" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="21" t="inlineStr">
-        <is>
-          <t>⏳ ממתין ל-push</t>
-        </is>
-      </c>
-      <c r="B104" s="22" t="inlineStr">
+      <c r="B114" s="22" t="inlineStr">
         <is>
           <t>הקוד מוכן מקומית — טרם נדחף/נפרס</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="21" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="21" t="inlineStr">
         <is>
           <t>⏳ דורש build</t>
         </is>
       </c>
-      <c r="B105" s="22" t="inlineStr">
+      <c r="B115" s="22" t="inlineStr">
         <is>
           <t>שינוי נייטיב — OTA לא מספיק, צריך AAB/APK חדש</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="23" t="inlineStr">
-        <is>
-          <t>סיכום Session 6</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="24" t="n"/>
-      <c r="B108" s="25" t="inlineStr">
-        <is>
-          <t>37  —  פריטים חדשים שנוספו (52-88)</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="24" t="n"/>
-      <c r="B109" s="25" t="inlineStr">
-        <is>
-          <t>32  —  כבר חיים בייצור או ב-OTA</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="24" t="n"/>
-      <c r="B110" s="25" t="inlineStr">
-        <is>
-          <t>3  —  ממתינים ל-push: no-store, סדרה שנתית, TTM של buyback</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="24" t="n"/>
-      <c r="B111" s="25" t="inlineStr">
-        <is>
-          <t>1  —  דורש build חדש: תמיכת טאבלט</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="24" t="n"/>
-      <c r="B112" s="25" t="inlineStr">
-        <is>
-          <t>11,646  —  שורות קוד שנקראו במלואן, 35 קבצים</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="24" t="n"/>
-      <c r="B113" s="25" t="inlineStr">
-        <is>
-          <t>27  —  חבילות בדיקה התנהגותיות עוברות</t>
+    <row r="116"/>
+    <row r="117">
+      <c r="A117" s="23" t="inlineStr">
+        <is>
+          <t>סיכום Session 6-7</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="24" t="n"/>
+      <c r="B118" s="25" t="inlineStr">
+        <is>
+          <t>45  —  פריטים חדשים שנוספו (52-96)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="24" t="n"/>
+      <c r="B119" s="25" t="inlineStr">
+        <is>
+          <t>44  —  חיים בייצור או ב-OTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="24" t="n"/>
+      <c r="B120" s="25" t="inlineStr">
+        <is>
+          <t>1  —  דורש build חדש: תמיכת טאבלט (פריט 68)</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="24" t="n"/>
+      <c r="B121" s="25" t="inlineStr">
+        <is>
+          <t>11,781  —  שורות קוד שנקראו במלואן, 36 קבצים</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="24" t="n"/>
+      <c r="B122" s="25" t="inlineStr">
+        <is>
+          <t>29  —  חבילות בדיקה התנהגותיות עוברות</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="24" t="n"/>
+      <c r="B123" s="25" t="inlineStr">
+        <is>
+          <t>18  —  ראוטים בשרת · 316 מפתחות i18n × 4 שפות</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
+    <mergeCell ref="A97:F97"/>
     <mergeCell ref="A107:F107"/>
     <mergeCell ref="A59:F59"/>
     <mergeCell ref="A25:F25"/>

--- a/BuddhaVest_Progress.xlsx
+++ b/BuddhaVest_Progress.xlsx
@@ -175,7 +175,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -250,6 +250,15 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -624,7 +633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F123"/>
+  <dimension ref="A1:F124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2335,22 +2344,22 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="26" t="inlineStr">
+      <c r="A60" s="30" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="B60" s="27" t="inlineStr">
+      <c r="B60" s="31" t="inlineStr">
         <is>
           <t>מרוץ שפות — 5 מסכים/רכיבים</t>
         </is>
       </c>
-      <c r="C60" s="26" t="inlineStr">
+      <c r="C60" s="30" t="inlineStr">
         <is>
           <t>Frontend / Bug Fix</t>
         </is>
       </c>
-      <c r="D60" s="28" t="inlineStr">
+      <c r="D60" s="32" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -2367,22 +2376,22 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="26" t="inlineStr">
+      <c r="A61" s="30" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="B61" s="27" t="inlineStr">
+      <c r="B61" s="31" t="inlineStr">
         <is>
           <t>Volume/Avg Vol ריקים לסירוגין</t>
         </is>
       </c>
-      <c r="C61" s="26" t="inlineStr">
+      <c r="C61" s="30" t="inlineStr">
         <is>
           <t>Backend / Bug Fix</t>
         </is>
       </c>
-      <c r="D61" s="28" t="inlineStr">
+      <c r="D61" s="32" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
@@ -2399,22 +2408,22 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="26" t="inlineStr">
+      <c r="A62" s="30" t="inlineStr">
         <is>
           <t>54</t>
         </is>
       </c>
-      <c r="B62" s="27" t="inlineStr">
+      <c r="B62" s="31" t="inlineStr">
         <is>
           <t>המרת אגורות→שקל למניות ת"א</t>
         </is>
       </c>
-      <c r="C62" s="26" t="inlineStr">
+      <c r="C62" s="30" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="D62" s="28" t="inlineStr">
+      <c r="D62" s="32" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
@@ -2431,22 +2440,22 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="26" t="inlineStr">
+      <c r="A63" s="30" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="B63" s="27" t="inlineStr">
+      <c r="B63" s="31" t="inlineStr">
         <is>
           <t>באג יחידות ב-Buyback (3500000000%)</t>
         </is>
       </c>
-      <c r="C63" s="26" t="inlineStr">
+      <c r="C63" s="30" t="inlineStr">
         <is>
           <t>Backend + Frontend</t>
         </is>
       </c>
-      <c r="D63" s="28" t="inlineStr">
+      <c r="D63" s="32" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
@@ -2463,22 +2472,22 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="26" t="inlineStr">
+      <c r="A64" s="30" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="B64" s="27" t="inlineStr">
+      <c r="B64" s="31" t="inlineStr">
         <is>
           <t>תיקוני נכונות במנוע הציון</t>
         </is>
       </c>
-      <c r="C64" s="26" t="inlineStr">
+      <c r="C64" s="30" t="inlineStr">
         <is>
           <t>Backend / Scoring</t>
         </is>
       </c>
-      <c r="D64" s="28" t="inlineStr">
+      <c r="D64" s="32" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
@@ -2495,22 +2504,22 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="26" t="inlineStr">
+      <c r="A65" s="30" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="B65" s="27" t="inlineStr">
+      <c r="B65" s="31" t="inlineStr">
         <is>
           <t>ניסוח דיבידנד כן — לא "משולם בעקביות"</t>
         </is>
       </c>
-      <c r="C65" s="26" t="inlineStr">
+      <c r="C65" s="30" t="inlineStr">
         <is>
           <t>Legal / Accuracy</t>
         </is>
       </c>
-      <c r="D65" s="28" t="inlineStr">
+      <c r="D65" s="32" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
@@ -2527,22 +2536,22 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="26" t="inlineStr">
+      <c r="A66" s="30" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="B66" s="27" t="inlineStr">
+      <c r="B66" s="31" t="inlineStr">
         <is>
           <t>SSRF — /translate-article</t>
         </is>
       </c>
-      <c r="C66" s="26" t="inlineStr">
+      <c r="C66" s="30" t="inlineStr">
         <is>
           <t>Backend / Security</t>
         </is>
       </c>
-      <c r="D66" s="28" t="inlineStr">
+      <c r="D66" s="32" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
@@ -2559,22 +2568,22 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="26" t="inlineStr">
+      <c r="A67" s="30" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="B67" s="27" t="inlineStr">
+      <c r="B67" s="31" t="inlineStr">
         <is>
           <t>XSS ב-WebView של הכתבות</t>
         </is>
       </c>
-      <c r="C67" s="26" t="inlineStr">
+      <c r="C67" s="30" t="inlineStr">
         <is>
           <t>Frontend / Security</t>
         </is>
       </c>
-      <c r="D67" s="28" t="inlineStr">
+      <c r="D67" s="32" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -2591,22 +2600,22 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="26" t="inlineStr">
+      <c r="A68" s="30" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="B68" s="27" t="inlineStr">
+      <c r="B68" s="31" t="inlineStr">
         <is>
           <t>הסרת /debug-pe ו-/debug-rows</t>
         </is>
       </c>
-      <c r="C68" s="26" t="inlineStr">
+      <c r="C68" s="30" t="inlineStr">
         <is>
           <t>Backend / Security</t>
         </is>
       </c>
-      <c r="D68" s="28" t="inlineStr">
+      <c r="D68" s="32" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
@@ -2623,22 +2632,22 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="26" t="inlineStr">
+      <c r="A69" s="30" t="inlineStr">
         <is>
           <t>61</t>
         </is>
       </c>
-      <c r="B69" s="27" t="inlineStr">
+      <c r="B69" s="31" t="inlineStr">
         <is>
           <t>5 דליפות של פרטי חריגה ללקוח</t>
         </is>
       </c>
-      <c r="C69" s="26" t="inlineStr">
+      <c r="C69" s="30" t="inlineStr">
         <is>
           <t>Backend / Security</t>
         </is>
       </c>
-      <c r="D69" s="28" t="inlineStr">
+      <c r="D69" s="32" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
@@ -2655,22 +2664,22 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="26" t="inlineStr">
+      <c r="A70" s="30" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="B70" s="27" t="inlineStr">
+      <c r="B70" s="31" t="inlineStr">
         <is>
           <t>פיצוץ זיכרון בעליית השרת</t>
         </is>
       </c>
-      <c r="C70" s="26" t="inlineStr">
+      <c r="C70" s="30" t="inlineStr">
         <is>
           <t>Backend / Performance</t>
         </is>
       </c>
-      <c r="D70" s="28" t="inlineStr">
+      <c r="D70" s="32" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
@@ -2687,22 +2696,22 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="26" t="inlineStr">
+      <c r="A71" s="30" t="inlineStr">
         <is>
           <t>63</t>
         </is>
       </c>
-      <c r="B71" s="27" t="inlineStr">
+      <c r="B71" s="31" t="inlineStr">
         <is>
           <t>תקרת מטמון + single-flight</t>
         </is>
       </c>
-      <c r="C71" s="26" t="inlineStr">
+      <c r="C71" s="30" t="inlineStr">
         <is>
           <t>Backend / Performance</t>
         </is>
       </c>
-      <c r="D71" s="28" t="inlineStr">
+      <c r="D71" s="32" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
@@ -2719,22 +2728,22 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="26" t="inlineStr">
+      <c r="A72" s="30" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="B72" s="27" t="inlineStr">
+      <c r="B72" s="31" t="inlineStr">
         <is>
           <t>חלון היסטוריה 10y במקום max</t>
         </is>
       </c>
-      <c r="C72" s="26" t="inlineStr">
+      <c r="C72" s="30" t="inlineStr">
         <is>
           <t>Backend / Performance</t>
         </is>
       </c>
-      <c r="D72" s="28" t="inlineStr">
+      <c r="D72" s="32" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
@@ -2751,22 +2760,22 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="26" t="inlineStr">
+      <c r="A73" s="30" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="B73" s="27" t="inlineStr">
+      <c r="B73" s="31" t="inlineStr">
         <is>
           <t>Debounce בחיפוש</t>
         </is>
       </c>
-      <c r="C73" s="26" t="inlineStr">
+      <c r="C73" s="30" t="inlineStr">
         <is>
           <t>Frontend / Performance</t>
         </is>
       </c>
-      <c r="D73" s="28" t="inlineStr">
+      <c r="D73" s="32" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -2783,22 +2792,22 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="26" t="inlineStr">
+      <c r="A74" s="30" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="B74" s="27" t="inlineStr">
+      <c r="B74" s="31" t="inlineStr">
         <is>
           <t>תקציב זמן ל-Stooq</t>
         </is>
       </c>
-      <c r="C74" s="26" t="inlineStr">
+      <c r="C74" s="30" t="inlineStr">
         <is>
           <t>Backend / Performance</t>
         </is>
       </c>
-      <c r="D74" s="28" t="inlineStr">
+      <c r="D74" s="32" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
@@ -2815,22 +2824,22 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="26" t="inlineStr">
+      <c r="A75" s="30" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="B75" s="27" t="inlineStr">
+      <c r="B75" s="31" t="inlineStr">
         <is>
           <t>אובדן נתונים ביומן המחקר</t>
         </is>
       </c>
-      <c r="C75" s="26" t="inlineStr">
+      <c r="C75" s="30" t="inlineStr">
         <is>
           <t>Frontend / Bug Fix</t>
         </is>
       </c>
-      <c r="D75" s="28" t="inlineStr">
+      <c r="D75" s="32" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -2879,22 +2888,22 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="26" t="inlineStr">
+      <c r="A77" s="30" t="inlineStr">
         <is>
           <t>69</t>
         </is>
       </c>
-      <c r="B77" s="27" t="inlineStr">
+      <c r="B77" s="31" t="inlineStr">
         <is>
           <t>מסך הסכמה בהפעלה ראשונה</t>
         </is>
       </c>
-      <c r="C77" s="26" t="inlineStr">
+      <c r="C77" s="30" t="inlineStr">
         <is>
           <t>Legal</t>
         </is>
       </c>
-      <c r="D77" s="28" t="inlineStr">
+      <c r="D77" s="32" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -2911,22 +2920,22 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="26" t="inlineStr">
+      <c r="A78" s="30" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="B78" s="27" t="inlineStr">
+      <c r="B78" s="31" t="inlineStr">
         <is>
           <t>שכתוב תיאור החנות — בלי הבטחות</t>
         </is>
       </c>
-      <c r="C78" s="26" t="inlineStr">
+      <c r="C78" s="30" t="inlineStr">
         <is>
           <t>Legal / Store</t>
         </is>
       </c>
-      <c r="D78" s="28" t="inlineStr">
+      <c r="D78" s="32" t="inlineStr">
         <is>
           <t>✅ מוכן</t>
         </is>
@@ -2943,22 +2952,22 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="26" t="inlineStr">
+      <c r="A79" s="30" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="B79" s="27" t="inlineStr">
+      <c r="B79" s="31" t="inlineStr">
         <is>
           <t>מדריך צילומי מסך לחנות</t>
         </is>
       </c>
-      <c r="C79" s="26" t="inlineStr">
+      <c r="C79" s="30" t="inlineStr">
         <is>
           <t>Store Assets</t>
         </is>
       </c>
-      <c r="D79" s="28" t="inlineStr">
+      <c r="D79" s="32" t="inlineStr">
         <is>
           <t>✅ הושלם</t>
         </is>
@@ -2975,22 +2984,22 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="26" t="inlineStr">
+      <c r="A80" s="30" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="B80" s="27" t="inlineStr">
+      <c r="B80" s="31" t="inlineStr">
         <is>
           <t>RTL בכל המסכים</t>
         </is>
       </c>
-      <c r="C80" s="26" t="inlineStr">
+      <c r="C80" s="30" t="inlineStr">
         <is>
           <t>Frontend / i18n</t>
         </is>
       </c>
-      <c r="D80" s="28" t="inlineStr">
+      <c r="D80" s="32" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -3007,22 +3016,22 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="26" t="inlineStr">
+      <c r="A81" s="30" t="inlineStr">
         <is>
           <t>73</t>
         </is>
       </c>
-      <c r="B81" s="27" t="inlineStr">
+      <c r="B81" s="31" t="inlineStr">
         <is>
           <t>תווית גרסה מ-app.json</t>
         </is>
       </c>
-      <c r="C81" s="26" t="inlineStr">
+      <c r="C81" s="30" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="D81" s="28" t="inlineStr">
+      <c r="D81" s="32" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -3039,22 +3048,22 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="26" t="inlineStr">
+      <c r="A82" s="30" t="inlineStr">
         <is>
           <t>74</t>
         </is>
       </c>
-      <c r="B82" s="27" t="inlineStr">
+      <c r="B82" s="31" t="inlineStr">
         <is>
           <t>טעינה דו-שלבית ברשימת המעקב</t>
         </is>
       </c>
-      <c r="C82" s="26" t="inlineStr">
+      <c r="C82" s="30" t="inlineStr">
         <is>
           <t>Frontend / Performance</t>
         </is>
       </c>
-      <c r="D82" s="28" t="inlineStr">
+      <c r="D82" s="32" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -3071,22 +3080,22 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="26" t="inlineStr">
+      <c r="A83" s="30" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="B83" s="27" t="inlineStr">
+      <c r="B83" s="31" t="inlineStr">
         <is>
           <t>/quotes: אגורות, שם חברה, מטבע</t>
         </is>
       </c>
-      <c r="C83" s="26" t="inlineStr">
+      <c r="C83" s="30" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="D83" s="28" t="inlineStr">
+      <c r="D83" s="32" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
@@ -3103,22 +3112,22 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="26" t="inlineStr">
+      <c r="A84" s="30" t="inlineStr">
         <is>
           <t>76</t>
         </is>
       </c>
-      <c r="B84" s="27" t="inlineStr">
+      <c r="B84" s="31" t="inlineStr">
         <is>
           <t>מיזוג במקום החלפה ברשימת המעקב</t>
         </is>
       </c>
-      <c r="C84" s="26" t="inlineStr">
+      <c r="C84" s="30" t="inlineStr">
         <is>
           <t>Frontend / Bug Fix</t>
         </is>
       </c>
-      <c r="D84" s="28" t="inlineStr">
+      <c r="D84" s="32" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -3135,22 +3144,22 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="26" t="inlineStr">
+      <c r="A85" s="30" t="inlineStr">
         <is>
           <t>77</t>
         </is>
       </c>
-      <c r="B85" s="27" t="inlineStr">
+      <c r="B85" s="31" t="inlineStr">
         <is>
           <t>מרוץ במסך הבית — market/FX</t>
         </is>
       </c>
-      <c r="C85" s="26" t="inlineStr">
+      <c r="C85" s="30" t="inlineStr">
         <is>
           <t>Frontend / Bug Fix</t>
         </is>
       </c>
-      <c r="D85" s="28" t="inlineStr">
+      <c r="D85" s="32" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -3167,22 +3176,22 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="26" t="inlineStr">
+      <c r="A86" s="30" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="B86" s="27" t="inlineStr">
+      <c r="B86" s="31" t="inlineStr">
         <is>
           <t>תשובה ריקה לא מוחקת נתונים טובים</t>
         </is>
       </c>
-      <c r="C86" s="26" t="inlineStr">
+      <c r="C86" s="30" t="inlineStr">
         <is>
           <t>Frontend / Bug Fix</t>
         </is>
       </c>
-      <c r="D86" s="28" t="inlineStr">
+      <c r="D86" s="32" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -3199,22 +3208,22 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="26" t="inlineStr">
+      <c r="A87" s="30" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="B87" s="27" t="inlineStr">
+      <c r="B87" s="31" t="inlineStr">
         <is>
           <t>תרגום כתבה ישנה דלף לחדשה</t>
         </is>
       </c>
-      <c r="C87" s="26" t="inlineStr">
+      <c r="C87" s="30" t="inlineStr">
         <is>
           <t>Frontend / Bug Fix</t>
         </is>
       </c>
-      <c r="D87" s="28" t="inlineStr">
+      <c r="D87" s="32" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -3231,22 +3240,22 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="26" t="inlineStr">
+      <c r="A88" s="30" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="B88" s="27" t="inlineStr">
+      <c r="B88" s="31" t="inlineStr">
         <is>
           <t>מרוץ ב"נסה שוב" של פירוט מדד</t>
         </is>
       </c>
-      <c r="C88" s="26" t="inlineStr">
+      <c r="C88" s="30" t="inlineStr">
         <is>
           <t>Frontend / Bug Fix</t>
         </is>
       </c>
-      <c r="D88" s="28" t="inlineStr">
+      <c r="D88" s="32" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -3263,22 +3272,22 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="26" t="inlineStr">
+      <c r="A89" s="30" t="inlineStr">
         <is>
           <t>81</t>
         </is>
       </c>
-      <c r="B89" s="27" t="inlineStr">
+      <c r="B89" s="31" t="inlineStr">
         <is>
           <t>סולם VIX לא מונוטוני</t>
         </is>
       </c>
-      <c r="C89" s="26" t="inlineStr">
+      <c r="C89" s="30" t="inlineStr">
         <is>
           <t>Frontend / i18n</t>
         </is>
       </c>
-      <c r="D89" s="28" t="inlineStr">
+      <c r="D89" s="32" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -3295,22 +3304,22 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="26" t="inlineStr">
+      <c r="A90" s="30" t="inlineStr">
         <is>
           <t>82</t>
         </is>
       </c>
-      <c r="B90" s="27" t="inlineStr">
+      <c r="B90" s="31" t="inlineStr">
         <is>
           <t>תיקוני תוכן בספרדית</t>
         </is>
       </c>
-      <c r="C90" s="26" t="inlineStr">
+      <c r="C90" s="30" t="inlineStr">
         <is>
           <t>i18n / Accuracy</t>
         </is>
       </c>
-      <c r="D90" s="28" t="inlineStr">
+      <c r="D90" s="32" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -3327,22 +3336,22 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="26" t="inlineStr">
+      <c r="A91" s="30" t="inlineStr">
         <is>
           <t>83</t>
         </is>
       </c>
-      <c r="B91" s="27" t="inlineStr">
+      <c r="B91" s="31" t="inlineStr">
         <is>
           <t>Cache-Control: no-store על כל ה-API</t>
         </is>
       </c>
-      <c r="C91" s="26" t="inlineStr">
+      <c r="C91" s="30" t="inlineStr">
         <is>
           <t>Backend / Bug Fix</t>
         </is>
       </c>
-      <c r="D91" s="28" t="inlineStr">
+      <c r="D91" s="32" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
@@ -3359,22 +3368,22 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="26" t="inlineStr">
+      <c r="A92" s="30" t="inlineStr">
         <is>
           <t>84</t>
         </is>
       </c>
-      <c r="B92" s="27" t="inlineStr">
+      <c r="B92" s="31" t="inlineStr">
         <is>
           <t>סדרה שנתית = סוף שנה, לא ינואר</t>
         </is>
       </c>
-      <c r="C92" s="26" t="inlineStr">
+      <c r="C92" s="30" t="inlineStr">
         <is>
           <t>Backend / Bug Fix</t>
         </is>
       </c>
-      <c r="D92" s="28" t="inlineStr">
+      <c r="D92" s="32" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
@@ -3391,22 +3400,22 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="26" t="inlineStr">
+      <c r="A93" s="30" t="inlineStr">
         <is>
           <t>85</t>
         </is>
       </c>
-      <c r="B93" s="27" t="inlineStr">
+      <c r="B93" s="31" t="inlineStr">
         <is>
           <t>TTM של Buyback דרש 2 רבעונים</t>
         </is>
       </c>
-      <c r="C93" s="26" t="inlineStr">
+      <c r="C93" s="30" t="inlineStr">
         <is>
           <t>Backend / Bug Fix</t>
         </is>
       </c>
-      <c r="D93" s="28" t="inlineStr">
+      <c r="D93" s="32" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
@@ -3423,22 +3432,22 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="26" t="inlineStr">
+      <c r="A94" s="30" t="inlineStr">
         <is>
           <t>86</t>
         </is>
       </c>
-      <c r="B94" s="27" t="inlineStr">
+      <c r="B94" s="31" t="inlineStr">
         <is>
           <t>ניקוי ריפו — cloudflared.exe 52MB</t>
         </is>
       </c>
-      <c r="C94" s="26" t="inlineStr">
+      <c r="C94" s="30" t="inlineStr">
         <is>
           <t>DevOps</t>
         </is>
       </c>
-      <c r="D94" s="28" t="inlineStr">
+      <c r="D94" s="32" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
@@ -3455,22 +3464,22 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="26" t="inlineStr">
+      <c r="A95" s="30" t="inlineStr">
         <is>
           <t>87</t>
         </is>
       </c>
-      <c r="B95" s="27" t="inlineStr">
+      <c r="B95" s="31" t="inlineStr">
         <is>
           <t>דיוק עמוד הפרטיות בנוגע ללוגים</t>
         </is>
       </c>
-      <c r="C95" s="26" t="inlineStr">
+      <c r="C95" s="30" t="inlineStr">
         <is>
           <t>Legal</t>
         </is>
       </c>
-      <c r="D95" s="28" t="inlineStr">
+      <c r="D95" s="32" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
@@ -3487,22 +3496,22 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="26" t="inlineStr">
+      <c r="A96" s="30" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="B96" s="27" t="inlineStr">
+      <c r="B96" s="31" t="inlineStr">
         <is>
           <t>ביקורת קוד מלאה — 35 קבצים</t>
         </is>
       </c>
-      <c r="C96" s="26" t="inlineStr">
+      <c r="C96" s="30" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="D96" s="28" t="inlineStr">
+      <c r="D96" s="32" t="inlineStr">
         <is>
           <t>✅ הושלם</t>
         </is>
@@ -3526,22 +3535,22 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="26" t="inlineStr">
+      <c r="A98" s="30" t="inlineStr">
         <is>
           <t>89</t>
         </is>
       </c>
-      <c r="B98" s="27" t="inlineStr">
+      <c r="B98" s="31" t="inlineStr">
         <is>
           <t>צבע הגרף לפי כיוון המדד</t>
         </is>
       </c>
-      <c r="C98" s="26" t="inlineStr">
+      <c r="C98" s="30" t="inlineStr">
         <is>
           <t>Frontend / UX</t>
         </is>
       </c>
-      <c r="D98" s="28" t="inlineStr">
+      <c r="D98" s="32" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -3558,22 +3567,22 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="26" t="inlineStr">
+      <c r="A99" s="30" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="B99" s="27" t="inlineStr">
+      <c r="B99" s="31" t="inlineStr">
         <is>
           <t>הצהרת טווח מלא לכל 24 המדדים</t>
         </is>
       </c>
-      <c r="C99" s="26" t="inlineStr">
+      <c r="C99" s="30" t="inlineStr">
         <is>
           <t>UX / Accuracy</t>
         </is>
       </c>
-      <c r="D99" s="28" t="inlineStr">
+      <c r="D99" s="32" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -3590,22 +3599,22 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="26" t="inlineStr">
+      <c r="A100" s="30" t="inlineStr">
         <is>
           <t>91</t>
         </is>
       </c>
-      <c r="B100" s="27" t="inlineStr">
+      <c r="B100" s="31" t="inlineStr">
         <is>
           <t>מדד שלא היה לו הסבר בכלל</t>
         </is>
       </c>
-      <c r="C100" s="26" t="inlineStr">
+      <c r="C100" s="30" t="inlineStr">
         <is>
           <t>UX / Bug Fix</t>
         </is>
       </c>
-      <c r="D100" s="28" t="inlineStr">
+      <c r="D100" s="32" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -3622,22 +3631,22 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="26" t="inlineStr">
+      <c r="A101" s="30" t="inlineStr">
         <is>
           <t>92</t>
         </is>
       </c>
-      <c r="B101" s="27" t="inlineStr">
+      <c r="B101" s="31" t="inlineStr">
         <is>
           <t>מספר וכיתוב באותו צבע</t>
         </is>
       </c>
-      <c r="C101" s="26" t="inlineStr">
+      <c r="C101" s="30" t="inlineStr">
         <is>
           <t>Frontend / UX</t>
         </is>
       </c>
-      <c r="D101" s="28" t="inlineStr">
+      <c r="D101" s="32" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -3654,22 +3663,22 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="26" t="inlineStr">
+      <c r="A102" s="30" t="inlineStr">
         <is>
           <t>93</t>
         </is>
       </c>
-      <c r="B102" s="27" t="inlineStr">
+      <c r="B102" s="31" t="inlineStr">
         <is>
           <t>כתום רק כשיש אזהרה</t>
         </is>
       </c>
-      <c r="C102" s="26" t="inlineStr">
+      <c r="C102" s="30" t="inlineStr">
         <is>
           <t>Frontend / UX</t>
         </is>
       </c>
-      <c r="D102" s="28" t="inlineStr">
+      <c r="D102" s="32" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -3686,22 +3695,22 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="26" t="inlineStr">
+      <c r="A103" s="30" t="inlineStr">
         <is>
           <t>94</t>
         </is>
       </c>
-      <c r="B103" s="27" t="inlineStr">
+      <c r="B103" s="31" t="inlineStr">
         <is>
           <t>הצבע שורד את המעבר בין מסכים</t>
         </is>
       </c>
-      <c r="C103" s="26" t="inlineStr">
+      <c r="C103" s="30" t="inlineStr">
         <is>
           <t>Frontend / Bug Fix</t>
         </is>
       </c>
-      <c r="D103" s="28" t="inlineStr">
+      <c r="D103" s="32" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -3718,22 +3727,22 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="26" t="inlineStr">
+      <c r="A104" s="30" t="inlineStr">
         <is>
           <t>95</t>
         </is>
       </c>
-      <c r="B104" s="27" t="inlineStr">
+      <c r="B104" s="31" t="inlineStr">
         <is>
           <t>חומת ההסכמה של גוגל — רוסית וספרדית</t>
         </is>
       </c>
-      <c r="C104" s="26" t="inlineStr">
+      <c r="C104" s="30" t="inlineStr">
         <is>
           <t>Frontend / i18n</t>
         </is>
       </c>
-      <c r="D104" s="28" t="inlineStr">
+      <c r="D104" s="32" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -3750,22 +3759,22 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="26" t="inlineStr">
+      <c r="A105" s="30" t="inlineStr">
         <is>
           <t>96</t>
         </is>
       </c>
-      <c r="B105" s="27" t="inlineStr">
+      <c r="B105" s="31" t="inlineStr">
         <is>
           <t>ביקורת כיסוי-שפות לכל השינויים</t>
         </is>
       </c>
-      <c r="C105" s="26" t="inlineStr">
+      <c r="C105" s="30" t="inlineStr">
         <is>
           <t>QA / i18n</t>
         </is>
       </c>
-      <c r="D105" s="28" t="inlineStr">
+      <c r="D105" s="32" t="inlineStr">
         <is>
           <t>✅ הושלם</t>
         </is>
@@ -3809,26 +3818,46 @@
       </c>
       <c r="F106" s="16" t="inlineStr">
         <is>
-          <t>תשואת דיבידנד/רכישה חוזרת יורדת גם כשהתשלום נחתך (רע) וגם כשהמחיר עולה מהר יותר (טוב). וולמארט העלתה דיבידנד 52 שנה ברציפות והתשואה ירדה 3.2%→0.9% — הגרף צבע את זה אדום. מהתשואה לבדה אי אפשר להבחין, אז הקו כחול = מידע ולא פסק דין.</t>
+          <t>תשואת דיבידנד/רכישה חוזרת יורדת גם כשהתשלום נחתך (רע) וגם כשהמחיר עולה מהר יותר (טוב). וולמארט העלתה דיבידנד 52 שנה ברציפות והתשואה ירדה 3.2%→0.9% — הגרף צבע אדום. הקו כחול = מידע, לא פסק דין.</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="3" t="inlineStr">
+      <c r="A107" s="33" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="B107" s="34" t="inlineStr">
+        <is>
+          <t>צבע הגרף = צבע האריח, לא המגמה</t>
+        </is>
+      </c>
+      <c r="C107" s="33" t="inlineStr">
+        <is>
+          <t>Frontend / UX</t>
+        </is>
+      </c>
+      <c r="D107" s="35" t="inlineStr">
+        <is>
+          <t>✅ Live (OTA)</t>
+        </is>
+      </c>
+      <c r="E107" s="16" t="inlineStr">
+        <is>
+          <t>PriceChart.js, MetricHistoryScreen.js</t>
+        </is>
+      </c>
+      <c r="F107" s="16" t="inlineStr">
+        <is>
+          <t>הגרף צבע לפי מגמה והאריח לפי רמה — שני דברים שיכולים לסתור. P/B שירד מ-14.9 ל-6.84 קיבל קו ירוק ("משתפר") בעוד 6.84 עדיין מעל סף היוקר 5 והאריח צבע אדום. עכשיו הקו נושא את אותו פסק דין; המגמה נראית מצורת הקו. מדד בלי סף ובלי ציון = קו כחול.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
         <is>
           <t>🔜  NOT YET STARTED</t>
-        </is>
-      </c>
-      <c r="B107" s="5" t="inlineStr"/>
-      <c r="C107" s="4" t="inlineStr"/>
-      <c r="D107" s="4" t="inlineStr"/>
-      <c r="E107" s="4" t="inlineStr"/>
-      <c r="F107" s="5" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="6" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="B108" s="4" t="n"/>
@@ -3838,37 +3867,33 @@
       <c r="F108" s="5" t="n"/>
     </row>
     <row r="109">
-      <c r="A109" s="10" t="inlineStr">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="n"/>
+      <c r="C109" s="4" t="n"/>
+      <c r="D109" s="4" t="n"/>
+      <c r="E109" s="4" t="n"/>
+      <c r="F109" s="5" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="10" t="inlineStr">
         <is>
           <t>Legend</t>
         </is>
       </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="6" t="inlineStr">
-        <is>
-          <t>✅ Live</t>
-        </is>
-      </c>
-      <c r="B110" s="7" t="inlineStr">
-        <is>
-          <t>פרוס ופעיל ב-Render — נראה לכל המשתמשים</t>
-        </is>
-      </c>
-      <c r="C110" s="6" t="inlineStr"/>
-      <c r="D110" s="8" t="inlineStr"/>
-      <c r="E110" s="9" t="inlineStr"/>
-      <c r="F110" s="9" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="6" t="inlineStr">
         <is>
-          <t>✅ In APK</t>
+          <t>✅ Live</t>
         </is>
       </c>
       <c r="B111" s="7" t="inlineStr">
         <is>
-          <t>כלול ב-APK המותקן — נראה לכל המשתמשים</t>
+          <t>פרוס ופעיל ב-Render — נראה לכל המשתמשים</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr"/>
@@ -3879,12 +3904,12 @@
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
         <is>
-          <t>⏳ Next APK</t>
+          <t>✅ In APK</t>
         </is>
       </c>
       <c r="B112" s="7" t="inlineStr">
         <is>
-          <t>הקוד מוזג — דורש build ו-APK חדש</t>
+          <t>כלול ב-APK המותקן — נראה לכל המשתמשים</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr"/>
@@ -3895,12 +3920,12 @@
     <row r="113">
       <c r="A113" s="6" t="inlineStr">
         <is>
-          <t>✅ Live (OTA)</t>
+          <t>⏳ Next APK</t>
         </is>
       </c>
       <c r="B113" s="7" t="inlineStr">
         <is>
-          <t>שינוי JS — מועבר אוטומטית בהפעלה הבאה</t>
+          <t>הקוד מוזג — דורש build ו-APK חדש</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr"/>
@@ -3909,42 +3934,50 @@
       <c r="F113" s="9" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="21" t="inlineStr">
-        <is>
-          <t>⏳ ממתין ל-push</t>
-        </is>
-      </c>
-      <c r="B114" s="22" t="inlineStr">
-        <is>
-          <t>הקוד מוכן מקומית — טרם נדחף/נפרס</t>
-        </is>
-      </c>
+      <c r="A114" s="6" t="inlineStr">
+        <is>
+          <t>✅ Live (OTA)</t>
+        </is>
+      </c>
+      <c r="B114" s="7" t="inlineStr">
+        <is>
+          <t>שינוי JS — מועבר אוטומטית בהפעלה הבאה</t>
+        </is>
+      </c>
+      <c r="C114" s="6" t="inlineStr"/>
+      <c r="D114" s="8" t="inlineStr"/>
+      <c r="E114" s="9" t="inlineStr"/>
+      <c r="F114" s="9" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="21" t="inlineStr">
         <is>
+          <t>⏳ ממתין ל-push</t>
+        </is>
+      </c>
+      <c r="B115" s="22" t="inlineStr">
+        <is>
+          <t>הקוד מוכן מקומית — טרם נדחף/נפרס</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="21" t="inlineStr">
+        <is>
           <t>⏳ דורש build</t>
         </is>
       </c>
-      <c r="B115" s="22" t="inlineStr">
+      <c r="B116" s="22" t="inlineStr">
         <is>
           <t>שינוי נייטיב — OTA לא מספיק, צריך AAB/APK חדש</t>
         </is>
       </c>
     </row>
-    <row r="116"/>
-    <row r="117">
-      <c r="A117" s="23" t="inlineStr">
+    <row r="117"/>
+    <row r="118">
+      <c r="A118" s="23" t="inlineStr">
         <is>
           <t>סיכום Session 6-7</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="24" t="n"/>
-      <c r="B118" s="25" t="inlineStr">
-        <is>
-          <t>45  —  פריטים חדשים שנוספו (52-96)</t>
         </is>
       </c>
     </row>
@@ -3952,7 +3985,7 @@
       <c r="A119" s="24" t="n"/>
       <c r="B119" s="25" t="inlineStr">
         <is>
-          <t>44  —  חיים בייצור או ב-OTA</t>
+          <t>45  —  פריטים חדשים שנוספו (52-96)</t>
         </is>
       </c>
     </row>
@@ -3960,7 +3993,7 @@
       <c r="A120" s="24" t="n"/>
       <c r="B120" s="25" t="inlineStr">
         <is>
-          <t>1  —  דורש build חדש: תמיכת טאבלט (פריט 68)</t>
+          <t>44  —  חיים בייצור או ב-OTA</t>
         </is>
       </c>
     </row>
@@ -3968,7 +4001,7 @@
       <c r="A121" s="24" t="n"/>
       <c r="B121" s="25" t="inlineStr">
         <is>
-          <t>11,781  —  שורות קוד שנקראו במלואן, 36 קבצים</t>
+          <t>1  —  דורש build חדש: תמיכת טאבלט (פריט 68)</t>
         </is>
       </c>
     </row>
@@ -3976,7 +4009,7 @@
       <c r="A122" s="24" t="n"/>
       <c r="B122" s="25" t="inlineStr">
         <is>
-          <t>29  —  חבילות בדיקה התנהגותיות עוברות</t>
+          <t>11,781  —  שורות קוד שנקראו במלואן, 36 קבצים</t>
         </is>
       </c>
     </row>
@@ -3984,14 +4017,22 @@
       <c r="A123" s="24" t="n"/>
       <c r="B123" s="25" t="inlineStr">
         <is>
+          <t>29  —  חבילות בדיקה התנהגותיות עוברות</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="24" t="n"/>
+      <c r="B124" s="25" t="inlineStr">
+        <is>
           <t>18  —  ראוטים בשרת · 316 מפתחות i18n × 4 שפות</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A107:F107"/>
     <mergeCell ref="A97:F97"/>
-    <mergeCell ref="A107:F107"/>
     <mergeCell ref="A59:F59"/>
     <mergeCell ref="A25:F25"/>
   </mergeCells>

--- a/BuddhaVest_Progress.xlsx
+++ b/BuddhaVest_Progress.xlsx
@@ -175,7 +175,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -266,6 +266,15 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -633,7 +642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F124"/>
+  <dimension ref="A1:F125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2344,22 +2353,22 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="30" t="inlineStr">
+      <c r="A60" s="33" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="B60" s="31" t="inlineStr">
+      <c r="B60" s="34" t="inlineStr">
         <is>
           <t>מרוץ שפות — 5 מסכים/רכיבים</t>
         </is>
       </c>
-      <c r="C60" s="30" t="inlineStr">
+      <c r="C60" s="33" t="inlineStr">
         <is>
           <t>Frontend / Bug Fix</t>
         </is>
       </c>
-      <c r="D60" s="32" t="inlineStr">
+      <c r="D60" s="35" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -2376,22 +2385,22 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="30" t="inlineStr">
+      <c r="A61" s="33" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="B61" s="31" t="inlineStr">
+      <c r="B61" s="34" t="inlineStr">
         <is>
           <t>Volume/Avg Vol ריקים לסירוגין</t>
         </is>
       </c>
-      <c r="C61" s="30" t="inlineStr">
+      <c r="C61" s="33" t="inlineStr">
         <is>
           <t>Backend / Bug Fix</t>
         </is>
       </c>
-      <c r="D61" s="32" t="inlineStr">
+      <c r="D61" s="35" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
@@ -2408,22 +2417,22 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="30" t="inlineStr">
+      <c r="A62" s="33" t="inlineStr">
         <is>
           <t>54</t>
         </is>
       </c>
-      <c r="B62" s="31" t="inlineStr">
+      <c r="B62" s="34" t="inlineStr">
         <is>
           <t>המרת אגורות→שקל למניות ת"א</t>
         </is>
       </c>
-      <c r="C62" s="30" t="inlineStr">
+      <c r="C62" s="33" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="D62" s="32" t="inlineStr">
+      <c r="D62" s="35" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
@@ -2440,22 +2449,22 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="30" t="inlineStr">
+      <c r="A63" s="33" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="B63" s="31" t="inlineStr">
+      <c r="B63" s="34" t="inlineStr">
         <is>
           <t>באג יחידות ב-Buyback (3500000000%)</t>
         </is>
       </c>
-      <c r="C63" s="30" t="inlineStr">
+      <c r="C63" s="33" t="inlineStr">
         <is>
           <t>Backend + Frontend</t>
         </is>
       </c>
-      <c r="D63" s="32" t="inlineStr">
+      <c r="D63" s="35" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
@@ -2472,22 +2481,22 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="30" t="inlineStr">
+      <c r="A64" s="33" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="B64" s="31" t="inlineStr">
+      <c r="B64" s="34" t="inlineStr">
         <is>
           <t>תיקוני נכונות במנוע הציון</t>
         </is>
       </c>
-      <c r="C64" s="30" t="inlineStr">
+      <c r="C64" s="33" t="inlineStr">
         <is>
           <t>Backend / Scoring</t>
         </is>
       </c>
-      <c r="D64" s="32" t="inlineStr">
+      <c r="D64" s="35" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
@@ -2504,22 +2513,22 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="30" t="inlineStr">
+      <c r="A65" s="33" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="B65" s="31" t="inlineStr">
+      <c r="B65" s="34" t="inlineStr">
         <is>
           <t>ניסוח דיבידנד כן — לא "משולם בעקביות"</t>
         </is>
       </c>
-      <c r="C65" s="30" t="inlineStr">
+      <c r="C65" s="33" t="inlineStr">
         <is>
           <t>Legal / Accuracy</t>
         </is>
       </c>
-      <c r="D65" s="32" t="inlineStr">
+      <c r="D65" s="35" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
@@ -2536,22 +2545,22 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="30" t="inlineStr">
+      <c r="A66" s="33" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="B66" s="31" t="inlineStr">
+      <c r="B66" s="34" t="inlineStr">
         <is>
           <t>SSRF — /translate-article</t>
         </is>
       </c>
-      <c r="C66" s="30" t="inlineStr">
+      <c r="C66" s="33" t="inlineStr">
         <is>
           <t>Backend / Security</t>
         </is>
       </c>
-      <c r="D66" s="32" t="inlineStr">
+      <c r="D66" s="35" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
@@ -2568,22 +2577,22 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="30" t="inlineStr">
+      <c r="A67" s="33" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="B67" s="31" t="inlineStr">
+      <c r="B67" s="34" t="inlineStr">
         <is>
           <t>XSS ב-WebView של הכתבות</t>
         </is>
       </c>
-      <c r="C67" s="30" t="inlineStr">
+      <c r="C67" s="33" t="inlineStr">
         <is>
           <t>Frontend / Security</t>
         </is>
       </c>
-      <c r="D67" s="32" t="inlineStr">
+      <c r="D67" s="35" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -2600,22 +2609,22 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="30" t="inlineStr">
+      <c r="A68" s="33" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="B68" s="31" t="inlineStr">
+      <c r="B68" s="34" t="inlineStr">
         <is>
           <t>הסרת /debug-pe ו-/debug-rows</t>
         </is>
       </c>
-      <c r="C68" s="30" t="inlineStr">
+      <c r="C68" s="33" t="inlineStr">
         <is>
           <t>Backend / Security</t>
         </is>
       </c>
-      <c r="D68" s="32" t="inlineStr">
+      <c r="D68" s="35" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
@@ -2632,22 +2641,22 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="30" t="inlineStr">
+      <c r="A69" s="33" t="inlineStr">
         <is>
           <t>61</t>
         </is>
       </c>
-      <c r="B69" s="31" t="inlineStr">
+      <c r="B69" s="34" t="inlineStr">
         <is>
           <t>5 דליפות של פרטי חריגה ללקוח</t>
         </is>
       </c>
-      <c r="C69" s="30" t="inlineStr">
+      <c r="C69" s="33" t="inlineStr">
         <is>
           <t>Backend / Security</t>
         </is>
       </c>
-      <c r="D69" s="32" t="inlineStr">
+      <c r="D69" s="35" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
@@ -2664,22 +2673,22 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="30" t="inlineStr">
+      <c r="A70" s="33" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="B70" s="31" t="inlineStr">
+      <c r="B70" s="34" t="inlineStr">
         <is>
           <t>פיצוץ זיכרון בעליית השרת</t>
         </is>
       </c>
-      <c r="C70" s="30" t="inlineStr">
+      <c r="C70" s="33" t="inlineStr">
         <is>
           <t>Backend / Performance</t>
         </is>
       </c>
-      <c r="D70" s="32" t="inlineStr">
+      <c r="D70" s="35" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
@@ -2696,22 +2705,22 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="30" t="inlineStr">
+      <c r="A71" s="33" t="inlineStr">
         <is>
           <t>63</t>
         </is>
       </c>
-      <c r="B71" s="31" t="inlineStr">
+      <c r="B71" s="34" t="inlineStr">
         <is>
           <t>תקרת מטמון + single-flight</t>
         </is>
       </c>
-      <c r="C71" s="30" t="inlineStr">
+      <c r="C71" s="33" t="inlineStr">
         <is>
           <t>Backend / Performance</t>
         </is>
       </c>
-      <c r="D71" s="32" t="inlineStr">
+      <c r="D71" s="35" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
@@ -2728,22 +2737,22 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="30" t="inlineStr">
+      <c r="A72" s="33" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="B72" s="31" t="inlineStr">
+      <c r="B72" s="34" t="inlineStr">
         <is>
           <t>חלון היסטוריה 10y במקום max</t>
         </is>
       </c>
-      <c r="C72" s="30" t="inlineStr">
+      <c r="C72" s="33" t="inlineStr">
         <is>
           <t>Backend / Performance</t>
         </is>
       </c>
-      <c r="D72" s="32" t="inlineStr">
+      <c r="D72" s="35" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
@@ -2760,22 +2769,22 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="30" t="inlineStr">
+      <c r="A73" s="33" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="B73" s="31" t="inlineStr">
+      <c r="B73" s="34" t="inlineStr">
         <is>
           <t>Debounce בחיפוש</t>
         </is>
       </c>
-      <c r="C73" s="30" t="inlineStr">
+      <c r="C73" s="33" t="inlineStr">
         <is>
           <t>Frontend / Performance</t>
         </is>
       </c>
-      <c r="D73" s="32" t="inlineStr">
+      <c r="D73" s="35" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -2792,22 +2801,22 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="30" t="inlineStr">
+      <c r="A74" s="33" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="B74" s="31" t="inlineStr">
+      <c r="B74" s="34" t="inlineStr">
         <is>
           <t>תקציב זמן ל-Stooq</t>
         </is>
       </c>
-      <c r="C74" s="30" t="inlineStr">
+      <c r="C74" s="33" t="inlineStr">
         <is>
           <t>Backend / Performance</t>
         </is>
       </c>
-      <c r="D74" s="32" t="inlineStr">
+      <c r="D74" s="35" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
@@ -2824,22 +2833,22 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="30" t="inlineStr">
+      <c r="A75" s="33" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="B75" s="31" t="inlineStr">
+      <c r="B75" s="34" t="inlineStr">
         <is>
           <t>אובדן נתונים ביומן המחקר</t>
         </is>
       </c>
-      <c r="C75" s="30" t="inlineStr">
+      <c r="C75" s="33" t="inlineStr">
         <is>
           <t>Frontend / Bug Fix</t>
         </is>
       </c>
-      <c r="D75" s="32" t="inlineStr">
+      <c r="D75" s="35" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -2863,7 +2872,7 @@
       </c>
       <c r="B76" s="18" t="inlineStr">
         <is>
-          <t>תמיכת טאבלט</t>
+          <t>הקלה חלקית לטאבלט (לא תמיכה מלאה)</t>
         </is>
       </c>
       <c r="C76" s="17" t="inlineStr">
@@ -2873,7 +2882,7 @@
       </c>
       <c r="D76" s="19" t="inlineStr">
         <is>
-          <t>⏳ דורש build</t>
+          <t>⚠️ חלקי</t>
         </is>
       </c>
       <c r="E76" s="20" t="inlineStr">
@@ -2883,27 +2892,27 @@
       </c>
       <c r="F76" s="20" t="inlineStr">
         <is>
-          <t>TabletFrame (רוחב ≥700 ממורכז ל-600), שחרור סיבוב לטאבלט ונעילת portrait לטלפון, כפתור צף שנצמד מחדש בסיבוב. supportsTablet=true.</t>
+          <t>תיאור מדויק: TabletFrame ממרכז את התוכן ל-600px, סיבוב משוחרר לטאבלט ונעול לטלפון, והכפתור הצף נצמד מחדש בסיבוב. זו אפליקציית טלפון ממורכזת — לא פריסת טאבלט. הטבלאות (טבלת השוק ב-HomeScreen, FinancialsCard) בנויות על רוחב עמודות קבוע בפיקסלים ולא מתאימות את עצמן. supportsTablet הוחזר ל-false עד שתיבנה פריסה אמיתית. תיעוד קודם תיאר את זה כ"תמיכה מלאה" — תיאור שלא היה לו כיסוי, תוקן כאן.</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="30" t="inlineStr">
+      <c r="A77" s="33" t="inlineStr">
         <is>
           <t>69</t>
         </is>
       </c>
-      <c r="B77" s="31" t="inlineStr">
+      <c r="B77" s="34" t="inlineStr">
         <is>
           <t>מסך הסכמה בהפעלה ראשונה</t>
         </is>
       </c>
-      <c r="C77" s="30" t="inlineStr">
+      <c r="C77" s="33" t="inlineStr">
         <is>
           <t>Legal</t>
         </is>
       </c>
-      <c r="D77" s="32" t="inlineStr">
+      <c r="D77" s="35" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -2920,22 +2929,22 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="30" t="inlineStr">
+      <c r="A78" s="33" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="B78" s="31" t="inlineStr">
+      <c r="B78" s="34" t="inlineStr">
         <is>
           <t>שכתוב תיאור החנות — בלי הבטחות</t>
         </is>
       </c>
-      <c r="C78" s="30" t="inlineStr">
+      <c r="C78" s="33" t="inlineStr">
         <is>
           <t>Legal / Store</t>
         </is>
       </c>
-      <c r="D78" s="32" t="inlineStr">
+      <c r="D78" s="35" t="inlineStr">
         <is>
           <t>✅ מוכן</t>
         </is>
@@ -2952,22 +2961,22 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="30" t="inlineStr">
+      <c r="A79" s="33" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="B79" s="31" t="inlineStr">
+      <c r="B79" s="34" t="inlineStr">
         <is>
           <t>מדריך צילומי מסך לחנות</t>
         </is>
       </c>
-      <c r="C79" s="30" t="inlineStr">
+      <c r="C79" s="33" t="inlineStr">
         <is>
           <t>Store Assets</t>
         </is>
       </c>
-      <c r="D79" s="32" t="inlineStr">
+      <c r="D79" s="35" t="inlineStr">
         <is>
           <t>✅ הושלם</t>
         </is>
@@ -2984,22 +2993,22 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="30" t="inlineStr">
+      <c r="A80" s="33" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="B80" s="31" t="inlineStr">
+      <c r="B80" s="34" t="inlineStr">
         <is>
           <t>RTL בכל המסכים</t>
         </is>
       </c>
-      <c r="C80" s="30" t="inlineStr">
+      <c r="C80" s="33" t="inlineStr">
         <is>
           <t>Frontend / i18n</t>
         </is>
       </c>
-      <c r="D80" s="32" t="inlineStr">
+      <c r="D80" s="35" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -3016,22 +3025,22 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="30" t="inlineStr">
+      <c r="A81" s="33" t="inlineStr">
         <is>
           <t>73</t>
         </is>
       </c>
-      <c r="B81" s="31" t="inlineStr">
+      <c r="B81" s="34" t="inlineStr">
         <is>
           <t>תווית גרסה מ-app.json</t>
         </is>
       </c>
-      <c r="C81" s="30" t="inlineStr">
+      <c r="C81" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="D81" s="32" t="inlineStr">
+      <c r="D81" s="35" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -3048,22 +3057,22 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="30" t="inlineStr">
+      <c r="A82" s="33" t="inlineStr">
         <is>
           <t>74</t>
         </is>
       </c>
-      <c r="B82" s="31" t="inlineStr">
+      <c r="B82" s="34" t="inlineStr">
         <is>
           <t>טעינה דו-שלבית ברשימת המעקב</t>
         </is>
       </c>
-      <c r="C82" s="30" t="inlineStr">
+      <c r="C82" s="33" t="inlineStr">
         <is>
           <t>Frontend / Performance</t>
         </is>
       </c>
-      <c r="D82" s="32" t="inlineStr">
+      <c r="D82" s="35" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -3080,22 +3089,22 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="30" t="inlineStr">
+      <c r="A83" s="33" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="B83" s="31" t="inlineStr">
+      <c r="B83" s="34" t="inlineStr">
         <is>
           <t>/quotes: אגורות, שם חברה, מטבע</t>
         </is>
       </c>
-      <c r="C83" s="30" t="inlineStr">
+      <c r="C83" s="33" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="D83" s="32" t="inlineStr">
+      <c r="D83" s="35" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
@@ -3112,22 +3121,22 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="30" t="inlineStr">
+      <c r="A84" s="33" t="inlineStr">
         <is>
           <t>76</t>
         </is>
       </c>
-      <c r="B84" s="31" t="inlineStr">
+      <c r="B84" s="34" t="inlineStr">
         <is>
           <t>מיזוג במקום החלפה ברשימת המעקב</t>
         </is>
       </c>
-      <c r="C84" s="30" t="inlineStr">
+      <c r="C84" s="33" t="inlineStr">
         <is>
           <t>Frontend / Bug Fix</t>
         </is>
       </c>
-      <c r="D84" s="32" t="inlineStr">
+      <c r="D84" s="35" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -3144,22 +3153,22 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="30" t="inlineStr">
+      <c r="A85" s="33" t="inlineStr">
         <is>
           <t>77</t>
         </is>
       </c>
-      <c r="B85" s="31" t="inlineStr">
+      <c r="B85" s="34" t="inlineStr">
         <is>
           <t>מרוץ במסך הבית — market/FX</t>
         </is>
       </c>
-      <c r="C85" s="30" t="inlineStr">
+      <c r="C85" s="33" t="inlineStr">
         <is>
           <t>Frontend / Bug Fix</t>
         </is>
       </c>
-      <c r="D85" s="32" t="inlineStr">
+      <c r="D85" s="35" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -3176,22 +3185,22 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="30" t="inlineStr">
+      <c r="A86" s="33" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="B86" s="31" t="inlineStr">
+      <c r="B86" s="34" t="inlineStr">
         <is>
           <t>תשובה ריקה לא מוחקת נתונים טובים</t>
         </is>
       </c>
-      <c r="C86" s="30" t="inlineStr">
+      <c r="C86" s="33" t="inlineStr">
         <is>
           <t>Frontend / Bug Fix</t>
         </is>
       </c>
-      <c r="D86" s="32" t="inlineStr">
+      <c r="D86" s="35" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -3208,22 +3217,22 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="30" t="inlineStr">
+      <c r="A87" s="33" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="B87" s="31" t="inlineStr">
+      <c r="B87" s="34" t="inlineStr">
         <is>
           <t>תרגום כתבה ישנה דלף לחדשה</t>
         </is>
       </c>
-      <c r="C87" s="30" t="inlineStr">
+      <c r="C87" s="33" t="inlineStr">
         <is>
           <t>Frontend / Bug Fix</t>
         </is>
       </c>
-      <c r="D87" s="32" t="inlineStr">
+      <c r="D87" s="35" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -3240,22 +3249,22 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="30" t="inlineStr">
+      <c r="A88" s="33" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="B88" s="31" t="inlineStr">
+      <c r="B88" s="34" t="inlineStr">
         <is>
           <t>מרוץ ב"נסה שוב" של פירוט מדד</t>
         </is>
       </c>
-      <c r="C88" s="30" t="inlineStr">
+      <c r="C88" s="33" t="inlineStr">
         <is>
           <t>Frontend / Bug Fix</t>
         </is>
       </c>
-      <c r="D88" s="32" t="inlineStr">
+      <c r="D88" s="35" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -3272,22 +3281,22 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="30" t="inlineStr">
+      <c r="A89" s="33" t="inlineStr">
         <is>
           <t>81</t>
         </is>
       </c>
-      <c r="B89" s="31" t="inlineStr">
+      <c r="B89" s="34" t="inlineStr">
         <is>
           <t>סולם VIX לא מונוטוני</t>
         </is>
       </c>
-      <c r="C89" s="30" t="inlineStr">
+      <c r="C89" s="33" t="inlineStr">
         <is>
           <t>Frontend / i18n</t>
         </is>
       </c>
-      <c r="D89" s="32" t="inlineStr">
+      <c r="D89" s="35" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -3304,22 +3313,22 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="30" t="inlineStr">
+      <c r="A90" s="33" t="inlineStr">
         <is>
           <t>82</t>
         </is>
       </c>
-      <c r="B90" s="31" t="inlineStr">
+      <c r="B90" s="34" t="inlineStr">
         <is>
           <t>תיקוני תוכן בספרדית</t>
         </is>
       </c>
-      <c r="C90" s="30" t="inlineStr">
+      <c r="C90" s="33" t="inlineStr">
         <is>
           <t>i18n / Accuracy</t>
         </is>
       </c>
-      <c r="D90" s="32" t="inlineStr">
+      <c r="D90" s="35" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -3336,22 +3345,22 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="30" t="inlineStr">
+      <c r="A91" s="33" t="inlineStr">
         <is>
           <t>83</t>
         </is>
       </c>
-      <c r="B91" s="31" t="inlineStr">
+      <c r="B91" s="34" t="inlineStr">
         <is>
           <t>Cache-Control: no-store על כל ה-API</t>
         </is>
       </c>
-      <c r="C91" s="30" t="inlineStr">
+      <c r="C91" s="33" t="inlineStr">
         <is>
           <t>Backend / Bug Fix</t>
         </is>
       </c>
-      <c r="D91" s="32" t="inlineStr">
+      <c r="D91" s="35" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
@@ -3368,22 +3377,22 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="30" t="inlineStr">
+      <c r="A92" s="33" t="inlineStr">
         <is>
           <t>84</t>
         </is>
       </c>
-      <c r="B92" s="31" t="inlineStr">
+      <c r="B92" s="34" t="inlineStr">
         <is>
           <t>סדרה שנתית = סוף שנה, לא ינואר</t>
         </is>
       </c>
-      <c r="C92" s="30" t="inlineStr">
+      <c r="C92" s="33" t="inlineStr">
         <is>
           <t>Backend / Bug Fix</t>
         </is>
       </c>
-      <c r="D92" s="32" t="inlineStr">
+      <c r="D92" s="35" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
@@ -3400,22 +3409,22 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="30" t="inlineStr">
+      <c r="A93" s="33" t="inlineStr">
         <is>
           <t>85</t>
         </is>
       </c>
-      <c r="B93" s="31" t="inlineStr">
+      <c r="B93" s="34" t="inlineStr">
         <is>
           <t>TTM של Buyback דרש 2 רבעונים</t>
         </is>
       </c>
-      <c r="C93" s="30" t="inlineStr">
+      <c r="C93" s="33" t="inlineStr">
         <is>
           <t>Backend / Bug Fix</t>
         </is>
       </c>
-      <c r="D93" s="32" t="inlineStr">
+      <c r="D93" s="35" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
@@ -3432,22 +3441,22 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="30" t="inlineStr">
+      <c r="A94" s="33" t="inlineStr">
         <is>
           <t>86</t>
         </is>
       </c>
-      <c r="B94" s="31" t="inlineStr">
+      <c r="B94" s="34" t="inlineStr">
         <is>
           <t>ניקוי ריפו — cloudflared.exe 52MB</t>
         </is>
       </c>
-      <c r="C94" s="30" t="inlineStr">
+      <c r="C94" s="33" t="inlineStr">
         <is>
           <t>DevOps</t>
         </is>
       </c>
-      <c r="D94" s="32" t="inlineStr">
+      <c r="D94" s="35" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
@@ -3464,22 +3473,22 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="30" t="inlineStr">
+      <c r="A95" s="33" t="inlineStr">
         <is>
           <t>87</t>
         </is>
       </c>
-      <c r="B95" s="31" t="inlineStr">
+      <c r="B95" s="34" t="inlineStr">
         <is>
           <t>דיוק עמוד הפרטיות בנוגע ללוגים</t>
         </is>
       </c>
-      <c r="C95" s="30" t="inlineStr">
+      <c r="C95" s="33" t="inlineStr">
         <is>
           <t>Legal</t>
         </is>
       </c>
-      <c r="D95" s="32" t="inlineStr">
+      <c r="D95" s="35" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
@@ -3496,22 +3505,22 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="30" t="inlineStr">
+      <c r="A96" s="33" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="B96" s="31" t="inlineStr">
+      <c r="B96" s="34" t="inlineStr">
         <is>
           <t>ביקורת קוד מלאה — 35 קבצים</t>
         </is>
       </c>
-      <c r="C96" s="30" t="inlineStr">
+      <c r="C96" s="33" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="D96" s="32" t="inlineStr">
+      <c r="D96" s="35" t="inlineStr">
         <is>
           <t>✅ הושלם</t>
         </is>
@@ -3535,22 +3544,22 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="30" t="inlineStr">
+      <c r="A98" s="33" t="inlineStr">
         <is>
           <t>89</t>
         </is>
       </c>
-      <c r="B98" s="31" t="inlineStr">
+      <c r="B98" s="34" t="inlineStr">
         <is>
           <t>צבע הגרף לפי כיוון המדד</t>
         </is>
       </c>
-      <c r="C98" s="30" t="inlineStr">
+      <c r="C98" s="33" t="inlineStr">
         <is>
           <t>Frontend / UX</t>
         </is>
       </c>
-      <c r="D98" s="32" t="inlineStr">
+      <c r="D98" s="35" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -3567,22 +3576,22 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="30" t="inlineStr">
+      <c r="A99" s="33" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="B99" s="31" t="inlineStr">
+      <c r="B99" s="34" t="inlineStr">
         <is>
           <t>הצהרת טווח מלא לכל 24 המדדים</t>
         </is>
       </c>
-      <c r="C99" s="30" t="inlineStr">
+      <c r="C99" s="33" t="inlineStr">
         <is>
           <t>UX / Accuracy</t>
         </is>
       </c>
-      <c r="D99" s="32" t="inlineStr">
+      <c r="D99" s="35" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -3599,22 +3608,22 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="30" t="inlineStr">
+      <c r="A100" s="33" t="inlineStr">
         <is>
           <t>91</t>
         </is>
       </c>
-      <c r="B100" s="31" t="inlineStr">
+      <c r="B100" s="34" t="inlineStr">
         <is>
           <t>מדד שלא היה לו הסבר בכלל</t>
         </is>
       </c>
-      <c r="C100" s="30" t="inlineStr">
+      <c r="C100" s="33" t="inlineStr">
         <is>
           <t>UX / Bug Fix</t>
         </is>
       </c>
-      <c r="D100" s="32" t="inlineStr">
+      <c r="D100" s="35" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -3631,22 +3640,22 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="30" t="inlineStr">
+      <c r="A101" s="33" t="inlineStr">
         <is>
           <t>92</t>
         </is>
       </c>
-      <c r="B101" s="31" t="inlineStr">
+      <c r="B101" s="34" t="inlineStr">
         <is>
           <t>מספר וכיתוב באותו צבע</t>
         </is>
       </c>
-      <c r="C101" s="30" t="inlineStr">
+      <c r="C101" s="33" t="inlineStr">
         <is>
           <t>Frontend / UX</t>
         </is>
       </c>
-      <c r="D101" s="32" t="inlineStr">
+      <c r="D101" s="35" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -3663,22 +3672,22 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="30" t="inlineStr">
+      <c r="A102" s="33" t="inlineStr">
         <is>
           <t>93</t>
         </is>
       </c>
-      <c r="B102" s="31" t="inlineStr">
+      <c r="B102" s="34" t="inlineStr">
         <is>
           <t>כתום רק כשיש אזהרה</t>
         </is>
       </c>
-      <c r="C102" s="30" t="inlineStr">
+      <c r="C102" s="33" t="inlineStr">
         <is>
           <t>Frontend / UX</t>
         </is>
       </c>
-      <c r="D102" s="32" t="inlineStr">
+      <c r="D102" s="35" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -3695,22 +3704,22 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="30" t="inlineStr">
+      <c r="A103" s="33" t="inlineStr">
         <is>
           <t>94</t>
         </is>
       </c>
-      <c r="B103" s="31" t="inlineStr">
+      <c r="B103" s="34" t="inlineStr">
         <is>
           <t>הצבע שורד את המעבר בין מסכים</t>
         </is>
       </c>
-      <c r="C103" s="30" t="inlineStr">
+      <c r="C103" s="33" t="inlineStr">
         <is>
           <t>Frontend / Bug Fix</t>
         </is>
       </c>
-      <c r="D103" s="32" t="inlineStr">
+      <c r="D103" s="35" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -3727,22 +3736,22 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="30" t="inlineStr">
+      <c r="A104" s="33" t="inlineStr">
         <is>
           <t>95</t>
         </is>
       </c>
-      <c r="B104" s="31" t="inlineStr">
+      <c r="B104" s="34" t="inlineStr">
         <is>
           <t>חומת ההסכמה של גוגל — רוסית וספרדית</t>
         </is>
       </c>
-      <c r="C104" s="30" t="inlineStr">
+      <c r="C104" s="33" t="inlineStr">
         <is>
           <t>Frontend / i18n</t>
         </is>
       </c>
-      <c r="D104" s="32" t="inlineStr">
+      <c r="D104" s="35" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -3759,22 +3768,22 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="30" t="inlineStr">
+      <c r="A105" s="33" t="inlineStr">
         <is>
           <t>96</t>
         </is>
       </c>
-      <c r="B105" s="31" t="inlineStr">
+      <c r="B105" s="34" t="inlineStr">
         <is>
           <t>ביקורת כיסוי-שפות לכל השינויים</t>
         </is>
       </c>
-      <c r="C105" s="30" t="inlineStr">
+      <c r="C105" s="33" t="inlineStr">
         <is>
           <t>QA / i18n</t>
         </is>
       </c>
-      <c r="D105" s="32" t="inlineStr">
+      <c r="D105" s="35" t="inlineStr">
         <is>
           <t>✅ הושלם</t>
         </is>
@@ -3791,22 +3800,22 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="30" t="inlineStr">
+      <c r="A106" s="33" t="inlineStr">
         <is>
           <t>97</t>
         </is>
       </c>
-      <c r="B106" s="31" t="inlineStr">
+      <c r="B106" s="34" t="inlineStr">
         <is>
           <t>מדדים דו-משמעיים — הגרף לא טוען טענה</t>
         </is>
       </c>
-      <c r="C106" s="30" t="inlineStr">
+      <c r="C106" s="33" t="inlineStr">
         <is>
           <t>Frontend / Accuracy</t>
         </is>
       </c>
-      <c r="D106" s="32" t="inlineStr">
+      <c r="D106" s="35" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -3828,48 +3837,43 @@
           <t>98</t>
         </is>
       </c>
-      <c r="B107" s="34" t="inlineStr">
-        <is>
-          <t>צבע הגרף = צבע האריח, לא המגמה</t>
-        </is>
-      </c>
-      <c r="C107" s="33" t="inlineStr">
-        <is>
-          <t>Frontend / UX</t>
-        </is>
-      </c>
-      <c r="D107" s="35" t="inlineStr">
-        <is>
-          <t>✅ Live (OTA)</t>
-        </is>
-      </c>
-      <c r="E107" s="16" t="inlineStr">
-        <is>
-          <t>PriceChart.js, MetricHistoryScreen.js</t>
-        </is>
-      </c>
-      <c r="F107" s="16" t="inlineStr">
-        <is>
-          <t>הגרף צבע לפי מגמה והאריח לפי רמה — שני דברים שיכולים לסתור. P/B שירד מ-14.9 ל-6.84 קיבל קו ירוק ("משתפר") בעוד 6.84 עדיין מעל סף היוקר 5 והאריח צבע אדום. עכשיו הקו נושא את אותו פסק דין; המגמה נראית מצורת הקו. מדד בלי סף ובלי ציון = קו כחול.</t>
-        </is>
-      </c>
     </row>
     <row r="108">
-      <c r="A108" s="3" t="inlineStr">
+      <c r="A108" s="36" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="B108" s="37" t="inlineStr">
+        <is>
+          <t>פריסת טאבלט אמיתית</t>
+        </is>
+      </c>
+      <c r="C108" s="36" t="inlineStr">
+        <is>
+          <t>Frontend / Layout</t>
+        </is>
+      </c>
+      <c r="D108" s="38" t="inlineStr">
+        <is>
+          <t>🔜 לא התחיל</t>
+        </is>
+      </c>
+      <c r="E108" s="20" t="inlineStr">
+        <is>
+          <t>HomeScreen.js, FinancialsCard.js, StockScreen.js</t>
+        </is>
+      </c>
+      <c r="F108" s="20" t="inlineStr">
+        <is>
+          <t>נדרש: רוחבי עמודות יחסיים במקום קבועים (COL ב-HomeScreen, 152px/80px ב-FinancialsCard), פריסה דו-טורית בלנדסקייפ, וגדלי גופן שמגיבים למסך. כל סבב בדיקה דורש בילד נייטיב. המלצה: לשחרר לחנות כאפליקציית טלפון ולטפל בטאבלט בגרסה נפרדת.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="inlineStr">
         <is>
           <t>🔜  NOT YET STARTED</t>
-        </is>
-      </c>
-      <c r="B108" s="4" t="n"/>
-      <c r="C108" s="4" t="n"/>
-      <c r="D108" s="4" t="n"/>
-      <c r="E108" s="4" t="n"/>
-      <c r="F108" s="5" t="n"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="6" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="B109" s="4" t="n"/>
@@ -3879,37 +3883,33 @@
       <c r="F109" s="5" t="n"/>
     </row>
     <row r="110">
-      <c r="A110" s="10" t="inlineStr">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="n"/>
+      <c r="C110" s="4" t="n"/>
+      <c r="D110" s="4" t="n"/>
+      <c r="E110" s="4" t="n"/>
+      <c r="F110" s="5" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="10" t="inlineStr">
         <is>
           <t>Legend</t>
         </is>
       </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="6" t="inlineStr">
-        <is>
-          <t>✅ Live</t>
-        </is>
-      </c>
-      <c r="B111" s="7" t="inlineStr">
-        <is>
-          <t>פרוס ופעיל ב-Render — נראה לכל המשתמשים</t>
-        </is>
-      </c>
-      <c r="C111" s="6" t="inlineStr"/>
-      <c r="D111" s="8" t="inlineStr"/>
-      <c r="E111" s="9" t="inlineStr"/>
-      <c r="F111" s="9" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
         <is>
-          <t>✅ In APK</t>
+          <t>✅ Live</t>
         </is>
       </c>
       <c r="B112" s="7" t="inlineStr">
         <is>
-          <t>כלול ב-APK המותקן — נראה לכל המשתמשים</t>
+          <t>פרוס ופעיל ב-Render — נראה לכל המשתמשים</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr"/>
@@ -3920,12 +3920,12 @@
     <row r="113">
       <c r="A113" s="6" t="inlineStr">
         <is>
-          <t>⏳ Next APK</t>
+          <t>✅ In APK</t>
         </is>
       </c>
       <c r="B113" s="7" t="inlineStr">
         <is>
-          <t>הקוד מוזג — דורש build ו-APK חדש</t>
+          <t>כלול ב-APK המותקן — נראה לכל המשתמשים</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr"/>
@@ -3936,12 +3936,12 @@
     <row r="114">
       <c r="A114" s="6" t="inlineStr">
         <is>
-          <t>✅ Live (OTA)</t>
+          <t>⏳ Next APK</t>
         </is>
       </c>
       <c r="B114" s="7" t="inlineStr">
         <is>
-          <t>שינוי JS — מועבר אוטומטית בהפעלה הבאה</t>
+          <t>הקוד מוזג — דורש build ו-APK חדש</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr"/>
@@ -3950,42 +3950,50 @@
       <c r="F114" s="9" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="21" t="inlineStr">
-        <is>
-          <t>⏳ ממתין ל-push</t>
-        </is>
-      </c>
-      <c r="B115" s="22" t="inlineStr">
-        <is>
-          <t>הקוד מוכן מקומית — טרם נדחף/נפרס</t>
-        </is>
-      </c>
+      <c r="A115" s="6" t="inlineStr">
+        <is>
+          <t>✅ Live (OTA)</t>
+        </is>
+      </c>
+      <c r="B115" s="7" t="inlineStr">
+        <is>
+          <t>שינוי JS — מועבר אוטומטית בהפעלה הבאה</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="inlineStr"/>
+      <c r="D115" s="8" t="inlineStr"/>
+      <c r="E115" s="9" t="inlineStr"/>
+      <c r="F115" s="9" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="21" t="inlineStr">
         <is>
+          <t>⏳ ממתין ל-push</t>
+        </is>
+      </c>
+      <c r="B116" s="22" t="inlineStr">
+        <is>
+          <t>הקוד מוכן מקומית — טרם נדחף/נפרס</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="21" t="inlineStr">
+        <is>
           <t>⏳ דורש build</t>
         </is>
       </c>
-      <c r="B116" s="22" t="inlineStr">
+      <c r="B117" s="22" t="inlineStr">
         <is>
           <t>שינוי נייטיב — OTA לא מספיק, צריך AAB/APK חדש</t>
         </is>
       </c>
     </row>
-    <row r="117"/>
-    <row r="118">
-      <c r="A118" s="23" t="inlineStr">
+    <row r="118"/>
+    <row r="119">
+      <c r="A119" s="23" t="inlineStr">
         <is>
           <t>סיכום Session 6-7</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="24" t="n"/>
-      <c r="B119" s="25" t="inlineStr">
-        <is>
-          <t>45  —  פריטים חדשים שנוספו (52-96)</t>
         </is>
       </c>
     </row>
@@ -3993,7 +4001,7 @@
       <c r="A120" s="24" t="n"/>
       <c r="B120" s="25" t="inlineStr">
         <is>
-          <t>44  —  חיים בייצור או ב-OTA</t>
+          <t>45  —  פריטים חדשים שנוספו (52-96)</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4009,7 @@
       <c r="A121" s="24" t="n"/>
       <c r="B121" s="25" t="inlineStr">
         <is>
-          <t>1  —  דורש build חדש: תמיכת טאבלט (פריט 68)</t>
+          <t>44  —  חיים בייצור או ב-OTA</t>
         </is>
       </c>
     </row>
@@ -4009,7 +4017,7 @@
       <c r="A122" s="24" t="n"/>
       <c r="B122" s="25" t="inlineStr">
         <is>
-          <t>11,781  —  שורות קוד שנקראו במלואן, 36 קבצים</t>
+          <t>1  —  דורש build חדש: תמיכת טאבלט (פריט 68)</t>
         </is>
       </c>
     </row>
@@ -4017,7 +4025,7 @@
       <c r="A123" s="24" t="n"/>
       <c r="B123" s="25" t="inlineStr">
         <is>
-          <t>29  —  חבילות בדיקה התנהגותיות עוברות</t>
+          <t>11,781  —  שורות קוד שנקראו במלואן, 36 קבצים</t>
         </is>
       </c>
     </row>
@@ -4025,16 +4033,24 @@
       <c r="A124" s="24" t="n"/>
       <c r="B124" s="25" t="inlineStr">
         <is>
+          <t>29  —  חבילות בדיקה התנהגותיות עוברות</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="24" t="n"/>
+      <c r="B125" s="25" t="inlineStr">
+        <is>
           <t>18  —  ראוטים בשרת · 316 מפתחות i18n × 4 שפות</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A97:F97"/>
+    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A59:F59"/>
     <mergeCell ref="A107:F107"/>
-    <mergeCell ref="A97:F97"/>
-    <mergeCell ref="A59:F59"/>
-    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BuddhaVest_Progress.xlsx
+++ b/BuddhaVest_Progress.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -59,6 +59,18 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -175,7 +187,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -276,6 +288,21 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -642,7 +669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F125"/>
+  <dimension ref="A1:F135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -663,7 +690,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Last updated: 2026-07-25  |  Session 7</t>
+          <t>Last updated: 2026-07-25  |  Session 8</t>
         </is>
       </c>
     </row>
@@ -2865,22 +2892,22 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="17" t="inlineStr">
+      <c r="A76" s="36" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="B76" s="18" t="inlineStr">
+      <c r="B76" s="37" t="inlineStr">
         <is>
           <t>הקלה חלקית לטאבלט (לא תמיכה מלאה)</t>
         </is>
       </c>
-      <c r="C76" s="17" t="inlineStr">
+      <c r="C76" s="36" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="D76" s="19" t="inlineStr">
+      <c r="D76" s="38" t="inlineStr">
         <is>
           <t>⚠️ חלקי</t>
         </is>
@@ -3832,9 +3859,34 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="33" t="inlineStr">
+      <c r="A107" s="39" t="inlineStr">
         <is>
           <t>98</t>
+        </is>
+      </c>
+      <c r="B107" s="40" t="inlineStr">
+        <is>
+          <t>מחוון "טוען" — הבאנר נראה תקוע</t>
+        </is>
+      </c>
+      <c r="C107" s="39" t="inlineStr">
+        <is>
+          <t>Frontend / UX</t>
+        </is>
+      </c>
+      <c r="D107" s="41" t="inlineStr">
+        <is>
+          <t>✅ Live (OTA)</t>
+        </is>
+      </c>
+      <c r="E107" s="42" t="inlineStr">
+        <is>
+          <t>HomeScreen.js, StockScreen.js, i18n.js</t>
+        </is>
+      </c>
+      <c r="F107" s="42" t="inlineStr">
+        <is>
+          <t>הבאנר "טוען נתונים עדכניים" היה טקסט סטטי — משתמש שראה אותו 40 שניות (Render מתעורר) לא ידע אם משהו קורה. נוסף ActivityIndicator לצד הטקסט, עם flexDirection הפוך ב-RTL. בנוסף: ב-StockScreen ה-state wakingUp חושב אך לא הוצג בכלל — קוד מת. 4 שפות.</t>
         </is>
       </c>
     </row>
@@ -3871,186 +3923,495 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="3" t="inlineStr">
-        <is>
-          <t>🔜  NOT YET STARTED</t>
-        </is>
-      </c>
-      <c r="B109" s="4" t="n"/>
-      <c r="C109" s="4" t="n"/>
-      <c r="D109" s="4" t="n"/>
-      <c r="E109" s="4" t="n"/>
-      <c r="F109" s="5" t="n"/>
+      <c r="A109" s="43" t="inlineStr">
+        <is>
+          <t>✅  Session 8 (2026-07-25): מטבע מסחר · מטבע דיווח · יחידות משנה</t>
+        </is>
+      </c>
     </row>
     <row r="110">
-      <c r="A110" s="6" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B110" s="4" t="n"/>
-      <c r="C110" s="4" t="n"/>
-      <c r="D110" s="4" t="n"/>
-      <c r="E110" s="4" t="n"/>
-      <c r="F110" s="5" t="n"/>
+      <c r="A110" s="39" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="B110" s="40" t="inlineStr">
+        <is>
+          <t>לונדון: מחיר גבוה פי 100</t>
+        </is>
+      </c>
+      <c r="C110" s="39" t="inlineStr">
+        <is>
+          <t>Backend / Bug Fix</t>
+        </is>
+      </c>
+      <c r="D110" s="41" t="inlineStr">
+        <is>
+          <t>⏳ ממתין ל-push</t>
+        </is>
+      </c>
+      <c r="E110" s="42" t="inlineStr">
+        <is>
+          <t>main.py</t>
+        </is>
+      </c>
+      <c r="F110" s="42" t="inlineStr">
+        <is>
+          <t>Yahoo מצטטת מניות בבורסת לונדון בפֶּנס ומסמנת זאת בשדה currency כ-"GBp" — באות p קטנה, כשהערך "GBP" פירושו לירות. הקוד הריץ .upper() לפני כל השוואה ומחק בכך את ההבחנה היחידה, כך שמניית Shell במחיר 2578.5 פנס היתה מוצגת "£2578.50" במקום "£25.79". אותה משפחת באג כמו האגורות בת"א, רק שלת"א היה טיפול ולונדון לא. הערה על רמת הראיה: הבאג אותר מקריאת הקוד ומתועד במקורות חיצוניים, אך לא הורץ מול ה-API החי — לסביבת הבדיקה אין יציאה לרשת כרגע. דורש אימות ידני על מניה בלונדון אחרי ה-push.</t>
+        </is>
+      </c>
     </row>
     <row r="111">
-      <c r="A111" s="10" t="inlineStr">
+      <c r="A111" s="39" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="B111" s="40" t="inlineStr">
+        <is>
+          <t>טבלת יחידות משנה במקום מקרה פרטי</t>
+        </is>
+      </c>
+      <c r="C111" s="39" t="inlineStr">
+        <is>
+          <t>Backend / Architecture</t>
+        </is>
+      </c>
+      <c r="D111" s="41" t="inlineStr">
+        <is>
+          <t>⏳ ממתין ל-push</t>
+        </is>
+      </c>
+      <c r="E111" s="42" t="inlineStr">
+        <is>
+          <t>main.py</t>
+        </is>
+      </c>
+      <c r="F111" s="42" t="inlineStr">
+        <is>
+          <t>_MINOR_UNIT ממפה GBp/GBX (פנס) · ZAc (סנט דרום-אפריקאי) · ILA (אגורות) אל המטבע הראשי והמחלק. המפתחות רגישים לאותיות גדולות/קטנות במכוון — "GBP" ו-"ZAR" חייבים להישאר בחוץ, כי המרה שלהם היתה יוצרת שגיאת פי-100 בכיוון ההפוך. 9 בדיקות רגישות-אותיות.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="39" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="B112" s="40" t="inlineStr">
+        <is>
+          <t>חלוקה רק לשדות של מחיר למניה</t>
+        </is>
+      </c>
+      <c r="C112" s="39" t="inlineStr">
+        <is>
+          <t>Backend / Accuracy</t>
+        </is>
+      </c>
+      <c r="D112" s="41" t="inlineStr">
+        <is>
+          <t>⏳ ממתין ל-push</t>
+        </is>
+      </c>
+      <c r="E112" s="42" t="inlineStr">
+        <is>
+          <t>main.py</t>
+        </is>
+      </c>
+      <c r="F112" s="42" t="inlineStr">
+        <is>
+          <t>_scale_price_fields מחלק מחיר נוכחי, שיא/שפל 52 שבועות וסדרת הגרף — ולא נוגע בשווי שוק, הכנסות, רווח נקי ומזומנים, שכבר מדווחים במטבע הראשי. האסימטריה הזו אומתה בת"א ותקפה גם בלונדון. הפונקציה משותפת לשני המסלולים כדי שלא יוכלו להיפרד שוב.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="39" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="B113" s="40" t="inlineStr">
+        <is>
+          <t>מכפילים שנגזרים ממחיר — דיכוי מורחב</t>
+        </is>
+      </c>
+      <c r="C113" s="39" t="inlineStr">
+        <is>
+          <t>Backend / Accuracy</t>
+        </is>
+      </c>
+      <c r="D113" s="41" t="inlineStr">
+        <is>
+          <t>⏳ ממתין ל-push</t>
+        </is>
+      </c>
+      <c r="E113" s="42" t="inlineStr">
+        <is>
+          <t>main.py</t>
+        </is>
+      </c>
+      <c r="F113" s="42" t="inlineStr">
+        <is>
+          <t>המכפילים ההיסטוריים (P/B, P/S, EV/EBITDA, Forward P/E) מחושבים מ-history()["Close"], שמגיע ביחידת המשנה, מול דוחות ביחידה הראשית. הדיכוי שהיה קיים ל-.TA בלבד הורחב ל-.L ול-.JO. false positive עולה גרף, false negative מפרסם מספר שגוי פי 100 — לכן הכיוון השמרני.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="39" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="B114" s="40" t="inlineStr">
+        <is>
+          <t>/quotes — אותו כלל כמו /analyze</t>
+        </is>
+      </c>
+      <c r="C114" s="39" t="inlineStr">
+        <is>
+          <t>Backend / Bug Fix</t>
+        </is>
+      </c>
+      <c r="D114" s="41" t="inlineStr">
+        <is>
+          <t>⏳ ממתין ל-push</t>
+        </is>
+      </c>
+      <c r="E114" s="42" t="inlineStr">
+        <is>
+          <t>main.py</t>
+        </is>
+      </c>
+      <c r="F114" s="42" t="inlineStr">
+        <is>
+          <t>רשימת המעקב צובעת מסך ראשון מ-/quotes ורק אז מחליפה בניתוח המלא. בלי אותו כלל, מניה בלונדון היתה מהבהבת מחיר פי-100 לרגע — בדיוק מה שקרה עם דלק (8173 במקום 81.73). כולל אתחול ccy_raw מחוץ ל-try, אחרת כשל רשת היה מפיל NameError.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="39" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="B115" s="40" t="inlineStr">
+        <is>
+          <t>סכום הדיבידנד עצמו</t>
+        </is>
+      </c>
+      <c r="C115" s="39" t="inlineStr">
+        <is>
+          <t>Backend / Bug Fix</t>
+        </is>
+      </c>
+      <c r="D115" s="41" t="inlineStr">
+        <is>
+          <t>⏳ ממתין ל-push</t>
+        </is>
+      </c>
+      <c r="E115" s="42" t="inlineStr">
+        <is>
+          <t>main.py</t>
+        </is>
+      </c>
+      <c r="F115" s="42" t="inlineStr">
+        <is>
+          <t>dividendRate מגיע במטבע ההצעה, כך שדיבידנד של 104 פנס היה מוצג "£104.00" במקום "£1.04". בנוסף הסימן היה ניחוש דו-כיווני ₪/$ בלבד — משלמת דיבידנד ביורו קיבלה סימן דולר באירוע בזמן שהכותרת הראתה €.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="39" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="B116" s="40" t="inlineStr">
+        <is>
+          <t>סימני מטבע — מקור אמת אחד</t>
+        </is>
+      </c>
+      <c r="C116" s="39" t="inlineStr">
+        <is>
+          <t>Frontend / Architecture</t>
+        </is>
+      </c>
+      <c r="D116" s="41" t="inlineStr">
+        <is>
+          <t>⏳ ממתין ל-push</t>
+        </is>
+      </c>
+      <c r="E116" s="42" t="inlineStr">
+        <is>
+          <t>utils/currency.js (חדש), StockScreen.js, WatchlistScreen.js</t>
+        </is>
+      </c>
+      <c r="F116" s="42" t="inlineStr">
+        <is>
+          <t>symbolFor היתה מועתקת ידנית בשני מסכים והספיקה כבר להתיישן: אף אחת מהן לא הכירה ין, ולונדון היתה דורשת לזכור לערוך את שתיהן. אותה מניה עם סימן אחד בשורת המעקב וסימן אחר בעמוד שלה הוא בדיוק הבאג שהקובץ הזה מונע. 22 מטבעות, מסונכרן מול _CCY_SYMBOL בשרת ונבדק צמד-צמד.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="39" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="B117" s="40" t="inlineStr">
+        <is>
+          <t>isUsd — השורה המשנית</t>
+        </is>
+      </c>
+      <c r="C117" s="39" t="inlineStr">
+        <is>
+          <t>Frontend / Bug Fix</t>
+        </is>
+      </c>
+      <c r="D117" s="41" t="inlineStr">
+        <is>
+          <t>⏳ ממתין ל-push</t>
+        </is>
+      </c>
+      <c r="E117" s="42" t="inlineStr">
+        <is>
+          <t>utils/currency.js, StockScreen.js, WatchlistScreen.js</t>
+        </is>
+      </c>
+      <c r="F117" s="42" t="inlineStr">
+        <is>
+          <t>שער ההמרה הוא דולר→מקומי, ולכן השורה המשנית תקפה רק כשהמחיר עצמו בדולר. הבדיקה "לא שקל" נתנה למניה ביורו לעבור והכפילה אותה בשער הדולר. בדיקה חיובית ל-USD במקום שלילית לשקל, בפונקציה אחת משותפת.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="39" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="B118" s="40" t="inlineStr">
+        <is>
+          <t>אימות חוצה-בורסות</t>
+        </is>
+      </c>
+      <c r="C118" s="39" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="D118" s="41" t="inlineStr">
+        <is>
+          <t>✅ הושלם</t>
+        </is>
+      </c>
+      <c r="E118" s="42" t="inlineStr">
+        <is>
+          <t>outputs/verify_minor_units.py, verify_multi_currency.js</t>
+        </is>
+      </c>
+      <c r="F118" s="42" t="inlineStr">
+        <is>
+          <t>חמש בורסות אומתו חי מול ה-API בסבבים קודמים: WMT ו-RIVN (דולר), ESLT.TA (נסחרת בשקל, מדווחת בדולר), DLEKG.TA (שקל), DHER.DE (יורו) — כל אחת חשפה מחלקה אחרת של באג. לונדון ויוהנסבורג נבדקו ביחידה בלבד (40 טענות: רגישות אותיות, שדות ריקים, אי-נגיעה בשווי שוק, סכום דיבידנד, התאמת סימנים שרת↔לקוח) ולא מול ה-API החי.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="39" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="B119" s="40" t="inlineStr">
+        <is>
+          <t>תיקון רתמת הבדיקות עצמה</t>
+        </is>
+      </c>
+      <c r="C119" s="39" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="D119" s="41" t="inlineStr">
+        <is>
+          <t>✅ הושלם</t>
+        </is>
+      </c>
+      <c r="E119" s="42" t="inlineStr">
+        <is>
+          <t>outputs/verify_analyzer_fixes.py, outputs/snapshots/</t>
+        </is>
+      </c>
+      <c r="F119" s="42" t="inlineStr">
+        <is>
+          <t>ההרצה דיווחה 5 כשלים שאף אחד מהם לא היה רגרסיה: 4 קבצים היו העתקי קוד מקור לבדיקת קומפילציה שהורצו בטעות כטסטים (הועברו ל-snapshots/), ואחד הכיל טענה שגויה שלי — היא בדקה תווית במקום את זוג הרבעונים שהלוגיקה הישנה קראה, והתווית יצאה נכונה במקרה. רתמה ששקרה בשני הכיוונים תוקנה.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="10" t="inlineStr">
         <is>
           <t>Legend</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="6" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="6" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
       </c>
-      <c r="B112" s="7" t="inlineStr">
+      <c r="B121" s="7" t="inlineStr">
         <is>
           <t>פרוס ופעיל ב-Render — נראה לכל המשתמשים</t>
         </is>
       </c>
-      <c r="C112" s="6" t="inlineStr"/>
-      <c r="D112" s="8" t="inlineStr"/>
-      <c r="E112" s="9" t="inlineStr"/>
-      <c r="F112" s="9" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="6" t="inlineStr">
+      <c r="C121" s="6" t="inlineStr"/>
+      <c r="D121" s="8" t="inlineStr"/>
+      <c r="E121" s="9" t="inlineStr"/>
+      <c r="F121" s="9" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="6" t="inlineStr">
         <is>
           <t>✅ In APK</t>
         </is>
       </c>
-      <c r="B113" s="7" t="inlineStr">
+      <c r="B122" s="7" t="inlineStr">
         <is>
           <t>כלול ב-APK המותקן — נראה לכל המשתמשים</t>
         </is>
       </c>
-      <c r="C113" s="6" t="inlineStr"/>
-      <c r="D113" s="8" t="inlineStr"/>
-      <c r="E113" s="9" t="inlineStr"/>
-      <c r="F113" s="9" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="6" t="inlineStr">
+      <c r="C122" s="6" t="inlineStr"/>
+      <c r="D122" s="8" t="inlineStr"/>
+      <c r="E122" s="9" t="inlineStr"/>
+      <c r="F122" s="9" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="6" t="inlineStr">
         <is>
           <t>⏳ Next APK</t>
         </is>
       </c>
-      <c r="B114" s="7" t="inlineStr">
+      <c r="B123" s="7" t="inlineStr">
         <is>
           <t>הקוד מוזג — דורש build ו-APK חדש</t>
         </is>
       </c>
-      <c r="C114" s="6" t="inlineStr"/>
-      <c r="D114" s="8" t="inlineStr"/>
-      <c r="E114" s="9" t="inlineStr"/>
-      <c r="F114" s="9" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="6" t="inlineStr">
+      <c r="C123" s="6" t="inlineStr"/>
+      <c r="D123" s="8" t="inlineStr"/>
+      <c r="E123" s="9" t="inlineStr"/>
+      <c r="F123" s="9" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="6" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
       </c>
-      <c r="B115" s="7" t="inlineStr">
+      <c r="B124" s="7" t="inlineStr">
         <is>
           <t>שינוי JS — מועבר אוטומטית בהפעלה הבאה</t>
         </is>
       </c>
-      <c r="C115" s="6" t="inlineStr"/>
-      <c r="D115" s="8" t="inlineStr"/>
-      <c r="E115" s="9" t="inlineStr"/>
-      <c r="F115" s="9" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="21" t="inlineStr">
+      <c r="C124" s="6" t="inlineStr"/>
+      <c r="D124" s="8" t="inlineStr"/>
+      <c r="E124" s="9" t="inlineStr"/>
+      <c r="F124" s="9" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="21" t="inlineStr">
         <is>
           <t>⏳ ממתין ל-push</t>
         </is>
       </c>
-      <c r="B116" s="22" t="inlineStr">
+      <c r="B125" s="22" t="inlineStr">
         <is>
           <t>הקוד מוכן מקומית — טרם נדחף/נפרס</t>
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="21" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="21" t="inlineStr">
         <is>
           <t>⏳ דורש build</t>
         </is>
       </c>
-      <c r="B117" s="22" t="inlineStr">
+      <c r="B126" s="22" t="inlineStr">
         <is>
           <t>שינוי נייטיב — OTA לא מספיק, צריך AAB/APK חדש</t>
         </is>
       </c>
     </row>
-    <row r="118"/>
-    <row r="119">
-      <c r="A119" s="23" t="inlineStr">
-        <is>
-          <t>סיכום Session 6-7</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="24" t="n"/>
-      <c r="B120" s="25" t="inlineStr">
-        <is>
-          <t>45  —  פריטים חדשים שנוספו (52-96)</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="24" t="n"/>
-      <c r="B121" s="25" t="inlineStr">
-        <is>
-          <t>44  —  חיים בייצור או ב-OTA</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="24" t="n"/>
-      <c r="B122" s="25" t="inlineStr">
-        <is>
-          <t>1  —  דורש build חדש: תמיכת טאבלט (פריט 68)</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="24" t="n"/>
-      <c r="B123" s="25" t="inlineStr">
-        <is>
-          <t>11,781  —  שורות קוד שנקראו במלואן, 36 קבצים</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="24" t="n"/>
-      <c r="B124" s="25" t="inlineStr">
-        <is>
-          <t>29  —  חבילות בדיקה התנהגותיות עוברות</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="24" t="n"/>
-      <c r="B125" s="25" t="inlineStr">
-        <is>
-          <t>18  —  ראוטים בשרת · 316 מפתחות i18n × 4 שפות</t>
+    <row r="128">
+      <c r="A128" s="23" t="inlineStr">
+        <is>
+          <t>סיכום Session 6-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="24" t="n"/>
+      <c r="B129" s="25" t="inlineStr">
+        <is>
+          <t>58  —  פריטים חדשים שנוספו (52-109)</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="24" t="n"/>
+      <c r="B130" s="25" t="inlineStr">
+        <is>
+          <t>48  —  חיים בייצור או ב-OTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="24" t="n"/>
+      <c r="B131" s="25" t="inlineStr">
+        <is>
+          <t>8  —  מוכנים מקומית, ממתינים ל-push (100-107)</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="24" t="n"/>
+      <c r="B132" s="25" t="inlineStr">
+        <is>
+          <t>2  —  פתוחים: פריסת טאבלט אמיתית (99) · הגשה ל-Play (19)</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="24" t="n"/>
+      <c r="B133" s="25" t="inlineStr">
+        <is>
+          <t>5  —  בורסות שאומתו חי · 2 נוספות (לונדון, יוהנסבורג) ביחידה בלבד</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="24" t="n"/>
+      <c r="B134" s="25" t="inlineStr">
+        <is>
+          <t>48  —  חבילות בדיקה התנהגותיות עוברות (48/48)</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>18  —  ראוטים בשרת · 324 מפתחות i18n × 4 שפות</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A97:F97"/>
+    <mergeCell ref="A109:F109"/>
+    <mergeCell ref="A59:F59"/>
     <mergeCell ref="A25:F25"/>
-    <mergeCell ref="A59:F59"/>
-    <mergeCell ref="A107:F107"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BuddhaVest_Progress.xlsx
+++ b/BuddhaVest_Progress.xlsx
@@ -3947,7 +3947,7 @@
       </c>
       <c r="D110" s="41" t="inlineStr">
         <is>
-          <t>⏳ ממתין ל-push</t>
+          <t>✅ Live</t>
         </is>
       </c>
       <c r="E110" s="42" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="F110" s="42" t="inlineStr">
         <is>
-          <t>Yahoo מצטטת מניות בבורסת לונדון בפֶּנס ומסמנת זאת בשדה currency כ-"GBp" — באות p קטנה, כשהערך "GBP" פירושו לירות. הקוד הריץ .upper() לפני כל השוואה ומחק בכך את ההבחנה היחידה, כך שמניית Shell במחיר 2578.5 פנס היתה מוצגת "£2578.50" במקום "£25.79". אותה משפחת באג כמו האגורות בת"א, רק שלת"א היה טיפול ולונדון לא. הערה על רמת הראיה: הבאג אותר מקריאת הקוד ומתועד במקורות חיצוניים, אך לא הורץ מול ה-API החי — לסביבת הבדיקה אין יציאה לרשת כרגע. דורש אימות ידני על מניה בלונדון אחרי ה-push.</t>
+          <t>Yahoo מצטטת מניות בבורסת לונדון בפֶּנס ומסמנת זאת בשדה currency כ-"GBp" — באות p קטנה, כשהערך "GBP" פירושו לירות. הקוד הריץ .upper() לפני כל השוואה ומחק בכך את ההבחנה היחידה. אומת חי לפני ולאחר: SHEL.L החזירה 3262.07 עם price_currency "USD" (האפליקציה הציגה "$3262.07"), ולאחר הפריסה 32.62 עם "GBP". גם BP.L 531.7→5.32 ו-ULVR.L 5027→50.27. אותה משפחת באג כמו האגורות בת"א, רק שלת"א היה טיפול ולונדון לא.</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="D111" s="41" t="inlineStr">
         <is>
-          <t>⏳ ממתין ל-push</t>
+          <t>✅ Live</t>
         </is>
       </c>
       <c r="E111" s="42" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="D112" s="41" t="inlineStr">
         <is>
-          <t>⏳ ממתין ל-push</t>
+          <t>✅ Live</t>
         </is>
       </c>
       <c r="E112" s="42" t="inlineStr">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="D113" s="41" t="inlineStr">
         <is>
-          <t>⏳ ממתין ל-push</t>
+          <t>✅ Live</t>
         </is>
       </c>
       <c r="E113" s="42" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="D114" s="41" t="inlineStr">
         <is>
-          <t>⏳ ממתין ל-push</t>
+          <t>✅ Live</t>
         </is>
       </c>
       <c r="E114" s="42" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="D115" s="41" t="inlineStr">
         <is>
-          <t>⏳ ממתין ל-push</t>
+          <t>✅ Live</t>
         </is>
       </c>
       <c r="E115" s="42" t="inlineStr">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="D116" s="41" t="inlineStr">
         <is>
-          <t>⏳ ממתין ל-push</t>
+          <t>✅ Live (OTA)</t>
         </is>
       </c>
       <c r="E116" s="42" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="D117" s="41" t="inlineStr">
         <is>
-          <t>⏳ ממתין ל-push</t>
+          <t>✅ Live (OTA)</t>
         </is>
       </c>
       <c r="E117" s="42" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="F118" s="42" t="inlineStr">
         <is>
-          <t>חמש בורסות אומתו חי מול ה-API בסבבים קודמים: WMT ו-RIVN (דולר), ESLT.TA (נסחרת בשקל, מדווחת בדולר), DLEKG.TA (שקל), DHER.DE (יורו) — כל אחת חשפה מחלקה אחרת של באג. לונדון ויוהנסבורג נבדקו ביחידה בלבד (40 טענות: רגישות אותיות, שדות ריקים, אי-נגיעה בשווי שוק, סכום דיבידנד, התאמת סימנים שרת↔לקוח) ולא מול ה-API החי.</t>
+          <t>שבע בורסות אומתו חי מול ה-API: WMT ו-RIVN (דולר), ESLT.TA (נסחרת בשקל, מדווחת בדולר), DLEKG.TA (שקל), DHER.DE (יורו), ולאחר הפריסה SHEL.L · BP.L · ULVR.L (לונדון, פנס). בקריאה אחת אחרי הפריסה: SHEL.L £32.62 · BP.L £5.32 · ULVR.L £50.27 · WMT $114.96 · DHER.DE €37.88 · DLEKG.TA ₪83.51 — כל אחת עם המטבע הנכון שלה. יוהנסבורג (ZAc) מכוסה ביחידה בלבד, אין מניה לבדוק. בנוסף 40 טענות יחידה: רגישות אותיות, שדות ריקים, אי-נגיעה בשווי שוק, סכום דיבידנד, התאמת סימנים שרת↔לקוח.</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       <c r="A130" s="24" t="n"/>
       <c r="B130" s="25" t="inlineStr">
         <is>
-          <t>48  —  חיים בייצור או ב-OTA</t>
+          <t>56  —  חיים בייצור או ב-OTA</t>
         </is>
       </c>
     </row>
@@ -4371,7 +4371,7 @@
       <c r="A131" s="24" t="n"/>
       <c r="B131" s="25" t="inlineStr">
         <is>
-          <t>8  —  מוכנים מקומית, ממתינים ל-push (100-107)</t>
+          <t>0  —  ממתינים ל-push: הכל נפרס (commit 91ee6d3)</t>
         </is>
       </c>
     </row>
@@ -4387,7 +4387,7 @@
       <c r="A133" s="24" t="n"/>
       <c r="B133" s="25" t="inlineStr">
         <is>
-          <t>5  —  בורסות שאומתו חי · 2 נוספות (לונדון, יוהנסבורג) ביחידה בלבד</t>
+          <t>8  —  בורסות שאומתו חי (NYSE · TASE · XETRA · LSE) · JSE ביחידה בלבד</t>
         </is>
       </c>
     </row>

--- a/BuddhaVest_Progress.xlsx
+++ b/BuddhaVest_Progress.xlsx
@@ -187,7 +187,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -303,6 +303,27 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -669,7 +690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F135"/>
+  <dimension ref="A1:F139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -690,7 +711,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Last updated: 2026-07-25  |  Session 8</t>
+          <t>Last updated: 2026-08-03  |  Session 9</t>
         </is>
       </c>
     </row>
@@ -4250,136 +4271,233 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="10" t="inlineStr">
+      <c r="A120" s="44" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="B120" s="45" t="inlineStr">
+        <is>
+          <t>עמוד הפרטיות הוגש מהמטמון</t>
+        </is>
+      </c>
+      <c r="C120" s="44" t="inlineStr">
+        <is>
+          <t>Backend / Legal / Bug Fix</t>
+        </is>
+      </c>
+      <c r="D120" s="46" t="inlineStr">
+        <is>
+          <t>⏳ ממתין ל-push</t>
+        </is>
+      </c>
+      <c r="E120" s="47" t="inlineStr">
+        <is>
+          <t>main.py</t>
+        </is>
+      </c>
+      <c r="F120" s="47" t="inlineStr">
+        <is>
+          <t>המידלוור שמונע מטמון החריג במפורש את /privacy, מתוך הנחה שדף משפטי סטטי כדאי לשמור. ההנחה היתה הפוכה. אומת חי: הכתובת הרגילה החזירה את הנוסח הישן ("the watchlist is never transmitted to our servers") בעוד שאותה כתובת עם פרמטר שאילתה חדש החזירה את המתוקן — כלומר הקוד תקין והתשובה נתקעה במטמון. גוגל משווה את הדף להצהרת Data Safety, כך שעותק ישן היה יוצר סתירה מולם. החריג הוסר; כל נתיב מקבל no-store.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="48" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="B121" s="49" t="inlineStr">
+        <is>
+          <t>טופס Data Safety מולא</t>
+        </is>
+      </c>
+      <c r="C121" s="48" t="inlineStr">
+        <is>
+          <t>Store / Legal</t>
+        </is>
+      </c>
+      <c r="D121" s="50" t="inlineStr">
+        <is>
+          <t>✅ הושלם</t>
+        </is>
+      </c>
+      <c r="E121" s="42" t="inlineStr">
+        <is>
+          <t>data-safety-answers.html</t>
+        </is>
+      </c>
+      <c r="F121" s="42" t="inlineStr">
+        <is>
+          <t>5 סוגי נתונים הוצהרו: אינטראקציות באפליקציה · היסטוריית חיפוש · תוכן שנוצר על ידי משתמשים · גלישה באינטרנט · מזהה המכשיר. כולם נאספים, אף אחד לא משותף, אף אחד לא זמני, מטרה יחידה פונקציונליות. לא הוצהרו: מידע אישי, פיננסי, מיקום, בריאות, אנשי קשר, קראש-לוגים — כל אחד אומת מול המניפסט ומול 19 התלויות. יומן המחקר לא הוצהר כי buddhavest_journal אף פעם לא מופיע בתוך fetch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="48" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="B122" s="49" t="inlineStr">
+        <is>
+          <t>צ׳קליסט טפסי Play Console</t>
+        </is>
+      </c>
+      <c r="C122" s="48" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="D122" s="50" t="inlineStr">
+        <is>
+          <t>✅ הושלם</t>
+        </is>
+      </c>
+      <c r="E122" s="42" t="inlineStr">
+        <is>
+          <t>play-console-checklist.html</t>
+        </is>
+      </c>
+      <c r="F122" s="42" t="inlineStr">
+        <is>
+          <t>תשובות לכל סעיפי App content שנותרו: גישה לאפליקציה, מודעות, דירוג תוכן, קהל יעד, תכונות פיננסיות, אפליקציית חדשות, בריאות, ממשלה, הרשאות רגישות. שתי ההצהרות הרגישות באפליקציה מסוג זה — "תכונות פיננסיות" ו"אפליקציית חדשות" — מנומקות בנפרד.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="44" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="B123" s="45" t="inlineStr">
+        <is>
+          <t>צילומי מסך לחנות</t>
+        </is>
+      </c>
+      <c r="C123" s="44" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="D123" s="46" t="inlineStr">
+        <is>
+          <t>🔜 לא התחיל</t>
+        </is>
+      </c>
+      <c r="E123" s="47" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F123" s="47" t="inlineStr">
+        <is>
+          <t>הפער היחיד שנותר בדף החנות. גוגל דורשת לפחות 2 צילומי טלפון, מומלץ 4-8. אייקון ו-feature graphic כבר קיימים במידות הנכונות (1024x1024 ו-1024x500). מדריך מוכן ב-מדריך-צילומי-מסך-לחנות.html.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="10" t="inlineStr">
         <is>
           <t>Legend</t>
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="6" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="6" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
       </c>
-      <c r="B121" s="7" t="inlineStr">
+      <c r="B125" s="7" t="inlineStr">
         <is>
           <t>פרוס ופעיל ב-Render — נראה לכל המשתמשים</t>
         </is>
       </c>
-      <c r="C121" s="6" t="inlineStr"/>
-      <c r="D121" s="8" t="inlineStr"/>
-      <c r="E121" s="9" t="inlineStr"/>
-      <c r="F121" s="9" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="6" t="inlineStr">
+      <c r="C125" s="6" t="inlineStr"/>
+      <c r="D125" s="8" t="inlineStr"/>
+      <c r="E125" s="9" t="inlineStr"/>
+      <c r="F125" s="9" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="6" t="inlineStr">
         <is>
           <t>✅ In APK</t>
         </is>
       </c>
-      <c r="B122" s="7" t="inlineStr">
+      <c r="B126" s="7" t="inlineStr">
         <is>
           <t>כלול ב-APK המותקן — נראה לכל המשתמשים</t>
         </is>
       </c>
-      <c r="C122" s="6" t="inlineStr"/>
-      <c r="D122" s="8" t="inlineStr"/>
-      <c r="E122" s="9" t="inlineStr"/>
-      <c r="F122" s="9" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="6" t="inlineStr">
+      <c r="C126" s="6" t="inlineStr"/>
+      <c r="D126" s="8" t="inlineStr"/>
+      <c r="E126" s="9" t="inlineStr"/>
+      <c r="F126" s="9" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="6" t="inlineStr">
         <is>
           <t>⏳ Next APK</t>
         </is>
       </c>
-      <c r="B123" s="7" t="inlineStr">
+      <c r="B127" s="7" t="inlineStr">
         <is>
           <t>הקוד מוזג — דורש build ו-APK חדש</t>
         </is>
       </c>
-      <c r="C123" s="6" t="inlineStr"/>
-      <c r="D123" s="8" t="inlineStr"/>
-      <c r="E123" s="9" t="inlineStr"/>
-      <c r="F123" s="9" t="inlineStr"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="6" t="inlineStr">
+      <c r="C127" s="6" t="inlineStr"/>
+      <c r="D127" s="8" t="inlineStr"/>
+      <c r="E127" s="9" t="inlineStr"/>
+      <c r="F127" s="9" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="6" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
       </c>
-      <c r="B124" s="7" t="inlineStr">
+      <c r="B128" s="7" t="inlineStr">
         <is>
           <t>שינוי JS — מועבר אוטומטית בהפעלה הבאה</t>
         </is>
       </c>
-      <c r="C124" s="6" t="inlineStr"/>
-      <c r="D124" s="8" t="inlineStr"/>
-      <c r="E124" s="9" t="inlineStr"/>
-      <c r="F124" s="9" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="21" t="inlineStr">
+      <c r="C128" s="6" t="inlineStr"/>
+      <c r="D128" s="8" t="inlineStr"/>
+      <c r="E128" s="9" t="inlineStr"/>
+      <c r="F128" s="9" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="21" t="inlineStr">
         <is>
           <t>⏳ ממתין ל-push</t>
         </is>
       </c>
-      <c r="B125" s="22" t="inlineStr">
+      <c r="B129" s="22" t="inlineStr">
         <is>
           <t>הקוד מוכן מקומית — טרם נדחף/נפרס</t>
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="21" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="21" t="inlineStr">
         <is>
           <t>⏳ דורש build</t>
         </is>
       </c>
-      <c r="B126" s="22" t="inlineStr">
+      <c r="B130" s="22" t="inlineStr">
         <is>
           <t>שינוי נייטיב — OTA לא מספיק, צריך AAB/APK חדש</t>
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="23" t="inlineStr">
+    <row r="131"/>
+    <row r="132">
+      <c r="A132" s="23" t="inlineStr">
         <is>
           <t>סיכום Session 6-8</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="24" t="n"/>
-      <c r="B129" s="25" t="inlineStr">
-        <is>
-          <t>58  —  פריטים חדשים שנוספו (52-109)</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="24" t="n"/>
-      <c r="B130" s="25" t="inlineStr">
-        <is>
-          <t>56  —  חיים בייצור או ב-OTA</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="24" t="n"/>
-      <c r="B131" s="25" t="inlineStr">
-        <is>
-          <t>0  —  ממתינים ל-push: הכל נפרס (commit 91ee6d3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="24" t="n"/>
-      <c r="B132" s="25" t="inlineStr">
-        <is>
-          <t>2  —  פתוחים: פריסת טאבלט אמיתית (99) · הגשה ל-Play (19)</t>
         </is>
       </c>
     </row>
@@ -4387,7 +4505,7 @@
       <c r="A133" s="24" t="n"/>
       <c r="B133" s="25" t="inlineStr">
         <is>
-          <t>8  —  בורסות שאומתו חי (NYSE · TASE · XETRA · LSE) · JSE ביחידה בלבד</t>
+          <t>58  —  פריטים חדשים שנוספו (52-109)</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4513,44 @@
       <c r="A134" s="24" t="n"/>
       <c r="B134" s="25" t="inlineStr">
         <is>
+          <t>56  —  חיים בייצור או ב-OTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="24" t="n"/>
+      <c r="B135" s="25" t="inlineStr">
+        <is>
+          <t>0  —  ממתינים ל-push: הכל נפרס (commit 91ee6d3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="24" t="n"/>
+      <c r="B136" s="25" t="inlineStr">
+        <is>
+          <t>2  —  פתוחים: פריסת טאבלט אמיתית (99) · הגשה ל-Play (19)</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="24" t="n"/>
+      <c r="B137" s="25" t="inlineStr">
+        <is>
+          <t>8  —  בורסות שאומתו חי (NYSE · TASE · XETRA · LSE) · JSE ביחידה בלבד</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="24" t="n"/>
+      <c r="B138" s="25" t="inlineStr">
+        <is>
           <t>48  —  חבילות בדיקה התנהגותיות עוברות (48/48)</t>
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="B135" t="inlineStr">
+    <row r="139">
+      <c r="B139" t="inlineStr">
         <is>
           <t>18  —  ראוטים בשרת · 324 מפתחות i18n × 4 שפות</t>
         </is>

--- a/BuddhaVest_Progress.xlsx
+++ b/BuddhaVest_Progress.xlsx
@@ -3880,22 +3880,22 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="39" t="inlineStr">
+      <c r="A107" s="48" t="inlineStr">
         <is>
           <t>98</t>
         </is>
       </c>
-      <c r="B107" s="40" t="inlineStr">
+      <c r="B107" s="49" t="inlineStr">
         <is>
           <t>מחוון "טוען" — הבאנר נראה תקוע</t>
         </is>
       </c>
-      <c r="C107" s="39" t="inlineStr">
+      <c r="C107" s="48" t="inlineStr">
         <is>
           <t>Frontend / UX</t>
         </is>
       </c>
-      <c r="D107" s="41" t="inlineStr">
+      <c r="D107" s="50" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -3951,22 +3951,22 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="39" t="inlineStr">
+      <c r="A110" s="48" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="B110" s="40" t="inlineStr">
+      <c r="B110" s="49" t="inlineStr">
         <is>
           <t>לונדון: מחיר גבוה פי 100</t>
         </is>
       </c>
-      <c r="C110" s="39" t="inlineStr">
+      <c r="C110" s="48" t="inlineStr">
         <is>
           <t>Backend / Bug Fix</t>
         </is>
       </c>
-      <c r="D110" s="41" t="inlineStr">
+      <c r="D110" s="50" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
@@ -3983,22 +3983,22 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="39" t="inlineStr">
+      <c r="A111" s="48" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="B111" s="40" t="inlineStr">
+      <c r="B111" s="49" t="inlineStr">
         <is>
           <t>טבלת יחידות משנה במקום מקרה פרטי</t>
         </is>
       </c>
-      <c r="C111" s="39" t="inlineStr">
+      <c r="C111" s="48" t="inlineStr">
         <is>
           <t>Backend / Architecture</t>
         </is>
       </c>
-      <c r="D111" s="41" t="inlineStr">
+      <c r="D111" s="50" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
@@ -4015,22 +4015,22 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="39" t="inlineStr">
+      <c r="A112" s="48" t="inlineStr">
         <is>
           <t>102</t>
         </is>
       </c>
-      <c r="B112" s="40" t="inlineStr">
+      <c r="B112" s="49" t="inlineStr">
         <is>
           <t>חלוקה רק לשדות של מחיר למניה</t>
         </is>
       </c>
-      <c r="C112" s="39" t="inlineStr">
+      <c r="C112" s="48" t="inlineStr">
         <is>
           <t>Backend / Accuracy</t>
         </is>
       </c>
-      <c r="D112" s="41" t="inlineStr">
+      <c r="D112" s="50" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
@@ -4047,22 +4047,22 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="39" t="inlineStr">
+      <c r="A113" s="48" t="inlineStr">
         <is>
           <t>103</t>
         </is>
       </c>
-      <c r="B113" s="40" t="inlineStr">
+      <c r="B113" s="49" t="inlineStr">
         <is>
           <t>מכפילים שנגזרים ממחיר — דיכוי מורחב</t>
         </is>
       </c>
-      <c r="C113" s="39" t="inlineStr">
+      <c r="C113" s="48" t="inlineStr">
         <is>
           <t>Backend / Accuracy</t>
         </is>
       </c>
-      <c r="D113" s="41" t="inlineStr">
+      <c r="D113" s="50" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
@@ -4079,22 +4079,22 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="39" t="inlineStr">
+      <c r="A114" s="48" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="B114" s="40" t="inlineStr">
+      <c r="B114" s="49" t="inlineStr">
         <is>
           <t>/quotes — אותו כלל כמו /analyze</t>
         </is>
       </c>
-      <c r="C114" s="39" t="inlineStr">
+      <c r="C114" s="48" t="inlineStr">
         <is>
           <t>Backend / Bug Fix</t>
         </is>
       </c>
-      <c r="D114" s="41" t="inlineStr">
+      <c r="D114" s="50" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
@@ -4111,22 +4111,22 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="39" t="inlineStr">
+      <c r="A115" s="48" t="inlineStr">
         <is>
           <t>105</t>
         </is>
       </c>
-      <c r="B115" s="40" t="inlineStr">
+      <c r="B115" s="49" t="inlineStr">
         <is>
           <t>סכום הדיבידנד עצמו</t>
         </is>
       </c>
-      <c r="C115" s="39" t="inlineStr">
+      <c r="C115" s="48" t="inlineStr">
         <is>
           <t>Backend / Bug Fix</t>
         </is>
       </c>
-      <c r="D115" s="41" t="inlineStr">
+      <c r="D115" s="50" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
@@ -4143,22 +4143,22 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="39" t="inlineStr">
+      <c r="A116" s="48" t="inlineStr">
         <is>
           <t>106</t>
         </is>
       </c>
-      <c r="B116" s="40" t="inlineStr">
+      <c r="B116" s="49" t="inlineStr">
         <is>
           <t>סימני מטבע — מקור אמת אחד</t>
         </is>
       </c>
-      <c r="C116" s="39" t="inlineStr">
+      <c r="C116" s="48" t="inlineStr">
         <is>
           <t>Frontend / Architecture</t>
         </is>
       </c>
-      <c r="D116" s="41" t="inlineStr">
+      <c r="D116" s="50" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -4175,22 +4175,22 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="39" t="inlineStr">
+      <c r="A117" s="48" t="inlineStr">
         <is>
           <t>107</t>
         </is>
       </c>
-      <c r="B117" s="40" t="inlineStr">
+      <c r="B117" s="49" t="inlineStr">
         <is>
           <t>isUsd — השורה המשנית</t>
         </is>
       </c>
-      <c r="C117" s="39" t="inlineStr">
+      <c r="C117" s="48" t="inlineStr">
         <is>
           <t>Frontend / Bug Fix</t>
         </is>
       </c>
-      <c r="D117" s="41" t="inlineStr">
+      <c r="D117" s="50" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
@@ -4207,22 +4207,22 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="39" t="inlineStr">
+      <c r="A118" s="48" t="inlineStr">
         <is>
           <t>108</t>
         </is>
       </c>
-      <c r="B118" s="40" t="inlineStr">
+      <c r="B118" s="49" t="inlineStr">
         <is>
           <t>אימות חוצה-בורסות</t>
         </is>
       </c>
-      <c r="C118" s="39" t="inlineStr">
+      <c r="C118" s="48" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="D118" s="41" t="inlineStr">
+      <c r="D118" s="50" t="inlineStr">
         <is>
           <t>✅ הושלם</t>
         </is>
@@ -4239,22 +4239,22 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="39" t="inlineStr">
+      <c r="A119" s="48" t="inlineStr">
         <is>
           <t>109</t>
         </is>
       </c>
-      <c r="B119" s="40" t="inlineStr">
+      <c r="B119" s="49" t="inlineStr">
         <is>
           <t>תיקון רתמת הבדיקות עצמה</t>
         </is>
       </c>
-      <c r="C119" s="39" t="inlineStr">
+      <c r="C119" s="48" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="D119" s="41" t="inlineStr">
+      <c r="D119" s="50" t="inlineStr">
         <is>
           <t>✅ הושלם</t>
         </is>
@@ -4303,34 +4303,34 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="48" t="inlineStr">
+      <c r="A121" s="44" t="inlineStr">
         <is>
           <t>111</t>
         </is>
       </c>
-      <c r="B121" s="49" t="inlineStr">
+      <c r="B121" s="45" t="inlineStr">
         <is>
           <t>טופס Data Safety מולא</t>
         </is>
       </c>
-      <c r="C121" s="48" t="inlineStr">
+      <c r="C121" s="44" t="inlineStr">
         <is>
           <t>Store / Legal</t>
         </is>
       </c>
-      <c r="D121" s="50" t="inlineStr">
-        <is>
-          <t>✅ הושלם</t>
-        </is>
-      </c>
-      <c r="E121" s="42" t="inlineStr">
+      <c r="D121" s="46" t="inlineStr">
+        <is>
+          <t>⏳ טיוטה — לא הוגש</t>
+        </is>
+      </c>
+      <c r="E121" s="47" t="inlineStr">
         <is>
           <t>data-safety-answers.html</t>
         </is>
       </c>
-      <c r="F121" s="42" t="inlineStr">
-        <is>
-          <t>5 סוגי נתונים הוצהרו: אינטראקציות באפליקציה · היסטוריית חיפוש · תוכן שנוצר על ידי משתמשים · גלישה באינטרנט · מזהה המכשיר. כולם נאספים, אף אחד לא משותף, אף אחד לא זמני, מטרה יחידה פונקציונליות. לא הוצהרו: מידע אישי, פיננסי, מיקום, בריאות, אנשי קשר, קראש-לוגים — כל אחד אומת מול המניפסט ומול 19 התלויות. יומן המחקר לא הוצהר כי buddhavest_journal אף פעם לא מופיע בתוך fetch.</t>
+      <c r="F121" s="47" t="inlineStr">
+        <is>
+          <t>התשובות מולאו ונשמרו כטיוטה, אבל הטופס מעולם לא הוגש — לוח הבקרה של Play מציג עיגול ריק ליד "אבטחת נתונים". אומת ישירות בקונסולה: הטופס נפתח בשלב 1 מתוך 5 עם כפתור "שמירת טיוטה" פעיל, והתשובות של שלב 2 (כן לאיסוף, כן להצפנה) שמורות. צריך לעבור שלבים 3-4-5 וללחוץ שליחה במסך התצוגה המקדימה. 5 סוגי נתונים שהוצהרו: אינטראקציות · חיפוש · תוכן משתמש · גלישה · מזהה מכשיר.</t>
         </is>
       </c>
     </row>
@@ -4493,7 +4493,6 @@
         </is>
       </c>
     </row>
-    <row r="131"/>
     <row r="132">
       <c r="A132" s="23" t="inlineStr">
         <is>

--- a/BuddhaVest_Progress.xlsx
+++ b/BuddhaVest_Progress.xlsx
@@ -187,7 +187,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -323,6 +323,15 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -690,7 +699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F139"/>
+  <dimension ref="A1:F145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4271,285 +4280,478 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="44" t="inlineStr">
+      <c r="A120" s="51" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="B120" s="52" t="inlineStr">
+        <is>
+          <t>AMD: אפס גרפים בכל המכפילים</t>
+        </is>
+      </c>
+      <c r="C120" s="51" t="inlineStr">
+        <is>
+          <t>Backend / Bug Fix</t>
+        </is>
+      </c>
+      <c r="D120" s="53" t="inlineStr">
+        <is>
+          <t>⏳ ממתין ל-push</t>
+        </is>
+      </c>
+      <c r="E120" s="47" t="inlineStr">
+        <is>
+          <t>main.py</t>
+        </is>
+      </c>
+      <c r="F120" s="47" t="inlineStr">
+        <is>
+          <t>החישוב ההיסטורי קרא את מספר המניות רק מ-info["sharesOutstanding"], ויאהו לא מחזירה את השדה הזה ל-AMD. שורה אחת — if not shares — הפילה את כל הענף, וכל המכפילים חזרו ריקים: P/B, P/S, EV/EBITDA ו-Forward P/E. אומת חי: /metric-history/AMD/price_to_book ו-/ev_to_ebitda שניהם quarterly:[] בעוד WMT מחזירה 43 נקודות. הנתונים היו קיימים כל הזמן — /financials/AMD מכיל Ordinary Shares Number 1,630,410,843 בכל דוח.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="51" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="B121" s="52" t="inlineStr">
+        <is>
+          <t>אותו באג במקום שני: רכישות חוזרות</t>
+        </is>
+      </c>
+      <c r="C121" s="51" t="inlineStr">
+        <is>
+          <t>Backend / Bug Fix</t>
+        </is>
+      </c>
+      <c r="D121" s="53" t="inlineStr">
+        <is>
+          <t>⏳ ממתין ל-push</t>
+        </is>
+      </c>
+      <c r="E121" s="47" t="inlineStr">
+        <is>
+          <t>main.py</t>
+        </is>
+      </c>
+      <c r="F121" s="47" t="inlineStr">
+        <is>
+          <t>ענף ה-buyback הכיל עותק שני של אותה שורה, כך שגם תשואת הרכישות החוזרות של AMD היתה ריקה. נמצא רק בגלל החיפוש היזום אחרי מופעים נוספים, לא מדיווח משתמש.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="51" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="B122" s="52" t="inlineStr">
+        <is>
+          <t>מקור אחד לספירת מניות</t>
+        </is>
+      </c>
+      <c r="C122" s="51" t="inlineStr">
+        <is>
+          <t>Backend / Architecture</t>
+        </is>
+      </c>
+      <c r="D122" s="53" t="inlineStr">
+        <is>
+          <t>⏳ ממתין ל-push</t>
+        </is>
+      </c>
+      <c r="E122" s="47" t="inlineStr">
+        <is>
+          <t>main.py</t>
+        </is>
+      </c>
+      <c r="F122" s="47" t="inlineStr">
+        <is>
+          <t>_shares_lookup ברמת המודול מחליף את שני העותקים: Ordinary Shares Number ← Share Issued ← Diluted Average Shares ← Basic Average Shares ← השדה ב-info. שני הענפים קוראים לאותה פונקציה, כך שהם לא יכולים להתפצל שוב. 18 בדיקות יחידה.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="51" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="B123" s="52" t="inlineStr">
+        <is>
+          <t>ספירת מניות לפי תאריך</t>
+        </is>
+      </c>
+      <c r="C123" s="51" t="inlineStr">
+        <is>
+          <t>Backend / Accuracy</t>
+        </is>
+      </c>
+      <c r="D123" s="53" t="inlineStr">
+        <is>
+          <t>⏳ ממתין ל-push</t>
+        </is>
+      </c>
+      <c r="E123" s="47" t="inlineStr">
+        <is>
+          <t>main.py</t>
+        </is>
+      </c>
+      <c r="F123" s="47" t="inlineStr">
+        <is>
+          <t>שיפור שנחשף תוך כדי: הקוד לקח ספירה נוכחית אחת והחיל אותה על חמש שנות מחירים. לכל חברה שרוכשת מניות בחזרה זה מעוות כל נקודת עבר. AMD: 1,616M ב-2023 מול 1,630M ב-2026. עכשיו כל נקודה מקבלת את הספירה שהיתה בתוקף באותו תאריך.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="51" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="B124" s="52" t="inlineStr">
+        <is>
+          <t>כשל שקט הופך לכשל מדווח</t>
+        </is>
+      </c>
+      <c r="C124" s="51" t="inlineStr">
+        <is>
+          <t>Backend / Observability</t>
+        </is>
+      </c>
+      <c r="D124" s="53" t="inlineStr">
+        <is>
+          <t>⏳ ממתין ל-push</t>
+        </is>
+      </c>
+      <c r="E124" s="47" t="inlineStr">
+        <is>
+          <t>main.py</t>
+        </is>
+      </c>
+      <c r="F124" s="47" t="inlineStr">
+        <is>
+          <t>כל 14 המקומות שמחזירים use_price מדווחים עכשיו empty_reason: no_share_count · no_price_history · no_repurchase_rows · no_eps_series · no_dividend_history · all_points_rejected · no_statement_rows · metric_not_tracked · exception. הבעיה המקורית היתה בלתי נראית כי האריח הראה ערך (מיאהו) בזמן שהגרף היה ריק — מסך ריק עם אריח מלא נראה כמו חוסר נתונים ולא כמו באג.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="51" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="B125" s="52" t="inlineStr">
+        <is>
+          <t>שם המניה במסך המדד</t>
+        </is>
+      </c>
+      <c r="C125" s="51" t="inlineStr">
+        <is>
+          <t>Frontend / UX</t>
+        </is>
+      </c>
+      <c r="D125" s="53" t="inlineStr">
+        <is>
+          <t>⏳ ממתין ל-push</t>
+        </is>
+      </c>
+      <c r="E125" s="47" t="inlineStr">
+        <is>
+          <t>MetricHistoryScreen.js, StockScreen.js, ETFCard.js</t>
+        </is>
+      </c>
+      <c r="F125" s="47" t="inlineStr">
+        <is>
+          <t>המסך הציג "EV/EBITDA · 103.36" בלי שום אינדיקציה לאיזו חברה המספר שייך. השם מופיע עכשיו מעל שם המדד. עודכנו כל 10 נקודות הכניסה — תשע מ-StockScreen ואחת מ-ETFCard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="44" t="inlineStr">
         <is>
           <t>110</t>
         </is>
       </c>
-      <c r="B120" s="45" t="inlineStr">
+      <c r="B126" s="45" t="inlineStr">
         <is>
           <t>עמוד הפרטיות הוגש מהמטמון</t>
         </is>
       </c>
-      <c r="C120" s="44" t="inlineStr">
+      <c r="C126" s="44" t="inlineStr">
         <is>
           <t>Backend / Legal / Bug Fix</t>
         </is>
       </c>
-      <c r="D120" s="46" t="inlineStr">
+      <c r="D126" s="46" t="inlineStr">
         <is>
           <t>⏳ ממתין ל-push</t>
         </is>
       </c>
-      <c r="E120" s="47" t="inlineStr">
+      <c r="E126" s="47" t="inlineStr">
         <is>
           <t>main.py</t>
         </is>
       </c>
-      <c r="F120" s="47" t="inlineStr">
+      <c r="F126" s="47" t="inlineStr">
         <is>
           <t>המידלוור שמונע מטמון החריג במפורש את /privacy, מתוך הנחה שדף משפטי סטטי כדאי לשמור. ההנחה היתה הפוכה. אומת חי: הכתובת הרגילה החזירה את הנוסח הישן ("the watchlist is never transmitted to our servers") בעוד שאותה כתובת עם פרמטר שאילתה חדש החזירה את המתוקן — כלומר הקוד תקין והתשובה נתקעה במטמון. גוגל משווה את הדף להצהרת Data Safety, כך שעותק ישן היה יוצר סתירה מולם. החריג הוסר; כל נתיב מקבל no-store.</t>
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="44" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="44" t="inlineStr">
         <is>
           <t>111</t>
         </is>
       </c>
-      <c r="B121" s="45" t="inlineStr">
+      <c r="B127" s="45" t="inlineStr">
         <is>
           <t>טופס Data Safety מולא</t>
         </is>
       </c>
-      <c r="C121" s="44" t="inlineStr">
+      <c r="C127" s="44" t="inlineStr">
         <is>
           <t>Store / Legal</t>
         </is>
       </c>
-      <c r="D121" s="46" t="inlineStr">
+      <c r="D127" s="46" t="inlineStr">
         <is>
           <t>⏳ טיוטה — לא הוגש</t>
         </is>
       </c>
-      <c r="E121" s="47" t="inlineStr">
+      <c r="E127" s="47" t="inlineStr">
         <is>
           <t>data-safety-answers.html</t>
         </is>
       </c>
-      <c r="F121" s="47" t="inlineStr">
+      <c r="F127" s="47" t="inlineStr">
         <is>
           <t>התשובות מולאו ונשמרו כטיוטה, אבל הטופס מעולם לא הוגש — לוח הבקרה של Play מציג עיגול ריק ליד "אבטחת נתונים". אומת ישירות בקונסולה: הטופס נפתח בשלב 1 מתוך 5 עם כפתור "שמירת טיוטה" פעיל, והתשובות של שלב 2 (כן לאיסוף, כן להצפנה) שמורות. צריך לעבור שלבים 3-4-5 וללחוץ שליחה במסך התצוגה המקדימה. 5 סוגי נתונים שהוצהרו: אינטראקציות · חיפוש · תוכן משתמש · גלישה · מזהה מכשיר.</t>
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="48" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="48" t="inlineStr">
         <is>
           <t>112</t>
         </is>
       </c>
-      <c r="B122" s="49" t="inlineStr">
+      <c r="B128" s="49" t="inlineStr">
         <is>
           <t>צ׳קליסט טפסי Play Console</t>
         </is>
       </c>
-      <c r="C122" s="48" t="inlineStr">
+      <c r="C128" s="48" t="inlineStr">
         <is>
           <t>Store</t>
         </is>
       </c>
-      <c r="D122" s="50" t="inlineStr">
+      <c r="D128" s="50" t="inlineStr">
         <is>
           <t>✅ הושלם</t>
         </is>
       </c>
-      <c r="E122" s="42" t="inlineStr">
+      <c r="E128" s="42" t="inlineStr">
         <is>
           <t>play-console-checklist.html</t>
         </is>
       </c>
-      <c r="F122" s="42" t="inlineStr">
+      <c r="F128" s="42" t="inlineStr">
         <is>
           <t>תשובות לכל סעיפי App content שנותרו: גישה לאפליקציה, מודעות, דירוג תוכן, קהל יעד, תכונות פיננסיות, אפליקציית חדשות, בריאות, ממשלה, הרשאות רגישות. שתי ההצהרות הרגישות באפליקציה מסוג זה — "תכונות פיננסיות" ו"אפליקציית חדשות" — מנומקות בנפרד.</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="44" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="44" t="inlineStr">
         <is>
           <t>113</t>
         </is>
       </c>
-      <c r="B123" s="45" t="inlineStr">
+      <c r="B129" s="45" t="inlineStr">
         <is>
           <t>צילומי מסך לחנות</t>
         </is>
       </c>
-      <c r="C123" s="44" t="inlineStr">
+      <c r="C129" s="44" t="inlineStr">
         <is>
           <t>Store</t>
         </is>
       </c>
-      <c r="D123" s="46" t="inlineStr">
+      <c r="D129" s="46" t="inlineStr">
         <is>
           <t>🔜 לא התחיל</t>
         </is>
       </c>
-      <c r="E123" s="47" t="inlineStr">
+      <c r="E129" s="47" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F123" s="47" t="inlineStr">
+      <c r="F129" s="47" t="inlineStr">
         <is>
           <t>הפער היחיד שנותר בדף החנות. גוגל דורשת לפחות 2 צילומי טלפון, מומלץ 4-8. אייקון ו-feature graphic כבר קיימים במידות הנכונות (1024x1024 ו-1024x500). מדריך מוכן ב-מדריך-צילומי-מסך-לחנות.html.</t>
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="10" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="10" t="inlineStr">
         <is>
           <t>Legend</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="6" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="6" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
       </c>
-      <c r="B125" s="7" t="inlineStr">
+      <c r="B131" s="7" t="inlineStr">
         <is>
           <t>פרוס ופעיל ב-Render — נראה לכל המשתמשים</t>
         </is>
       </c>
-      <c r="C125" s="6" t="inlineStr"/>
-      <c r="D125" s="8" t="inlineStr"/>
-      <c r="E125" s="9" t="inlineStr"/>
-      <c r="F125" s="9" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="6" t="inlineStr">
+      <c r="C131" s="6" t="inlineStr"/>
+      <c r="D131" s="8" t="inlineStr"/>
+      <c r="E131" s="9" t="inlineStr"/>
+      <c r="F131" s="9" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="6" t="inlineStr">
         <is>
           <t>✅ In APK</t>
         </is>
       </c>
-      <c r="B126" s="7" t="inlineStr">
+      <c r="B132" s="7" t="inlineStr">
         <is>
           <t>כלול ב-APK המותקן — נראה לכל המשתמשים</t>
         </is>
       </c>
-      <c r="C126" s="6" t="inlineStr"/>
-      <c r="D126" s="8" t="inlineStr"/>
-      <c r="E126" s="9" t="inlineStr"/>
-      <c r="F126" s="9" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="6" t="inlineStr">
+      <c r="C132" s="6" t="inlineStr"/>
+      <c r="D132" s="8" t="inlineStr"/>
+      <c r="E132" s="9" t="inlineStr"/>
+      <c r="F132" s="9" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="6" t="inlineStr">
         <is>
           <t>⏳ Next APK</t>
         </is>
       </c>
-      <c r="B127" s="7" t="inlineStr">
+      <c r="B133" s="7" t="inlineStr">
         <is>
           <t>הקוד מוזג — דורש build ו-APK חדש</t>
         </is>
       </c>
-      <c r="C127" s="6" t="inlineStr"/>
-      <c r="D127" s="8" t="inlineStr"/>
-      <c r="E127" s="9" t="inlineStr"/>
-      <c r="F127" s="9" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="6" t="inlineStr">
+      <c r="C133" s="6" t="inlineStr"/>
+      <c r="D133" s="8" t="inlineStr"/>
+      <c r="E133" s="9" t="inlineStr"/>
+      <c r="F133" s="9" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="6" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
       </c>
-      <c r="B128" s="7" t="inlineStr">
+      <c r="B134" s="7" t="inlineStr">
         <is>
           <t>שינוי JS — מועבר אוטומטית בהפעלה הבאה</t>
         </is>
       </c>
-      <c r="C128" s="6" t="inlineStr"/>
-      <c r="D128" s="8" t="inlineStr"/>
-      <c r="E128" s="9" t="inlineStr"/>
-      <c r="F128" s="9" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="21" t="inlineStr">
+      <c r="C134" s="6" t="inlineStr"/>
+      <c r="D134" s="8" t="inlineStr"/>
+      <c r="E134" s="9" t="inlineStr"/>
+      <c r="F134" s="9" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="21" t="inlineStr">
         <is>
           <t>⏳ ממתין ל-push</t>
         </is>
       </c>
-      <c r="B129" s="22" t="inlineStr">
+      <c r="B135" s="22" t="inlineStr">
         <is>
           <t>הקוד מוכן מקומית — טרם נדחף/נפרס</t>
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="21" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="21" t="inlineStr">
         <is>
           <t>⏳ דורש build</t>
         </is>
       </c>
-      <c r="B130" s="22" t="inlineStr">
+      <c r="B136" s="22" t="inlineStr">
         <is>
           <t>שינוי נייטיב — OTA לא מספיק, צריך AAB/APK חדש</t>
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="23" t="inlineStr">
+    <row r="137"/>
+    <row r="138">
+      <c r="A138" s="23" t="inlineStr">
         <is>
           <t>סיכום Session 6-8</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="24" t="n"/>
-      <c r="B133" s="25" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="24" t="n"/>
+      <c r="B139" s="25" t="inlineStr">
         <is>
           <t>58  —  פריטים חדשים שנוספו (52-109)</t>
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="24" t="n"/>
-      <c r="B134" s="25" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="24" t="n"/>
+      <c r="B140" s="25" t="inlineStr">
         <is>
           <t>56  —  חיים בייצור או ב-OTA</t>
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="24" t="n"/>
-      <c r="B135" s="25" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="24" t="n"/>
+      <c r="B141" s="25" t="inlineStr">
         <is>
           <t>0  —  ממתינים ל-push: הכל נפרס (commit 91ee6d3)</t>
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="24" t="n"/>
-      <c r="B136" s="25" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="24" t="n"/>
+      <c r="B142" s="25" t="inlineStr">
         <is>
           <t>2  —  פתוחים: פריסת טאבלט אמיתית (99) · הגשה ל-Play (19)</t>
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="24" t="n"/>
-      <c r="B137" s="25" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="24" t="n"/>
+      <c r="B143" s="25" t="inlineStr">
         <is>
           <t>8  —  בורסות שאומתו חי (NYSE · TASE · XETRA · LSE) · JSE ביחידה בלבד</t>
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="24" t="n"/>
-      <c r="B138" s="25" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="24" t="n"/>
+      <c r="B144" s="25" t="inlineStr">
         <is>
           <t>48  —  חבילות בדיקה התנהגותיות עוברות (48/48)</t>
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="B139" t="inlineStr">
+    <row r="145">
+      <c r="B145" t="inlineStr">
         <is>
           <t>18  —  ראוטים בשרת · 324 מפתחות i18n × 4 שפות</t>
         </is>

--- a/BuddhaVest_Progress.xlsx
+++ b/BuddhaVest_Progress.xlsx
@@ -74,7 +74,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -114,6 +114,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4E4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDEDED"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -187,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -333,6 +348,63 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -699,7 +771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F145"/>
+  <dimension ref="A1:F204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -720,7 +792,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Last updated: 2026-08-03  |  Session 9</t>
+          <t>Last updated: 2026-08-08  |  Session 10  |  אומת חי: /status build=8602f21 · lkg=redis · sentry=on · CI passing</t>
         </is>
       </c>
     </row>
@@ -4297,7 +4369,7 @@
       </c>
       <c r="D120" s="53" t="inlineStr">
         <is>
-          <t>⏳ ממתין ל-push</t>
+          <t>✅ Live</t>
         </is>
       </c>
       <c r="E120" s="47" t="inlineStr">
@@ -4307,7 +4379,7 @@
       </c>
       <c r="F120" s="47" t="inlineStr">
         <is>
-          <t>החישוב ההיסטורי קרא את מספר המניות רק מ-info["sharesOutstanding"], ויאהו לא מחזירה את השדה הזה ל-AMD. שורה אחת — if not shares — הפילה את כל הענף, וכל המכפילים חזרו ריקים: P/B, P/S, EV/EBITDA ו-Forward P/E. אומת חי: /metric-history/AMD/price_to_book ו-/ev_to_ebitda שניהם quarterly:[] בעוד WMT מחזירה 43 נקודות. הנתונים היו קיימים כל הזמן — /financials/AMD מכיל Ordinary Shares Number 1,630,410,843 בכל דוח.</t>
+          <t>החישוב ההיסטורי קרא את מספר המניות רק מ-info["sharesOutstanding"], ויאהו לא מחזירה את השדה הזה ל-AMD. שורה אחת — if not shares — הפילה את כל הענף, וכל המכפילים חזרו ריקים: P/B, P/S, EV/EBITDA ו-Forward P/E. אומת חי: /metric-history/AMD/price_to_book ו-/ev_to_ebitda שניהם quarterly:[] בעוד WMT מחזירה 43 נקודות. הנתונים היו קיימים כל הזמן — /financials/AMD מכיל Ordinary Shares Number 1,630,410,843 בכל דוח.  ✔ נפרס ואומת ב-8/8: /status build=8602f21.</t>
         </is>
       </c>
     </row>
@@ -4329,7 +4401,7 @@
       </c>
       <c r="D121" s="53" t="inlineStr">
         <is>
-          <t>⏳ ממתין ל-push</t>
+          <t>✅ Live</t>
         </is>
       </c>
       <c r="E121" s="47" t="inlineStr">
@@ -4339,7 +4411,7 @@
       </c>
       <c r="F121" s="47" t="inlineStr">
         <is>
-          <t>ענף ה-buyback הכיל עותק שני של אותה שורה, כך שגם תשואת הרכישות החוזרות של AMD היתה ריקה. נמצא רק בגלל החיפוש היזום אחרי מופעים נוספים, לא מדיווח משתמש.</t>
+          <t>ענף ה-buyback הכיל עותק שני של אותה שורה, כך שגם תשואת הרכישות החוזרות של AMD היתה ריקה. נמצא רק בגלל החיפוש היזום אחרי מופעים נוספים, לא מדיווח משתמש.  ✔ נפרס ואומת ב-8/8: /status build=8602f21.</t>
         </is>
       </c>
     </row>
@@ -4361,7 +4433,7 @@
       </c>
       <c r="D122" s="53" t="inlineStr">
         <is>
-          <t>⏳ ממתין ל-push</t>
+          <t>✅ Live</t>
         </is>
       </c>
       <c r="E122" s="47" t="inlineStr">
@@ -4371,7 +4443,7 @@
       </c>
       <c r="F122" s="47" t="inlineStr">
         <is>
-          <t>_shares_lookup ברמת המודול מחליף את שני העותקים: Ordinary Shares Number ← Share Issued ← Diluted Average Shares ← Basic Average Shares ← השדה ב-info. שני הענפים קוראים לאותה פונקציה, כך שהם לא יכולים להתפצל שוב. 18 בדיקות יחידה.</t>
+          <t>_shares_lookup ברמת המודול מחליף את שני העותקים: Ordinary Shares Number ← Share Issued ← Diluted Average Shares ← Basic Average Shares ← השדה ב-info. שני הענפים קוראים לאותה פונקציה, כך שהם לא יכולים להתפצל שוב. 18 בדיקות יחידה.  ✔ נפרס ואומת ב-8/8: /status build=8602f21.</t>
         </is>
       </c>
     </row>
@@ -4393,7 +4465,7 @@
       </c>
       <c r="D123" s="53" t="inlineStr">
         <is>
-          <t>⏳ ממתין ל-push</t>
+          <t>✅ Live</t>
         </is>
       </c>
       <c r="E123" s="47" t="inlineStr">
@@ -4403,7 +4475,7 @@
       </c>
       <c r="F123" s="47" t="inlineStr">
         <is>
-          <t>שיפור שנחשף תוך כדי: הקוד לקח ספירה נוכחית אחת והחיל אותה על חמש שנות מחירים. לכל חברה שרוכשת מניות בחזרה זה מעוות כל נקודת עבר. AMD: 1,616M ב-2023 מול 1,630M ב-2026. עכשיו כל נקודה מקבלת את הספירה שהיתה בתוקף באותו תאריך.</t>
+          <t>שיפור שנחשף תוך כדי: הקוד לקח ספירה נוכחית אחת והחיל אותה על חמש שנות מחירים. לכל חברה שרוכשת מניות בחזרה זה מעוות כל נקודת עבר. AMD: 1,616M ב-2023 מול 1,630M ב-2026. עכשיו כל נקודה מקבלת את הספירה שהיתה בתוקף באותו תאריך.  ✔ נפרס ואומת ב-8/8: /status build=8602f21.</t>
         </is>
       </c>
     </row>
@@ -4425,7 +4497,7 @@
       </c>
       <c r="D124" s="53" t="inlineStr">
         <is>
-          <t>⏳ ממתין ל-push</t>
+          <t>✅ Live</t>
         </is>
       </c>
       <c r="E124" s="47" t="inlineStr">
@@ -4435,7 +4507,7 @@
       </c>
       <c r="F124" s="47" t="inlineStr">
         <is>
-          <t>כל 14 המקומות שמחזירים use_price מדווחים עכשיו empty_reason: no_share_count · no_price_history · no_repurchase_rows · no_eps_series · no_dividend_history · all_points_rejected · no_statement_rows · metric_not_tracked · exception. הבעיה המקורית היתה בלתי נראית כי האריח הראה ערך (מיאהו) בזמן שהגרף היה ריק — מסך ריק עם אריח מלא נראה כמו חוסר נתונים ולא כמו באג.</t>
+          <t>כל 14 המקומות שמחזירים use_price מדווחים עכשיו empty_reason: no_share_count · no_price_history · no_repurchase_rows · no_eps_series · no_dividend_history · all_points_rejected · no_statement_rows · metric_not_tracked · exception. הבעיה המקורית היתה בלתי נראית כי האריח הראה ערך (מיאהו) בזמן שהגרף היה ריק — מסך ריק עם אריח מלא נראה כמו חוסר נתונים ולא כמו באג.  ✔ נפרס ואומת ב-8/8: /status build=8602f21.</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4529,7 @@
       </c>
       <c r="D125" s="53" t="inlineStr">
         <is>
-          <t>⏳ ממתין ל-push</t>
+          <t>✅ Live</t>
         </is>
       </c>
       <c r="E125" s="47" t="inlineStr">
@@ -4467,29 +4539,29 @@
       </c>
       <c r="F125" s="47" t="inlineStr">
         <is>
-          <t>המסך הציג "EV/EBITDA · 103.36" בלי שום אינדיקציה לאיזו חברה המספר שייך. השם מופיע עכשיו מעל שם המדד. עודכנו כל 10 נקודות הכניסה — תשע מ-StockScreen ואחת מ-ETFCard.</t>
+          <t>המסך הציג "EV/EBITDA · 103.36" בלי שום אינדיקציה לאיזו חברה המספר שייך. השם מופיע עכשיו מעל שם המדד. עודכנו כל 10 נקודות הכניסה — תשע מ-StockScreen ואחת מ-ETFCard.  ✔ נפרס ואומת ב-8/8: /status build=8602f21.</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="44" t="inlineStr">
+      <c r="A126" s="51" t="inlineStr">
         <is>
           <t>110</t>
         </is>
       </c>
-      <c r="B126" s="45" t="inlineStr">
+      <c r="B126" s="52" t="inlineStr">
         <is>
           <t>עמוד הפרטיות הוגש מהמטמון</t>
         </is>
       </c>
-      <c r="C126" s="44" t="inlineStr">
+      <c r="C126" s="51" t="inlineStr">
         <is>
           <t>Backend / Legal / Bug Fix</t>
         </is>
       </c>
-      <c r="D126" s="46" t="inlineStr">
-        <is>
-          <t>⏳ ממתין ל-push</t>
+      <c r="D126" s="53" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
         </is>
       </c>
       <c r="E126" s="47" t="inlineStr">
@@ -4499,27 +4571,27 @@
       </c>
       <c r="F126" s="47" t="inlineStr">
         <is>
-          <t>המידלוור שמונע מטמון החריג במפורש את /privacy, מתוך הנחה שדף משפטי סטטי כדאי לשמור. ההנחה היתה הפוכה. אומת חי: הכתובת הרגילה החזירה את הנוסח הישן ("the watchlist is never transmitted to our servers") בעוד שאותה כתובת עם פרמטר שאילתה חדש החזירה את המתוקן — כלומר הקוד תקין והתשובה נתקעה במטמון. גוגל משווה את הדף להצהרת Data Safety, כך שעותק ישן היה יוצר סתירה מולם. החריג הוסר; כל נתיב מקבל no-store.</t>
+          <t>המידלוור שמונע מטמון החריג במפורש את /privacy, מתוך הנחה שדף משפטי סטטי כדאי לשמור. ההנחה היתה הפוכה. אומת חי: הכתובת הרגילה החזירה את הנוסח הישן ("the watchlist is never transmitted to our servers") בעוד שאותה כתובת עם פרמטר שאילתה חדש החזירה את המתוקן — כלומר הקוד תקין והתשובה נתקעה במטמון. גוגל משווה את הדף להצהרת Data Safety, כך שעותק ישן היה יוצר סתירה מולם. החריג הוסר; כל נתיב מקבל no-store.  ✔ נפרס ואומת ב-8/8: /status build=8602f21.</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="44" t="inlineStr">
+      <c r="A127" s="51" t="inlineStr">
         <is>
           <t>111</t>
         </is>
       </c>
-      <c r="B127" s="45" t="inlineStr">
+      <c r="B127" s="52" t="inlineStr">
         <is>
           <t>טופס Data Safety מולא</t>
         </is>
       </c>
-      <c r="C127" s="44" t="inlineStr">
+      <c r="C127" s="51" t="inlineStr">
         <is>
           <t>Store / Legal</t>
         </is>
       </c>
-      <c r="D127" s="46" t="inlineStr">
+      <c r="D127" s="53" t="inlineStr">
         <is>
           <t>⏳ טיוטה — לא הוגש</t>
         </is>
@@ -4568,22 +4640,22 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="44" t="inlineStr">
+      <c r="A129" s="51" t="inlineStr">
         <is>
           <t>113</t>
         </is>
       </c>
-      <c r="B129" s="45" t="inlineStr">
+      <c r="B129" s="52" t="inlineStr">
         <is>
           <t>צילומי מסך לחנות</t>
         </is>
       </c>
-      <c r="C129" s="44" t="inlineStr">
+      <c r="C129" s="51" t="inlineStr">
         <is>
           <t>Store</t>
         </is>
       </c>
-      <c r="D129" s="46" t="inlineStr">
+      <c r="D129" s="53" t="inlineStr">
         <is>
           <t>🔜 לא התחיל</t>
         </is>
@@ -4595,174 +4667,1503 @@
       </c>
       <c r="F129" s="47" t="inlineStr">
         <is>
-          <t>הפער היחיד שנותר בדף החנות. גוגל דורשת לפחות 2 צילומי טלפון, מומלץ 4-8. אייקון ו-feature graphic כבר קיימים במידות הנכונות (1024x1024 ו-1024x500). מדריך מוכן ב-מדריך-צילומי-מסך-לחנות.html.</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="10" t="inlineStr">
+          <t>הפער היחיד שנותר בדף החנות.  ◀ ראה פריט 156: המדריך והבודק האוטומטי מוכנים, ו-5 הקבצים שהיו בתיקייה התבררו כ-placeholder ריקים.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="8" customHeight="1"/>
+    <row r="131" ht="20" customHeight="1">
+      <c r="A131" s="54" t="inlineStr">
+        <is>
+          <t>✅  Session 10 (2026-08-08): סקירת מערכת מקצה לקצה · תשתית · אמינות · הוכחה בייצור</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="55" t="n">
+        <v>120</v>
+      </c>
+      <c r="B132" s="56" t="inlineStr">
+        <is>
+          <t>תוויות ציר X בגרף — חפיפה</t>
+        </is>
+      </c>
+      <c r="C132" s="55" t="inlineStr">
+        <is>
+          <t>Frontend / UX</t>
+        </is>
+      </c>
+      <c r="D132" s="57" t="inlineStr">
+        <is>
+          <t>✅ Live (OTA)</t>
+        </is>
+      </c>
+      <c r="E132" s="58" t="inlineStr">
+        <is>
+          <t>components/PriceChart.js</t>
+        </is>
+      </c>
+      <c r="F132" s="58" t="inlineStr">
+        <is>
+          <t>השנים בתחתית הגרף נדבקו זו לזו. הכלל הישן הוסיף תמיד את הנקודה האחרונה בלי לבדוק מרחק. סרקתי 8–140 נקודות ומצאתי 16 אורכים עם חפיפה (עד 17.6 פיקסלים). התיקון הראשון שלי עדיין נכשל בבדיקה שלי עצמה (29.6px), והוחלף באכיפת מרווח מינימלי של 46px. אומת על 3,990 צירופים — המרווח הגרוע ביותר בדיוק 46.0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="55" t="n">
+        <v>121</v>
+      </c>
+      <c r="B133" s="56" t="inlineStr">
+        <is>
+          <t>טבלת השוק — עמודת שווי שוק נחתכת</t>
+        </is>
+      </c>
+      <c r="C133" s="55" t="inlineStr">
+        <is>
+          <t>Frontend / UX</t>
+        </is>
+      </c>
+      <c r="D133" s="57" t="inlineStr">
+        <is>
+          <t>✅ Live (OTA)</t>
+        </is>
+      </c>
+      <c r="E133" s="58" t="inlineStr">
+        <is>
+          <t>screens/HomeScreen.js</t>
+        </is>
+      </c>
+      <c r="F133" s="58" t="inlineStr">
+        <is>
+          <t>רוחבי העמודות היו קבועים בפיקסלים. במסך 393dp עמודת השווי נחתכה ב-21 פיקסלים. הוחלף ביחסי אחוזים לפי useWindowDimensions, והעמודה האחרונה סופגת את שארית העיגול.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="55" t="n">
+        <v>122</v>
+      </c>
+      <c r="B134" s="56" t="inlineStr">
+        <is>
+          <t>רשימת המעקב — undefined דרס מחירים תקינים</t>
+        </is>
+      </c>
+      <c r="C134" s="55" t="inlineStr">
+        <is>
+          <t>Frontend / Bug Fix</t>
+        </is>
+      </c>
+      <c r="D134" s="57" t="inlineStr">
+        <is>
+          <t>✅ Live (OTA)</t>
+        </is>
+      </c>
+      <c r="E134" s="58" t="inlineStr">
+        <is>
+          <t>screens/WatchlistScreen.js</t>
+        </is>
+      </c>
+      <c r="F134" s="58" t="inlineStr">
+        <is>
+          <t>שלב 2 החליף אובייקט שלם, אז שדה שחזר undefined מחק ערך טוב משלב 1. mergeDefined ממזג רק ערכים שאינם null/undefined.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="55" t="n">
+        <v>123</v>
+      </c>
+      <c r="B135" s="56" t="inlineStr">
+        <is>
+          <t>הערת שיטת החישוב — שבב מתחת למספר</t>
+        </is>
+      </c>
+      <c r="C135" s="55" t="inlineStr">
+        <is>
+          <t>Frontend / UX</t>
+        </is>
+      </c>
+      <c r="D135" s="57" t="inlineStr">
+        <is>
+          <t>✅ Live (OTA)</t>
+        </is>
+      </c>
+      <c r="E135" s="58" t="inlineStr">
+        <is>
+          <t>screens/MetricHistoryScreen.js</t>
+        </is>
+      </c>
+      <c r="F135" s="58" t="inlineStr">
+        <is>
+          <t>ההערה הייתה פסקה מעל הגרף. הועברה לשבב קצר מתחת למספר, עם ⓘ, ומופיעה רק במדדים שבהם הכותרת והגרף באמת מחושבים אחרת.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="55" t="n">
+        <v>124</v>
+      </c>
+      <c r="B136" s="56" t="inlineStr">
+        <is>
+          <t>push.bat — קידוד עברית שיבר את הקובץ</t>
+        </is>
+      </c>
+      <c r="C136" s="55" t="inlineStr">
+        <is>
+          <t>Tooling</t>
+        </is>
+      </c>
+      <c r="D136" s="57" t="inlineStr">
+        <is>
+          <t>✅ הושלם</t>
+        </is>
+      </c>
+      <c r="E136" s="58" t="inlineStr">
+        <is>
+          <t>push.bat</t>
+        </is>
+      </c>
+      <c r="F136" s="58" t="inlineStr">
+        <is>
+          <t>cmd.exe קורא קובץ bat לפי היסט בתים. שורת chcp באמצע הזיזה כל שורה אחריה וכל echo הפך ל-'is not recognized'. נכתב מחדש ב-ASCII בלבד, עם בדיקת שגיאה אחרי כל שלב ועצירה בקול.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="55" t="n">
+        <v>125</v>
+      </c>
+      <c r="B137" s="56" t="inlineStr">
+        <is>
+          <t>release.bat — פרסום לערוץ production</t>
+        </is>
+      </c>
+      <c r="C137" s="55" t="inlineStr">
+        <is>
+          <t>Tooling</t>
+        </is>
+      </c>
+      <c r="D137" s="57" t="inlineStr">
+        <is>
+          <t>✅ הושלם</t>
+        </is>
+      </c>
+      <c r="E137" s="58" t="inlineStr">
+        <is>
+          <t>release.bat</t>
+        </is>
+      </c>
+      <c r="F137" s="58" t="inlineStr">
+        <is>
+          <t>הפרדה מפורשת בין preview (בדיקות) ל-production (חנות), כדי שלא ייצא עדכון לערוץ הלא נכון.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="55" t="n">
+        <v>126</v>
+      </c>
+      <c r="B138" s="56" t="inlineStr">
+        <is>
+          <t>נכסי חנות — אייקון וגרפיקה ראשית</t>
+        </is>
+      </c>
+      <c r="C138" s="55" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="D138" s="57" t="inlineStr">
+        <is>
+          <t>✅ הושלם</t>
+        </is>
+      </c>
+      <c r="E138" s="58" t="inlineStr">
+        <is>
+          <t>store-assets/icon-512.png, feature-graphic-1024x500.png</t>
+        </is>
+      </c>
+      <c r="F138" s="58" t="inlineStr">
+        <is>
+          <t>512x512 ו-1024x500 לפי דרישות גוגל.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="55" t="n">
+        <v>127</v>
+      </c>
+      <c r="B139" s="56" t="inlineStr">
+        <is>
+          <t>app.json / eas.json לקראת הגשה</t>
+        </is>
+      </c>
+      <c r="C139" s="55" t="inlineStr">
+        <is>
+          <t>Config</t>
+        </is>
+      </c>
+      <c r="D139" s="57" t="inlineStr">
+        <is>
+          <t>✅ הושלם</t>
+        </is>
+      </c>
+      <c r="E139" s="58" t="inlineStr">
+        <is>
+          <t>app.json, eas.json</t>
+        </is>
+      </c>
+      <c r="F139" s="58" t="inlineStr">
+        <is>
+          <t>versionCode 3, שם חבילה com.buddhavest.app (קבוע לצמיתות), הרשאות INTERNET ו-ACCESS_NETWORK_STATE בלבד, פרופיל production מייצר app-bundle עם autoIncrement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="55" t="n">
+        <v>128</v>
+      </c>
+      <c r="B140" s="56" t="inlineStr">
+        <is>
+          <t>סשן yfinance מותאם — בוטל</t>
+        </is>
+      </c>
+      <c r="C140" s="55" t="inlineStr">
+        <is>
+          <t>Backend / Incident</t>
+        </is>
+      </c>
+      <c r="D140" s="57" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="E140" s="58" t="inlineStr">
+        <is>
+          <t>assets/1BuddhaVest/data_fetcher.py</t>
+        </is>
+      </c>
+      <c r="F140" s="58" t="inlineStr">
+        <is>
+          <t>הכשל החמור של היום. העברת session משלנו ל-yf.Ticker לא זרקה שגיאה — היא רוקנה את stock.info לכל מניה, בזמן ש-fast_info המשיך לעבוד. התוצאה: מחירים הופיעו כרגיל אבל שמות חברה, נפח וכל חמשת המכפילים נעלמו. בוטל לגמרי; ההגבלה עברה לרמת הבקשה. הקוד מתעד את זה כאזהרה מפורשת.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="55" t="n">
+        <v>129</v>
+      </c>
+      <c r="B141" s="56" t="inlineStr">
+        <is>
+          <t>תקציב זמן לכל 8 נקודות הקצה הכבדות</t>
+        </is>
+      </c>
+      <c r="C141" s="55" t="inlineStr">
+        <is>
+          <t>Backend / Reliability</t>
+        </is>
+      </c>
+      <c r="D141" s="57" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="E141" s="58" t="inlineStr">
+        <is>
+          <t>assets/1BuddhaVest/main.py</t>
+        </is>
+      </c>
+      <c r="F141" s="58" t="inlineStr">
+        <is>
+          <t>רק /analyze היה מוגבל בזמן. 7 האחרות יכלו לתפוס את העובד היחיד לנצח — /analyze/AMD נמדד פתוח אחרי 180 שניות והשבית את כל השירות. עכשיו: analyze 25 שניות, market-overview/quotes/financials/metric-history 20, signals/events/etf-info 15.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="55" t="n">
+        <v>130</v>
+      </c>
+      <c r="B142" s="56" t="inlineStr">
+        <is>
+          <t>מכפילי שווי מחושבים מהדוחות</t>
+        </is>
+      </c>
+      <c r="C142" s="55" t="inlineStr">
+        <is>
+          <t>Backend / Data</t>
+        </is>
+      </c>
+      <c r="D142" s="57" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="E142" s="58" t="inlineStr">
+        <is>
+          <t>assets/1BuddhaVest/main.py</t>
+        </is>
+      </c>
+      <c r="F142" s="58" t="inlineStr">
+        <is>
+          <t>כשהספק לא מחזיר מכפילים, 4 מתוך 5 מחושבים מהמאזן ומדוח רווח והפסד. forward_pe במכוון לא — הוא דורש תחזית אנליסטים ואי אפשר לגזור אותו.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="55" t="n">
+        <v>131</v>
+      </c>
+      <c r="B143" s="56" t="inlineStr">
+        <is>
+          <t>/market-overview — תקציב זמן ותמונה ישנה</t>
+        </is>
+      </c>
+      <c r="C143" s="55" t="inlineStr">
+        <is>
+          <t>Backend / Reliability</t>
+        </is>
+      </c>
+      <c r="D143" s="57" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="E143" s="58" t="inlineStr">
+        <is>
+          <t>assets/1BuddhaVest/main.py</t>
+        </is>
+      </c>
+      <c r="F143" s="58" t="inlineStr">
+        <is>
+          <t>פוצל לעטיפה עם תקציב זמן וגוף פנימי. בחריגה מוחזרת התמונה הטובה האחרונה במקום מסך מקפים.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="55" t="n">
+        <v>132</v>
+      </c>
+      <c r="B144" s="56" t="inlineStr">
+        <is>
+          <t>מקביליות מופחתת מול Yahoo</t>
+        </is>
+      </c>
+      <c r="C144" s="55" t="inlineStr">
+        <is>
+          <t>Backend / Performance</t>
+        </is>
+      </c>
+      <c r="D144" s="57" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="E144" s="58" t="inlineStr">
+        <is>
+          <t>assets/1BuddhaVest/main.py</t>
+        </is>
+      </c>
+      <c r="F144" s="58" t="inlineStr">
+        <is>
+          <t>19 בקשות בו-זמנית הזמינו חסימה. הורד ל-3 למדדים, 4 לטבלה, 4 ל-Stooq. איטי יותר על הנייר, מהיר יותר בפועל כי לא נחסמים.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="20" customHeight="1">
+      <c r="A145" s="54" t="inlineStr">
+        <is>
+          <t>🔍  הסקירה שביקשת (5 סעיפים) — והביצוע שלה, פריט אחר פריט</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="55" t="n">
+        <v>133</v>
+      </c>
+      <c r="B146" s="56" t="inlineStr">
+        <is>
+          <t>סקירת מערכת מקצה לקצה</t>
+        </is>
+      </c>
+      <c r="C146" s="55" t="inlineStr">
+        <is>
+          <t>Audit</t>
+        </is>
+      </c>
+      <c r="D146" s="57" t="inlineStr">
+        <is>
+          <t>✅ הושלם</t>
+        </is>
+      </c>
+      <c r="E146" s="58" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F146" s="58" t="inlineStr">
+        <is>
+          <t>דוח ב-5 סעיפים: תקציר מנהלים, כשלים לפי חומרה (H1–H5, M1–M6, L1–L4), מה מיושם היטב, תוכנית תיקון, וצעדים מיידיים. הציון: מוכנות 6.5/10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="55" t="n">
+        <v>134</v>
+      </c>
+      <c r="B147" s="56" t="inlineStr">
+        <is>
+          <t>H3 · הגבלת קצב + צמצום CORS</t>
+        </is>
+      </c>
+      <c r="C147" s="55" t="inlineStr">
+        <is>
+          <t>Backend / Security</t>
+        </is>
+      </c>
+      <c r="D147" s="57" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="E147" s="58" t="inlineStr">
+        <is>
+          <t>main.py, requirements.txt</t>
+        </is>
+      </c>
+      <c r="F147" s="58" t="inlineStr">
+        <is>
+          <t>slowapi בשלוש רמות: 20/דקה לכבדות, 60 לרגילות, 120 לקלות. תפסתי לפני הדחיפה שכל 14 נקודות הקצה היו נכשלות בעליית השרת — slowapi דורש פרמטר request: Request, ואף אחת לא קיבלה אותו. אומת בירי 24 בקשות: 20 עוברות, ה-21 מחזירה 429. CORS צומצם ל-GET ו-POST בלבד.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="55" t="n">
+        <v>135</v>
+      </c>
+      <c r="B148" s="56" t="inlineStr">
+        <is>
+          <t>H2 · Sentry — שרת ולקוח</t>
+        </is>
+      </c>
+      <c r="C148" s="55" t="inlineStr">
+        <is>
+          <t>Backend / Observability</t>
+        </is>
+      </c>
+      <c r="D148" s="57" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="E148" s="58" t="inlineStr">
+        <is>
+          <t>observability.py (חדש), utils/monitoring.js (חדש), App.js</t>
+        </is>
+      </c>
+      <c r="F148" s="58" t="inlineStr">
+        <is>
+          <t>לא היה שום ניטור. כל תקלה התגלתה כי מישהו הסתכל על מסך. עכשיו report() ו-captureIssue() ב-3 נקודות בלקוח. send_default_pii=False — בלי כתובות IP ובלי headers. אומת בלוג הפריסה: [startup] Sentry enabled, ו-/status מחזיר sentry:on.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="55" t="n">
+        <v>136</v>
+      </c>
+      <c r="B149" s="56" t="inlineStr">
+        <is>
+          <t>H4 · אחסון קבוע — Upstash Redis</t>
+        </is>
+      </c>
+      <c r="C149" s="55" t="inlineStr">
+        <is>
+          <t>Backend / Reliability</t>
+        </is>
+      </c>
+      <c r="D149" s="57" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="E149" s="58" t="inlineStr">
+        <is>
+          <t>main.py, render.yaml</t>
+        </is>
+      </c>
+      <c r="F149" s="58" t="inlineStr">
+        <is>
+          <t>ה-LKG (נפח, נפח ממוצע, שווי שוק אחרונים תקינים) ישב ב-/tmp ש-Render מוחק בכל פריסה — רשת הביטחון נהרסה בדיוק ברגע שהיה בה צורך. עבר ל-Upstash Redis בשכבה חינמית, עם נפילה חזרה לדיסק ואז ל-/tmp. ההוכחה מהלוג: [startup] LKG restored: 18 entries (backend: redis) — 18 ערכים שרדו פריסה מלאה.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="55" t="n">
+        <v>137</v>
+      </c>
+      <c r="B150" s="56" t="inlineStr">
+        <is>
+          <t>M6 · CI ב-GitHub Actions</t>
+        </is>
+      </c>
+      <c r="C150" s="55" t="inlineStr">
+        <is>
+          <t>QA / Infrastructure</t>
+        </is>
+      </c>
+      <c r="D150" s="57" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="E150" s="58" t="inlineStr">
+        <is>
+          <t>.github/workflows/ci.yml (חדש)</t>
+        </is>
+      </c>
+      <c r="F150" s="58" t="inlineStr">
+        <is>
+          <t>18 שלבים על כל דחיפה: קומפילציה, ייבוא main.py, i18n ב-4 שפות, מפתחות עיצוב, catch ריקים, בליעות שקטות, קונפיג הגשה, סודות. אומת: הבדיקה בשלב ה-i18n נכתבה מחדש מ-regex ל-Babel AST אחרי שייצרה 27 התרעות שווא. check.bat מאשר: last run PASSED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="55" t="n">
+        <v>138</v>
+      </c>
+      <c r="B151" s="56" t="inlineStr">
+        <is>
+          <t>M2 · 40 בליעות שקטות בשרת, 17 בלקוח</t>
+        </is>
+      </c>
+      <c r="C151" s="55" t="inlineStr">
+        <is>
+          <t>Backend / Observability</t>
+        </is>
+      </c>
+      <c r="D151" s="57" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="E151" s="58" t="inlineStr">
+        <is>
+          <t>observability.py, main.py, analyzer.py, data_fetcher.py, stooq_fallback.py + 11 קבצי JS</t>
+        </is>
+      </c>
+      <c r="F151" s="58" t="inlineStr">
+        <is>
+          <t>except Exception: pass הופיע 40 פעם. כל אחד מחק את הראיה היחידה לכשל שהמשתמש רואה את תוצאתו. הוחלף ב-swallow(where, exc) שרושם וממשיך. שתיים נשארו שקטות במכוון ומתועדות בשם. הבדיקה שלי תפסה ש-swallow עצמו יכול לזרוק (str על אובייקט עם __str__ שבור) — כלומר להפוך כשל מטופל לקריסה. תוקן.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="55" t="n">
+        <v>139</v>
+      </c>
+      <c r="B152" s="56" t="inlineStr">
+        <is>
+          <t>M3 · הודעות שגיאה מובחנות</t>
+        </is>
+      </c>
+      <c r="C152" s="55" t="inlineStr">
+        <is>
+          <t>Frontend / UX</t>
+        </is>
+      </c>
+      <c r="D152" s="57" t="inlineStr">
+        <is>
+          <t>✅ Live (OTA)</t>
+        </is>
+      </c>
+      <c r="E152" s="58" t="inlineStr">
+        <is>
+          <t>utils/errors.js (חדש), constants/i18n.js, StockScreen.js, MetricHistoryScreen.js, ArticleScreen.js</t>
+        </is>
+      </c>
+      <c r="F152" s="58" t="inlineStr">
+        <is>
+          <t>הקוד זרק את קוד הסטטוס: throw new Error('Server error'). השרת החזיר 404 לסימול לא קיים, 429 להגבלה, 504 לתקיעה — וכולם הגיעו כ'בדוק את החיבור לאינטרנט'. עכשיו 6 מצבים מובחנים, 48 מפתחות תרגום חדשים (259 בכל שפה), וכפתור 'נסה שוב' לא מוצג על 404/429 כי הוא רק משחזר את אותה שגיאה. גם בוטלה המתנה של 8 שניות + בקשה נוספת על סימול שגוי.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="55" t="n">
+        <v>140</v>
+      </c>
+      <c r="B153" s="56" t="inlineStr">
+        <is>
+          <t>M4 · קוקיז צד-שלישי ב-WebView</t>
+        </is>
+      </c>
+      <c r="C153" s="55" t="inlineStr">
+        <is>
+          <t>Security / Legal</t>
+        </is>
+      </c>
+      <c r="D153" s="57" t="inlineStr">
+        <is>
+          <t>✅ Live (OTA)</t>
+        </is>
+      </c>
+      <c r="E153" s="58" t="inlineStr">
+        <is>
+          <t>screens/ArticleScreen.js</t>
+        </is>
+      </c>
+      <c r="F153" s="58" t="inlineStr">
+        <is>
+          <t>thirdPartyCookiesEnabled ו-sharedCookiesEnabled היו דלוקים — אתרי חדשות יכלו לכתוב ולקרוא קוקיז מעקב בתוך האפליקציה ולחלוק את מאגר הקוקיז של המכשיר. זה לא הוצהר לא ב-Data Safety ולא במדיניות הפרטיות. כובו; קריאת כתבה לא צריכה אותם.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="55" t="n">
+        <v>141</v>
+      </c>
+      <c r="B154" s="56" t="inlineStr">
+        <is>
+          <t>M5 · מאגרי threads משותפים</t>
+        </is>
+      </c>
+      <c r="C154" s="55" t="inlineStr">
+        <is>
+          <t>Backend / Performance</t>
+        </is>
+      </c>
+      <c r="D154" s="57" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="E154" s="58" t="inlineStr">
+        <is>
+          <t>assets/1BuddhaVest/main.py</t>
+        </is>
+      </c>
+      <c r="F154" s="58" t="inlineStr">
+        <is>
+          <t>8 מאגרים נבנו ונהרסו בתוך כל בקשה. נמדד: 25 threads על פני 6 מחזורי עבודה מלאים, מול 174 יצירות קודם. המגבלות הקטנות (3 ו-4 עובדים) נשמרו בכוונה — הן מגבלת נימוס מול Yahoo, לא חיסכון בזיכרון. המאגרים מופרדים לפי תפקיד כדי שמשימה לא תמתין למאגר של עצמה.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="59" t="n">
+        <v>142</v>
+      </c>
+      <c r="B155" s="60" t="inlineStr">
+        <is>
+          <t>H1 · ספק נתונים שני</t>
+        </is>
+      </c>
+      <c r="C155" s="59" t="inlineStr">
+        <is>
+          <t>Backend / Reliability</t>
+        </is>
+      </c>
+      <c r="D155" s="61" t="inlineStr">
+        <is>
+          <t>⚠️ פרוס — לא רץ בייצור</t>
+        </is>
+      </c>
+      <c r="E155" s="62" t="inlineStr">
+        <is>
+          <t>assets/1BuddhaVest/data_fetcher.py, test_chart_meta.py (חדש)</t>
+        </is>
+      </c>
+      <c r="F155" s="62" t="inlineStr">
+        <is>
+          <t>נקודת v8/chart הלא-מאומתת של Yahoo — אותה אחת שמסך המדדים כבר משתמש בה, כלומר נתיב עם ותק בקוד ולא תלות חדשה. שני חוקים נאכפים ב-47 בדיקות: מוסיף רק שדות חסרים ולעולם לא דורס, ולעולם לא זורק. חשוב: Yahoo תקין כרגע, ולכן מסלול הגיבוי עוד לא הופעל אף פעם בייצור. נדע ברגע ש-Sentry יקבל provider_fallback_used.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="20" customHeight="1">
+      <c r="A156" s="54" t="inlineStr">
+        <is>
+          <t>🐛  באגים שהתגלו תוך כדי — ורובם היו בלתי נראים לפני היום</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="55" t="n">
+        <v>143</v>
+      </c>
+      <c r="B157" s="56" t="inlineStr">
+        <is>
+          <t>9 מפתחות עיצוב שנקראו ולא הוגדרו</t>
+        </is>
+      </c>
+      <c r="C157" s="55" t="inlineStr">
+        <is>
+          <t>Frontend / Bug Fix</t>
+        </is>
+      </c>
+      <c r="D157" s="57" t="inlineStr">
+        <is>
+          <t>✅ Live (OTA)</t>
+        </is>
+      </c>
+      <c r="E157" s="58" t="inlineStr">
+        <is>
+          <t>screens/StockScreen.js</t>
+        </is>
+      </c>
+      <c r="F157" s="58" t="inlineStr">
+        <is>
+          <t>loadWrap, loadText, errorWrap, errorTitle, errorMsg, retryBtn, loadRow, noData, noteSmall — כולם נקראו מה-StyleSheet וכולם החזירו undefined. React Native מקבל style={undefined} בשקט, אז שום דבר לא קרס ושום דבר לא התריע. בפועל: ספינר 'מנתח...' שמופיע בכל פתיחת מניה לא היה ממורכז אלא דחוק לפינה, וכל מסך השגיאה רונדר בלי עיצוב.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="55" t="n">
+        <v>144</v>
+      </c>
+      <c r="B158" s="56" t="inlineStr">
+        <is>
+          <t>tileValue ב-ETFCard</t>
+        </is>
+      </c>
+      <c r="C158" s="55" t="inlineStr">
+        <is>
+          <t>Frontend / Bug Fix</t>
+        </is>
+      </c>
+      <c r="D158" s="57" t="inlineStr">
+        <is>
+          <t>✅ Live (OTA)</t>
+        </is>
+      </c>
+      <c r="E158" s="58" t="inlineStr">
+        <is>
+          <t>components/ETFCard.js</t>
+        </is>
+      </c>
+      <c r="F158" s="58" t="inlineStr">
+        <is>
+          <t>אותה משפחה: המפתח נקרא בכל אריח ולא הוגדר, אז המספרים רונדרו כטקסט רגיל 14px — זהה בדיוק לגרסה ה'קטנה', מה שהפך את tileValueSmall לחסר משמעות.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="55" t="n">
+        <v>145</v>
+      </c>
+      <c r="B159" s="56" t="inlineStr">
+        <is>
+          <t>הידרדרות חלקית של הספק — הטריגר לא נורה</t>
+        </is>
+      </c>
+      <c r="C159" s="55" t="inlineStr">
+        <is>
+          <t>Backend / Bug Fix</t>
+        </is>
+      </c>
+      <c r="D159" s="57" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="E159" s="58" t="inlineStr">
+        <is>
+          <t>data_fetcher.py, main.py, test_partial_degradation.py (חדש)</t>
+        </is>
+      </c>
+      <c r="F159" s="58" t="inlineStr">
+        <is>
+          <t>הבאג הכי מלמד של היום, ושלי. בניתי את הספק השני עם בדיקה 'האם יש שם?' כסימן שהתגובה פגומה. אבל Yahoo לא נופל בבת אחת — הוא מתפורר שדה-שדה. נמדד חי: /quotes החזיר 'Apple Inc.' ובאותה דקה /market-overview החזיר 'AAPL' עם volume ריק. longName הגיע, shortName ו-volume לא. הטריגר ראה שם תקין, יצא מוקדם, והגיבוי שנועד בדיוק למלא volume חסר מעולם לא רץ — אפילו לא פעם אחת.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="55" t="n">
+        <v>146</v>
+      </c>
+      <c r="B160" s="56" t="inlineStr">
+        <is>
+          <t>_one_mover קרא shortName בלבד</t>
+        </is>
+      </c>
+      <c r="C160" s="55" t="inlineStr">
+        <is>
+          <t>Backend / Bug Fix</t>
+        </is>
+      </c>
+      <c r="D160" s="57" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="E160" s="58" t="inlineStr">
+        <is>
+          <t>assets/1BuddhaVest/main.py</t>
+        </is>
+      </c>
+      <c r="F160" s="58" t="inlineStr">
+        <is>
+          <t>טבלת 15 המניות קראה shortName, בעוד /quotes ו-/analyze קוראים longName or shortName. אותה תגובה בדיוק החזירה שתי תשובות שונות — שם מלא במסך אחד, סימול חשוף בשני.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="55" t="n">
+        <v>147</v>
+      </c>
+      <c r="B161" s="56" t="inlineStr">
+        <is>
+          <t>מכפיל רווח חסר הוצג כ'החברה לא רווחית'</t>
+        </is>
+      </c>
+      <c r="C161" s="55" t="inlineStr">
+        <is>
+          <t>Backend / Correctness</t>
+        </is>
+      </c>
+      <c r="D161" s="57" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="E161" s="58" t="inlineStr">
+        <is>
+          <t>analyzer.py, i18n_data.py</t>
+        </is>
+      </c>
+      <c r="F161" s="58" t="inlineStr">
+        <is>
+          <t>החמור מכולם. כש-trailingPE לא הגיע מהספק, האפליקציה כתבה על אפל 'אין מכפיל רווח - החברה עדיין לא רווחית' — באותו מסך שהראה שולי רווח נקי 26.9%, רווח נקי 112 מיליארד וצומח, ומכפיל 42 בכרטיס המדדים הנוספים. שדה חסר אצל הספק הוצג כקביעה על העסק. תוקן: כשהמכפיל חסר הוא מחושב ממחיר חלקי רווח למניה מהדוח, ונאמר במפורש שהוא חושב אצלנו; כשבאמת אין רווחים — עדיין 'לא רווחית'; כשאי אפשר לדעת — 'לא זמין ממקור הנתונים'. 3 מפתחות חדשים ב-4 שפות. תוצאה נמדדת: ציון אפל עבר מ-81 ל-64, כי עמוד השווי היה null והציון חושב מ-2 עמודים במקום 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="55" t="n">
+        <v>148</v>
+      </c>
+      <c r="B162" s="56" t="inlineStr">
+        <is>
+          <t>חימום החדשות נשבר מהגבלת הקצב</t>
+        </is>
+      </c>
+      <c r="C162" s="55" t="inlineStr">
+        <is>
+          <t>Backend / Bug Fix</t>
+        </is>
+      </c>
+      <c r="D162" s="57" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="E162" s="58" t="inlineStr">
+        <is>
+          <t>assets/1BuddhaVest/main.py</t>
+        </is>
+      </c>
+      <c r="F162" s="58" t="inlineStr">
+        <is>
+          <t>נתפס בלוג הייצור בזכות M2, שעה אחרי שהוא נכנס. החימום קרא ל-general_news() ישירות; אחרי הוספת הגבלת הקצב הפונקציה קיבלה request: Request כפרמטר ראשון, אז הקריאה נשברה פעמיים — slowapi דחה אותה, וגם בלי זה _lang היה נכנס במקום request ו-lang נשאר 'en'. התוצאה: החימום נכשל בכל 4 השפות, והמשתמש הראשון אחרי כל פריסה חיכה לטעינה קרה. הגוף הוצא ל-_general_news_uncached, ונוסף שלב CI שסורק ב-AST ונכשל אם מישהו קורא לנקודת קצה מוגבלת כפונקציה.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="55" t="n">
+        <v>149</v>
+      </c>
+      <c r="B163" s="56" t="inlineStr">
+        <is>
+          <t>/status הכריז redis גם כשנדחה</t>
+        </is>
+      </c>
+      <c r="C163" s="55" t="inlineStr">
+        <is>
+          <t>Backend / Observability</t>
+        </is>
+      </c>
+      <c r="D163" s="57" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="E163" s="58" t="inlineStr">
+        <is>
+          <t>assets/1BuddhaVest/main.py</t>
+        </is>
+      </c>
+      <c r="F163" s="58" t="inlineStr">
+        <is>
+          <t>אחרי שהטוקן הראשון של Upstash הוחזר עם 401, /status עדיין דיווח lkg:redis — כי הוא בדק רק שמשתני הסביבה קיימים. זו בדיוק ההרגעה השקרית שכתבתי נגדה ב-render.yaml ואז בניתי בעצמי. עכשיו: שורת הפתיחה אומרת 'configured — verifying' ולא מכריזה persistent לפני שנבדק, 401 מקבל שורה מפורשת שאומרת מה לתקן, /status מבחין בין redis ל-redis-rejected, ואחרי 3 כישלונות ברצף המערכת נופלת לקובץ מקומי במקום לנסות לנצח.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="55" t="n">
+        <v>150</v>
+      </c>
+      <c r="B164" s="56" t="inlineStr">
+        <is>
+          <t>אייקון החנות היה 24-bit בלי אלפא</t>
+        </is>
+      </c>
+      <c r="C164" s="55" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="D164" s="57" t="inlineStr">
+        <is>
+          <t>✅ הושלם</t>
+        </is>
+      </c>
+      <c r="E164" s="58" t="inlineStr">
+        <is>
+          <t>store-assets/icon-512.png</t>
+        </is>
+      </c>
+      <c r="F164" s="58" t="inlineStr">
+        <is>
+          <t>גוגל דורשת 32-bit PNG עם ערוץ אלפא לאייקון (ולהיפך לצילומי מסך — 24-bit בלי אלפא). הקובץ היה 24-bit RGB. הומר; אותם פיקסלים בדיוק, אלפא אטום מלא.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="55" t="n">
+        <v>151</v>
+      </c>
+      <c r="B165" s="56" t="inlineStr">
+        <is>
+          <t>כתיבות ה-LKG רוכזו</t>
+        </is>
+      </c>
+      <c r="C165" s="55" t="inlineStr">
+        <is>
+          <t>Backend / Performance</t>
+        </is>
+      </c>
+      <c r="D165" s="57" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="E165" s="58" t="inlineStr">
+        <is>
+          <t>assets/1BuddhaVest/main.py</t>
+        </is>
+      </c>
+      <c r="F165" s="58" t="inlineStr">
+        <is>
+          <t>השמירה נקראה מתוך /analyze. מול קובץ זו הייתה קריאת מערכת זולה; מול Redis זו קריאת רשת בנתיב הבקשה, ובתקרת הגבלת הקצב יוצא כ-28,800 כתיבות ביום — מעבר לשכבה החינמית. עבר לדגל 'מלוכלך' + flush ברקע כל 60 שניות. נמדד: 500 סימונים ← כתיבה אחת.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="20" customHeight="1">
+      <c r="A166" s="54" t="inlineStr">
+        <is>
+          <t>🛠️  כלי אימות — כדי שלא תצטרך להאמין לאף אחד</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="55" t="n">
+        <v>152</v>
+      </c>
+      <c r="B167" s="56" t="inlineStr">
+        <is>
+          <t>check.bat — מה באמת נכון ברגע זה</t>
+        </is>
+      </c>
+      <c r="C167" s="55" t="inlineStr">
+        <is>
+          <t>Tooling / QA</t>
+        </is>
+      </c>
+      <c r="D167" s="57" t="inlineStr">
+        <is>
+          <t>✅ הושלם</t>
+        </is>
+      </c>
+      <c r="E167" s="58" t="inlineStr">
+        <is>
+          <t>check.bat (חדש), scripts/check-live.js (חדש)</t>
+        </is>
+      </c>
+      <c r="F167" s="58" t="inlineStr">
+        <is>
+          <t>פקודה אחת שעונה בלי לשאול אף אחד: האם הכול מקומט ונדחף, איזה קומיט באמת רץ בשרת, האם אפסטאש מחובר בפועל, האם Sentry דולק, ומה מצב ה-CI (קורא את ה-badge של GitHub). מבחין בין שלושה נתיבי משלוח — שרת (Render), אפליקציה (OTA), וקבצים שלא מגיעים לאף אחד — ונכשל רק כשקוד שרת באמת לא נפרס. הגרסה הראשונה שלי צעקה אדום גם על קומיט שנוגע רק בסקריפטים; תוקן, כי בדיקה שמתריעה לשווא מפסיקים להסתכל עליה.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="55" t="n">
+        <v>153</v>
+      </c>
+      <c r="B168" s="56" t="inlineStr">
+        <is>
+          <t>/status — build, lkg, sentry</t>
+        </is>
+      </c>
+      <c r="C168" s="55" t="inlineStr">
+        <is>
+          <t>Backend / Observability</t>
+        </is>
+      </c>
+      <c r="D168" s="57" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="E168" s="58" t="inlineStr">
+        <is>
+          <t>assets/1BuddhaVest/main.py</t>
+        </is>
+      </c>
+      <c r="F168" s="58" t="inlineStr">
+        <is>
+          <t>נבנה אחרי שהתברר שאין שום דרך לענות מבחוץ על 'האם התיקון שלי חי' ו'האם האחסון פעיל'. build = הקומיט שרץ בפועל, lkg = redis/disk/ephemeral/redis-rejected, sentry = on/off. בלי טוקנים ובלי כתובות; יש בדיקת CI שמוודאת שכלום לא דולף לשם.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="55" t="n">
+        <v>154</v>
+      </c>
+      <c r="B169" s="56" t="inlineStr">
+        <is>
+          <t>מדריך צילומי מסך + בודק אוטומטי</t>
+        </is>
+      </c>
+      <c r="C169" s="55" t="inlineStr">
+        <is>
+          <t>Store / QA</t>
+        </is>
+      </c>
+      <c r="D169" s="57" t="inlineStr">
+        <is>
+          <t>✅ הושלם</t>
+        </is>
+      </c>
+      <c r="E169" s="58" t="inlineStr">
+        <is>
+          <t>store-assets/SCREENSHOT-GUIDE.md, store-assets/check_screenshots.py</t>
+        </is>
+      </c>
+      <c r="F169" s="58" t="inlineStr">
+        <is>
+          <t>הדרישות נשלפו מהתיעוד הרשמי של גוגל ב-7/8, לא מהזיכרון. המדריך: אילו 6 מסכים, איזו מניה בכל אחד, כללי שורת הסטטוס (סוללה מלאה, בלי שם מפעיל — זה מה שמפילים עליו), מה אסור, וסקריפט חיתוך ל-1080x1920 מדויק. הבודק בדק את 5 קבצי ה-placeholder שישבו בתיקייה: כולם עברו מידות, יחס, פורמט וגודל — ורק בדיקת 'אחוז צבע יחיד' תפסה אותם (86%). הועברו ל-PLACEHOLDERS-DO-NOT-UPLOAD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="55" t="n">
+        <v>155</v>
+      </c>
+      <c r="B170" s="56" t="inlineStr">
+        <is>
+          <t>.gitignore — קבצי pyc</t>
+        </is>
+      </c>
+      <c r="C170" s="55" t="inlineStr">
+        <is>
+          <t>Tooling</t>
+        </is>
+      </c>
+      <c r="D170" s="57" t="inlineStr">
+        <is>
+          <t>✅ הושלם</t>
+        </is>
+      </c>
+      <c r="E170" s="58" t="inlineStr">
+        <is>
+          <t>.gitignore</t>
+        </is>
+      </c>
+      <c r="F170" s="58" t="inlineStr">
+        <is>
+          <t>__pycache__ לא היה מוחרג. קובץ pyc ישן שמגיע לפריסה עלול לרוץ במקום המקור שנדחף — באג 'התיקון לא נכנס' בלי שום סימן.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="20" customHeight="1">
+      <c r="A171" s="54" t="inlineStr">
+        <is>
+          <t>⏸️  נדחה במודע · 🔜 פתוח</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="63" t="n">
+        <v>156</v>
+      </c>
+      <c r="B172" s="64" t="inlineStr">
+        <is>
+          <t>צילומי מסך לחנות</t>
+        </is>
+      </c>
+      <c r="C172" s="63" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="D172" s="65" t="inlineStr">
+        <is>
+          <t>🔜 פתוח — חוסם הגשה</t>
+        </is>
+      </c>
+      <c r="E172" s="66" t="inlineStr">
+        <is>
+          <t>store-assets/screenshots/ (ריק)</t>
+        </is>
+      </c>
+      <c r="F172" s="66" t="inlineStr">
+        <is>
+          <t>הפריט היחיד שחוסם בפועל את ההגשה. מדריך וסקריפט בדיקה מוכנים (154). דורש את האפליקציה רצה על מכשיר — 6 מסכים, 1080x1920.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="67" t="n">
+        <v>157</v>
+      </c>
+      <c r="B173" s="68" t="inlineStr">
+        <is>
+          <t>M1 · פיצול main.py</t>
+        </is>
+      </c>
+      <c r="C173" s="67" t="inlineStr">
+        <is>
+          <t>Backend / Architecture</t>
+        </is>
+      </c>
+      <c r="D173" s="69" t="inlineStr">
+        <is>
+          <t>⏸️ נדחה למועד שאחרי ההשקה</t>
+        </is>
+      </c>
+      <c r="E173" s="70" t="inlineStr">
+        <is>
+          <t>assets/1BuddhaVest/main.py</t>
+        </is>
+      </c>
+      <c r="F173" s="70" t="inlineStr">
+        <is>
+          <t>3,420 שורות; _metric_history_uncached לבדה 552 שורות. הבעיה איננה האורך אלא 38 משתני מצב ברמת המודול (מטמון, מנעולים, מאגרי threads, LKG, מגביל קצב) שכמעט כל פונקציה נוגעת בהם — פיצול דורש להוציא אותם למודול משותף ולסדר מחדש את סדר הייבוא. כבר נתקלנו בזה היום: observability.py נולד בדיוק כי main מייבא את analyzer ו-data_fetcher והם לא יכלו לייבא ממנו בחזרה. שקיפות: הפריט הופיע בתוכנית התיקון שלי ולא נכנס לרשימת המשימות — פספסתי אותו ודיווחתי 'הכול בוצע' בלעדיו.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="67" t="n">
+        <v>158</v>
+      </c>
+      <c r="B174" s="68" t="inlineStr">
+        <is>
+          <t>L1–L4 · חוב תחזוקה</t>
+        </is>
+      </c>
+      <c r="C174" s="67" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
+      <c r="D174" s="69" t="inlineStr">
+        <is>
+          <t>⏸️ נדחה למועד שאחרי ההשקה</t>
+        </is>
+      </c>
+      <c r="E174" s="70" t="inlineStr">
+        <is>
+          <t>StockScreen.js, constants/i18n.js, story.txt</t>
+        </is>
+      </c>
+      <c r="F174" s="70" t="inlineStr">
+        <is>
+          <t>StockScreen 888 שורות · i18n.js בקובץ אחד · אין TypeScript (באג משתנה לא מוגדר היה נתפס בקומפילציה) · הפרשי CRLF ב-story.txt שנגררים בכל commit. אף אחד מהם אינו באג פעיל.</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="63" t="n">
+        <v>159</v>
+      </c>
+      <c r="B175" s="64" t="inlineStr">
+        <is>
+          <t>בדיקה סגורה — 14 יום</t>
+        </is>
+      </c>
+      <c r="C175" s="63" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="D175" s="65" t="inlineStr">
+        <is>
+          <t>🔜 החסם הארוך ביותר</t>
+        </is>
+      </c>
+      <c r="E175" s="66" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F175" s="66" t="inlineStr">
+        <is>
+          <t>12 בודקים במשך 14 ימים רצופים, נדרש לחשבון מפתח אישי. השעון רץ בין אם הקוד מושלם ובין אם לא — ולכן זה הפריט שכדאי להתחיל בו ראשון אחרי הצילומים.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="8" customHeight="1"/>
+    <row r="177">
+      <c r="A177" s="10" t="inlineStr">
         <is>
           <t>Legend</t>
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="6" t="inlineStr">
-        <is>
-          <t>✅ Live</t>
-        </is>
-      </c>
-      <c r="B131" s="7" t="inlineStr">
+    <row r="178">
+      <c r="A178" s="6" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="B178" s="7" t="inlineStr">
         <is>
           <t>פרוס ופעיל ב-Render — נראה לכל המשתמשים</t>
         </is>
       </c>
-      <c r="C131" s="6" t="inlineStr"/>
-      <c r="D131" s="8" t="inlineStr"/>
-      <c r="E131" s="9" t="inlineStr"/>
-      <c r="F131" s="9" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="6" t="inlineStr">
+      <c r="C178" s="6" t="inlineStr"/>
+      <c r="D178" s="8" t="inlineStr"/>
+      <c r="E178" s="9" t="inlineStr"/>
+      <c r="F178" s="9" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="6" t="inlineStr">
         <is>
           <t>✅ In APK</t>
         </is>
       </c>
-      <c r="B132" s="7" t="inlineStr">
+      <c r="B179" s="7" t="inlineStr">
         <is>
           <t>כלול ב-APK המותקן — נראה לכל המשתמשים</t>
         </is>
       </c>
-      <c r="C132" s="6" t="inlineStr"/>
-      <c r="D132" s="8" t="inlineStr"/>
-      <c r="E132" s="9" t="inlineStr"/>
-      <c r="F132" s="9" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="6" t="inlineStr">
+      <c r="C179" s="6" t="inlineStr"/>
+      <c r="D179" s="8" t="inlineStr"/>
+      <c r="E179" s="9" t="inlineStr"/>
+      <c r="F179" s="9" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="6" t="inlineStr">
         <is>
           <t>⏳ Next APK</t>
         </is>
       </c>
-      <c r="B133" s="7" t="inlineStr">
+      <c r="B180" s="7" t="inlineStr">
         <is>
           <t>הקוד מוזג — דורש build ו-APK חדש</t>
         </is>
       </c>
-      <c r="C133" s="6" t="inlineStr"/>
-      <c r="D133" s="8" t="inlineStr"/>
-      <c r="E133" s="9" t="inlineStr"/>
-      <c r="F133" s="9" t="inlineStr"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="6" t="inlineStr">
+      <c r="C180" s="6" t="inlineStr"/>
+      <c r="D180" s="8" t="inlineStr"/>
+      <c r="E180" s="9" t="inlineStr"/>
+      <c r="F180" s="9" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="6" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
       </c>
-      <c r="B134" s="7" t="inlineStr">
+      <c r="B181" s="7" t="inlineStr">
         <is>
           <t>שינוי JS — מועבר אוטומטית בהפעלה הבאה</t>
         </is>
       </c>
-      <c r="C134" s="6" t="inlineStr"/>
-      <c r="D134" s="8" t="inlineStr"/>
-      <c r="E134" s="9" t="inlineStr"/>
-      <c r="F134" s="9" t="inlineStr"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="21" t="inlineStr">
+      <c r="C181" s="6" t="inlineStr"/>
+      <c r="D181" s="8" t="inlineStr"/>
+      <c r="E181" s="9" t="inlineStr"/>
+      <c r="F181" s="9" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="21" t="inlineStr">
         <is>
           <t>⏳ ממתין ל-push</t>
         </is>
       </c>
-      <c r="B135" s="22" t="inlineStr">
+      <c r="B182" s="22" t="inlineStr">
         <is>
           <t>הקוד מוכן מקומית — טרם נדחף/נפרס</t>
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="21" t="inlineStr">
+    <row r="183">
+      <c r="A183" s="21" t="inlineStr">
         <is>
           <t>⏳ דורש build</t>
         </is>
       </c>
-      <c r="B136" s="22" t="inlineStr">
+      <c r="B183" s="22" t="inlineStr">
         <is>
           <t>שינוי נייטיב — OTA לא מספיק, צריך AAB/APK חדש</t>
         </is>
       </c>
     </row>
-    <row r="137"/>
-    <row r="138">
-      <c r="A138" s="23" t="inlineStr">
+    <row r="185">
+      <c r="A185" s="23" t="inlineStr">
         <is>
           <t>סיכום Session 6-8</t>
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="24" t="n"/>
-      <c r="B139" s="25" t="inlineStr">
+    <row r="186">
+      <c r="A186" s="24" t="n"/>
+      <c r="B186" s="25" t="inlineStr">
         <is>
           <t>58  —  פריטים חדשים שנוספו (52-109)</t>
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="24" t="n"/>
-      <c r="B140" s="25" t="inlineStr">
+    <row r="187">
+      <c r="A187" s="24" t="n"/>
+      <c r="B187" s="25" t="inlineStr">
         <is>
           <t>56  —  חיים בייצור או ב-OTA</t>
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="24" t="n"/>
-      <c r="B141" s="25" t="inlineStr">
+    <row r="188">
+      <c r="A188" s="24" t="n"/>
+      <c r="B188" s="25" t="inlineStr">
         <is>
           <t>0  —  ממתינים ל-push: הכל נפרס (commit 91ee6d3)</t>
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="24" t="n"/>
-      <c r="B142" s="25" t="inlineStr">
+    <row r="189">
+      <c r="A189" s="24" t="n"/>
+      <c r="B189" s="25" t="inlineStr">
         <is>
           <t>2  —  פתוחים: פריסת טאבלט אמיתית (99) · הגשה ל-Play (19)</t>
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="24" t="n"/>
-      <c r="B143" s="25" t="inlineStr">
+    <row r="190">
+      <c r="A190" s="24" t="n"/>
+      <c r="B190" s="25" t="inlineStr">
         <is>
           <t>8  —  בורסות שאומתו חי (NYSE · TASE · XETRA · LSE) · JSE ביחידה בלבד</t>
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="24" t="n"/>
-      <c r="B144" s="25" t="inlineStr">
+    <row r="191">
+      <c r="A191" s="24" t="n"/>
+      <c r="B191" s="25" t="inlineStr">
         <is>
           <t>48  —  חבילות בדיקה התנהגותיות עוברות (48/48)</t>
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="B145" t="inlineStr">
+    <row r="192">
+      <c r="B192" t="inlineStr">
         <is>
           <t>18  —  ראוטים בשרת · 324 מפתחות i18n × 4 שפות</t>
         </is>
       </c>
     </row>
+    <row r="194">
+      <c r="A194" s="23" t="inlineStr">
+        <is>
+          <t>סיכום Session 10  (2026-08-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="71" t="n"/>
+      <c r="B195" s="71" t="inlineStr">
+        <is>
+          <t>40  —  פריטים חדשים שנוספו (120-159)</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="71" t="n"/>
+      <c r="B196" s="71" t="inlineStr">
+        <is>
+          <t>36  —  חיים בייצור ואומתו — /status build=8602f21 · lkg=redis · sentry=on</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="71" t="n"/>
+      <c r="B197" s="71" t="inlineStr">
+        <is>
+          <t>0  —  ממתינים ל-push</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="71" t="n"/>
+      <c r="B198" s="71" t="inlineStr">
+        <is>
+          <t>1  —  פרוס אך טרם רץ בייצור: ספק נתונים שני (142). Yahoo תקין, הגיבוי לא הופעל אף פעם</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="71" t="n"/>
+      <c r="B199" s="71" t="inlineStr">
+        <is>
+          <t>2  —  פתוחים: צילומי מסך (156) · בדיקה סגורה 14 יום (159)</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="71" t="n"/>
+      <c r="B200" s="71" t="inlineStr">
+        <is>
+          <t>2  —  נדחו במודע לאחר ההשקה: פיצול main.py (157) · חוב תחזוקה L1-L4 (158)</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="71" t="n"/>
+      <c r="B201" s="71" t="inlineStr">
+        <is>
+          <t>11  —  באגים שהתגלו ותוקנו היום. 9 מהם היו בלתי נראים לפני שהבליעות השקטות הוחלפו</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="71" t="n"/>
+      <c r="B202" s="71" t="inlineStr">
+        <is>
+          <t>18  —  שלבי CI על כל דחיפה · 4 חבילות בדיקה עוברות</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="71" t="n"/>
+      <c r="B203" s="71" t="inlineStr">
+        <is>
+          <t>259  —  מפתחות i18n בכל אחת מ-4 השפות (היו 247)</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="72" t="n"/>
+      <c r="B204" s="72" t="inlineStr">
+        <is>
+          <t>אימות עצמאי:  .\check.bat  —  מי רץ בשרת, אם אפסטאש מחובר, אם Sentry דולק, ומצב ה-CI</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="10">
+    <mergeCell ref="A166:F166"/>
+    <mergeCell ref="A194:F194"/>
     <mergeCell ref="A97:F97"/>
+    <mergeCell ref="A131:F131"/>
+    <mergeCell ref="A145:F145"/>
+    <mergeCell ref="A171:F171"/>
     <mergeCell ref="A109:F109"/>
     <mergeCell ref="A59:F59"/>
     <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A156:F156"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BuddhaVest_Progress.xlsx
+++ b/BuddhaVest_Progress.xlsx
@@ -202,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -404,6 +404,10 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -771,7 +775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F204"/>
+  <dimension ref="A1:F237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5907,255 +5911,960 @@
         </is>
       </c>
     </row>
-    <row r="176" ht="8" customHeight="1"/>
+    <row r="176" ht="8" customHeight="1">
+      <c r="A176" s="63" t="n">
+        <v>160</v>
+      </c>
+      <c r="B176" s="64" t="inlineStr">
+        <is>
+          <t>באג · מכפיל רווח 16955.4 על ORA.TA</t>
+        </is>
+      </c>
+      <c r="C176" s="63" t="inlineStr">
+        <is>
+          <t>Backend / Correctness</t>
+        </is>
+      </c>
+      <c r="D176" s="65" t="inlineStr">
+        <is>
+          <t>✅ Live — אומת חי</t>
+        </is>
+      </c>
+      <c r="E176" s="66" t="inlineStr">
+        <is>
+          <t>assets/1BuddhaVest/analyzer.py</t>
+        </is>
+      </c>
+      <c r="F176" s="66" t="inlineStr">
+        <is>
+          <t>החישוב שהוספתי אתמול חילק מחיר באגורות (34,250) ב-EPS בדולר (2.02). 34250/2.02=16955.4 בדיוק. פי 299: 100 מהאגורות ועוד 2.99 משער החליפין. הנכון 56.6. האפליקציה נתנה לזה ציון 20 וכתבה 'יקר'.</t>
+        </is>
+      </c>
+    </row>
     <row r="177">
-      <c r="A177" s="10" t="inlineStr">
+      <c r="A177" s="63" t="n">
+        <v>161</v>
+      </c>
+      <c r="B177" s="64" t="inlineStr">
+        <is>
+          <t>תיקון · מכפיל רווח מחושב רק כשהיחידות מוכחות</t>
+        </is>
+      </c>
+      <c r="C177" s="63" t="inlineStr">
+        <is>
+          <t>Backend / Correctness</t>
+        </is>
+      </c>
+      <c r="D177" s="65" t="inlineStr">
+        <is>
+          <t>✅ Live — אומת חי</t>
+        </is>
+      </c>
+      <c r="E177" s="66" t="inlineStr">
+        <is>
+          <t>analyzer.py · _price_eps_units_agree</t>
+        </is>
+      </c>
+      <c r="F177" s="66" t="inlineStr">
+        <is>
+          <t>חוסם לפי סיומת בורסה (.TA/.L/.JO) וגם לפי קוד מטבע (ILA/GBp/ZAc), חוסם פער מוצהר בין מטבע מסחר לדיווח, ותקרת שפיות 500. כל השאר -&gt; 'לא זמין', הודעה שכבר קיימת ב-4 שפות. main.py כבר סירב לחשב מכפילים כאלה; שברתי את זה מקובץ אחר.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="63" t="n">
+        <v>162</v>
+      </c>
+      <c r="B178" s="64" t="inlineStr">
+        <is>
+          <t>באג · שווי שוק פי 100 בכל מניות ת"א/לונדון/יוהנסבורג</t>
+        </is>
+      </c>
+      <c r="C178" s="63" t="inlineStr">
+        <is>
+          <t>Backend / Correctness</t>
+        </is>
+      </c>
+      <c r="D178" s="65" t="inlineStr">
+        <is>
+          <t>✅ Live — אומת חי</t>
+        </is>
+      </c>
+      <c r="E178" s="66" t="inlineStr">
+        <is>
+          <t>assets/1BuddhaVest/main.py</t>
+        </is>
+      </c>
+      <c r="F178" s="66" t="inlineStr">
+        <is>
+          <t>ORA.TA הוצגה ₪2,106 מיליארד במקום ₪21. POLI.TA (בנק הפועלים) ₪10,048 מיליארד במקום ₪101 — חברת 10 טריליון שקל, במסך המניה וגם בטבלת השוק שם זה עיוות את המיון. docstring בקוד טען את ההפך ובגלל זה איש לא תפס.</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="63" t="n">
+        <v>163</v>
+      </c>
+      <c r="B179" s="64" t="inlineStr">
+        <is>
+          <t>תיקון · שווי שוק מוצלב מול מניות × מחיר</t>
+        </is>
+      </c>
+      <c r="C179" s="63" t="inlineStr">
+        <is>
+          <t>Backend / Correctness</t>
+        </is>
+      </c>
+      <c r="D179" s="65" t="inlineStr">
+        <is>
+          <t>✅ Live — אומת חי</t>
+        </is>
+      </c>
+      <c r="E179" s="66" t="inlineStr">
+        <is>
+          <t>main.py · _reconcile_market_cap, _shares_outstanding</t>
+        </is>
+      </c>
+      <c r="F179" s="66" t="inlineStr">
+        <is>
+          <t>לא מחלק ב-100 עיוור — מחשב מחדש מ-sharesOutstanding, ואם חסר אז מרווח נקי÷EPS (חסר-יחידות, שורד פיצול מטבע). יחס ~1 נשאר, ~100 מתוקן, אחר -&gt; לא מפרסם כלום ושולח ל-Sentry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="63" t="n">
+        <v>164</v>
+      </c>
+      <c r="B180" s="64" t="inlineStr">
+        <is>
+          <t>באג · מטבע דוחות מנוחש = מטבע מסחר</t>
+        </is>
+      </c>
+      <c r="C180" s="63" t="inlineStr">
+        <is>
+          <t>Backend / Correctness</t>
+        </is>
+      </c>
+      <c r="D180" s="65" t="inlineStr">
+        <is>
+          <t>✅ Live — אומת חי</t>
+        </is>
+      </c>
+      <c r="E180" s="66" t="inlineStr">
+        <is>
+          <t>main.py</t>
+        </is>
+      </c>
+      <c r="F180" s="66" t="inlineStr">
+        <is>
+          <t>financialCurrency חסר ב-ORA.TA, השרת נפל חזרה למטבע המסחר וסימן $989.5M הכנסות כ-₪989.5M. האמת ₪2.96 מיליארד. פי 3 על הכנסות, רווח נקי, מזומן ותזרים — עם סימן מטבע שגרם למספר להיראות מדויק.</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="63" t="n">
+        <v>165</v>
+      </c>
+      <c r="B181" s="64" t="inlineStr">
+        <is>
+          <t>תיקון · השרת מודה כשהוא לא יודע</t>
+        </is>
+      </c>
+      <c r="C181" s="63" t="inlineStr">
+        <is>
+          <t>Backend / Correctness</t>
+        </is>
+      </c>
+      <c r="D181" s="65" t="inlineStr">
+        <is>
+          <t>✅ Live — אומת חי</t>
+        </is>
+      </c>
+      <c r="E181" s="66" t="inlineStr">
+        <is>
+          <t>main.py · financial_currency_known</t>
+        </is>
+      </c>
+      <c r="F181" s="66" t="inlineStr">
+        <is>
+          <t>שדה חדש. בבורסות שבהן פיצול נפוץ השרת שולח known=false והלקוח מציג בלי סימן מטבע. מספר בלי תווית חלקי; מספר עם תווית שגויה שקר — ורק את הראשון הקורא יכול לתקן.</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="63" t="n">
+        <v>166</v>
+      </c>
+      <c r="B182" s="64" t="inlineStr">
+        <is>
+          <t>שיפור · זיהוי מטבע הדוחות מהחשבון</t>
+        </is>
+      </c>
+      <c r="C182" s="63" t="inlineStr">
+        <is>
+          <t>Backend / Correctness</t>
+        </is>
+      </c>
+      <c r="D182" s="65" t="inlineStr">
+        <is>
+          <t>✅ Live — אומת חי</t>
+        </is>
+      </c>
+      <c r="E182" s="66" t="inlineStr">
+        <is>
+          <t>main.py · _infer_financial_currency</t>
+        </is>
+      </c>
+      <c r="F182" s="66" t="inlineStr">
+        <is>
+          <t>שווי שוק במטבע מסחר, רווח נקי במטבע דיווח -&gt; היחס הוא מכפיל אמיתי כששניהם זהים, ומכפיל×שער כשלא. ORA.TA 169 גולמי / 56.6 מחולק; POLI.TA 10.4 / 3.5. בדיוק אחד סביר בכל מניה, ובשתיהן זה הנכון. לעולם לא דורס ערך שהספק דיווח; דו-משמעי = לא ידוע.</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="63" t="n">
+        <v>167</v>
+      </c>
+      <c r="B183" s="64" t="inlineStr">
+        <is>
+          <t>באג · מחרוזת ריקה חזרה להיות סימן דולר</t>
+        </is>
+      </c>
+      <c r="C183" s="63" t="inlineStr">
+        <is>
+          <t>App / Correctness</t>
+        </is>
+      </c>
+      <c r="D183" s="65" t="inlineStr">
+        <is>
+          <t>⏳ דורש OTA</t>
+        </is>
+      </c>
+      <c r="E183" s="66" t="inlineStr">
+        <is>
+          <t>screens/MetricHistoryScreen.js</t>
+        </is>
+      </c>
+      <c r="F183" s="66" t="inlineStr">
+        <is>
+          <t>'' הוא falsy, ו-route.params.cur || '$' החזיר את הדולר. התיקון החזיק על האריח ונשבר לחיצה אחת אחריו — סימן דולר על מספר שאיש לא קבע אם הוא שקל או דולר.</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="63" t="n">
+        <v>168</v>
+      </c>
+      <c r="B184" s="64" t="inlineStr">
+        <is>
+          <t>תיקון · ?? במקום || בכל סימני המטבע</t>
+        </is>
+      </c>
+      <c r="C184" s="63" t="inlineStr">
+        <is>
+          <t>App / Correctness</t>
+        </is>
+      </c>
+      <c r="D184" s="65" t="inlineStr">
+        <is>
+          <t>⏳ דורש OTA</t>
+        </is>
+      </c>
+      <c r="E184" s="66" t="inlineStr">
+        <is>
+          <t>MetricHistoryScreen.js · StockScreen.js · PriceChart.js</t>
+        </is>
+      </c>
+      <c r="F184" s="66" t="inlineStr">
+        <is>
+          <t>3 קבצים + שלב CI שסורק את ה-AST של הלקוח ונופל על כל סימן מטבע עם ברירת מחדל ||. השלב כבר תפס אחד ב-PriceChart שלא הייתי מודע אליו.</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="63" t="n">
+        <v>169</v>
+      </c>
+      <c r="B185" s="64" t="inlineStr">
+        <is>
+          <t>באג · /status דיווח קומיט ישן בשתי דחיפות</t>
+        </is>
+      </c>
+      <c r="C185" s="63" t="inlineStr">
+        <is>
+          <t>Infra / Trust</t>
+        </is>
+      </c>
+      <c r="D185" s="65" t="inlineStr">
+        <is>
+          <t>✅ Live — אומת חי</t>
+        </is>
+      </c>
+      <c r="E185" s="66" t="inlineStr">
+        <is>
+          <t>main.py · /status</t>
+        </is>
+      </c>
+      <c r="F185" s="66" t="inlineStr">
+        <is>
+          <t>הפריסה עברה והקוד החדש רץ בוודאות (ORA.TA השתנתה), ו-build עדיין הראה קומיט משתי דחיפות אחורה. RENDER_GIT_COMMIT הוא משתנה סביבה: הוא אומר מה אמרו ל-Render, לא מה רץ. check.bat היה מדווח על פריסה מוצלחת ככישלון.</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="63" t="n">
+        <v>170</v>
+      </c>
+      <c r="B186" s="64" t="inlineStr">
+        <is>
+          <t>תיקון · /status מחזיר טביעת אצבע של המקור</t>
+        </is>
+      </c>
+      <c r="C186" s="63" t="inlineStr">
+        <is>
+          <t>Infra / Trust</t>
+        </is>
+      </c>
+      <c r="D186" s="65" t="inlineStr">
+        <is>
+          <t>✅ Live — אומת חי</t>
+        </is>
+      </c>
+      <c r="E186" s="66" t="inlineStr">
+        <is>
+          <t>main.py · _source_digest · scripts/check-live.js</t>
+        </is>
+      </c>
+      <c r="F186" s="66" t="inlineStr">
+        <is>
+          <t>code=8423c9284668 — sha256 על 8 קבצי השרת שהתהליך באמת טען. לא יכול לסטות, כי הוא מחושב מהבייטים בזיכרון. check.bat מחשב את אותה טביעה מהתיקייה ומשווה; הקומיט נשאר כמידע בלבד. \r מוסר בשני הצדדים (CRLF בחלונות מול LF בלינוקס).</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="63" t="n">
+        <v>171</v>
+      </c>
+      <c r="B187" s="64" t="inlineStr">
+        <is>
+          <t>באג · הבנייה ב-GitHub נכשלה על except: pass</t>
+        </is>
+      </c>
+      <c r="C187" s="63" t="inlineStr">
+        <is>
+          <t>Infra / Process</t>
+        </is>
+      </c>
+      <c r="D187" s="65" t="inlineStr">
+        <is>
+          <t>✅ Live — אומת חי</t>
+        </is>
+      </c>
+      <c r="E187" s="66" t="inlineStr">
+        <is>
+          <t>main.py · _shares_outstanding</t>
+        </is>
+      </c>
+      <c r="F187" s="66" t="inlineStr">
+        <is>
+          <t>כלל שאני כתבתי באותו יום תפס טיפול חריגות שקט שאני כתבתי באותו יום. הוא גם הסתיר באג אמיתי: float(True)=1.0, כלומר בוליאני היה הופך למספר מניות אחת ושווי השוק היה 'מאומת' מול מחיר מניה בודדת.</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="63" t="n">
+        <v>172</v>
+      </c>
+      <c r="B188" s="64" t="inlineStr">
+        <is>
+          <t>תיקון · בדיקת טיפוס במקום try/except</t>
+        </is>
+      </c>
+      <c r="C188" s="63" t="inlineStr">
+        <is>
+          <t>Backend / Correctness</t>
+        </is>
+      </c>
+      <c r="D188" s="65" t="inlineStr">
+        <is>
+          <t>✅ Live — אומת חי</t>
+        </is>
+      </c>
+      <c r="E188" s="66" t="inlineStr">
+        <is>
+          <t>main.py · _shares_outstanding · test_market_cap.py</t>
+        </is>
+      </c>
+      <c r="F188" s="66" t="inlineStr">
+        <is>
+          <t>דוחה בוליאנים, NaN, inf, מחרוזות ומספרים שליליים. 12 בדיקות ג'אנק חדשות.</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="63" t="n">
+        <v>173</v>
+      </c>
+      <c r="B189" s="64" t="inlineStr">
+        <is>
+          <t>כלי · הרצת כל ה-CI מקומית לפני דחיפה</t>
+        </is>
+      </c>
+      <c r="C189" s="63" t="inlineStr">
+        <is>
+          <t>Infra / Process</t>
+        </is>
+      </c>
+      <c r="D189" s="65" t="inlineStr">
+        <is>
+          <t>✅ מוכן</t>
+        </is>
+      </c>
+      <c r="E189" s="66" t="inlineStr">
+        <is>
+          <t>scripts/run-ci.js · ci.bat</t>
+        </is>
+      </c>
+      <c r="F189" s="66" t="inlineStr">
+        <is>
+          <t>השורש לא היה השורה אלא ההרגל: הרצתי את קבצי הטסטים והחלטתי שזה CI. יותר מחצי מ-ci.yml הן בדיקות lint על המקור, וזה החצי שנשבר. run-ci.js קורא את ci.yml ומריץ כל שלב כפי שהוא — לא משכפל, ולכן לא יכול להתפצל ממה ש-GitHub מריץ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="63" t="n">
+        <v>174</v>
+      </c>
+      <c r="B190" s="64" t="inlineStr">
+        <is>
+          <t>כלי · push.bat עם שער CI ודילוג על OTA</t>
+        </is>
+      </c>
+      <c r="C190" s="63" t="inlineStr">
+        <is>
+          <t>Infra / Process</t>
+        </is>
+      </c>
+      <c r="D190" s="65" t="inlineStr">
+        <is>
+          <t>✅ מוכן</t>
+        </is>
+      </c>
+      <c r="E190" s="66" t="inlineStr">
+        <is>
+          <t>push.bat</t>
+        </is>
+      </c>
+      <c r="F190" s="66" t="inlineStr">
+        <is>
+          <t>.\push.bat "msg" ci מריץ את הבדיקות ועוצר על אדום. .\push.bat "msg" noota מדלג על ה-bundle. השער הוא opt-in אחרי שהתברר שהוא לא סיבת הקריסות.</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="63" t="n">
+        <v>175</v>
+      </c>
+      <c r="B191" s="64" t="inlineStr">
+        <is>
+          <t>חקירה · המחשב נכבה שלוש פעמים</t>
+        </is>
+      </c>
+      <c r="C191" s="63" t="inlineStr">
+        <is>
+          <t>Infra / Environment</t>
+        </is>
+      </c>
+      <c r="D191" s="65" t="inlineStr">
+        <is>
+          <t>🔎 לא נסגר</t>
+        </is>
+      </c>
+      <c r="E191" s="66" t="inlineStr">
+        <is>
+          <t>Event Viewer · push.bat</t>
+        </is>
+      </c>
+      <c r="F191" s="66" t="inlineStr">
+        <is>
+          <t>12/08 15:52 · 12/08 16:38 · 13/08 10:45. כולן Event 41+6008, אף אחת לא 1074 — שום תוכנה לא ביקשה כיבוי, המחשב נתקע או איבד חשמל. שתי הראשונות לפני שער ה-CI, כלומר הוא לא הסיבה. דחיפה עם noota שרדה. החשוד: bundle של Metro על 12 ליבות. לא הוכח — אם זו חומרה, maxWorkers רק ידחה את זה.</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="63" t="n">
+        <v>176</v>
+      </c>
+      <c r="B192" s="64" t="inlineStr">
+        <is>
+          <t>תיקון · הגבלת מספר ה-workers של Metro</t>
+        </is>
+      </c>
+      <c r="C192" s="63" t="inlineStr">
+        <is>
+          <t>Infra / Environment</t>
+        </is>
+      </c>
+      <c r="D192" s="65" t="inlineStr">
+        <is>
+          <t>⏳ נכנס לתוקף ב-bundle הבא</t>
+        </is>
+      </c>
+      <c r="E192" s="66" t="inlineStr">
+        <is>
+          <t>metro.config.js (חדש)</t>
+        </is>
+      </c>
+      <c r="F192" s="66" t="inlineStr">
+        <is>
+          <t>לא היה קובץ בכלל, כלומר worker לכל ליבה = 12. עכשיו 4, כשליש מהמעבד. bundle איטי שמסתיים עדיף על מהיר שמפיל את המחשב.</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="63" t="n">
+        <v>177</v>
+      </c>
+      <c r="B193" s="64" t="inlineStr">
+        <is>
+          <t>שיפור · ה-OTA רץ על שרת GitHub, לא על המחשב</t>
+        </is>
+      </c>
+      <c r="C193" s="63" t="inlineStr">
+        <is>
+          <t>Infra / Environment</t>
+        </is>
+      </c>
+      <c r="D193" s="65" t="inlineStr">
+        <is>
+          <t>✅ הורץ בהצלחה</t>
+        </is>
+      </c>
+      <c r="E193" s="66" t="inlineStr">
+        <is>
+          <t>.github/workflows/ota.yml (חדש)</t>
+        </is>
+      </c>
+      <c r="F193" s="66" t="inlineStr">
+        <is>
+          <t>מסיר את העומס במקום לקצץ אותו. הפעלה ידנית — רוב הדחיפות כאן הן שרת בלבד ו-Render נפרס מהן לבד. דורש סוד EXPO_TOKEN; השלב הראשון אומר את זה מפורשות במקום ליפול שלוש דקות לתוך bundle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="63" t="n">
+        <v>178</v>
+      </c>
+      <c r="B194" s="64" t="inlineStr">
+        <is>
+          <t>תיקון · run-ci.js לעולם לא מפעיל את bash של WSL</t>
+        </is>
+      </c>
+      <c r="C194" s="63" t="inlineStr">
+        <is>
+          <t>Infra / Environment</t>
+        </is>
+      </c>
+      <c r="D194" s="65" t="inlineStr">
+        <is>
+          <t>✅ מוכן</t>
+        </is>
+      </c>
+      <c r="E194" s="66" t="inlineStr">
+        <is>
+          <t>scripts/run-ci.js · resolveBash</t>
+        </is>
+      </c>
+      <c r="F194" s="66" t="inlineStr">
+        <is>
+          <t>where.exe bash מחזיר את C:/Windows/System32/bash.exe ראשון, וזה משגר WSL ולא מעטפת — כל קריאה מפעילה מכונה וירטואלית שתופסת זיכרון, ו-run-ci קורא לו 23 פעמים ברצף. Git Bash כלל לא ב-PATH. resolveBash מאתר את ה-bash שליד git.exe, פוסל כל דבר תחת System32, ולא נופל חזרה ל-PATH אלא עוצר עם הסבר.</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="63" t="n">
+        <v>179</v>
+      </c>
+      <c r="B195" s="64" t="inlineStr">
+        <is>
+          <t>תיקון · מדיניות הפרטיות לא הזכירה את Sentry</t>
+        </is>
+      </c>
+      <c r="C195" s="63" t="inlineStr">
+        <is>
+          <t>Legal / Store</t>
+        </is>
+      </c>
+      <c r="D195" s="65" t="inlineStr">
+        <is>
+          <t>⏳ ממתין ל-push</t>
+        </is>
+      </c>
+      <c r="E195" s="66" t="inlineStr">
+        <is>
+          <t>main.py · /privacy</t>
+        </is>
+      </c>
+      <c r="F195" s="66" t="inlineStr">
+        <is>
+          <t>הטענה 'סמלי מניות לא נשמרים' הפכה ללא מדויקת ברגע ש-report(ticker=...) שולח אותם ל-Sentry. נוסף חריג מפורש והפניה למדיניות של Sentry. ניטור בצד הלקוח כבוי לגמרי — אין DSN והחבילה לא מותקנת — אז שום דבר לא עוזב את המכשיר.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="63" t="n">
+        <v>180</v>
+      </c>
+      <c r="B196" s="64" t="inlineStr">
+        <is>
+          <t>בדיקות · שלוש חבילות חדשות + 3 שלבי CI</t>
+        </is>
+      </c>
+      <c r="C196" s="63" t="inlineStr">
+        <is>
+          <t>Testing</t>
+        </is>
+      </c>
+      <c r="D196" s="65" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="E196" s="66" t="inlineStr">
+        <is>
+          <t>test_pe_units.py · test_market_cap.py · test_fin_currency.py</t>
+        </is>
+      </c>
+      <c r="F196" s="66" t="inlineStr">
+        <is>
+          <t>כל אחת נועלת את המדידה החיה שהובילה לתיקון, ובעיקר את מצב הכישלון: מותר לקוד לא לדעת, אסור לו לטעות בביטחון. סה"כ 22 שלבי CI, 8 חבילות בדיקה.</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="10" t="inlineStr">
         <is>
           <t>Legend</t>
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="6" t="inlineStr">
-        <is>
-          <t>✅ Live</t>
-        </is>
-      </c>
-      <c r="B178" s="7" t="inlineStr">
+    <row r="199">
+      <c r="A199" s="6" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="B199" s="7" t="inlineStr">
         <is>
           <t>פרוס ופעיל ב-Render — נראה לכל המשתמשים</t>
         </is>
       </c>
-      <c r="C178" s="6" t="inlineStr"/>
-      <c r="D178" s="8" t="inlineStr"/>
-      <c r="E178" s="9" t="inlineStr"/>
-      <c r="F178" s="9" t="inlineStr"/>
-    </row>
-    <row r="179">
-      <c r="A179" s="6" t="inlineStr">
+      <c r="C199" s="6" t="inlineStr"/>
+      <c r="D199" s="8" t="inlineStr"/>
+      <c r="E199" s="9" t="inlineStr"/>
+      <c r="F199" s="9" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="6" t="inlineStr">
         <is>
           <t>✅ In APK</t>
         </is>
       </c>
-      <c r="B179" s="7" t="inlineStr">
+      <c r="B200" s="7" t="inlineStr">
         <is>
           <t>כלול ב-APK המותקן — נראה לכל המשתמשים</t>
         </is>
       </c>
-      <c r="C179" s="6" t="inlineStr"/>
-      <c r="D179" s="8" t="inlineStr"/>
-      <c r="E179" s="9" t="inlineStr"/>
-      <c r="F179" s="9" t="inlineStr"/>
-    </row>
-    <row r="180">
-      <c r="A180" s="6" t="inlineStr">
+      <c r="C200" s="6" t="inlineStr"/>
+      <c r="D200" s="8" t="inlineStr"/>
+      <c r="E200" s="9" t="inlineStr"/>
+      <c r="F200" s="9" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="6" t="inlineStr">
         <is>
           <t>⏳ Next APK</t>
         </is>
       </c>
-      <c r="B180" s="7" t="inlineStr">
+      <c r="B201" s="7" t="inlineStr">
         <is>
           <t>הקוד מוזג — דורש build ו-APK חדש</t>
         </is>
       </c>
-      <c r="C180" s="6" t="inlineStr"/>
-      <c r="D180" s="8" t="inlineStr"/>
-      <c r="E180" s="9" t="inlineStr"/>
-      <c r="F180" s="9" t="inlineStr"/>
-    </row>
-    <row r="181">
-      <c r="A181" s="6" t="inlineStr">
+      <c r="C201" s="6" t="inlineStr"/>
+      <c r="D201" s="8" t="inlineStr"/>
+      <c r="E201" s="9" t="inlineStr"/>
+      <c r="F201" s="9" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="6" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
       </c>
-      <c r="B181" s="7" t="inlineStr">
+      <c r="B202" s="7" t="inlineStr">
         <is>
           <t>שינוי JS — מועבר אוטומטית בהפעלה הבאה</t>
         </is>
       </c>
-      <c r="C181" s="6" t="inlineStr"/>
-      <c r="D181" s="8" t="inlineStr"/>
-      <c r="E181" s="9" t="inlineStr"/>
-      <c r="F181" s="9" t="inlineStr"/>
-    </row>
-    <row r="182">
-      <c r="A182" s="21" t="inlineStr">
+      <c r="C202" s="6" t="inlineStr"/>
+      <c r="D202" s="8" t="inlineStr"/>
+      <c r="E202" s="9" t="inlineStr"/>
+      <c r="F202" s="9" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="21" t="inlineStr">
         <is>
           <t>⏳ ממתין ל-push</t>
         </is>
       </c>
-      <c r="B182" s="22" t="inlineStr">
+      <c r="B203" s="22" t="inlineStr">
         <is>
           <t>הקוד מוכן מקומית — טרם נדחף/נפרס</t>
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="21" t="inlineStr">
+    <row r="204">
+      <c r="A204" s="21" t="inlineStr">
         <is>
           <t>⏳ דורש build</t>
         </is>
       </c>
-      <c r="B183" s="22" t="inlineStr">
+      <c r="B204" s="22" t="inlineStr">
         <is>
           <t>שינוי נייטיב — OTA לא מספיק, צריך AAB/APK חדש</t>
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="23" t="inlineStr">
+    <row r="206">
+      <c r="A206" s="23" t="inlineStr">
         <is>
           <t>סיכום Session 6-8</t>
         </is>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" s="24" t="n"/>
-      <c r="B186" s="25" t="inlineStr">
+    <row r="207">
+      <c r="A207" s="24" t="n"/>
+      <c r="B207" s="25" t="inlineStr">
         <is>
           <t>58  —  פריטים חדשים שנוספו (52-109)</t>
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="24" t="n"/>
-      <c r="B187" s="25" t="inlineStr">
+    <row r="208">
+      <c r="A208" s="24" t="n"/>
+      <c r="B208" s="25" t="inlineStr">
         <is>
           <t>56  —  חיים בייצור או ב-OTA</t>
         </is>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" s="24" t="n"/>
-      <c r="B188" s="25" t="inlineStr">
+    <row r="209">
+      <c r="A209" s="24" t="n"/>
+      <c r="B209" s="25" t="inlineStr">
         <is>
           <t>0  —  ממתינים ל-push: הכל נפרס (commit 91ee6d3)</t>
         </is>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" s="24" t="n"/>
-      <c r="B189" s="25" t="inlineStr">
+    <row r="210">
+      <c r="A210" s="24" t="n"/>
+      <c r="B210" s="25" t="inlineStr">
         <is>
           <t>2  —  פתוחים: פריסת טאבלט אמיתית (99) · הגשה ל-Play (19)</t>
         </is>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" s="24" t="n"/>
-      <c r="B190" s="25" t="inlineStr">
+    <row r="211">
+      <c r="A211" s="24" t="n"/>
+      <c r="B211" s="25" t="inlineStr">
         <is>
           <t>8  —  בורסות שאומתו חי (NYSE · TASE · XETRA · LSE) · JSE ביחידה בלבד</t>
         </is>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" s="24" t="n"/>
-      <c r="B191" s="25" t="inlineStr">
+    <row r="212">
+      <c r="A212" s="24" t="n"/>
+      <c r="B212" s="25" t="inlineStr">
         <is>
           <t>48  —  חבילות בדיקה התנהגותיות עוברות (48/48)</t>
         </is>
       </c>
     </row>
-    <row r="192">
-      <c r="B192" t="inlineStr">
+    <row r="213">
+      <c r="B213" t="inlineStr">
         <is>
           <t>18  —  ראוטים בשרת · 324 מפתחות i18n × 4 שפות</t>
         </is>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" s="23" t="inlineStr">
+    <row r="215">
+      <c r="A215" s="23" t="inlineStr">
         <is>
           <t>סיכום Session 10  (2026-08-08)</t>
         </is>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" s="71" t="n"/>
-      <c r="B195" s="71" t="inlineStr">
+    <row r="216">
+      <c r="A216" s="71" t="n"/>
+      <c r="B216" s="71" t="inlineStr">
         <is>
           <t>40  —  פריטים חדשים שנוספו (120-159)</t>
         </is>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" s="71" t="n"/>
-      <c r="B196" s="71" t="inlineStr">
+    <row r="217">
+      <c r="A217" s="71" t="n"/>
+      <c r="B217" s="71" t="inlineStr">
         <is>
           <t>36  —  חיים בייצור ואומתו — /status build=8602f21 · lkg=redis · sentry=on</t>
         </is>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" s="71" t="n"/>
-      <c r="B197" s="71" t="inlineStr">
+    <row r="218">
+      <c r="A218" s="71" t="n"/>
+      <c r="B218" s="71" t="inlineStr">
         <is>
           <t>0  —  ממתינים ל-push</t>
         </is>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" s="71" t="n"/>
-      <c r="B198" s="71" t="inlineStr">
+    <row r="219">
+      <c r="A219" s="71" t="n"/>
+      <c r="B219" s="71" t="inlineStr">
         <is>
           <t>1  —  פרוס אך טרם רץ בייצור: ספק נתונים שני (142). Yahoo תקין, הגיבוי לא הופעל אף פעם</t>
         </is>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" s="71" t="n"/>
-      <c r="B199" s="71" t="inlineStr">
+    <row r="220">
+      <c r="A220" s="71" t="n"/>
+      <c r="B220" s="71" t="inlineStr">
         <is>
           <t>2  —  פתוחים: צילומי מסך (156) · בדיקה סגורה 14 יום (159)</t>
         </is>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" s="71" t="n"/>
-      <c r="B200" s="71" t="inlineStr">
+    <row r="221">
+      <c r="A221" s="71" t="n"/>
+      <c r="B221" s="71" t="inlineStr">
         <is>
           <t>2  —  נדחו במודע לאחר ההשקה: פיצול main.py (157) · חוב תחזוקה L1-L4 (158)</t>
         </is>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" s="71" t="n"/>
-      <c r="B201" s="71" t="inlineStr">
+    <row r="222">
+      <c r="A222" s="71" t="n"/>
+      <c r="B222" s="71" t="inlineStr">
         <is>
           <t>11  —  באגים שהתגלו ותוקנו היום. 9 מהם היו בלתי נראים לפני שהבליעות השקטות הוחלפו</t>
         </is>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" s="71" t="n"/>
-      <c r="B202" s="71" t="inlineStr">
+    <row r="223">
+      <c r="A223" s="71" t="n"/>
+      <c r="B223" s="71" t="inlineStr">
         <is>
           <t>18  —  שלבי CI על כל דחיפה · 4 חבילות בדיקה עוברות</t>
         </is>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" s="71" t="n"/>
-      <c r="B203" s="71" t="inlineStr">
+    <row r="224">
+      <c r="A224" s="71" t="n"/>
+      <c r="B224" s="71" t="inlineStr">
         <is>
           <t>259  —  מפתחות i18n בכל אחת מ-4 השפות (היו 247)</t>
         </is>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" s="72" t="n"/>
-      <c r="B204" s="72" t="inlineStr">
+    <row r="225">
+      <c r="A225" s="72" t="n"/>
+      <c r="B225" s="72" t="inlineStr">
         <is>
           <t>אימות עצמאי:  .\check.bat  —  מי רץ בשרת, אם אפסטאש מחובר, אם Sentry דולק, ומצב ה-CI</t>
         </is>
       </c>
     </row>
+    <row r="227">
+      <c r="A227" s="73" t="inlineStr">
+        <is>
+          <t>סיכום סשן 11 — 13/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="B228" s="74" t="inlineStr">
+        <is>
+          <t>21  —  פריטים חדשים (160-180)</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="B229" s="74" t="inlineStr">
+        <is>
+          <t>17  —  חיים בייצור ואומתו חי — /status build=b096bf3 · code=8423c9284668 · lkg=redis · sentry=on</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="B230" s="74" t="inlineStr">
+        <is>
+          <t>2  —  ממתינים ל-OTA: סימן המטבע החסר (167,168). השרת כבר שולח את הדגל הנכון.</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="B231" s="74" t="inlineStr">
+        <is>
+          <t>1  —  ממתין ל-push: תיקון מדיניות הפרטיות (179)</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="B232" s="74" t="inlineStr">
+        <is>
+          <t>1  —  לא נסגר: סיבת הקריסות של המחשב (175). מוצע חשוד, לא הוכח.</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="B233" s="74" t="inlineStr">
+        <is>
+          <t>6  —  באגים שהתגלו היום. 4 מהם היו שלי, 3 מתוכם נולדו בתיקון של אתמול.</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="B234" s="74" t="inlineStr">
+        <is>
+          <t>22  —  שלבי CI על כל דחיפה · 8 חבילות בדיקה · run-ci.js מריץ את כולם מקומית</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="B235" s="74" t="inlineStr">
+        <is>
+          <t>מדידות חיות: ORA.TA שווי שוק ₪2,106מ' -&gt; ₪20.69מ' · מכפיל 16955.4 -&gt; לא זמין · מטבע דוחות USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="B236" s="74" t="inlineStr">
+        <is>
+          <t>מדידות חיות: POLI.TA שווי שוק ₪10,048מ' -&gt; ₪100.89מ' · מטבע דוחות ILS</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="B237" s="74" t="inlineStr">
+        <is>
+          <t>אימות עצמאי:  .\check.bat  —  משווה טביעת אצבע של המקור, לא קומיט. .\ci.bat  —  כל 22 השלבים.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="9">
     <mergeCell ref="A166:F166"/>
-    <mergeCell ref="A194:F194"/>
     <mergeCell ref="A97:F97"/>
     <mergeCell ref="A131:F131"/>
     <mergeCell ref="A145:F145"/>

--- a/BuddhaVest_Progress.xlsx
+++ b/BuddhaVest_Progress.xlsx
@@ -202,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -409,6 +409,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -775,7 +778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F237"/>
+  <dimension ref="A1:F255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4597,7 +4600,7 @@
       </c>
       <c r="D127" s="53" t="inlineStr">
         <is>
-          <t>⏳ טיוטה — לא הוגש</t>
+          <t>✅ הושלם ואומת בתמליל</t>
         </is>
       </c>
       <c r="E127" s="47" t="inlineStr">
@@ -4607,7 +4610,7 @@
       </c>
       <c r="F127" s="47" t="inlineStr">
         <is>
-          <t>התשובות מולאו ונשמרו כטיוטה, אבל הטופס מעולם לא הוגש — לוח הבקרה של Play מציג עיגול ריק ליד "אבטחת נתונים". אומת ישירות בקונסולה: הטופס נפתח בשלב 1 מתוך 5 עם כפתור "שמירת טיוטה" פעיל, והתשובות של שלב 2 (כן לאיסוף, כן להצפנה) שמורות. צריך לעבור שלבים 3-4-5 וללחוץ שליחה במסך התצוגה המקדימה. 5 סוגי נתונים שהוצהרו: אינטראקציות · חיפוש · תוכן משתמש · גלישה · מזהה מכשיר.</t>
+          <t>התשובות מולאו, כל 5 השלבים הושלמו ונשמרו. אומת ב-13/08/2026 מול התמליל: התצוגה המקדימה הציגה 'לא מתבצע שיתוף נתונים' + שלוש קטגוריות שנאספות (גלישה באינטרנט · פעילות באפליקציות · מזהה המכשיר), והמשתמש אישר שמירה. הסטטוס הקודם כאן ('טיוטה — לא הוגש') היה נכון לרגע מוקדם יותר ולא עודכן.</t>
         </is>
       </c>
     </row>
@@ -4661,7 +4664,7 @@
       </c>
       <c r="D129" s="53" t="inlineStr">
         <is>
-          <t>🔜 לא התחיל</t>
+          <t>✅ הושלם — 12 קבצים</t>
         </is>
       </c>
       <c r="E129" s="47" t="inlineStr">
@@ -4671,7 +4674,7 @@
       </c>
       <c r="F129" s="47" t="inlineStr">
         <is>
-          <t>הפער היחיד שנותר בדף החנות.  ◀ ראה פריט 156: המדריך והבודק האוטומטי מוכנים, ו-5 הקבצים שהיו בתיקייה התבררו כ-placeholder ריקים.</t>
+          <t>6 באנגלית + 6 בעברית, 1080x1920, יחס 1.78 (מתחת לתקרת ה-2:1 של גוגל, כלומר גם כשירים לקידום). צולמו מהמכשיר, הועברו ב-USB ונחתכו. הועלו ל-Play Console ב-15/08/2026.</t>
         </is>
       </c>
     </row>
@@ -5807,7 +5810,7 @@
       </c>
       <c r="D172" s="65" t="inlineStr">
         <is>
-          <t>🔜 פתוח — חוסם הגשה</t>
+          <t>✅ הושלם — כבר לא חוסם</t>
         </is>
       </c>
       <c r="E172" s="66" t="inlineStr">
@@ -5817,7 +5820,7 @@
       </c>
       <c r="F172" s="66" t="inlineStr">
         <is>
-          <t>הפריט היחיד שחוסם בפועל את ההגשה. מדריך וסקריפט בדיקה מוכנים (154). דורש את האפליקציה רצה על מכשיר — 6 מסכים, 1080x1920.</t>
+          <t>store-screenshots/en-play/ ו-he-play/, 6 בכל אחת. אומת: 1080x1920 · יחס 1.78 · ללא ערוץ אלפא. הועלו לדף החנות. זה היה החסם האחרון בהגשה והוא נסגר.</t>
         </is>
       </c>
     </row>
@@ -6542,323 +6545,695 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="10" t="inlineStr">
+      <c r="A198" t="n">
+        <v>181</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Play Console · גישה לאפליקציה</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>✅ הוגש</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>'לא' — אין חלקים מוגבלים, אין מסך התחברות, אין תוכן בתשלום. עקבי עם ההצהרה ב-Data Safety שהאפליקציה לא מאפשרת יצירת חשבון.</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>182</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Play Console · מודעות</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>✅ הוגש</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>'לא'. נסרקו כל התלויות ב-package.json — אין AdMob, אין רשת פרסום, אין מזהה פרסום. הצהרה הפיכה: ביום שיתווסף AdMob צריך לשנות גם כאן וגם ב-Data Safety (מזהה פרסום + מטרת שיווק).</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>183</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Play Console · דירוג תוכן (IARC)</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>✅ הוגש</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>קטגוריה 'כל סוגי האפליקציות האחרים'. כל התשובות 'לא' חוץ מ'תוכן מקוון' = כן, כי ה-WebView טוען כתבות מאתרים חיצוניים. התוצאה: 3+ · PEGI 3 · USK כל הגילאים, בלי מתאר תוכן באף רשות.</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>184</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Play Console · קהל יעד</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>✅ הוגש</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>18 ומעלה בלבד. התיבה האופציונלית לחסימת קטינים לא סומנה — הוחלט מפורשות אחרי שהמשתמש חלק על ההמלצה שלי, ובצדק: אין באפליקציה מסחר, כסף או נתונים אישיים שמהם צריך להגן על בן 16.</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>185</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Play Console · תכונות פיננסיות</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>✅ הוגש</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>אף אחת מ-15 האפשרויות לא סומנה. גוגל מגדירה 'תכונה פיננסית' ברשימה סגורה: הלוואות, בנקאות, אשראי, תשלומים, העברות, קריפטו, NFT, מימון המונים, מסחר וניהול תיקים. BuddhaVest לא מבצעת אף אחת — אין ברוקר, אין פקודות, אין כסף. רשימת המעקב שומרת {ticker,name} בלבד, בלי כמויות או מחירי קנייה. סימון 'אחר' היה פותח דרישת רישיונות מיותרת.</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>186</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Play Console · ממשלתי · בריאות · COVID</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>✅ הוגש</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>שלוש הצהרות, כולן 'לא'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>187</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Play Console · הגדרות החנות</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>✅ הוגש</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>קטגוריה: כלכלה (Finance). אימייל: supportbuddhavest@gmail.com. אתר: buddhavest.onrender.com. 'שיווק חיצוני' נשאר מסומן — טעיתי וקראתי את הניסוח הפוך, המשתמש תפס את זה. מסומן = גוגל מקדמת את האפליקציה גם מחוץ ל-Play, וזה מה שרוצים. שינוי לוקח עד 60 יום להיכנס לתוקף.</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>188</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Play Console · דף האפליקציה בחנות</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>✅ הוגש 15/08/2026</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>store-listing.md · store-assets/ · store-screenshots/en-play/</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>שפת ברירת מחדל en-US. שם (27/30), תיאור קצר (76/80), תיאור מלא — כולם מ-store-listing.md, בניסוח שנמנע ממילים 'המלצה', 'ייעוץ' ו-'AI'. אייקון 512x512 עם אלפא, גרפיקה ראשית 1024x500, 6 צילומי מסך. וידאו נשאר ריק (אופציונלי, קישור יוטיוב בלבד). עברית תתווסף כשפה נוספת.</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>189</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Play Console · תיוג נכסי AI</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Store / Legal</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>✅ הוגש</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>נבחרה האפשרות 'לרצות להוסיף תוויות'. תויגו: סמל האפליקציה והגרפיקה הראשית — איורי הנזיר נוצרו בכלים גנרטיביים (ChatGPT, Gemini, Leonardo). 6 צילומי המסך לא תויגו: אלה צילומים של תוכנה אמיתית שרצה, והעובדה שאיור בתוכה נוצר ב-AI לא הופכת את הצילום לסינתטי. הדרישה נובעת מרגולציה אירופית על תוכן סינתטי.</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>190</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>באג · הגרפיקה הראשית הצהירה 'AI-Powered Stock Recommendations'</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Store / Legal</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>✅ תוקן</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>store-assets/feature-graphic-1024x500.png</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>שתי המילים שגויות ואחת מהן מסוכנת. הציון הוא analyzer.py — משקלים קבועים 40/35/25, אותו חישוב לכל חברה, לא AI. ו'Recommendations' + 'Buy · Hold · Avoid signals' הופכים את הגרפיקה להצהרת ייעוץ פיננסי — בסתירה ישירה לטקסט שמתחתיה, שנוסח בכוונה כדי להימנע מזה. דף חנות שמתווכח עם עצמו. בנוסף: שני תווים יצאו ריבועים ריקים, והמונק היה הגרסה עם רקע לבן על פאנל כהה.</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>191</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>עיצוב · גרפיקה ראשית בצבעי האפליקציה</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>✅ הושלם</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>store-assets/feature-graphic-1024x500.png · assets/feature-graphic.png</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>צבעים ישירות מ-constants/colors.js: רקע #f0f2f5, כתום #d97706, ירוק #15803d, טקסט #0f1117. הלוגו הוא הנכס האמיתי brand_light_text.png ולא הקלדה מחדש. ה'חיות' הגיעה ממחוון הציון — האלמנט החתימה של האפליקציה — ומצ'יפים בצבעי המערכת, במקום ממילות שיווק. נוספה שורת 'A research tool — not financial advice'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="10" t="inlineStr">
         <is>
           <t>Legend</t>
         </is>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" s="6" t="inlineStr">
+    <row r="210">
+      <c r="A210" s="6" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
       </c>
-      <c r="B199" s="7" t="inlineStr">
+      <c r="B210" s="7" t="inlineStr">
         <is>
           <t>פרוס ופעיל ב-Render — נראה לכל המשתמשים</t>
         </is>
       </c>
-      <c r="C199" s="6" t="inlineStr"/>
-      <c r="D199" s="8" t="inlineStr"/>
-      <c r="E199" s="9" t="inlineStr"/>
-      <c r="F199" s="9" t="inlineStr"/>
-    </row>
-    <row r="200">
-      <c r="A200" s="6" t="inlineStr">
+      <c r="C210" s="6" t="inlineStr"/>
+      <c r="D210" s="8" t="inlineStr"/>
+      <c r="E210" s="9" t="inlineStr"/>
+      <c r="F210" s="9" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="6" t="inlineStr">
         <is>
           <t>✅ In APK</t>
         </is>
       </c>
-      <c r="B200" s="7" t="inlineStr">
+      <c r="B211" s="7" t="inlineStr">
         <is>
           <t>כלול ב-APK המותקן — נראה לכל המשתמשים</t>
         </is>
       </c>
-      <c r="C200" s="6" t="inlineStr"/>
-      <c r="D200" s="8" t="inlineStr"/>
-      <c r="E200" s="9" t="inlineStr"/>
-      <c r="F200" s="9" t="inlineStr"/>
-    </row>
-    <row r="201">
-      <c r="A201" s="6" t="inlineStr">
+      <c r="C211" s="6" t="inlineStr"/>
+      <c r="D211" s="8" t="inlineStr"/>
+      <c r="E211" s="9" t="inlineStr"/>
+      <c r="F211" s="9" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="6" t="inlineStr">
         <is>
           <t>⏳ Next APK</t>
         </is>
       </c>
-      <c r="B201" s="7" t="inlineStr">
+      <c r="B212" s="7" t="inlineStr">
         <is>
           <t>הקוד מוזג — דורש build ו-APK חדש</t>
         </is>
       </c>
-      <c r="C201" s="6" t="inlineStr"/>
-      <c r="D201" s="8" t="inlineStr"/>
-      <c r="E201" s="9" t="inlineStr"/>
-      <c r="F201" s="9" t="inlineStr"/>
-    </row>
-    <row r="202">
-      <c r="A202" s="6" t="inlineStr">
+      <c r="C212" s="6" t="inlineStr"/>
+      <c r="D212" s="8" t="inlineStr"/>
+      <c r="E212" s="9" t="inlineStr"/>
+      <c r="F212" s="9" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="6" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
       </c>
-      <c r="B202" s="7" t="inlineStr">
+      <c r="B213" s="7" t="inlineStr">
         <is>
           <t>שינוי JS — מועבר אוטומטית בהפעלה הבאה</t>
         </is>
       </c>
-      <c r="C202" s="6" t="inlineStr"/>
-      <c r="D202" s="8" t="inlineStr"/>
-      <c r="E202" s="9" t="inlineStr"/>
-      <c r="F202" s="9" t="inlineStr"/>
-    </row>
-    <row r="203">
-      <c r="A203" s="21" t="inlineStr">
+      <c r="C213" s="6" t="inlineStr"/>
+      <c r="D213" s="8" t="inlineStr"/>
+      <c r="E213" s="9" t="inlineStr"/>
+      <c r="F213" s="9" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="21" t="inlineStr">
         <is>
           <t>⏳ ממתין ל-push</t>
         </is>
       </c>
-      <c r="B203" s="22" t="inlineStr">
+      <c r="B214" s="22" t="inlineStr">
         <is>
           <t>הקוד מוכן מקומית — טרם נדחף/נפרס</t>
         </is>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" s="21" t="inlineStr">
+    <row r="215">
+      <c r="A215" s="21" t="inlineStr">
         <is>
           <t>⏳ דורש build</t>
         </is>
       </c>
-      <c r="B204" s="22" t="inlineStr">
+      <c r="B215" s="22" t="inlineStr">
         <is>
           <t>שינוי נייטיב — OTA לא מספיק, צריך AAB/APK חדש</t>
         </is>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" s="23" t="inlineStr">
+    <row r="217">
+      <c r="A217" s="23" t="inlineStr">
         <is>
           <t>סיכום Session 6-8</t>
         </is>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" s="24" t="n"/>
-      <c r="B207" s="25" t="inlineStr">
+    <row r="218">
+      <c r="A218" s="24" t="n"/>
+      <c r="B218" s="25" t="inlineStr">
         <is>
           <t>58  —  פריטים חדשים שנוספו (52-109)</t>
         </is>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" s="24" t="n"/>
-      <c r="B208" s="25" t="inlineStr">
+    <row r="219">
+      <c r="A219" s="24" t="n"/>
+      <c r="B219" s="25" t="inlineStr">
         <is>
           <t>56  —  חיים בייצור או ב-OTA</t>
         </is>
       </c>
     </row>
-    <row r="209">
-      <c r="A209" s="24" t="n"/>
-      <c r="B209" s="25" t="inlineStr">
+    <row r="220">
+      <c r="A220" s="24" t="n"/>
+      <c r="B220" s="25" t="inlineStr">
         <is>
           <t>0  —  ממתינים ל-push: הכל נפרס (commit 91ee6d3)</t>
         </is>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" s="24" t="n"/>
-      <c r="B210" s="25" t="inlineStr">
+    <row r="221">
+      <c r="A221" s="24" t="n"/>
+      <c r="B221" s="25" t="inlineStr">
         <is>
           <t>2  —  פתוחים: פריסת טאבלט אמיתית (99) · הגשה ל-Play (19)</t>
         </is>
       </c>
     </row>
-    <row r="211">
-      <c r="A211" s="24" t="n"/>
-      <c r="B211" s="25" t="inlineStr">
+    <row r="222">
+      <c r="A222" s="24" t="n"/>
+      <c r="B222" s="25" t="inlineStr">
         <is>
           <t>8  —  בורסות שאומתו חי (NYSE · TASE · XETRA · LSE) · JSE ביחידה בלבד</t>
         </is>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" s="24" t="n"/>
-      <c r="B212" s="25" t="inlineStr">
+    <row r="223">
+      <c r="A223" s="24" t="n"/>
+      <c r="B223" s="25" t="inlineStr">
         <is>
           <t>48  —  חבילות בדיקה התנהגותיות עוברות (48/48)</t>
         </is>
       </c>
     </row>
-    <row r="213">
-      <c r="B213" t="inlineStr">
+    <row r="224">
+      <c r="B224" t="inlineStr">
         <is>
           <t>18  —  ראוטים בשרת · 324 מפתחות i18n × 4 שפות</t>
         </is>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" s="23" t="inlineStr">
+    <row r="226">
+      <c r="A226" s="23" t="inlineStr">
         <is>
           <t>סיכום Session 10  (2026-08-08)</t>
         </is>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" s="71" t="n"/>
-      <c r="B216" s="71" t="inlineStr">
+    <row r="227">
+      <c r="A227" s="71" t="n"/>
+      <c r="B227" s="71" t="inlineStr">
         <is>
           <t>40  —  פריטים חדשים שנוספו (120-159)</t>
         </is>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" s="71" t="n"/>
-      <c r="B217" s="71" t="inlineStr">
+    <row r="228">
+      <c r="A228" s="71" t="n"/>
+      <c r="B228" s="71" t="inlineStr">
         <is>
           <t>36  —  חיים בייצור ואומתו — /status build=8602f21 · lkg=redis · sentry=on</t>
         </is>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" s="71" t="n"/>
-      <c r="B218" s="71" t="inlineStr">
+    <row r="229">
+      <c r="A229" s="71" t="n"/>
+      <c r="B229" s="71" t="inlineStr">
         <is>
           <t>0  —  ממתינים ל-push</t>
         </is>
       </c>
     </row>
-    <row r="219">
-      <c r="A219" s="71" t="n"/>
-      <c r="B219" s="71" t="inlineStr">
+    <row r="230">
+      <c r="A230" s="71" t="n"/>
+      <c r="B230" s="71" t="inlineStr">
         <is>
           <t>1  —  פרוס אך טרם רץ בייצור: ספק נתונים שני (142). Yahoo תקין, הגיבוי לא הופעל אף פעם</t>
         </is>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" s="71" t="n"/>
-      <c r="B220" s="71" t="inlineStr">
+    <row r="231">
+      <c r="A231" s="71" t="n"/>
+      <c r="B231" s="71" t="inlineStr">
         <is>
           <t>2  —  פתוחים: צילומי מסך (156) · בדיקה סגורה 14 יום (159)</t>
         </is>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" s="71" t="n"/>
-      <c r="B221" s="71" t="inlineStr">
+    <row r="232">
+      <c r="A232" s="71" t="n"/>
+      <c r="B232" s="71" t="inlineStr">
         <is>
           <t>2  —  נדחו במודע לאחר ההשקה: פיצול main.py (157) · חוב תחזוקה L1-L4 (158)</t>
         </is>
       </c>
     </row>
-    <row r="222">
-      <c r="A222" s="71" t="n"/>
-      <c r="B222" s="71" t="inlineStr">
+    <row r="233">
+      <c r="A233" s="71" t="n"/>
+      <c r="B233" s="71" t="inlineStr">
         <is>
           <t>11  —  באגים שהתגלו ותוקנו היום. 9 מהם היו בלתי נראים לפני שהבליעות השקטות הוחלפו</t>
         </is>
       </c>
     </row>
-    <row r="223">
-      <c r="A223" s="71" t="n"/>
-      <c r="B223" s="71" t="inlineStr">
+    <row r="234">
+      <c r="A234" s="71" t="n"/>
+      <c r="B234" s="71" t="inlineStr">
         <is>
           <t>18  —  שלבי CI על כל דחיפה · 4 חבילות בדיקה עוברות</t>
         </is>
       </c>
     </row>
-    <row r="224">
-      <c r="A224" s="71" t="n"/>
-      <c r="B224" s="71" t="inlineStr">
+    <row r="235">
+      <c r="A235" s="71" t="n"/>
+      <c r="B235" s="71" t="inlineStr">
         <is>
           <t>259  —  מפתחות i18n בכל אחת מ-4 השפות (היו 247)</t>
         </is>
       </c>
     </row>
-    <row r="225">
-      <c r="A225" s="72" t="n"/>
-      <c r="B225" s="72" t="inlineStr">
+    <row r="236">
+      <c r="A236" s="72" t="n"/>
+      <c r="B236" s="72" t="inlineStr">
         <is>
           <t>אימות עצמאי:  .\check.bat  —  מי רץ בשרת, אם אפסטאש מחובר, אם Sentry דולק, ומצב ה-CI</t>
         </is>
       </c>
     </row>
-    <row r="227">
-      <c r="A227" s="73" t="inlineStr">
+    <row r="238">
+      <c r="A238" s="73" t="inlineStr">
         <is>
           <t>סיכום סשן 11 — 13/08/2026</t>
         </is>
       </c>
     </row>
-    <row r="228">
-      <c r="B228" s="74" t="inlineStr">
+    <row r="239">
+      <c r="B239" s="74" t="inlineStr">
         <is>
           <t>21  —  פריטים חדשים (160-180)</t>
         </is>
       </c>
     </row>
-    <row r="229">
-      <c r="B229" s="74" t="inlineStr">
+    <row r="240">
+      <c r="B240" s="74" t="inlineStr">
         <is>
           <t>17  —  חיים בייצור ואומתו חי — /status build=b096bf3 · code=8423c9284668 · lkg=redis · sentry=on</t>
         </is>
       </c>
     </row>
-    <row r="230">
-      <c r="B230" s="74" t="inlineStr">
+    <row r="241">
+      <c r="B241" s="74" t="inlineStr">
         <is>
           <t>2  —  ממתינים ל-OTA: סימן המטבע החסר (167,168). השרת כבר שולח את הדגל הנכון.</t>
         </is>
       </c>
     </row>
-    <row r="231">
-      <c r="B231" s="74" t="inlineStr">
+    <row r="242">
+      <c r="B242" s="74" t="inlineStr">
         <is>
           <t>1  —  ממתין ל-push: תיקון מדיניות הפרטיות (179)</t>
         </is>
       </c>
     </row>
-    <row r="232">
-      <c r="B232" s="74" t="inlineStr">
+    <row r="243">
+      <c r="B243" s="74" t="inlineStr">
         <is>
           <t>1  —  לא נסגר: סיבת הקריסות של המחשב (175). מוצע חשוד, לא הוכח.</t>
         </is>
       </c>
     </row>
-    <row r="233">
-      <c r="B233" s="74" t="inlineStr">
+    <row r="244">
+      <c r="B244" s="74" t="inlineStr">
         <is>
           <t>6  —  באגים שהתגלו היום. 4 מהם היו שלי, 3 מתוכם נולדו בתיקון של אתמול.</t>
         </is>
       </c>
     </row>
-    <row r="234">
-      <c r="B234" s="74" t="inlineStr">
+    <row r="245">
+      <c r="B245" s="74" t="inlineStr">
         <is>
           <t>22  —  שלבי CI על כל דחיפה · 8 חבילות בדיקה · run-ci.js מריץ את כולם מקומית</t>
         </is>
       </c>
     </row>
-    <row r="235">
-      <c r="B235" s="74" t="inlineStr">
+    <row r="246">
+      <c r="B246" s="74" t="inlineStr">
         <is>
           <t>מדידות חיות: ORA.TA שווי שוק ₪2,106מ' -&gt; ₪20.69מ' · מכפיל 16955.4 -&gt; לא זמין · מטבע דוחות USD</t>
         </is>
       </c>
     </row>
-    <row r="236">
-      <c r="B236" s="74" t="inlineStr">
+    <row r="247">
+      <c r="B247" s="74" t="inlineStr">
         <is>
           <t>מדידות חיות: POLI.TA שווי שוק ₪10,048מ' -&gt; ₪100.89מ' · מטבע דוחות ILS</t>
         </is>
       </c>
     </row>
-    <row r="237">
-      <c r="B237" s="74" t="inlineStr">
+    <row r="248">
+      <c r="B248" s="74" t="inlineStr">
         <is>
           <t>אימות עצמאי:  .\check.bat  —  משווה טביעת אצבע של המקור, לא קומיט. .\ci.bat  —  כל 22 השלבים.</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="73" t="inlineStr">
+        <is>
+          <t>סיכום סשן 11 — המשך: Play Console</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="B251" s="75" t="inlineStr">
+        <is>
+          <t>11  —  פריטים חדשים (181-191): כל טפסי App content + דף החנות</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="B252" s="75" t="inlineStr">
+        <is>
+          <t>3   —  פריטים שהיו לא מדויקים ותוקנו: 111 (Data Safety 'טיוטה' -&gt; הוגש) · 113 · 156 (צילומי מסך)</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="B253" s="75" t="inlineStr">
+        <is>
+          <t>אומת מול התמליל, לא מהזיכרון: גישה · מודעות · דירוג תוכן · קהל יעד · תכונות פיננסיות · ממשלתי · בריאות · הגדרות חנות — כולם הוגשו בסשן קודם</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="B254" s="75" t="inlineStr">
+        <is>
+          <t>נותר לפני הבדיקה הסגורה: העלאת ה-AAB למסלול closed testing · Render $7 · 12 בודקים</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="B255" s="75" t="inlineStr">
+        <is>
+          <t>עברית תתווסף כשפה נוספת בדף החנות — לא חוסם</t>
         </is>
       </c>
     </row>
@@ -6866,8 +7241,8 @@
   <mergeCells count="9">
     <mergeCell ref="A166:F166"/>
     <mergeCell ref="A97:F97"/>
+    <mergeCell ref="A145:F145"/>
     <mergeCell ref="A131:F131"/>
-    <mergeCell ref="A145:F145"/>
     <mergeCell ref="A171:F171"/>
     <mergeCell ref="A109:F109"/>
     <mergeCell ref="A59:F59"/>

--- a/BuddhaVest_Progress.xlsx
+++ b/BuddhaVest_Progress.xlsx
@@ -778,7 +778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F255"/>
+  <dimension ref="A1:F260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>⏳ Next APK</t>
+          <t>✅ In APK</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>נזיר על חץ זהב — 1024×1024, רקע לבן.</t>
+          <t>assets/icon.png ו-adaptive-icon.png נכללים ב-AAB שנבנה ב-15/08/2026. סומלץ המיסוך של אנדרואיד ואומת שהנזיר לא נחתך.</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>⏳ Next APK</t>
+          <t>✅ הועלה לחנות</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>באנר 1024×500 לGoogle Play.</t>
+          <t>נכס חנות, לא חלק ב-APK. 1024x500, הועלה לדף החנות ב-15/08/2026. נבנה מחדש באותו יום אחרי שהתברר שהוא הצהיר 'AI-Powered Stock Recommendations' — ראה 190.</t>
         </is>
       </c>
     </row>
@@ -1433,13 +1433,13 @@
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>⏳ לאחר בדיקה</t>
+          <t>✅ נבנה 15/08/2026</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr"/>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>eas build --profile production → AAB חתום לPlay Store.</t>
+          <t>eas build --profile production --platform android, רץ על שרתי EAS. versionCode 5 (autoIncrement מ-4). ממתין להעלאה למסלול closed testing.</t>
         </is>
       </c>
     </row>
@@ -2435,7 +2435,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>⏳ npm install + commit</t>
+          <t>✅ מסונכרן</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>בניית preview נכשלה ב-Install dependencies בגלל lock לא מסונכרן אחרי הסרת הכפילות.</t>
+          <t>אומת 15/08/2026: npm ls --depth=0 חוזר נקי, אין invalid/missing/UNMET, ו-package-lock.json לא מופיע כשונה ב-git status.</t>
         </is>
       </c>
     </row>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>⏳ בתהליך</t>
+          <t>✅ הוחלף בבניית production</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>אחרי ה-push: eas build --profile preview → התקנה → בדיקת אייקון, ספלאש, התראות.</t>
+          <t>נועד לאמת אייקון וספלאש. הוחלף בבניית ה-AAB עצמה (18) שמכילה את אותם נכסים.</t>
         </is>
       </c>
     </row>
@@ -6140,7 +6140,7 @@
       </c>
       <c r="D183" s="65" t="inlineStr">
         <is>
-          <t>⏳ דורש OTA</t>
+          <t>✅ Live (OTA)</t>
         </is>
       </c>
       <c r="E183" s="66" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="F183" s="66" t="inlineStr">
         <is>
-          <t>'' הוא falsy, ו-route.params.cur || '$' החזיר את הדולר. התיקון החזיק על האריח ונשבר לחיצה אחת אחריו — סימן דולר על מספר שאיש לא קבע אם הוא שקל או דולר.</t>
+          <t>ה-OTA פורסם מ-GitHub Actions ב-15/08/2026 על b096bf3. אומת: 84b4819 (שמכיל את התיקון) הוא אב-קדמון שלו. גם נכלל ב-AAB.</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="D184" s="65" t="inlineStr">
         <is>
-          <t>⏳ דורש OTA</t>
+          <t>✅ Live (OTA)</t>
         </is>
       </c>
       <c r="E184" s="66" t="inlineStr">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="F184" s="66" t="inlineStr">
         <is>
-          <t>3 קבצים + שלב CI שסורק את ה-AST של הלקוח ונופל על כל סימן מטבע עם ברירת מחדל ||. השלב כבר תפס אחד ב-PriceChart שלא הייתי מודע אליו.</t>
+          <t>אותו OTA. בנוסף: שלב CI חדש סורק את ה-AST של הלקוח ונופל על כל סימן מטבע עם ברירת מחדל || במקום ??.</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
       </c>
       <c r="D192" s="65" t="inlineStr">
         <is>
-          <t>⏳ נכנס לתוקף ב-bundle הבא</t>
+          <t>✅ פעיל</t>
         </is>
       </c>
       <c r="E192" s="66" t="inlineStr">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="F192" s="66" t="inlineStr">
         <is>
-          <t>לא היה קובץ בכלל, כלומר worker לכל ליבה = 12. עכשיו 4, כשליש מהמעבד. bundle איטי שמסתיים עדיף על מהיר שמפיל את המחשב.</t>
+          <t>metro.config.js נכלל ב-b096bf3, כלומר גם ה-bundle של ה-OTA ב-GitHub וגם בניית ה-AAB רצו עם maxWorkers=4.</t>
         </is>
       </c>
     </row>
@@ -6500,7 +6500,7 @@
       </c>
       <c r="D195" s="65" t="inlineStr">
         <is>
-          <t>⏳ ממתין ל-push</t>
+          <t>✅ Live — אומת חי</t>
         </is>
       </c>
       <c r="E195" s="66" t="inlineStr">
@@ -6510,7 +6510,7 @@
       </c>
       <c r="F195" s="66" t="inlineStr">
         <is>
-          <t>הטענה 'סמלי מניות לא נשמרים' הפכה ללא מדויקת ברגע ש-report(ticker=...) שולח אותם ל-Sentry. נוסף חריג מפורש והפניה למדיניות של Sentry. ניטור בצד הלקוח כבוי לגמרי — אין DSN והחבילה לא מותקנת — אז שום דבר לא עוזב את המכשיר.</t>
+          <t>נדחף ב-57459ea. אומת ב-15/08/2026 מול https://buddhavest.onrender.com/privacy — החריג על דוחות תקלה ו-Sentry ברשימת הצדדים השלישיים מופיעים בעמוד החי.</t>
         </is>
       </c>
     </row>
@@ -6544,6 +6544,7 @@
         </is>
       </c>
     </row>
+    <row r="197"/>
     <row r="198">
       <c r="A198" t="n">
         <v>181</v>
@@ -6875,144 +6876,255 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="10" t="inlineStr">
+      <c r="A209" t="n">
+        <v>192</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>ממצא · טבלת השוק תדפיס $ על ערך שקלי אם יוסיפו מניה זרה</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Backend / Latent</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>⚠️ לא חי — ננעל</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>main.py · watchlist_symbols · HomeScreen.fmtBig</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>אותה משפחת באגים של היום, רק שהיא עוד לא ירתה. fmtBig מקודד '$' קשיח ו-_one_mover לא שולח מטבע ולא מריץ את שווי השוק דרך _reconcile_market_cap. הרשימה קבועה ומכילה 15 מניות NYSE/NASDAQ בלבד, ולכן היום התצוגה נכונה. הוספת סמל .TA/.L/.JO תשבור את שניהם בבת אחת בשקט. לא תוקן בקוד הלקוח במכוון — זה היה מחייב בנייה חוזרת של ה-AAB עבור באג שלא יכול לירות. במקומו: הערה מפורשת מעל הרשימה ושלב CI שנופל אם מישהו יוסיף סמל עם נקודה.</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>193</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>בדיקה · הרצת מטענים חיים דרך קוד התצוגה של הלקוח</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Testing</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>✅ עבר</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>/tmp/clientfns.js (חילוץ מ-StockScreen · HomeScreen · currency)</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>חולצו symbolFor, formatBigNumber, metricValueDisplay ו-fmtBig מקוד המקור האמיתי והורצו על התשובות החיות של ORA.TA, POLI.TA, AAPL ו-SHEL.L. 184 מקרים כולל null, NaN, Infinity, 1e21, בוליאנים, מחרוזות, אובייקטים ומערכים — אף אחד לא זרק חריגה. כאן התגלה 192.</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>194</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>בדיקה · סריקת שפה בעייתית ב-1,344 מחרוזות</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Legal / Store</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>✅ עבר</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>constants/i18n.js · store-listing.md</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>נסרקו רק ערכי מחרוזת שמוצגים למשתמש (AST, לא grep על קוד והערות) בארבע השפות. שלושה מבחנים: האם הציון מתואר כ-AI · האם מובטחת תשואה · האם יש הוראה ישירה לקנות או למכור. שלושתם נקיים. הסריקה הראשונה שלי החזירה 58 'ממצאים' שכולם היו טקסטי ההסתייגות עצמם — הבודק היה שגוי, לא התוכן.</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>195</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>ממצא · versionCode עלה ל-5 ולא היה ב-commit</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Release</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>✅ תוקן</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>app.json</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>EAS עם autoIncrement מעלה את versionCode בקובץ המקומי בכל בנייה. הקומיט החזיק 4 והקובץ החזיק 5, כלומר ה-AAB נבנה עם 5 והערך הזה חי רק על הדיסק. אם היה הולך לאיבוד, הבנייה הבאה היתה מייצרת 5 שוב ו-Play היתה דוחה אותה כ'קוד גרסה שכבר קיים'. נכלל ב-commit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>196</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>ממצא · מדיניות הפרטיות סתרה את עצמה אחרי הוספת Sentry</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>✅ תוקן</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>main.py · /privacy</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>סעיף 1 הבטיח על רשימת המעקב 'never share it with anyone', והחריג שהוספתי בסעיף 2 מסייג את זה — סמל שנכשל יכול להגיע לדוח תקלה אצל צד שלישי. נוסף מצביע מפורש מסעיף 1 לחריג. גוגל משווה בין מדיניות הפרטיות לטופס Data Safety, וסתירה פנימית היא בדיוק מה שנתפס שם.</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="10" t="inlineStr">
         <is>
           <t>Legend</t>
         </is>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" s="6" t="inlineStr">
+    <row r="215">
+      <c r="A215" s="6" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
       </c>
-      <c r="B210" s="7" t="inlineStr">
+      <c r="B215" s="7" t="inlineStr">
         <is>
           <t>פרוס ופעיל ב-Render — נראה לכל המשתמשים</t>
         </is>
       </c>
-      <c r="C210" s="6" t="inlineStr"/>
-      <c r="D210" s="8" t="inlineStr"/>
-      <c r="E210" s="9" t="inlineStr"/>
-      <c r="F210" s="9" t="inlineStr"/>
-    </row>
-    <row r="211">
-      <c r="A211" s="6" t="inlineStr">
+      <c r="C215" s="6" t="inlineStr"/>
+      <c r="D215" s="8" t="inlineStr"/>
+      <c r="E215" s="9" t="inlineStr"/>
+      <c r="F215" s="9" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="6" t="inlineStr">
         <is>
           <t>✅ In APK</t>
         </is>
       </c>
-      <c r="B211" s="7" t="inlineStr">
+      <c r="B216" s="7" t="inlineStr">
         <is>
           <t>כלול ב-APK המותקן — נראה לכל המשתמשים</t>
         </is>
       </c>
-      <c r="C211" s="6" t="inlineStr"/>
-      <c r="D211" s="8" t="inlineStr"/>
-      <c r="E211" s="9" t="inlineStr"/>
-      <c r="F211" s="9" t="inlineStr"/>
-    </row>
-    <row r="212">
-      <c r="A212" s="6" t="inlineStr">
+      <c r="C216" s="6" t="inlineStr"/>
+      <c r="D216" s="8" t="inlineStr"/>
+      <c r="E216" s="9" t="inlineStr"/>
+      <c r="F216" s="9" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="6" t="inlineStr">
         <is>
           <t>⏳ Next APK</t>
         </is>
       </c>
-      <c r="B212" s="7" t="inlineStr">
+      <c r="B217" s="7" t="inlineStr">
         <is>
           <t>הקוד מוזג — דורש build ו-APK חדש</t>
         </is>
       </c>
-      <c r="C212" s="6" t="inlineStr"/>
-      <c r="D212" s="8" t="inlineStr"/>
-      <c r="E212" s="9" t="inlineStr"/>
-      <c r="F212" s="9" t="inlineStr"/>
-    </row>
-    <row r="213">
-      <c r="A213" s="6" t="inlineStr">
+      <c r="C217" s="6" t="inlineStr"/>
+      <c r="D217" s="8" t="inlineStr"/>
+      <c r="E217" s="9" t="inlineStr"/>
+      <c r="F217" s="9" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="6" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
       </c>
-      <c r="B213" s="7" t="inlineStr">
+      <c r="B218" s="7" t="inlineStr">
         <is>
           <t>שינוי JS — מועבר אוטומטית בהפעלה הבאה</t>
         </is>
       </c>
-      <c r="C213" s="6" t="inlineStr"/>
-      <c r="D213" s="8" t="inlineStr"/>
-      <c r="E213" s="9" t="inlineStr"/>
-      <c r="F213" s="9" t="inlineStr"/>
-    </row>
-    <row r="214">
-      <c r="A214" s="21" t="inlineStr">
+      <c r="C218" s="6" t="inlineStr"/>
+      <c r="D218" s="8" t="inlineStr"/>
+      <c r="E218" s="9" t="inlineStr"/>
+      <c r="F218" s="9" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="21" t="inlineStr">
         <is>
           <t>⏳ ממתין ל-push</t>
         </is>
       </c>
-      <c r="B214" s="22" t="inlineStr">
+      <c r="B219" s="22" t="inlineStr">
         <is>
           <t>הקוד מוכן מקומית — טרם נדחף/נפרס</t>
         </is>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" s="21" t="inlineStr">
+    <row r="220">
+      <c r="A220" s="21" t="inlineStr">
         <is>
           <t>⏳ דורש build</t>
         </is>
       </c>
-      <c r="B215" s="22" t="inlineStr">
+      <c r="B220" s="22" t="inlineStr">
         <is>
           <t>שינוי נייטיב — OTA לא מספיק, צריך AAB/APK חדש</t>
         </is>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" s="23" t="inlineStr">
+    <row r="221"/>
+    <row r="222">
+      <c r="A222" s="23" t="inlineStr">
         <is>
           <t>סיכום Session 6-8</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" s="24" t="n"/>
-      <c r="B218" s="25" t="inlineStr">
-        <is>
-          <t>58  —  פריטים חדשים שנוספו (52-109)</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" s="24" t="n"/>
-      <c r="B219" s="25" t="inlineStr">
-        <is>
-          <t>56  —  חיים בייצור או ב-OTA</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" s="24" t="n"/>
-      <c r="B220" s="25" t="inlineStr">
-        <is>
-          <t>0  —  ממתינים ל-push: הכל נפרס (commit 91ee6d3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" s="24" t="n"/>
-      <c r="B221" s="25" t="inlineStr">
-        <is>
-          <t>2  —  פתוחים: פריסת טאבלט אמיתית (99) · הגשה ל-Play (19)</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" s="24" t="n"/>
-      <c r="B222" s="25" t="inlineStr">
-        <is>
-          <t>8  —  בורסות שאומתו חי (NYSE · TASE · XETRA · LSE) · JSE ביחידה בלבד</t>
         </is>
       </c>
     </row>
@@ -7020,61 +7132,62 @@
       <c r="A223" s="24" t="n"/>
       <c r="B223" s="25" t="inlineStr">
         <is>
+          <t>58  —  פריטים חדשים שנוספו (52-109)</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="24" t="n"/>
+      <c r="B224" s="25" t="inlineStr">
+        <is>
+          <t>56  —  חיים בייצור או ב-OTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="24" t="n"/>
+      <c r="B225" s="25" t="inlineStr">
+        <is>
+          <t>0  —  ממתינים ל-push: הכל נפרס (commit 91ee6d3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="24" t="n"/>
+      <c r="B226" s="25" t="inlineStr">
+        <is>
+          <t>2  —  פתוחים: פריסת טאבלט אמיתית (99) · הגשה ל-Play (19)</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="24" t="n"/>
+      <c r="B227" s="25" t="inlineStr">
+        <is>
+          <t>8  —  בורסות שאומתו חי (NYSE · TASE · XETRA · LSE) · JSE ביחידה בלבד</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="24" t="n"/>
+      <c r="B228" s="25" t="inlineStr">
+        <is>
           <t>48  —  חבילות בדיקה התנהגותיות עוברות (48/48)</t>
         </is>
       </c>
     </row>
-    <row r="224">
-      <c r="B224" t="inlineStr">
+    <row r="229">
+      <c r="B229" t="inlineStr">
         <is>
           <t>18  —  ראוטים בשרת · 324 מפתחות i18n × 4 שפות</t>
         </is>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" s="23" t="inlineStr">
+    <row r="230"/>
+    <row r="231">
+      <c r="A231" s="23" t="inlineStr">
         <is>
           <t>סיכום Session 10  (2026-08-08)</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" s="71" t="n"/>
-      <c r="B227" s="71" t="inlineStr">
-        <is>
-          <t>40  —  פריטים חדשים שנוספו (120-159)</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="71" t="n"/>
-      <c r="B228" s="71" t="inlineStr">
-        <is>
-          <t>36  —  חיים בייצור ואומתו — /status build=8602f21 · lkg=redis · sentry=on</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="71" t="n"/>
-      <c r="B229" s="71" t="inlineStr">
-        <is>
-          <t>0  —  ממתינים ל-push</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="71" t="n"/>
-      <c r="B230" s="71" t="inlineStr">
-        <is>
-          <t>1  —  פרוס אך טרם רץ בייצור: ספק נתונים שני (142). Yahoo תקין, הגיבוי לא הופעל אף פעם</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="71" t="n"/>
-      <c r="B231" s="71" t="inlineStr">
-        <is>
-          <t>2  —  פתוחים: צילומי מסך (156) · בדיקה סגורה 14 יום (159)</t>
         </is>
       </c>
     </row>
@@ -7082,7 +7195,7 @@
       <c r="A232" s="71" t="n"/>
       <c r="B232" s="71" t="inlineStr">
         <is>
-          <t>2  —  נדחו במודע לאחר ההשקה: פיצול main.py (157) · חוב תחזוקה L1-L4 (158)</t>
+          <t>40  —  פריטים חדשים שנוספו (120-159)</t>
         </is>
       </c>
     </row>
@@ -7090,7 +7203,7 @@
       <c r="A233" s="71" t="n"/>
       <c r="B233" s="71" t="inlineStr">
         <is>
-          <t>11  —  באגים שהתגלו ותוקנו היום. 9 מהם היו בלתי נראים לפני שהבליעות השקטות הוחלפו</t>
+          <t>36  —  חיים בייצור ואומתו — /status build=8602f21 · lkg=redis · sentry=on</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7211,7 @@
       <c r="A234" s="71" t="n"/>
       <c r="B234" s="71" t="inlineStr">
         <is>
-          <t>18  —  שלבי CI על כל דחיפה · 4 חבילות בדיקה עוברות</t>
+          <t>0  —  ממתינים ל-push</t>
         </is>
       </c>
     </row>
@@ -7106,132 +7219,174 @@
       <c r="A235" s="71" t="n"/>
       <c r="B235" s="71" t="inlineStr">
         <is>
+          <t>1  —  פרוס אך טרם רץ בייצור: ספק נתונים שני (142). Yahoo תקין, הגיבוי לא הופעל אף פעם</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="71" t="n"/>
+      <c r="B236" s="71" t="inlineStr">
+        <is>
+          <t>2  —  פתוחים: צילומי מסך (156) · בדיקה סגורה 14 יום (159)</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="71" t="n"/>
+      <c r="B237" s="71" t="inlineStr">
+        <is>
+          <t>2  —  נדחו במודע לאחר ההשקה: פיצול main.py (157) · חוב תחזוקה L1-L4 (158)</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="71" t="n"/>
+      <c r="B238" s="71" t="inlineStr">
+        <is>
+          <t>11  —  באגים שהתגלו ותוקנו היום. 9 מהם היו בלתי נראים לפני שהבליעות השקטות הוחלפו</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="71" t="n"/>
+      <c r="B239" s="71" t="inlineStr">
+        <is>
+          <t>18  —  שלבי CI על כל דחיפה · 4 חבילות בדיקה עוברות</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="71" t="n"/>
+      <c r="B240" s="71" t="inlineStr">
+        <is>
           <t>259  —  מפתחות i18n בכל אחת מ-4 השפות (היו 247)</t>
         </is>
       </c>
     </row>
-    <row r="236">
-      <c r="A236" s="72" t="n"/>
-      <c r="B236" s="72" t="inlineStr">
+    <row r="241">
+      <c r="A241" s="72" t="n"/>
+      <c r="B241" s="72" t="inlineStr">
         <is>
           <t>אימות עצמאי:  .\check.bat  —  מי רץ בשרת, אם אפסטאש מחובר, אם Sentry דולק, ומצב ה-CI</t>
         </is>
       </c>
     </row>
-    <row r="238">
-      <c r="A238" s="73" t="inlineStr">
+    <row r="242"/>
+    <row r="243">
+      <c r="A243" s="73" t="inlineStr">
         <is>
           <t>סיכום סשן 11 — 13/08/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="B239" s="74" t="inlineStr">
-        <is>
-          <t>21  —  פריטים חדשים (160-180)</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="B240" s="74" t="inlineStr">
-        <is>
-          <t>17  —  חיים בייצור ואומתו חי — /status build=b096bf3 · code=8423c9284668 · lkg=redis · sentry=on</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="B241" s="74" t="inlineStr">
-        <is>
-          <t>2  —  ממתינים ל-OTA: סימן המטבע החסר (167,168). השרת כבר שולח את הדגל הנכון.</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="B242" s="74" t="inlineStr">
-        <is>
-          <t>1  —  ממתין ל-push: תיקון מדיניות הפרטיות (179)</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="B243" s="74" t="inlineStr">
-        <is>
-          <t>1  —  לא נסגר: סיבת הקריסות של המחשב (175). מוצע חשוד, לא הוכח.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="B244" s="74" t="inlineStr">
         <is>
-          <t>6  —  באגים שהתגלו היום. 4 מהם היו שלי, 3 מתוכם נולדו בתיקון של אתמול.</t>
+          <t>21  —  פריטים חדשים (160-180)</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="B245" s="74" t="inlineStr">
         <is>
-          <t>22  —  שלבי CI על כל דחיפה · 8 חבילות בדיקה · run-ci.js מריץ את כולם מקומית</t>
+          <t>17  —  חיים בייצור ואומתו חי — /status build=b096bf3 · code=8423c9284668 · lkg=redis · sentry=on</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="B246" s="74" t="inlineStr">
         <is>
-          <t>מדידות חיות: ORA.TA שווי שוק ₪2,106מ' -&gt; ₪20.69מ' · מכפיל 16955.4 -&gt; לא זמין · מטבע דוחות USD</t>
+          <t>2  —  ממתינים ל-OTA: סימן המטבע החסר (167,168). השרת כבר שולח את הדגל הנכון.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="B247" s="74" t="inlineStr">
         <is>
-          <t>מדידות חיות: POLI.TA שווי שוק ₪10,048מ' -&gt; ₪100.89מ' · מטבע דוחות ILS</t>
+          <t>1  —  ממתין ל-push: תיקון מדיניות הפרטיות (179)</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="B248" s="74" t="inlineStr">
         <is>
+          <t>1  —  לא נסגר: סיבת הקריסות של המחשב (175). מוצע חשוד, לא הוכח.</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="B249" s="74" t="inlineStr">
+        <is>
+          <t>6  —  באגים שהתגלו היום. 4 מהם היו שלי, 3 מתוכם נולדו בתיקון של אתמול.</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="B250" s="74" t="inlineStr">
+        <is>
+          <t>22  —  שלבי CI על כל דחיפה · 8 חבילות בדיקה · run-ci.js מריץ את כולם מקומית</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="B251" s="74" t="inlineStr">
+        <is>
+          <t>מדידות חיות: ORA.TA שווי שוק ₪2,106מ' -&gt; ₪20.69מ' · מכפיל 16955.4 -&gt; לא זמין · מטבע דוחות USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="B252" s="74" t="inlineStr">
+        <is>
+          <t>מדידות חיות: POLI.TA שווי שוק ₪10,048מ' -&gt; ₪100.89מ' · מטבע דוחות ILS</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="B253" s="74" t="inlineStr">
+        <is>
           <t>אימות עצמאי:  .\check.bat  —  משווה טביעת אצבע של המקור, לא קומיט. .\ci.bat  —  כל 22 השלבים.</t>
         </is>
       </c>
     </row>
-    <row r="250">
-      <c r="A250" s="73" t="inlineStr">
+    <row r="254"/>
+    <row r="255">
+      <c r="A255" s="73" t="inlineStr">
         <is>
           <t>סיכום סשן 11 — המשך: Play Console</t>
         </is>
       </c>
     </row>
-    <row r="251">
-      <c r="B251" s="75" t="inlineStr">
+    <row r="256">
+      <c r="B256" s="75" t="inlineStr">
         <is>
           <t>11  —  פריטים חדשים (181-191): כל טפסי App content + דף החנות</t>
         </is>
       </c>
     </row>
-    <row r="252">
-      <c r="B252" s="75" t="inlineStr">
+    <row r="257">
+      <c r="B257" s="75" t="inlineStr">
         <is>
           <t>3   —  פריטים שהיו לא מדויקים ותוקנו: 111 (Data Safety 'טיוטה' -&gt; הוגש) · 113 · 156 (צילומי מסך)</t>
         </is>
       </c>
     </row>
-    <row r="253">
-      <c r="B253" s="75" t="inlineStr">
+    <row r="258">
+      <c r="B258" s="75" t="inlineStr">
         <is>
           <t>אומת מול התמליל, לא מהזיכרון: גישה · מודעות · דירוג תוכן · קהל יעד · תכונות פיננסיות · ממשלתי · בריאות · הגדרות חנות — כולם הוגשו בסשן קודם</t>
         </is>
       </c>
     </row>
-    <row r="254">
-      <c r="B254" s="75" t="inlineStr">
+    <row r="259">
+      <c r="B259" s="75" t="inlineStr">
         <is>
           <t>נותר לפני הבדיקה הסגורה: העלאת ה-AAB למסלול closed testing · Render $7 · 12 בודקים</t>
         </is>
       </c>
     </row>
-    <row r="255">
-      <c r="B255" s="75" t="inlineStr">
+    <row r="260">
+      <c r="B260" s="75" t="inlineStr">
         <is>
           <t>עברית תתווסף כשפה נוספת בדף החנות — לא חוסם</t>
         </is>

--- a/BuddhaVest_Progress.xlsx
+++ b/BuddhaVest_Progress.xlsx
@@ -778,7 +778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F260"/>
+  <dimension ref="A1:F278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1436,7 +1436,11 @@
           <t>✅ נבנה 15/08/2026</t>
         </is>
       </c>
-      <c r="E24" s="9" t="inlineStr"/>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>app.json · eas.json (profile: production)</t>
+        </is>
+      </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
           <t>eas build --profile production --platform android, רץ על שרתי EAS. versionCode 5 (autoIncrement מ-4). ממתין להעלאה למסלול closed testing.</t>
@@ -6544,7 +6548,6 @@
         </is>
       </c>
     </row>
-    <row r="197"/>
     <row r="198">
       <c r="A198" t="n">
         <v>181</v>
@@ -7026,369 +7029,737 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="10" t="inlineStr">
+      <c r="A214" t="n">
+        <v>197</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>באג · כתבות מתורגמות נקטעו באמצע</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Backend / Content</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>✅ תוקן</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>main.py · translate_article_endpoint</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>‏`if len(items) &gt;= 20: break` — הכתבה נעצרה אחרי 20 בלוקים. כתבה רגילה היא 30-60, אז הקורא קיבל שליש בלי שום סימן שיש המשך. הוחלף בתקציב תווים (24,000, כתבת עומק ארוכה) עם תקרת 200 בלוקים כגיבוי. הגבלה לפי תוכן ולא לפי ספירת בלוקים פירושה שכתבה עם פסקאות קצרות כבר לא נחתכת בשליש.</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>198</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>באג · הכתבה נבנתה מחדש מפסקאות — ולכן היתה ריקה</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Backend / Content</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>✅ תוקן</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>main.py · translate_article_endpoint</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>הסיבה האמיתית לתחושת הריקנות, ולא הקטיעה. הקוד קרא את הדף, שלף כותרות ופסקאות, ובנה דף חדש. תמונות, גרפים, טבלאות, רשימות, ציטוטים, קישורים והדגשות נמחקו לפני שמשהו אחר רץ — הם פשוט לא היו ברשימת התגים. הרמת המגבלה תיקנה את הקטיעה והשאירה את זה, כי זה היה התכנון ולא תקלה.</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>199</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>שכתוב · שימור ה-HTML של הכתבה, החלפת מילים בלבד</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Backend / Content</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>main.py · _pick_article_root · _sanitize_article</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>לא בונה מחדש. מאתר את גוף הכתבה, מחטא, ומגיש כמו שהוא — מחליף רק את צמתי הטקסט. תמונות, כיתובים, טבלאות ועיצוב שורדים כי הם לא מפורקים מלכתחילה. רווחים לפני ואחרי כל צומת נשמרים כדי שמילים לא יידבקו לתגים.</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>200</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>אבטחה · חיטוי HTML של צד שלישי לפני הצגה ב-WebView</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Backend / Security</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>main.py · _sanitize_article</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>הפלט מוצג ב-WebView, אז זה גבול אבטחה ולא ניקיון. כל תג מריץ-קוד נמחק (script, style, iframe, form, svg, embed). כל attribute נזרק חוץ מ-href על קישור, src/alt על תמונה ו-colspan/rowspan על תאים — מה שמסלק כל on* וכל style מעצם הבנייה ולא לפי רשימה שחורה. javascript:/data:/vbscript: נחסמים, השאר מוחלט עם rel=noopener. כל תמונה עוברת _validate_public_url.</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>201</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>באג שנתפס בטסט · מחיקת צמתים תוך כדי מעבר ביטלה את כל החיטוי</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Backend / Security</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>✅ תוקן</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>main.py · _sanitize_article</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>‏find_all מחזיר snapshot. מחיקת הורה מנתקת את ילדיו אך הם נשארים ברשימה, ו-.get() על צומת מנותק זורק כי ה-attrs נעלמו. הגרסה הראשונה לא בדקה .decomposed, ה-AttributeError נבלע, וכל פעולת החיטוי בוטלה — script ו-onclick נשארו בפלט. חי 20 דקות, בין כתיבת הקוד להרצת הטסט על זבל מקונן. נתפס בטסט, לא בייצור.</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>202</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>ממצא · יאהו לא שולח תמונות בכלל — הן נטענות ב-JavaScript</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Backend / Content</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>✅ נפתר</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>main.py · hero (og:image + 4 מקורות)</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>נמדד ב-15/08/2026. יאהו, שממנו רוב הכתבות, שולח את הטקסט ב-HTML (למנועי חיפוש) ומכניס תמונות ב-JS אחרי הטעינה. השרת מקבל דף בלי אף img. ההוכחה היתה בפלט עצמו: 'מקור תמונה: Getty Images' הגיע שלם ולידו כלום — הכיתוב הוא טקסט, התמונה לא היתה במסמך. אימתתי גם ש-7 מ-7 כתובות התמונה האמיתיות מהפיד עוברות את פילטר הזבל, כלומר הוא לא היה האשם כפי שהנחתי. הפתרון: התמונה מה-head — og:image, twitter:image, twitter:image:src, link rel=image_src, JSON-LD (מחרוזת/רשימה/ImageObject).</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>203</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>באג · הכותרת הופיעה פעמיים עם התמונה באמצע</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Backend / Content</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>✅ תוקן</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>main.py · translate_article_endpoint</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>ה-h1 של הדף נמצא בתוך הגוף, ואני הדפסתי עוד אחד מעליו. העותק שבגוף נמחק כשהוא תואם. ההשוואה על אותיות וספרות בלבד — שתי הגרסאות נבדלות בפיסוק ורווחים מספיק כדי ש-== יפספס.</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>204</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>באג · הפוטר של האתר נקרא כחלק מהכתבה</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Backend / Content</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>✅ תוקן</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>main.py · _trim_article_tail</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>אחרי הכתבה הגיעו בלוק הפרסום, 'ל-Motley Fool יש פוזיציות', 'Stock Advisor חוזר החל מ', 'פורסם במקור על ידי', ואז תנאים | מדיניות פרטיות | לוח מחוונים | מידע נוסף. בעברית הכל נקרא כמו המשך הכתבה. שתי מעברות זהירות: ביטוי סוף-כתבה חותך משם והלאה אך רק בחצי השני של הדף (כדי שכתבה שמזכירה 'מדיניות גילוי' בפתיחה לא תיערף), ואז בלוקים בסוף שהם 70% קישורים נקלפים, עד 12.</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>205</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>שיפור · קישור למקור בארבע השפות</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Backend / Content</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>main.py · _SOURCE_LABEL</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>כותרת, שם האתר, וקישור 'לקריאת המקור'. כתבה מתורגמת בלי דרך חזרה למקור היא מבוי סתום, וייחוס הוא גם הדבר הנכון לעשות. ארבע השפות קבועות ולא עוברות בתרגום — ביטוי אחד, אין טעם בבקשת רשת לכל כתבה.</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>206</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>שינוי התנהגות · יש עכשיו קישורים פעילים בתוך הכתבה</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>App / UX</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>⚠️ לידיעה</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>screens/ArticleScreen.js · handleNavChange</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>החילוץ הישן מחק את כל הקישורים; עכשיו הם שורדים. לחיצה תנווט את ה-WebView לדף המקורי — handleNavChange חוזר מוקדם ברגע ש-resolvedUrl מוגדר, אז הניווט עובר. לא קריסה, ויש X לחזרה. לא נגעתי כי זו התנהגות סבירה של מצב קריאה, וכי כל שינוי כאן דורש בנייה חדשה. אם תרצה לנטרל — זה שינוי צד-שרת של שורה אחת (להסיר href מרשימת ה-attributes המותרים).</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>207</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>בדיקות · חבילה לחילוץ כתבות + שלב CI</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Testing</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>test_article_images.py</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>כ-60 בדיקות. הכבדות הן על בחירת כתובת התמונה (lazy loading, srcset, נתיבים יחסיים, לוגואים ופיקסלי מעקב) ועל החיטוי — מה חייב להימחק ומה חייב לשרוד. שלוש מציפיות שלי בטסט היו שגויות ותוקנו במקום לעקוף: srcset נפתר מול תיקיית הכתבה ולא מול שורש האתר, ו-'len(items) &gt;= 20' היא תת-מחרוזת של '&gt;= 200' כך שהבדיקה עברה במקרה.</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="10" t="inlineStr">
         <is>
           <t>Legend</t>
         </is>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" s="6" t="inlineStr">
+    <row r="226">
+      <c r="A226" s="6" t="inlineStr">
         <is>
           <t>✅ Live</t>
         </is>
       </c>
-      <c r="B215" s="7" t="inlineStr">
+      <c r="B226" s="7" t="inlineStr">
         <is>
           <t>פרוס ופעיל ב-Render — נראה לכל המשתמשים</t>
         </is>
       </c>
-      <c r="C215" s="6" t="inlineStr"/>
-      <c r="D215" s="8" t="inlineStr"/>
-      <c r="E215" s="9" t="inlineStr"/>
-      <c r="F215" s="9" t="inlineStr"/>
-    </row>
-    <row r="216">
-      <c r="A216" s="6" t="inlineStr">
+      <c r="C226" s="6" t="inlineStr"/>
+      <c r="D226" s="8" t="inlineStr"/>
+      <c r="E226" s="9" t="inlineStr"/>
+      <c r="F226" s="9" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="6" t="inlineStr">
         <is>
           <t>✅ In APK</t>
         </is>
       </c>
-      <c r="B216" s="7" t="inlineStr">
+      <c r="B227" s="7" t="inlineStr">
         <is>
           <t>כלול ב-APK המותקן — נראה לכל המשתמשים</t>
         </is>
       </c>
-      <c r="C216" s="6" t="inlineStr"/>
-      <c r="D216" s="8" t="inlineStr"/>
-      <c r="E216" s="9" t="inlineStr"/>
-      <c r="F216" s="9" t="inlineStr"/>
-    </row>
-    <row r="217">
-      <c r="A217" s="6" t="inlineStr">
+      <c r="C227" s="6" t="inlineStr"/>
+      <c r="D227" s="8" t="inlineStr"/>
+      <c r="E227" s="9" t="inlineStr"/>
+      <c r="F227" s="9" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="6" t="inlineStr">
         <is>
           <t>⏳ Next APK</t>
         </is>
       </c>
-      <c r="B217" s="7" t="inlineStr">
+      <c r="B228" s="7" t="inlineStr">
         <is>
           <t>הקוד מוזג — דורש build ו-APK חדש</t>
         </is>
       </c>
-      <c r="C217" s="6" t="inlineStr"/>
-      <c r="D217" s="8" t="inlineStr"/>
-      <c r="E217" s="9" t="inlineStr"/>
-      <c r="F217" s="9" t="inlineStr"/>
-    </row>
-    <row r="218">
-      <c r="A218" s="6" t="inlineStr">
+      <c r="C228" s="6" t="inlineStr"/>
+      <c r="D228" s="8" t="inlineStr"/>
+      <c r="E228" s="9" t="inlineStr"/>
+      <c r="F228" s="9" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="6" t="inlineStr">
         <is>
           <t>✅ Live (OTA)</t>
         </is>
       </c>
-      <c r="B218" s="7" t="inlineStr">
+      <c r="B229" s="7" t="inlineStr">
         <is>
           <t>שינוי JS — מועבר אוטומטית בהפעלה הבאה</t>
         </is>
       </c>
-      <c r="C218" s="6" t="inlineStr"/>
-      <c r="D218" s="8" t="inlineStr"/>
-      <c r="E218" s="9" t="inlineStr"/>
-      <c r="F218" s="9" t="inlineStr"/>
-    </row>
-    <row r="219">
-      <c r="A219" s="21" t="inlineStr">
+      <c r="C229" s="6" t="inlineStr"/>
+      <c r="D229" s="8" t="inlineStr"/>
+      <c r="E229" s="9" t="inlineStr"/>
+      <c r="F229" s="9" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="21" t="inlineStr">
         <is>
           <t>⏳ ממתין ל-push</t>
         </is>
       </c>
-      <c r="B219" s="22" t="inlineStr">
+      <c r="B230" s="22" t="inlineStr">
         <is>
           <t>הקוד מוכן מקומית — טרם נדחף/נפרס</t>
         </is>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" s="21" t="inlineStr">
+    <row r="231">
+      <c r="A231" s="21" t="inlineStr">
         <is>
           <t>⏳ דורש build</t>
         </is>
       </c>
-      <c r="B220" s="22" t="inlineStr">
+      <c r="B231" s="22" t="inlineStr">
         <is>
           <t>שינוי נייטיב — OTA לא מספיק, צריך AAB/APK חדש</t>
         </is>
       </c>
     </row>
-    <row r="221"/>
-    <row r="222">
-      <c r="A222" s="23" t="inlineStr">
+    <row r="233">
+      <c r="A233" s="23" t="inlineStr">
         <is>
           <t>סיכום Session 6-8</t>
         </is>
       </c>
     </row>
-    <row r="223">
-      <c r="A223" s="24" t="n"/>
-      <c r="B223" s="25" t="inlineStr">
+    <row r="234">
+      <c r="A234" s="24" t="n"/>
+      <c r="B234" s="25" t="inlineStr">
         <is>
           <t>58  —  פריטים חדשים שנוספו (52-109)</t>
         </is>
       </c>
     </row>
-    <row r="224">
-      <c r="A224" s="24" t="n"/>
-      <c r="B224" s="25" t="inlineStr">
+    <row r="235">
+      <c r="A235" s="24" t="n"/>
+      <c r="B235" s="25" t="inlineStr">
         <is>
           <t>56  —  חיים בייצור או ב-OTA</t>
         </is>
       </c>
     </row>
-    <row r="225">
-      <c r="A225" s="24" t="n"/>
-      <c r="B225" s="25" t="inlineStr">
+    <row r="236">
+      <c r="A236" s="24" t="n"/>
+      <c r="B236" s="25" t="inlineStr">
         <is>
           <t>0  —  ממתינים ל-push: הכל נפרס (commit 91ee6d3)</t>
         </is>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" s="24" t="n"/>
-      <c r="B226" s="25" t="inlineStr">
+    <row r="237">
+      <c r="A237" s="24" t="n"/>
+      <c r="B237" s="25" t="inlineStr">
         <is>
           <t>2  —  פתוחים: פריסת טאבלט אמיתית (99) · הגשה ל-Play (19)</t>
         </is>
       </c>
     </row>
-    <row r="227">
-      <c r="A227" s="24" t="n"/>
-      <c r="B227" s="25" t="inlineStr">
+    <row r="238">
+      <c r="A238" s="24" t="n"/>
+      <c r="B238" s="25" t="inlineStr">
         <is>
           <t>8  —  בורסות שאומתו חי (NYSE · TASE · XETRA · LSE) · JSE ביחידה בלבד</t>
         </is>
       </c>
     </row>
-    <row r="228">
-      <c r="A228" s="24" t="n"/>
-      <c r="B228" s="25" t="inlineStr">
+    <row r="239">
+      <c r="A239" s="24" t="n"/>
+      <c r="B239" s="25" t="inlineStr">
         <is>
           <t>48  —  חבילות בדיקה התנהגותיות עוברות (48/48)</t>
         </is>
       </c>
     </row>
-    <row r="229">
-      <c r="B229" t="inlineStr">
+    <row r="240">
+      <c r="B240" t="inlineStr">
         <is>
           <t>18  —  ראוטים בשרת · 324 מפתחות i18n × 4 שפות</t>
         </is>
       </c>
     </row>
-    <row r="230"/>
-    <row r="231">
-      <c r="A231" s="23" t="inlineStr">
+    <row r="242">
+      <c r="A242" s="23" t="inlineStr">
         <is>
           <t>סיכום Session 10  (2026-08-08)</t>
         </is>
       </c>
     </row>
-    <row r="232">
-      <c r="A232" s="71" t="n"/>
-      <c r="B232" s="71" t="inlineStr">
+    <row r="243">
+      <c r="A243" s="71" t="n"/>
+      <c r="B243" s="71" t="inlineStr">
         <is>
           <t>40  —  פריטים חדשים שנוספו (120-159)</t>
         </is>
       </c>
     </row>
-    <row r="233">
-      <c r="A233" s="71" t="n"/>
-      <c r="B233" s="71" t="inlineStr">
+    <row r="244">
+      <c r="A244" s="71" t="n"/>
+      <c r="B244" s="71" t="inlineStr">
         <is>
           <t>36  —  חיים בייצור ואומתו — /status build=8602f21 · lkg=redis · sentry=on</t>
         </is>
       </c>
     </row>
-    <row r="234">
-      <c r="A234" s="71" t="n"/>
-      <c r="B234" s="71" t="inlineStr">
+    <row r="245">
+      <c r="A245" s="71" t="n"/>
+      <c r="B245" s="71" t="inlineStr">
         <is>
           <t>0  —  ממתינים ל-push</t>
         </is>
       </c>
     </row>
-    <row r="235">
-      <c r="A235" s="71" t="n"/>
-      <c r="B235" s="71" t="inlineStr">
+    <row r="246">
+      <c r="A246" s="71" t="n"/>
+      <c r="B246" s="71" t="inlineStr">
         <is>
           <t>1  —  פרוס אך טרם רץ בייצור: ספק נתונים שני (142). Yahoo תקין, הגיבוי לא הופעל אף פעם</t>
         </is>
       </c>
     </row>
-    <row r="236">
-      <c r="A236" s="71" t="n"/>
-      <c r="B236" s="71" t="inlineStr">
+    <row r="247">
+      <c r="A247" s="71" t="n"/>
+      <c r="B247" s="71" t="inlineStr">
         <is>
           <t>2  —  פתוחים: צילומי מסך (156) · בדיקה סגורה 14 יום (159)</t>
         </is>
       </c>
     </row>
-    <row r="237">
-      <c r="A237" s="71" t="n"/>
-      <c r="B237" s="71" t="inlineStr">
+    <row r="248">
+      <c r="A248" s="71" t="n"/>
+      <c r="B248" s="71" t="inlineStr">
         <is>
           <t>2  —  נדחו במודע לאחר ההשקה: פיצול main.py (157) · חוב תחזוקה L1-L4 (158)</t>
         </is>
       </c>
     </row>
-    <row r="238">
-      <c r="A238" s="71" t="n"/>
-      <c r="B238" s="71" t="inlineStr">
+    <row r="249">
+      <c r="A249" s="71" t="n"/>
+      <c r="B249" s="71" t="inlineStr">
         <is>
           <t>11  —  באגים שהתגלו ותוקנו היום. 9 מהם היו בלתי נראים לפני שהבליעות השקטות הוחלפו</t>
         </is>
       </c>
     </row>
-    <row r="239">
-      <c r="A239" s="71" t="n"/>
-      <c r="B239" s="71" t="inlineStr">
+    <row r="250">
+      <c r="A250" s="71" t="n"/>
+      <c r="B250" s="71" t="inlineStr">
         <is>
           <t>18  —  שלבי CI על כל דחיפה · 4 חבילות בדיקה עוברות</t>
         </is>
       </c>
     </row>
-    <row r="240">
-      <c r="A240" s="71" t="n"/>
-      <c r="B240" s="71" t="inlineStr">
+    <row r="251">
+      <c r="A251" s="71" t="n"/>
+      <c r="B251" s="71" t="inlineStr">
         <is>
           <t>259  —  מפתחות i18n בכל אחת מ-4 השפות (היו 247)</t>
         </is>
       </c>
     </row>
-    <row r="241">
-      <c r="A241" s="72" t="n"/>
-      <c r="B241" s="72" t="inlineStr">
+    <row r="252">
+      <c r="A252" s="72" t="n"/>
+      <c r="B252" s="72" t="inlineStr">
         <is>
           <t>אימות עצמאי:  .\check.bat  —  מי רץ בשרת, אם אפסטאש מחובר, אם Sentry דולק, ומצב ה-CI</t>
         </is>
       </c>
     </row>
-    <row r="242"/>
-    <row r="243">
-      <c r="A243" s="73" t="inlineStr">
+    <row r="254">
+      <c r="A254" s="73" t="inlineStr">
         <is>
           <t>סיכום סשן 11 — 13/08/2026</t>
         </is>
       </c>
     </row>
-    <row r="244">
-      <c r="B244" s="74" t="inlineStr">
+    <row r="255">
+      <c r="B255" s="74" t="inlineStr">
         <is>
           <t>21  —  פריטים חדשים (160-180)</t>
         </is>
       </c>
     </row>
-    <row r="245">
-      <c r="B245" s="74" t="inlineStr">
+    <row r="256">
+      <c r="B256" s="74" t="inlineStr">
         <is>
           <t>17  —  חיים בייצור ואומתו חי — /status build=b096bf3 · code=8423c9284668 · lkg=redis · sentry=on</t>
         </is>
       </c>
     </row>
-    <row r="246">
-      <c r="B246" s="74" t="inlineStr">
+    <row r="257">
+      <c r="B257" s="74" t="inlineStr">
         <is>
           <t>2  —  ממתינים ל-OTA: סימן המטבע החסר (167,168). השרת כבר שולח את הדגל הנכון.</t>
         </is>
       </c>
     </row>
-    <row r="247">
-      <c r="B247" s="74" t="inlineStr">
+    <row r="258">
+      <c r="B258" s="74" t="inlineStr">
         <is>
           <t>1  —  ממתין ל-push: תיקון מדיניות הפרטיות (179)</t>
         </is>
       </c>
     </row>
-    <row r="248">
-      <c r="B248" s="74" t="inlineStr">
+    <row r="259">
+      <c r="B259" s="74" t="inlineStr">
         <is>
           <t>1  —  לא נסגר: סיבת הקריסות של המחשב (175). מוצע חשוד, לא הוכח.</t>
         </is>
       </c>
     </row>
-    <row r="249">
-      <c r="B249" s="74" t="inlineStr">
+    <row r="260">
+      <c r="B260" s="74" t="inlineStr">
         <is>
           <t>6  —  באגים שהתגלו היום. 4 מהם היו שלי, 3 מתוכם נולדו בתיקון של אתמול.</t>
         </is>
       </c>
     </row>
-    <row r="250">
-      <c r="B250" s="74" t="inlineStr">
+    <row r="261">
+      <c r="B261" s="74" t="inlineStr">
         <is>
           <t>22  —  שלבי CI על כל דחיפה · 8 חבילות בדיקה · run-ci.js מריץ את כולם מקומית</t>
         </is>
       </c>
     </row>
-    <row r="251">
-      <c r="B251" s="74" t="inlineStr">
+    <row r="262">
+      <c r="B262" s="74" t="inlineStr">
         <is>
           <t>מדידות חיות: ORA.TA שווי שוק ₪2,106מ' -&gt; ₪20.69מ' · מכפיל 16955.4 -&gt; לא זמין · מטבע דוחות USD</t>
         </is>
       </c>
     </row>
-    <row r="252">
-      <c r="B252" s="74" t="inlineStr">
+    <row r="263">
+      <c r="B263" s="74" t="inlineStr">
         <is>
           <t>מדידות חיות: POLI.TA שווי שוק ₪10,048מ' -&gt; ₪100.89מ' · מטבע דוחות ILS</t>
         </is>
       </c>
     </row>
-    <row r="253">
-      <c r="B253" s="74" t="inlineStr">
+    <row r="264">
+      <c r="B264" s="74" t="inlineStr">
         <is>
           <t>אימות עצמאי:  .\check.bat  —  משווה טביעת אצבע של המקור, לא קומיט. .\ci.bat  —  כל 22 השלבים.</t>
         </is>
       </c>
     </row>
-    <row r="254"/>
-    <row r="255">
-      <c r="A255" s="73" t="inlineStr">
+    <row r="266">
+      <c r="A266" s="73" t="inlineStr">
         <is>
           <t>סיכום סשן 11 — המשך: Play Console</t>
         </is>
       </c>
     </row>
-    <row r="256">
-      <c r="B256" s="75" t="inlineStr">
+    <row r="267">
+      <c r="B267" s="75" t="inlineStr">
         <is>
           <t>11  —  פריטים חדשים (181-191): כל טפסי App content + דף החנות</t>
         </is>
       </c>
     </row>
-    <row r="257">
-      <c r="B257" s="75" t="inlineStr">
+    <row r="268">
+      <c r="B268" s="75" t="inlineStr">
         <is>
           <t>3   —  פריטים שהיו לא מדויקים ותוקנו: 111 (Data Safety 'טיוטה' -&gt; הוגש) · 113 · 156 (צילומי מסך)</t>
         </is>
       </c>
     </row>
-    <row r="258">
-      <c r="B258" s="75" t="inlineStr">
+    <row r="269">
+      <c r="B269" s="75" t="inlineStr">
         <is>
           <t>אומת מול התמליל, לא מהזיכרון: גישה · מודעות · דירוג תוכן · קהל יעד · תכונות פיננסיות · ממשלתי · בריאות · הגדרות חנות — כולם הוגשו בסשן קודם</t>
         </is>
       </c>
     </row>
-    <row r="259">
-      <c r="B259" s="75" t="inlineStr">
+    <row r="270">
+      <c r="B270" s="75" t="inlineStr">
         <is>
           <t>נותר לפני הבדיקה הסגורה: העלאת ה-AAB למסלול closed testing · Render $7 · 12 בודקים</t>
         </is>
       </c>
     </row>
-    <row r="260">
-      <c r="B260" s="75" t="inlineStr">
+    <row r="271">
+      <c r="B271" s="75" t="inlineStr">
         <is>
           <t>עברית תתווסף כשפה נוספת בדף החנות — לא חוסם</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="73" t="inlineStr">
+        <is>
+          <t>סיכום סשן 11 — סופי, לפני העלאת ה-AAB</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="B274" s="75" t="inlineStr">
+        <is>
+          <t>47  —  פריטים חדשים היום (160-207)</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="B275" s="75" t="inlineStr">
+        <is>
+          <t>ה-AAB תקף. נבדק קובץ-קובץ מול 57459ea, הקומיט שממנו נבנה: 9 קבצים השתנו מאז, 8 מהם לא נכנסים ל-APK כלל (שרת, CI, תיעוד, נכסי חנות). התשיעי הוא app.json — שורה אחת, versionCode 4→5, ש-EAS כתב בזמן הבנייה עצמה.</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="B276" s="75" t="inlineStr">
+        <is>
+          <t>כל תיקוני הכתבות הם צד שרת. מגיעים למכשיר בלי בנייה ובלי OTA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="B277" s="75" t="inlineStr">
+        <is>
+          <t>נותר: העלאת ה-AAB ל-closed testing · 12 בודקים · 14 יום</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="B278" s="75" t="inlineStr">
+        <is>
+          <t>פתוחים ביודעין: קריסות המחשב (175) · טאבלט (99) · פיצול main.py (157) · חוב תחזוקה (158) · ספק שני שלא רץ בייצור (142) · טבלת שוק ננעלת ל-USD (192) · קישורים מנווטים בקורא (206)</t>
         </is>
       </c>
     </row>

--- a/BuddhaVest_Progress.xlsx
+++ b/BuddhaVest_Progress.xlsx
@@ -778,7 +778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F278"/>
+  <dimension ref="A1:F281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6548,6 +6548,7 @@
         </is>
       </c>
     </row>
+    <row r="197"/>
     <row r="198">
       <c r="A198" t="n">
         <v>181</v>
@@ -7359,69 +7360,111 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="10" t="inlineStr">
+      <c r="A225" t="n">
+        <v>208</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>תכונה · שורת מטבע מקומי מתחת לכל סכום כספי</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>App / UX</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>⏳ דורש OTA לערוץ production</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>components/MetricTile.js · screens/StockScreen.js</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>בדיוק כמו מחיר המניה: המספר הראשי במטבע הדיווח, ומתחתיו קטן ואפור אותו סכום במטבע שנבחר לפי השפה. חל על רווח נקי, תזרים חופשי, תזרים תפעולי, מזומנים, עלות המכר ורכישה חוזרת כשהיא סכום. לא חל על יחסים, אחוזים וחודשים — יחס שוטף 0.81 לא הופך ל-2.42 שקלים.</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>209</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>החלטה · הגארד של השורה החדשה נפרד מזה של המחיר</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>App / Correctness</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>✅ מיושם</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>screens/StockScreen.js · metricSecondaryDisplay</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>‏showSecondaryCcy נבדק על מטבע המחיר, והשענות עליו היתה חוסמת את ההמרה בדיוק במקרה שהוליד אותה: אורמת נסחרת בשקל (אז שורת המחיר כבויה) ומדווחת בדולר (אז דווקא נתוני הדוחות שלה שווים המרה). שני מטבעות, שתי שאלות, שני גארדים. ההמרה קורית רק כשמטבע הדיווח הוא דולר — הגארד שמונע את הבאג שכבר קרה פעם: בדיקת 'לא שקל' במקום 'כן דולר' הכפילה יורו בשער הדולר, ו-€37.95 הוצג כ-₪115.75.</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>210</v>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>בדיקות · חבילה להמרת מטבע + שלב CI</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Testing</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>✅ Live</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>scripts/test-currency-secondary.js</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>24 בדיקות על הנתונים החיים של ORA.TA ו-POLI.TA. הכבדות הן על מה ש*לא* מומר: יורו ולירה לעולם לא מוכפלים בשער הדולר, מטבע דיווח לא ידוע לא ממיר כלום, יחסים ואחוזים לא נוגעים, ורכישה חוזרת מומרת רק כשהיא סכום ולא אחוז. קורא אנגלית לא רואה שורה שנייה בכלל.</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="10" t="inlineStr">
         <is>
           <t>Legend</t>
         </is>
       </c>
-    </row>
-    <row r="226">
-      <c r="A226" s="6" t="inlineStr">
-        <is>
-          <t>✅ Live</t>
-        </is>
-      </c>
-      <c r="B226" s="7" t="inlineStr">
-        <is>
-          <t>פרוס ופעיל ב-Render — נראה לכל המשתמשים</t>
-        </is>
-      </c>
-      <c r="C226" s="6" t="inlineStr"/>
-      <c r="D226" s="8" t="inlineStr"/>
-      <c r="E226" s="9" t="inlineStr"/>
-      <c r="F226" s="9" t="inlineStr"/>
-    </row>
-    <row r="227">
-      <c r="A227" s="6" t="inlineStr">
-        <is>
-          <t>✅ In APK</t>
-        </is>
-      </c>
-      <c r="B227" s="7" t="inlineStr">
-        <is>
-          <t>כלול ב-APK המותקן — נראה לכל המשתמשים</t>
-        </is>
-      </c>
-      <c r="C227" s="6" t="inlineStr"/>
-      <c r="D227" s="8" t="inlineStr"/>
-      <c r="E227" s="9" t="inlineStr"/>
-      <c r="F227" s="9" t="inlineStr"/>
-    </row>
-    <row r="228">
-      <c r="A228" s="6" t="inlineStr">
-        <is>
-          <t>⏳ Next APK</t>
-        </is>
-      </c>
-      <c r="B228" s="7" t="inlineStr">
-        <is>
-          <t>הקוד מוזג — דורש build ו-APK חדש</t>
-        </is>
-      </c>
-      <c r="C228" s="6" t="inlineStr"/>
-      <c r="D228" s="8" t="inlineStr"/>
-      <c r="E228" s="9" t="inlineStr"/>
-      <c r="F228" s="9" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="6" t="inlineStr">
         <is>
-          <t>✅ Live (OTA)</t>
+          <t>✅ Live</t>
         </is>
       </c>
       <c r="B229" s="7" t="inlineStr">
         <is>
-          <t>שינוי JS — מועבר אוטומטית בהפעלה הבאה</t>
+          <t>פרוס ופעיל ב-Render — נראה לכל המשתמשים</t>
         </is>
       </c>
       <c r="C229" s="6" t="inlineStr"/>
@@ -7430,57 +7473,82 @@
       <c r="F229" s="9" t="inlineStr"/>
     </row>
     <row r="230">
-      <c r="A230" s="21" t="inlineStr">
+      <c r="A230" s="6" t="inlineStr">
+        <is>
+          <t>✅ In APK</t>
+        </is>
+      </c>
+      <c r="B230" s="7" t="inlineStr">
+        <is>
+          <t>כלול ב-APK המותקן — נראה לכל המשתמשים</t>
+        </is>
+      </c>
+      <c r="C230" s="6" t="inlineStr"/>
+      <c r="D230" s="8" t="inlineStr"/>
+      <c r="E230" s="9" t="inlineStr"/>
+      <c r="F230" s="9" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="6" t="inlineStr">
+        <is>
+          <t>⏳ Next APK</t>
+        </is>
+      </c>
+      <c r="B231" s="7" t="inlineStr">
+        <is>
+          <t>הקוד מוזג — דורש build ו-APK חדש</t>
+        </is>
+      </c>
+      <c r="C231" s="6" t="inlineStr"/>
+      <c r="D231" s="8" t="inlineStr"/>
+      <c r="E231" s="9" t="inlineStr"/>
+      <c r="F231" s="9" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="6" t="inlineStr">
+        <is>
+          <t>✅ Live (OTA)</t>
+        </is>
+      </c>
+      <c r="B232" s="7" t="inlineStr">
+        <is>
+          <t>שינוי JS — מועבר אוטומטית בהפעלה הבאה</t>
+        </is>
+      </c>
+      <c r="C232" s="6" t="inlineStr"/>
+      <c r="D232" s="8" t="inlineStr"/>
+      <c r="E232" s="9" t="inlineStr"/>
+      <c r="F232" s="9" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="21" t="inlineStr">
         <is>
           <t>⏳ ממתין ל-push</t>
         </is>
       </c>
-      <c r="B230" s="22" t="inlineStr">
+      <c r="B233" s="22" t="inlineStr">
         <is>
           <t>הקוד מוכן מקומית — טרם נדחף/נפרס</t>
         </is>
       </c>
     </row>
-    <row r="231">
-      <c r="A231" s="21" t="inlineStr">
+    <row r="234">
+      <c r="A234" s="21" t="inlineStr">
         <is>
           <t>⏳ דורש build</t>
         </is>
       </c>
-      <c r="B231" s="22" t="inlineStr">
+      <c r="B234" s="22" t="inlineStr">
         <is>
           <t>שינוי נייטיב — OTA לא מספיק, צריך AAB/APK חדש</t>
         </is>
       </c>
     </row>
-    <row r="233">
-      <c r="A233" s="23" t="inlineStr">
+    <row r="235"/>
+    <row r="236">
+      <c r="A236" s="23" t="inlineStr">
         <is>
           <t>סיכום Session 6-8</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" s="24" t="n"/>
-      <c r="B234" s="25" t="inlineStr">
-        <is>
-          <t>58  —  פריטים חדשים שנוספו (52-109)</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" s="24" t="n"/>
-      <c r="B235" s="25" t="inlineStr">
-        <is>
-          <t>56  —  חיים בייצור או ב-OTA</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="24" t="n"/>
-      <c r="B236" s="25" t="inlineStr">
-        <is>
-          <t>0  —  ממתינים ל-push: הכל נפרס (commit 91ee6d3)</t>
         </is>
       </c>
     </row>
@@ -7488,7 +7556,7 @@
       <c r="A237" s="24" t="n"/>
       <c r="B237" s="25" t="inlineStr">
         <is>
-          <t>2  —  פתוחים: פריסת טאבלט אמיתית (99) · הגשה ל-Play (19)</t>
+          <t>58  —  פריטים חדשים שנוספו (52-109)</t>
         </is>
       </c>
     </row>
@@ -7496,7 +7564,7 @@
       <c r="A238" s="24" t="n"/>
       <c r="B238" s="25" t="inlineStr">
         <is>
-          <t>8  —  בורסות שאומתו חי (NYSE · TASE · XETRA · LSE) · JSE ביחידה בלבד</t>
+          <t>56  —  חיים בייצור או ב-OTA</t>
         </is>
       </c>
     </row>
@@ -7504,45 +7572,46 @@
       <c r="A239" s="24" t="n"/>
       <c r="B239" s="25" t="inlineStr">
         <is>
+          <t>0  —  ממתינים ל-push: הכל נפרס (commit 91ee6d3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="24" t="n"/>
+      <c r="B240" s="25" t="inlineStr">
+        <is>
+          <t>2  —  פתוחים: פריסת טאבלט אמיתית (99) · הגשה ל-Play (19)</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="24" t="n"/>
+      <c r="B241" s="25" t="inlineStr">
+        <is>
+          <t>8  —  בורסות שאומתו חי (NYSE · TASE · XETRA · LSE) · JSE ביחידה בלבד</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="24" t="n"/>
+      <c r="B242" s="25" t="inlineStr">
+        <is>
           <t>48  —  חבילות בדיקה התנהגותיות עוברות (48/48)</t>
         </is>
       </c>
     </row>
-    <row r="240">
-      <c r="B240" t="inlineStr">
+    <row r="243">
+      <c r="B243" t="inlineStr">
         <is>
           <t>18  —  ראוטים בשרת · 324 מפתחות i18n × 4 שפות</t>
         </is>
       </c>
     </row>
-    <row r="242">
-      <c r="A242" s="23" t="inlineStr">
+    <row r="244"/>
+    <row r="245">
+      <c r="A245" s="23" t="inlineStr">
         <is>
           <t>סיכום Session 10  (2026-08-08)</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" s="71" t="n"/>
-      <c r="B243" s="71" t="inlineStr">
-        <is>
-          <t>40  —  פריטים חדשים שנוספו (120-159)</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" s="71" t="n"/>
-      <c r="B244" s="71" t="inlineStr">
-        <is>
-          <t>36  —  חיים בייצור ואומתו — /status build=8602f21 · lkg=redis · sentry=on</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" s="71" t="n"/>
-      <c r="B245" s="71" t="inlineStr">
-        <is>
-          <t>0  —  ממתינים ל-push</t>
         </is>
       </c>
     </row>
@@ -7550,7 +7619,7 @@
       <c r="A246" s="71" t="n"/>
       <c r="B246" s="71" t="inlineStr">
         <is>
-          <t>1  —  פרוס אך טרם רץ בייצור: ספק נתונים שני (142). Yahoo תקין, הגיבוי לא הופעל אף פעם</t>
+          <t>40  —  פריטים חדשים שנוספו (120-159)</t>
         </is>
       </c>
     </row>
@@ -7558,7 +7627,7 @@
       <c r="A247" s="71" t="n"/>
       <c r="B247" s="71" t="inlineStr">
         <is>
-          <t>2  —  פתוחים: צילומי מסך (156) · בדיקה סגורה 14 יום (159)</t>
+          <t>36  —  חיים בייצור ואומתו — /status build=8602f21 · lkg=redis · sentry=on</t>
         </is>
       </c>
     </row>
@@ -7566,7 +7635,7 @@
       <c r="A248" s="71" t="n"/>
       <c r="B248" s="71" t="inlineStr">
         <is>
-          <t>2  —  נדחו במודע לאחר ההשקה: פיצול main.py (157) · חוב תחזוקה L1-L4 (158)</t>
+          <t>0  —  ממתינים ל-push</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7643,7 @@
       <c r="A249" s="71" t="n"/>
       <c r="B249" s="71" t="inlineStr">
         <is>
-          <t>11  —  באגים שהתגלו ותוקנו היום. 9 מהם היו בלתי נראים לפני שהבליעות השקטות הוחלפו</t>
+          <t>1  —  פרוס אך טרם רץ בייצור: ספק נתונים שני (142). Yahoo תקין, הגיבוי לא הופעל אף פעם</t>
         </is>
       </c>
     </row>
@@ -7582,7 +7651,7 @@
       <c r="A250" s="71" t="n"/>
       <c r="B250" s="71" t="inlineStr">
         <is>
-          <t>18  —  שלבי CI על כל דחיפה · 4 חבילות בדיקה עוברות</t>
+          <t>2  —  פתוחים: צילומי מסך (156) · בדיקה סגורה 14 יום (159)</t>
         </is>
       </c>
     </row>
@@ -7590,174 +7659,201 @@
       <c r="A251" s="71" t="n"/>
       <c r="B251" s="71" t="inlineStr">
         <is>
+          <t>2  —  נדחו במודע לאחר ההשקה: פיצול main.py (157) · חוב תחזוקה L1-L4 (158)</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="71" t="n"/>
+      <c r="B252" s="71" t="inlineStr">
+        <is>
+          <t>11  —  באגים שהתגלו ותוקנו היום. 9 מהם היו בלתי נראים לפני שהבליעות השקטות הוחלפו</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="71" t="n"/>
+      <c r="B253" s="71" t="inlineStr">
+        <is>
+          <t>18  —  שלבי CI על כל דחיפה · 4 חבילות בדיקה עוברות</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="71" t="n"/>
+      <c r="B254" s="71" t="inlineStr">
+        <is>
           <t>259  —  מפתחות i18n בכל אחת מ-4 השפות (היו 247)</t>
         </is>
       </c>
     </row>
-    <row r="252">
-      <c r="A252" s="72" t="n"/>
-      <c r="B252" s="72" t="inlineStr">
+    <row r="255">
+      <c r="A255" s="72" t="n"/>
+      <c r="B255" s="72" t="inlineStr">
         <is>
           <t>אימות עצמאי:  .\check.bat  —  מי רץ בשרת, אם אפסטאש מחובר, אם Sentry דולק, ומצב ה-CI</t>
         </is>
       </c>
     </row>
-    <row r="254">
-      <c r="A254" s="73" t="inlineStr">
+    <row r="256"/>
+    <row r="257">
+      <c r="A257" s="73" t="inlineStr">
         <is>
           <t>סיכום סשן 11 — 13/08/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="B255" s="74" t="inlineStr">
-        <is>
-          <t>21  —  פריטים חדשים (160-180)</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="B256" s="74" t="inlineStr">
-        <is>
-          <t>17  —  חיים בייצור ואומתו חי — /status build=b096bf3 · code=8423c9284668 · lkg=redis · sentry=on</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="B257" s="74" t="inlineStr">
-        <is>
-          <t>2  —  ממתינים ל-OTA: סימן המטבע החסר (167,168). השרת כבר שולח את הדגל הנכון.</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="B258" s="74" t="inlineStr">
         <is>
-          <t>1  —  ממתין ל-push: תיקון מדיניות הפרטיות (179)</t>
+          <t>21  —  פריטים חדשים (160-180)</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="B259" s="74" t="inlineStr">
         <is>
-          <t>1  —  לא נסגר: סיבת הקריסות של המחשב (175). מוצע חשוד, לא הוכח.</t>
+          <t>17  —  חיים בייצור ואומתו חי — /status build=b096bf3 · code=8423c9284668 · lkg=redis · sentry=on</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="B260" s="74" t="inlineStr">
         <is>
-          <t>6  —  באגים שהתגלו היום. 4 מהם היו שלי, 3 מתוכם נולדו בתיקון של אתמול.</t>
+          <t>2  —  ממתינים ל-OTA: סימן המטבע החסר (167,168). השרת כבר שולח את הדגל הנכון.</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="B261" s="74" t="inlineStr">
         <is>
-          <t>22  —  שלבי CI על כל דחיפה · 8 חבילות בדיקה · run-ci.js מריץ את כולם מקומית</t>
+          <t>1  —  ממתין ל-push: תיקון מדיניות הפרטיות (179)</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="B262" s="74" t="inlineStr">
         <is>
-          <t>מדידות חיות: ORA.TA שווי שוק ₪2,106מ' -&gt; ₪20.69מ' · מכפיל 16955.4 -&gt; לא זמין · מטבע דוחות USD</t>
+          <t>1  —  לא נסגר: סיבת הקריסות של המחשב (175). מוצע חשוד, לא הוכח.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="B263" s="74" t="inlineStr">
         <is>
-          <t>מדידות חיות: POLI.TA שווי שוק ₪10,048מ' -&gt; ₪100.89מ' · מטבע דוחות ILS</t>
+          <t>6  —  באגים שהתגלו היום. 4 מהם היו שלי, 3 מתוכם נולדו בתיקון של אתמול.</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="B264" s="74" t="inlineStr">
         <is>
+          <t>22  —  שלבי CI על כל דחיפה · 8 חבילות בדיקה · run-ci.js מריץ את כולם מקומית</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="B265" s="74" t="inlineStr">
+        <is>
+          <t>מדידות חיות: ORA.TA שווי שוק ₪2,106מ' -&gt; ₪20.69מ' · מכפיל 16955.4 -&gt; לא זמין · מטבע דוחות USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="B266" s="74" t="inlineStr">
+        <is>
+          <t>מדידות חיות: POLI.TA שווי שוק ₪10,048מ' -&gt; ₪100.89מ' · מטבע דוחות ILS</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="B267" s="74" t="inlineStr">
+        <is>
           <t>אימות עצמאי:  .\check.bat  —  משווה טביעת אצבע של המקור, לא קומיט. .\ci.bat  —  כל 22 השלבים.</t>
         </is>
       </c>
     </row>
-    <row r="266">
-      <c r="A266" s="73" t="inlineStr">
+    <row r="268"/>
+    <row r="269">
+      <c r="A269" s="73" t="inlineStr">
         <is>
           <t>סיכום סשן 11 — המשך: Play Console</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="B267" s="75" t="inlineStr">
-        <is>
-          <t>11  —  פריטים חדשים (181-191): כל טפסי App content + דף החנות</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="B268" s="75" t="inlineStr">
-        <is>
-          <t>3   —  פריטים שהיו לא מדויקים ותוקנו: 111 (Data Safety 'טיוטה' -&gt; הוגש) · 113 · 156 (צילומי מסך)</t>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="B269" s="75" t="inlineStr">
-        <is>
-          <t>אומת מול התמליל, לא מהזיכרון: גישה · מודעות · דירוג תוכן · קהל יעד · תכונות פיננסיות · ממשלתי · בריאות · הגדרות חנות — כולם הוגשו בסשן קודם</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="B270" s="75" t="inlineStr">
         <is>
-          <t>נותר לפני הבדיקה הסגורה: העלאת ה-AAB למסלול closed testing · Render $7 · 12 בודקים</t>
+          <t>11  —  פריטים חדשים (181-191): כל טפסי App content + דף החנות</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="B271" s="75" t="inlineStr">
         <is>
-          <t>עברית תתווסף כשפה נוספת בדף החנות — לא חוסם</t>
+          <t>3   —  פריטים שהיו לא מדויקים ותוקנו: 111 (Data Safety 'טיוטה' -&gt; הוגש) · 113 · 156 (צילומי מסך)</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="B272" s="75" t="inlineStr">
+        <is>
+          <t>אומת מול התמליל, לא מהזיכרון: גישה · מודעות · דירוג תוכן · קהל יעד · תכונות פיננסיות · ממשלתי · בריאות · הגדרות חנות — כולם הוגשו בסשן קודם</t>
         </is>
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="73" t="inlineStr">
-        <is>
-          <t>סיכום סשן 11 — סופי, לפני העלאת ה-AAB</t>
+      <c r="B273" s="75" t="inlineStr">
+        <is>
+          <t>נותר לפני הבדיקה הסגורה: העלאת ה-AAB למסלול closed testing · Render $7 · 12 בודקים</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="B274" s="75" t="inlineStr">
         <is>
-          <t>47  —  פריטים חדשים היום (160-207)</t>
-        </is>
-      </c>
-    </row>
-    <row r="275">
-      <c r="B275" s="75" t="inlineStr">
-        <is>
-          <t>ה-AAB תקף. נבדק קובץ-קובץ מול 57459ea, הקומיט שממנו נבנה: 9 קבצים השתנו מאז, 8 מהם לא נכנסים ל-APK כלל (שרת, CI, תיעוד, נכסי חנות). התשיעי הוא app.json — שורה אחת, versionCode 4→5, ש-EAS כתב בזמן הבנייה עצמה.</t>
-        </is>
-      </c>
-    </row>
+          <t>עברית תתווסף כשפה נוספת בדף החנות — לא חוסם</t>
+        </is>
+      </c>
+    </row>
+    <row r="275"/>
     <row r="276">
-      <c r="B276" s="75" t="inlineStr">
-        <is>
-          <t>כל תיקוני הכתבות הם צד שרת. מגיעים למכשיר בלי בנייה ובלי OTA.</t>
+      <c r="A276" s="73" t="inlineStr">
+        <is>
+          <t>סיכום סשן 11 — סופי, לפני העלאת ה-AAB</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="B277" s="75" t="inlineStr">
         <is>
-          <t>נותר: העלאת ה-AAB ל-closed testing · 12 בודקים · 14 יום</t>
+          <t>47  —  פריטים חדשים היום (160-207)</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="B278" s="75" t="inlineStr">
+        <is>
+          <t>ה-AAB תקף. נבדק קובץ-קובץ מול 57459ea, הקומיט שממנו נבנה: 9 קבצים השתנו מאז, 8 מהם לא נכנסים ל-APK כלל (שרת, CI, תיעוד, נכסי חנות). התשיעי הוא app.json — שורה אחת, versionCode 4→5, ש-EAS כתב בזמן הבנייה עצמה.</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="B279" s="75" t="inlineStr">
+        <is>
+          <t>כל תיקוני הכתבות הם צד שרת. מגיעים למכשיר בלי בנייה ובלי OTA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="B280" s="75" t="inlineStr">
+        <is>
+          <t>נותר: העלאת ה-AAB ל-closed testing · 12 בודקים · 14 יום</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="B281" s="75" t="inlineStr">
         <is>
           <t>פתוחים ביודעין: קריסות המחשב (175) · טאבלט (99) · פיצול main.py (157) · חוב תחזוקה (158) · ספק שני שלא רץ בייצור (142) · טבלת שוק ננעלת ל-USD (192) · קישורים מנווטים בקורא (206)</t>
         </is>
